--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R212b4b9f9fc346ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R6e9152ddd4134790"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R1a5ec813541b4c65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R7815105165a9498b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="R484f93c31ef54859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R2753866374c4446a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R2b9ecc2e232c4856"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R2ce999600d0f4252"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R59c595e390414e66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R3415fec85e8f41ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Re2d75cebc01843d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="Rce6cbd40336845a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -110,7 +110,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -174,6 +174,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -569,7 +572,7 @@
         <x:v>Design Components</x:v>
       </x:c>
       <x:c r="E5" s="9" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -591,7 +594,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>0.9</x:v>
+        <x:v>0.10</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Requirements with Design</x:v>
@@ -619,7 +622,7 @@
         <x:v>Baseline Date</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-08</x:v>
+        <x:v>2026-08-09</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>Test Case IDs</x:v>
@@ -775,7 +778,7 @@
     <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="21" t="str">
         <x:v>Requirement ID</x:v>
       </x:c>
@@ -786,7 +789,7 @@
         <x:v>Functional Specification ID</x:v>
       </x:c>
       <x:c r="D1" s="21" t="str">
-        <x:v>Design Component</x:v>
+        <x:v>Design Component ID / Name</x:v>
       </x:c>
       <x:c r="E1" s="21" t="str">
         <x:v>Verification Method</x:v>
@@ -801,7 +804,7 @@
         <x:v>Source Requirement IDs</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="32" customHeight="1">
+    <x:row r="2" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A2" s="22" t="str">
         <x:v>REQ-FUNC-001</x:v>
       </x:c>
@@ -812,7 +815,7 @@
         <x:v>FS-INIT-001</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>CAPL ABI Adapter; EmulatorContext</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-02 EmulatorContext</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
         <x:v>CANalyzer 9.x x86 DLL 로딩 및 중복 Context 시험</x:v>
@@ -825,7 +828,7 @@
         <x:v>FR-LIFE-009,016; IF-CTX-001~003,007</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="32" customHeight="1">
+    <x:row r="3" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A3" s="22" t="str">
         <x:v>REQ-FUNC-002</x:v>
       </x:c>
@@ -836,7 +839,7 @@
         <x:v>FS-LIFE-001,FS-LIFE-002,FS-LIFE-003</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>LifecycleController</x:v>
+        <x:v>DC-03 LifecycleController</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
         <x:v>Lifecycle 상태·Generation·Busy 처리 통합 시험</x:v>
@@ -849,7 +852,7 @@
         <x:v>FR-LIFE-010~015</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="32" customHeight="1">
+    <x:row r="4" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A4" s="22" t="str">
         <x:v>REQ-FUNC-003</x:v>
       </x:c>
@@ -860,7 +863,7 @@
         <x:v>FS-LIFE-003</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>LifecycleController</x:v>
+        <x:v>DC-03 LifecycleController</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
         <x:v>상태 전이 및 완료 결과 손실 방지 시험</x:v>
@@ -873,7 +876,7 @@
         <x:v>FR-LIFE-013~015; IF-CONST-003; IF-LSTAT-001~014</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="32" customHeight="1">
+    <x:row r="5" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A5" s="22" t="str">
         <x:v>REQ-FUNC-004</x:v>
       </x:c>
@@ -884,7 +887,7 @@
         <x:v>FS-LIFE-001</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>LifecycleController; Win32SerialPort; PortWorker</x:v>
+        <x:v>DC-03 LifecycleController; DC-09 Win32SerialPort; DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
         <x:v>두 번째 Port 실패 강제 및 전체 Rollback 시험</x:v>
@@ -897,7 +900,7 @@
         <x:v>FR-PORT-007~017</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="32" customHeight="1">
+    <x:row r="6" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A6" s="22" t="str">
         <x:v>REQ-FUNC-005</x:v>
       </x:c>
@@ -908,7 +911,7 @@
         <x:v>FS-LIFE-002</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>LifecycleController; SnapshotService</x:v>
+        <x:v>DC-03 LifecycleController; DC-11 SnapshotService</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
         <x:v>Disconnect/재Connect 데이터 보존 시험</x:v>
@@ -921,7 +924,7 @@
         <x:v>FR-LIFE-020,025,033</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="32" customHeight="1">
+    <x:row r="7" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A7" s="22" t="str">
         <x:v>REQ-FUNC-006</x:v>
       </x:c>
@@ -932,7 +935,7 @@
         <x:v>FS-LIFE-004</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>LifecycleController; PortWorker</x:v>
+        <x:v>DC-03 LifecycleController; DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
         <x:v>USB 제거·복귀, 10회 실패 및 수동 복구 시험</x:v>
@@ -945,7 +948,7 @@
         <x:v>FR-LIFE-023~032</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="32" customHeight="1">
+    <x:row r="8" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A8" s="22" t="str">
         <x:v>REQ-FUNC-007</x:v>
       </x:c>
@@ -956,7 +959,7 @@
         <x:v>FS-LIFE-004</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>LifecycleController</x:v>
+        <x:v>DC-03 LifecycleController</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
         <x:v>부분 Open Rollback과 데이터 보존 시험</x:v>
@@ -969,7 +972,7 @@
         <x:v>FR-LIFE-025~032; ERR-037~038</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="32" customHeight="1">
+    <x:row r="9" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A9" s="22" t="str">
         <x:v>REQ-FUNC-008</x:v>
       </x:c>
@@ -980,7 +983,7 @@
         <x:v>FS-SHUT-001</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>EmulatorContext; LifecycleController</x:v>
+        <x:v>DC-02 EmulatorContext; DC-03 LifecycleController</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
         <x:v>각 상태 Finalize, Cancel I/O, 재초기화 시험</x:v>
@@ -993,7 +996,7 @@
         <x:v>FR-LIFE-017~022</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="32" customHeight="1">
+    <x:row r="10" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A10" s="22" t="str">
         <x:v>REQ-FUNC-009</x:v>
       </x:c>
@@ -1004,7 +1007,7 @@
         <x:v>FS-CSV-001</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>CAPL Core; ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-13 CAPL Core</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
         <x:v>프로젝트 이동·파일명 변경·경로 변환 실패 시험</x:v>
@@ -1017,7 +1020,7 @@
         <x:v>FR-CSV-001~003; DATA-001~002</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="32" customHeight="1">
+    <x:row r="11" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A11" s="22" t="str">
         <x:v>REQ-FUNC-010</x:v>
       </x:c>
@@ -1028,7 +1031,7 @@
         <x:v>FS-CSV-001</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
         <x:v>다수 CSV 혼재 환경의 정확한 파일 선택 시험</x:v>
@@ -1041,7 +1044,7 @@
         <x:v>FR-CSV-001~003; IF-CORE-009</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="32" customHeight="1">
+    <x:row r="12" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A12" s="22" t="str">
         <x:v>REQ-FUNC-011</x:v>
       </x:c>
@@ -1052,7 +1055,7 @@
         <x:v>FS-CSV-002,FS-CSV-003</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>ConfigurationLoader; LifecycleController</x:v>
+        <x:v>DC-03 LifecycleController; DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
         <x:v>성공/실패 원자성 및 Connected 거부 시험</x:v>
@@ -1065,7 +1068,7 @@
         <x:v>FR-CSV-004~010,014~019</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="32" customHeight="1">
+    <x:row r="13" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A13" s="22" t="str">
         <x:v>REQ-FUNC-012</x:v>
       </x:c>
@@ -1076,7 +1079,7 @@
         <x:v>FS-CSV-003</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>ConfigurationLoader; SnapshotService; DiagnosticService</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
         <x:v>Refresh 전후 값과 런타임 상태 초기화 시험</x:v>
@@ -1089,7 +1092,7 @@
         <x:v>FR-CSV-005,012,017~019</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="32" customHeight="1">
+    <x:row r="14" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A14" s="22" t="str">
         <x:v>REQ-FUNC-013</x:v>
       </x:c>
@@ -1100,7 +1103,7 @@
         <x:v>FS-CSV-003</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>ConfigurationLoader; LifecycleController</x:v>
+        <x:v>DC-03 LifecycleController; DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
         <x:v>Stale Configuration 차단 및 재시도 시험</x:v>
@@ -1113,7 +1116,7 @@
         <x:v>FR-CSV-006~008,015~016; ERR-035~036</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="32" customHeight="1">
+    <x:row r="15" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A15" s="22" t="str">
         <x:v>REQ-FUNC-014</x:v>
       </x:c>
@@ -1124,7 +1127,7 @@
         <x:v>FS-DEV-001</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>DeviceRegistry</x:v>
+        <x:v>DC-05 DeviceRegistry</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
         <x:v>동일 Port 다중 Slave와 다른 Port 동일 Slave ID 시험</x:v>
@@ -1137,7 +1140,7 @@
         <x:v>FR-RTU-007; DATA-DEV-001~006</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="32" customHeight="1">
+    <x:row r="16" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A16" s="22" t="str">
         <x:v>REQ-FUNC-015</x:v>
       </x:c>
@@ -1148,7 +1151,7 @@
         <x:v>FS-REG-001</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>RegisterService; DeviceRegistry</x:v>
+        <x:v>DC-05 DeviceRegistry; DC-06 RegisterService</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
         <x:v>동일 Address의 FC03/FC04 동일값 시험</x:v>
@@ -1161,7 +1164,7 @@
         <x:v>FR-REG-001~009</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="32" customHeight="1">
+    <x:row r="17" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A17" s="22" t="str">
         <x:v>REQ-FUNC-016</x:v>
       </x:c>
@@ -1172,7 +1175,7 @@
         <x:v>FS-REG-001,FS-REG-002</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>RegisterService</x:v>
+        <x:v>DC-06 RegisterService</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
         <x:v>Rule-only, Map-only, 공백 범위 접근 시험</x:v>
@@ -1185,7 +1188,7 @@
         <x:v>FR-REG-013~017; DATA-020,024</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="32" customHeight="1">
+    <x:row r="18" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A18" s="22" t="str">
         <x:v>REQ-FUNC-017</x:v>
       </x:c>
@@ -1196,7 +1199,7 @@
         <x:v>FS-REG-001,FS-REG-002</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>RegisterService</x:v>
+        <x:v>DC-06 RegisterService</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
         <x:v>경계·Buffer 부족·동시 접근 원자성 시험</x:v>
@@ -1209,7 +1212,7 @@
         <x:v>FR-REG-015~018; IF-REG-001~012</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="32" customHeight="1">
+    <x:row r="19" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A19" s="22" t="str">
         <x:v>REQ-FUNC-018</x:v>
       </x:c>
@@ -1220,7 +1223,7 @@
         <x:v>FS-REG-002,FS-MON-004</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>RegisterService; SnapshotService</x:v>
+        <x:v>DC-06 RegisterService; DC-11 SnapshotService</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
         <x:v>중첩 Rule, 동일값 Write 및 중복 제거 시험</x:v>
@@ -1233,7 +1236,7 @@
         <x:v>FR-REG-010~012,018</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="32" customHeight="1">
+    <x:row r="20" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A20" s="22" t="str">
         <x:v>REQ-FUNC-019</x:v>
       </x:c>
@@ -1244,7 +1247,7 @@
         <x:v>FS-REG-003</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>RegisterService; SnapshotService</x:v>
+        <x:v>DC-06 RegisterService; DC-11 SnapshotService</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
         <x:v>Connected/Disconnected Reset과 실패 Rollback 시험</x:v>
@@ -1257,7 +1260,7 @@
         <x:v>FR-RESET-001~007</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="32" customHeight="1">
+    <x:row r="21" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A21" s="22" t="str">
         <x:v>REQ-FUNC-020</x:v>
       </x:c>
@@ -1268,7 +1271,7 @@
         <x:v>FS-SIG-001,FS-SIG-002,FS-SIG-003</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>SignalCodec</x:v>
+        <x:v>DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E21" s="9" t="str">
         <x:v>SignalName 대소문자·중복·미존재 시험</x:v>
@@ -1281,7 +1284,7 @@
         <x:v>FR-SIG-001~006; DATA-MAP-023</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="32" customHeight="1">
+    <x:row r="22" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A22" s="22" t="str">
         <x:v>REQ-FUNC-021</x:v>
       </x:c>
@@ -1292,7 +1295,7 @@
         <x:v>FS-SIG-002,FS-SIG-003,FS-SIG-004</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>SignalCodec</x:v>
+        <x:v>DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
         <x:v>양·음수 Scale/Offset 및 ±0.5 반올림 시험</x:v>
@@ -1305,7 +1308,7 @@
         <x:v>FR-SIG-025~030</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="32" customHeight="1">
+    <x:row r="23" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A23" s="22" t="str">
         <x:v>REQ-FUNC-022</x:v>
       </x:c>
@@ -1316,7 +1319,7 @@
         <x:v>FS-SIG-002,FS-SIG-003,FS-SIG-004</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>SignalCodec</x:v>
+        <x:v>DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
         <x:v>Float/Double Raw round-trip 및 비유한 값 시험</x:v>
@@ -1329,7 +1332,7 @@
         <x:v>FR-SIG-007~008; DATA-MAP-008~009</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="32" customHeight="1">
+    <x:row r="24" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A24" s="22" t="str">
         <x:v>REQ-FUNC-023</x:v>
       </x:c>
@@ -1340,7 +1343,7 @@
         <x:v>FS-SIG-001~004</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>SignalCodec</x:v>
+        <x:v>DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
         <x:v>2/4 Word Address별 Raw 배치 시험</x:v>
@@ -1353,7 +1356,7 @@
         <x:v>FR-SIG-009~010; DATA-MAP-010</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="32" customHeight="1">
+    <x:row r="25" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A25" s="22" t="str">
         <x:v>REQ-FUNC-024</x:v>
       </x:c>
@@ -1364,7 +1367,7 @@
         <x:v>FS-SIG-001~004</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>SignalCodec</x:v>
+        <x:v>DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
         <x:v>Length 2/4/6/8의 Bit 경계·비정렬 Signal 시험</x:v>
@@ -1377,7 +1380,7 @@
         <x:v>FR-SIG-011~014</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="32" customHeight="1">
+    <x:row r="26" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A26" s="22" t="str">
         <x:v>REQ-FUNC-025</x:v>
       </x:c>
@@ -1388,7 +1391,7 @@
         <x:v>FS-SIG-001~004</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>SignalCodec</x:v>
+        <x:v>DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
         <x:v>Big/Little Endian Read/Write 역변환 시험</x:v>
@@ -1401,7 +1404,7 @@
         <x:v>FR-SIG-020~024</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="32" customHeight="1">
+    <x:row r="27" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A27" s="22" t="str">
         <x:v>REQ-FUNC-026</x:v>
       </x:c>
@@ -1412,7 +1415,7 @@
         <x:v>FS-CSV-002,FS-SIG-001</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>ConfigurationLoader; SignalCodec</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
         <x:v>Frame 공유·중복·경계 검증 시험</x:v>
@@ -1425,7 +1428,7 @@
         <x:v>FR-SIG-012,015~019; DATA-MAP-011~014</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="32" customHeight="1">
+    <x:row r="28" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A28" s="22" t="str">
         <x:v>REQ-FUNC-027</x:v>
       </x:c>
@@ -1436,7 +1439,7 @@
         <x:v>FS-SIG-004</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>ConfigurationLoader; SignalCodec</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
         <x:v>행 순서 변경·부분 실패 Rollback 시험</x:v>
@@ -1449,7 +1452,7 @@
         <x:v>FR-SIG-025~027; DATA-MAP-004</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="32" customHeight="1">
+    <x:row r="29" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A29" s="22" t="str">
         <x:v>REQ-FUNC-028</x:v>
       </x:c>
@@ -1460,7 +1463,7 @@
         <x:v>FS-SIG-002~004</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>SignalCodec; RegisterService</x:v>
+        <x:v>DC-06 RegisterService; DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
         <x:v>Min/Max 경계, Raw 우회 및 NaN/Infinity 시험</x:v>
@@ -1473,7 +1476,7 @@
         <x:v>FR-SIG-031~037</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="32" customHeight="1">
+    <x:row r="30" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A30" s="22" t="str">
         <x:v>REQ-FUNC-029</x:v>
       </x:c>
@@ -1484,7 +1487,7 @@
         <x:v>FS-SIG-002,FS-SIG-003</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>CAPL ABI Adapter; SignalCodec</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
         <x:v>±2^53 경계 및 word[4] Raw 우회 시험</x:v>
@@ -1497,7 +1500,7 @@
         <x:v>FR-SIG-038~041; IF-SIG-006~007</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="32" customHeight="1">
+    <x:row r="31" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A31" s="22" t="str">
         <x:v>REQ-FUNC-030</x:v>
       </x:c>
@@ -1508,7 +1511,7 @@
         <x:v>FS-MON-001</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>CAPL UI; SnapshotService</x:v>
+        <x:v>DC-11 SnapshotService; DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
         <x:v>ON/OFF 중 RTU 유지와 Queue 정책 시험</x:v>
@@ -1521,7 +1524,7 @@
         <x:v>FR-LIFE-004~006; FR-CAN-049~056</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="32" customHeight="1">
+    <x:row r="32" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A32" s="22" t="str">
         <x:v>REQ-FUNC-031</x:v>
       </x:c>
@@ -1532,7 +1535,7 @@
         <x:v>FS-MON-002</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
         <x:v>다중 Checkbox 원자 적용·복원 시험</x:v>
@@ -1545,7 +1548,7 @@
         <x:v>FR-CAN-020~027,047,057</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="32" customHeight="1">
+    <x:row r="33" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A33" s="22" t="str">
         <x:v>REQ-FUNC-032</x:v>
       </x:c>
@@ -1556,7 +1559,7 @@
         <x:v>FS-MON-001,FS-MON-003</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>CAPL Monitoring; SnapshotService</x:v>
+        <x:v>DC-11 SnapshotService; DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
         <x:v>Connect/ReadSwitch 순서 및 최초 출력 시험</x:v>
@@ -1569,7 +1572,7 @@
         <x:v>FR-LIFE-007~008; FR-CAN-055</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="32" customHeight="1">
+    <x:row r="34" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A34" s="22" t="str">
         <x:v>REQ-FUNC-033</x:v>
       </x:c>
@@ -1580,7 +1583,7 @@
         <x:v>FS-MON-003,FS-MON-006</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
         <x:v>Deadline Miss·Latest-wins·공정성 시험</x:v>
@@ -1593,7 +1596,7 @@
         <x:v>FR-CAN-022,042~048; FR-LOAD-007</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="32" customHeight="1">
+    <x:row r="35" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A35" s="22" t="str">
         <x:v>REQ-FUNC-034</x:v>
       </x:c>
@@ -1604,7 +1607,7 @@
         <x:v>FS-MON-004</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>SnapshotService; CAPL Monitoring</x:v>
+        <x:v>DC-11 SnapshotService; DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
         <x:v>동시 Write·불변 Snapshot·Buffer 부족 시험</x:v>
@@ -1617,7 +1620,7 @@
         <x:v>FR-CAN-029~037; IF-MON-006~010</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="32" customHeight="1">
+    <x:row r="36" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A36" s="22" t="str">
         <x:v>REQ-FUNC-035</x:v>
       </x:c>
@@ -1628,7 +1631,7 @@
         <x:v>FS-MON-004,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>SnapshotService; DiagnosticService</x:v>
+        <x:v>DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
         <x:v>Queue 257건 입력 및 oldest-drop 시험</x:v>
@@ -1641,7 +1644,7 @@
         <x:v>FR-CAN-038~039; ERR-008; FR-LOAD-008</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="32" customHeight="1">
+    <x:row r="37" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A37" s="22" t="str">
         <x:v>REQ-FUNC-036</x:v>
       </x:c>
@@ -1652,7 +1655,7 @@
         <x:v>FS-MON-006</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
         <x:v>두 Port Burst·Rule Cursor·묶음 원자 출력 시험</x:v>
@@ -1665,7 +1668,7 @@
         <x:v>FR-CAN-040~046; DES-CAN-014~017</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="32" customHeight="1">
+    <x:row r="38" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A38" s="22" t="str">
         <x:v>REQ-FUNC-037</x:v>
       </x:c>
@@ -1676,7 +1679,7 @@
         <x:v>FS-MON-006</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
         <x:v>Quantity 125 Snapshot과 Tick 시간 실측</x:v>
@@ -1689,7 +1692,7 @@
         <x:v>FR-LOAD-006,019</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="32" customHeight="1">
+    <x:row r="39" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A39" s="22" t="str">
         <x:v>REQ-FUNC-038</x:v>
       </x:c>
@@ -1700,7 +1703,7 @@
         <x:v>FS-MON-002,FS-MON-006</x:v>
       </x:c>
       <x:c r="D39" s="9" t="str">
-        <x:v>CAPL Monitoring; DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService; DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
         <x:v>Performance Monitor 유무·임의값 불변 동작 시험</x:v>
@@ -1713,7 +1716,7 @@
         <x:v>FR-LOAD-001~005,010,018</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="32" customHeight="1">
+    <x:row r="40" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A40" s="22" t="str">
         <x:v>REQ-FUNC-039</x:v>
       </x:c>
@@ -1724,7 +1727,7 @@
         <x:v>FS-MON-001,FS-MON-004</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
-        <x:v>SnapshotService</x:v>
+        <x:v>DC-11 SnapshotService</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
         <x:v>OFF 전후 Queue·Counter·재시작 Burst 시험</x:v>
@@ -1737,7 +1740,7 @@
         <x:v>FR-CAN-051~056; FR-LOAD-015~018</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="32" customHeight="1">
+    <x:row r="41" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A41" s="22" t="str">
         <x:v>REQ-FUNC-040</x:v>
       </x:c>
@@ -1748,7 +1751,7 @@
         <x:v>FS-UI-001,FS-UI-002,FS-UI-003</x:v>
       </x:c>
       <x:c r="D41" s="9" t="str">
-        <x:v>CAPL Core; CAPL Monitoring; CAPL UI</x:v>
+        <x:v>DC-13 CAPL Core; DC-14 CAPL Monitoring; DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E41" s="9" t="str">
         <x:v>CAPL 정적 분석 및 컴파일 시험</x:v>
@@ -1761,7 +1764,7 @@
         <x:v>FR-CAPL-001~006; IF-CTX-006</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="32" customHeight="1">
+    <x:row r="42" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A42" s="22" t="str">
         <x:v>REQ-FUNC-041</x:v>
       </x:c>
@@ -1772,7 +1775,7 @@
         <x:v>FS-UI-001</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>CAPL UI; RegisterService</x:v>
+        <x:v>DC-06 RegisterService; DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
         <x:v>Panel 수동 Read 및 실패 시 결과 유지 시험</x:v>
@@ -1785,7 +1788,7 @@
         <x:v>FR-UI-001~006; IF-REG-001,004</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="32" customHeight="1">
+    <x:row r="43" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A43" s="22" t="str">
         <x:v>REQ-FUNC-042</x:v>
       </x:c>
@@ -1796,7 +1799,7 @@
         <x:v>FS-UI-002</x:v>
       </x:c>
       <x:c r="D43" s="9" t="str">
-        <x:v>CAPL UI; RegisterService</x:v>
+        <x:v>DC-06 RegisterService; DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
         <x:v>Panel 편집 중간 상태와 실행 Snapshot 분리 시험</x:v>
@@ -1809,7 +1812,7 @@
         <x:v>FR-UI-007~011; IF-REG-002~016</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="32" customHeight="1">
+    <x:row r="44" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A44" s="22" t="str">
         <x:v>REQ-FUNC-043</x:v>
       </x:c>
@@ -1820,7 +1823,7 @@
         <x:v>FS-UI-001</x:v>
       </x:c>
       <x:c r="D44" s="9" t="str">
-        <x:v>CAPL UI</x:v>
+        <x:v>DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
         <x:v>Auto Read, Send momentary 및 invalid edit 시험</x:v>
@@ -1833,7 +1836,7 @@
         <x:v>FR-UI-012~016</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="32" customHeight="1">
+    <x:row r="45" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A45" s="22" t="str">
         <x:v>REQ-FUNC-044</x:v>
       </x:c>
@@ -1844,7 +1847,7 @@
         <x:v>FS-UI-003</x:v>
       </x:c>
       <x:c r="D45" s="9" t="str">
-        <x:v>CAPL UI; SignalCodec</x:v>
+        <x:v>DC-07 SignalCodec; DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E45" s="9" t="str">
         <x:v>양수·음수·소수 Panel round-trip 시험</x:v>
@@ -1857,7 +1860,7 @@
         <x:v>FR-SIG-003; IF-SIG-001~007</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="32" customHeight="1">
+    <x:row r="46" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A46" s="22" t="str">
         <x:v>REQ-COM-001</x:v>
       </x:c>
@@ -1868,7 +1871,7 @@
         <x:v>FS-COM-001</x:v>
       </x:c>
       <x:c r="D46" s="9" t="str">
-        <x:v>Win32SerialPort</x:v>
+        <x:v>DC-09 Win32SerialPort</x:v>
       </x:c>
       <x:c r="E46" s="9" t="str">
         <x:v>회사 환경 SystemBase Multi USB-485 통합 시험</x:v>
@@ -1881,7 +1884,7 @@
         <x:v>ENV-003,014~015; CON-017</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="32" customHeight="1">
+    <x:row r="47" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A47" s="22" t="str">
         <x:v>REQ-COM-002</x:v>
       </x:c>
@@ -1892,7 +1895,7 @@
         <x:v>FS-COM-001</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
-        <x:v>DeviceRegistry; CAPL Core</x:v>
+        <x:v>DC-05 DeviceRegistry; DC-13 CAPL Core</x:v>
       </x:c>
       <x:c r="E47" s="9" t="str">
         <x:v>Port 등록 순서·중복·누락·Routing 시험</x:v>
@@ -1905,7 +1908,7 @@
         <x:v>ENV-003~005; FR-PORT-018~020</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="32" customHeight="1">
+    <x:row r="48" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A48" s="22" t="str">
         <x:v>REQ-COM-003</x:v>
       </x:c>
@@ -1916,7 +1919,7 @@
         <x:v>FS-COM-001</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>Win32SerialPort</x:v>
+        <x:v>DC-09 Win32SerialPort</x:v>
       </x:c>
       <x:c r="E48" s="9" t="str">
         <x:v>지원/비지원 설정 및 상태 제한 시험</x:v>
@@ -1929,7 +1932,7 @@
         <x:v>FR-PORT-001~006</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="32" customHeight="1">
+    <x:row r="49" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A49" s="22" t="str">
         <x:v>REQ-COM-004</x:v>
       </x:c>
@@ -1940,7 +1943,7 @@
         <x:v>FS-COM-001</x:v>
       </x:c>
       <x:c r="D49" s="9" t="str">
-        <x:v>Win32SerialPort</x:v>
+        <x:v>DC-09 Win32SerialPort</x:v>
       </x:c>
       <x:c r="E49" s="9" t="str">
         <x:v>BaudRate·Parity·StopBits 조합과 OS 오류 Context 시험</x:v>
@@ -1953,7 +1956,7 @@
         <x:v>FR-PORT-002,010~012</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="32" customHeight="1">
+    <x:row r="50" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A50" s="22" t="str">
         <x:v>REQ-COM-005</x:v>
       </x:c>
@@ -1964,7 +1967,7 @@
         <x:v>FS-COM-001</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>Win32SerialPort</x:v>
+        <x:v>DC-09 Win32SerialPort</x:v>
       </x:c>
       <x:c r="E50" s="9" t="str">
         <x:v>RTS 미조작 및 Echo 없는 Adapter 확인</x:v>
@@ -1977,7 +1980,7 @@
         <x:v>FR-PORT-022~023</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="32" customHeight="1">
+    <x:row r="51" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A51" s="22" t="str">
         <x:v>REQ-COM-006</x:v>
       </x:c>
@@ -1988,7 +1991,7 @@
         <x:v>FS-MODBUS-002~005</x:v>
       </x:c>
       <x:c r="D51" s="9" t="str">
-        <x:v>ModbusRtuEngine</x:v>
+        <x:v>DC-08 ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="E51" s="9" t="str">
         <x:v>Function별 정상·미지원 요청 시험</x:v>
@@ -2001,7 +2004,7 @@
         <x:v>FR-RTU-001~006,015~016</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="32" customHeight="1">
+    <x:row r="52" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A52" s="22" t="str">
         <x:v>REQ-COM-007</x:v>
       </x:c>
@@ -2012,7 +2015,7 @@
         <x:v>FS-MODBUS-002~005</x:v>
       </x:c>
       <x:c r="D52" s="9" t="str">
-        <x:v>ModbusRtuEngine</x:v>
+        <x:v>DC-08 ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="E52" s="9" t="str">
         <x:v>최소·최대·초과 및 ByteCount 오류 시험</x:v>
@@ -2025,7 +2028,7 @@
         <x:v>FR-RTU-017~020,028~031</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="32" customHeight="1">
+    <x:row r="53" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A53" s="22" t="str">
         <x:v>REQ-COM-008</x:v>
       </x:c>
@@ -2036,7 +2039,7 @@
         <x:v>FS-MODBUS-002~004</x:v>
       </x:c>
       <x:c r="D53" s="9" t="str">
-        <x:v>ModbusRtuEngine; RegisterService</x:v>
+        <x:v>DC-06 RegisterService; DC-08 ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="E53" s="9" t="str">
         <x:v>인접·중첩 Rule 횡단과 공백 거부 시험</x:v>
@@ -2049,7 +2052,7 @@
         <x:v>FR-RTU-010~014; DATA-RULE-012</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="32" customHeight="1">
+    <x:row r="54" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A54" s="22" t="str">
         <x:v>REQ-COM-009</x:v>
       </x:c>
@@ -2060,7 +2063,7 @@
         <x:v>FS-MODBUS-004</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
-        <x:v>ModbusRtuEngine; RegisterService</x:v>
+        <x:v>DC-06 RegisterService; DC-08 ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="E54" s="9" t="str">
         <x:v>적용 전/후 송신 실패 Stage 시험</x:v>
@@ -2073,7 +2076,7 @@
         <x:v>FR-RTU-031~032; ERR-043</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="32" customHeight="1">
+    <x:row r="55" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A55" s="22" t="str">
         <x:v>REQ-COM-010</x:v>
       </x:c>
@@ -2084,7 +2087,7 @@
         <x:v>FS-MODBUS-001,FS-MODBUS-005</x:v>
       </x:c>
       <x:c r="D55" s="9" t="str">
-        <x:v>DeviceRegistry; ModbusRtuEngine</x:v>
+        <x:v>DC-05 DeviceRegistry; DC-08 ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="E55" s="9" t="str">
         <x:v>Broadcast·예약·미등록 주소 시험</x:v>
@@ -2097,7 +2100,7 @@
         <x:v>FR-RTU-021~022</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="32" customHeight="1">
+    <x:row r="56" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A56" s="22" t="str">
         <x:v>REQ-COM-011</x:v>
       </x:c>
@@ -2108,7 +2111,7 @@
         <x:v>FS-COM-003</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>ModbusRtuEngine</x:v>
+        <x:v>DC-08 ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="E56" s="9" t="str">
         <x:v>공식 CRC Vector·최대 ADU 시험</x:v>
@@ -2121,7 +2124,7 @@
         <x:v>FR-RTU-023,026~030</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="32" customHeight="1">
+    <x:row r="57" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A57" s="22" t="str">
         <x:v>REQ-COM-012</x:v>
       </x:c>
@@ -2132,7 +2135,7 @@
         <x:v>FS-COM-002</x:v>
       </x:c>
       <x:c r="D57" s="9" t="str">
-        <x:v>PortWorker; Win32SerialPort</x:v>
+        <x:v>DC-09 Win32SerialPort; DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E57" s="9" t="str">
         <x:v>Partial Read, Noise, t1.5/t3.5 경계 시험</x:v>
@@ -2145,7 +2148,7 @@
         <x:v>FR-RTU-024~025,035; FR-PORT-021</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="32" customHeight="1">
+    <x:row r="58" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A58" s="22" t="str">
         <x:v>REQ-COM-013</x:v>
       </x:c>
@@ -2156,7 +2159,7 @@
         <x:v>FS-COM-002</x:v>
       </x:c>
       <x:c r="D58" s="9" t="str">
-        <x:v>PortWorker</x:v>
+        <x:v>DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E58" s="9" t="str">
         <x:v>다양한 BaudRate/Parity/StopBits Timing 시험</x:v>
@@ -2169,7 +2172,7 @@
         <x:v>FR-RTU-025; FR-PORT-021</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="32" customHeight="1">
+    <x:row r="59" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A59" s="22" t="str">
         <x:v>REQ-COM-014</x:v>
       </x:c>
@@ -2180,7 +2183,7 @@
         <x:v>FS-COM-003,FS-MODBUS-005</x:v>
       </x:c>
       <x:c r="D59" s="9" t="str">
-        <x:v>ModbusRtuEngine; DiagnosticService</x:v>
+        <x:v>DC-08 ModbusRtuEngine; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E59" s="9" t="str">
         <x:v>Noise 반복 시 FIFO 고갈 방지 시험</x:v>
@@ -2193,7 +2196,7 @@
         <x:v>FR-RTU-027; ERR-040</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="32" customHeight="1">
+    <x:row r="60" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A60" s="22" t="str">
         <x:v>REQ-COM-015</x:v>
       </x:c>
@@ -2204,7 +2207,7 @@
         <x:v>FS-MODBUS-001</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
-        <x:v>PortWorker</x:v>
+        <x:v>DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E60" s="9" t="str">
         <x:v>두 Port 동시 요청·순서·격리 시험</x:v>
@@ -2217,7 +2220,7 @@
         <x:v>FR-RTU-034</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="32" customHeight="1">
+    <x:row r="61" ht="15" hidden="0" customHeight="1">
       <x:c r="A61" s="22" t="str">
         <x:v>REQ-COM-016</x:v>
       </x:c>
@@ -2228,7 +2231,7 @@
         <x:v>FS-MON-005</x:v>
       </x:c>
       <x:c r="D61" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E61" s="9" t="str">
         <x:v>두 가상 채널 Extended CAN 출력 시험</x:v>
@@ -2241,7 +2244,7 @@
         <x:v>ENV-007,012</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="32" customHeight="1">
+    <x:row r="62" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A62" s="22" t="str">
         <x:v>REQ-COM-017</x:v>
       </x:c>
@@ -2252,7 +2255,7 @@
         <x:v>FS-MON-005</x:v>
       </x:c>
       <x:c r="D62" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E62" s="9" t="str">
         <x:v>실제 ID/Vector 표현 Mask 시험</x:v>
@@ -2265,7 +2268,7 @@
         <x:v>FR-CAN-001~002,021; CON-001</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="32" customHeight="1">
+    <x:row r="63" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A63" s="22" t="str">
         <x:v>REQ-COM-018</x:v>
       </x:c>
@@ -2276,7 +2279,7 @@
         <x:v>FS-MON-005</x:v>
       </x:c>
       <x:c r="D63" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E63" s="9" t="str">
         <x:v>Quantity 1,4,5,125 Frame 수·mm 시험</x:v>
@@ -2289,7 +2292,7 @@
         <x:v>FR-CAN-003~019,028</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="32" customHeight="1">
+    <x:row r="64" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A64" s="22" t="str">
         <x:v>REQ-COM-019</x:v>
       </x:c>
@@ -2300,7 +2303,7 @@
         <x:v>FS-MON-005</x:v>
       </x:c>
       <x:c r="D64" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E64" s="9" t="str">
         <x:v>Header Byte 단위 Golden Vector 시험</x:v>
@@ -2313,7 +2316,7 @@
         <x:v>FR-CAN-003~012</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="32" customHeight="1">
+    <x:row r="65" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A65" s="22" t="str">
         <x:v>REQ-COM-020</x:v>
       </x:c>
@@ -2324,7 +2327,7 @@
         <x:v>FS-MON-005</x:v>
       </x:c>
       <x:c r="D65" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E65" s="9" t="str">
         <x:v>마지막 가변 DLC 및 무패딩 시험</x:v>
@@ -2337,7 +2340,7 @@
         <x:v>FR-CAN-013~019</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="32" customHeight="1">
+    <x:row r="66" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A66" s="22" t="str">
         <x:v>REQ-COM-021</x:v>
       </x:c>
@@ -2348,7 +2351,7 @@
         <x:v>FS-MON-003~005</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
-        <x:v>SnapshotService</x:v>
+        <x:v>DC-11 SnapshotService</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
         <x:v>원인별 Header 및 0x04 미송출 시험</x:v>
@@ -2361,7 +2364,7 @@
         <x:v>FR-SRC-001~005; FR-LIFE-008</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="32" customHeight="1">
+    <x:row r="67" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A67" s="22" t="str">
         <x:v>REQ-DATA-001</x:v>
       </x:c>
@@ -2372,7 +2375,7 @@
         <x:v>FS-CSV-002,FS-MODBUS-002~004</x:v>
       </x:c>
       <x:c r="D67" s="9" t="str">
-        <x:v>ConfigurationLoader; RegisterService</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-06 RegisterService</x:v>
       </x:c>
       <x:c r="E67" s="9" t="str">
         <x:v>Address 0,40000,65535 경계 시험</x:v>
@@ -2385,7 +2388,7 @@
         <x:v>DATA-005; TBD-031</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="32" customHeight="1">
+    <x:row r="68" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A68" s="22" t="str">
         <x:v>REQ-DATA-002</x:v>
       </x:c>
@@ -2396,7 +2399,7 @@
         <x:v>FS-CSV-002</x:v>
       </x:c>
       <x:c r="D68" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E68" s="9" t="str">
         <x:v>인코딩·Quote·개행 오류 시험</x:v>
@@ -2409,7 +2412,7 @@
         <x:v>DATA-003,015~019</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="32" customHeight="1">
+    <x:row r="69" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A69" s="22" t="str">
         <x:v>REQ-DATA-003</x:v>
       </x:c>
@@ -2420,7 +2423,7 @@
         <x:v>FS-CSV-002</x:v>
       </x:c>
       <x:c r="D69" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E69" s="9" t="str">
         <x:v>Header 별칭·순서·칼럼 수 오류 시험</x:v>
@@ -2433,7 +2436,7 @@
         <x:v>DATA-006,011; ERR-020,022</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="32" customHeight="1">
+    <x:row r="70" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A70" s="22" t="str">
         <x:v>REQ-DATA-004</x:v>
       </x:c>
@@ -2444,7 +2447,7 @@
         <x:v>FS-CSV-002</x:v>
       </x:c>
       <x:c r="D70" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E70" s="9" t="str">
         <x:v>숫자 문법·범위·NaN/Infinity 시험</x:v>
@@ -2457,7 +2460,7 @@
         <x:v>DATA-007~009; ERR-018,021</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="32" customHeight="1">
+    <x:row r="71" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A71" s="22" t="str">
         <x:v>REQ-DATA-005</x:v>
       </x:c>
@@ -2468,7 +2471,7 @@
         <x:v>FS-CSV-002</x:v>
       </x:c>
       <x:c r="D71" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E71" s="9" t="str">
         <x:v>빈 Cell·공백·필수값 시험</x:v>
@@ -2481,7 +2484,7 @@
         <x:v>DATA-010~014</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="32" customHeight="1">
+    <x:row r="72" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A72" s="22" t="str">
         <x:v>REQ-DATA-006</x:v>
       </x:c>
@@ -2492,7 +2495,7 @@
         <x:v>FS-CSV-002,FS-DEV-001</x:v>
       </x:c>
       <x:c r="D72" s="9" t="str">
-        <x:v>ConfigurationLoader; DeviceRegistry</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-05 DeviceRegistry</x:v>
       </x:c>
       <x:c r="E72" s="9" t="str">
         <x:v>Schema와 Index/Port/Slave 유일성 시험</x:v>
@@ -2505,7 +2508,7 @@
         <x:v>DATA-DEV-001~006</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="32" customHeight="1">
+    <x:row r="73" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A73" s="22" t="str">
         <x:v>REQ-DATA-007</x:v>
       </x:c>
@@ -2516,7 +2519,7 @@
         <x:v>FS-CSV-002</x:v>
       </x:c>
       <x:c r="D73" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E73" s="9" t="str">
         <x:v>Schema, Rule_ID, Quantity, 완전 중복 시험</x:v>
@@ -2529,7 +2532,7 @@
         <x:v>DATA-RULE-001~012</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="32" customHeight="1">
+    <x:row r="74" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A74" s="22" t="str">
         <x:v>REQ-DATA-008</x:v>
       </x:c>
@@ -2540,7 +2543,7 @@
         <x:v>FS-CSV-002</x:v>
       </x:c>
       <x:c r="D74" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E74" s="9" t="str">
         <x:v>Rule 충돌 조합 시험</x:v>
@@ -2553,7 +2556,7 @@
         <x:v>DATA-RULE-007~010</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="32" customHeight="1">
+    <x:row r="75" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A75" s="22" t="str">
         <x:v>REQ-DATA-009</x:v>
       </x:c>
@@ -2564,7 +2567,7 @@
         <x:v>FS-CSV-002,FS-SIG-001</x:v>
       </x:c>
       <x:c r="D75" s="9" t="str">
-        <x:v>ConfigurationLoader; SignalCodec</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E75" s="9" t="str">
         <x:v>Schema와 행 단위 검증 시험</x:v>
@@ -2577,7 +2580,7 @@
         <x:v>DATA-MAP-001~023</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="32" customHeight="1">
+    <x:row r="76" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A76" s="22" t="str">
         <x:v>REQ-DATA-010</x:v>
       </x:c>
@@ -2588,7 +2591,7 @@
         <x:v>FS-CSV-002,FS-SIG-001</x:v>
       </x:c>
       <x:c r="D76" s="9" t="str">
-        <x:v>ConfigurationLoader; SignalCodec</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E76" s="9" t="str">
         <x:v>Enum 별칭·오타 거부 시험</x:v>
@@ -2601,7 +2604,7 @@
         <x:v>DATA-MAP-001~003</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="32" customHeight="1">
+    <x:row r="77" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A77" s="22" t="str">
         <x:v>REQ-DATA-011</x:v>
       </x:c>
@@ -2612,7 +2615,7 @@
         <x:v>FS-CSV-002</x:v>
       </x:c>
       <x:c r="D77" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E77" s="9" t="str">
         <x:v>Value_Table 유무/내용 변경의 Runtime 불변 시험</x:v>
@@ -2625,7 +2628,7 @@
         <x:v>DATA-MAP-005,017~021</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="32" customHeight="1">
+    <x:row r="78" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A78" s="22" t="str">
         <x:v>REQ-DATA-012</x:v>
       </x:c>
@@ -2636,7 +2639,7 @@
         <x:v>FS-CSV-002</x:v>
       </x:c>
       <x:c r="D78" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E78" s="9" t="str">
         <x:v>한도/초과 및 x86 Peak 메모리 시험</x:v>
@@ -2649,7 +2652,7 @@
         <x:v>IF-LIMIT-003; DATA-DEV-006; DATA-RULE-011; DATA-MAP-022</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="32" customHeight="1">
+    <x:row r="79" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A79" s="22" t="str">
         <x:v>REQ-DATA-013</x:v>
       </x:c>
@@ -2660,7 +2663,7 @@
         <x:v>FS-CSV-002</x:v>
       </x:c>
       <x:c r="D79" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E79" s="9" t="str">
         <x:v>Byte 기반 한도·UTF-8 다중 Byte 시험</x:v>
@@ -2673,7 +2676,7 @@
         <x:v>IF-LIMIT-004~005; DATA-022~023</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="32" customHeight="1">
+    <x:row r="80" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A80" s="22" t="str">
         <x:v>REQ-DATA-014</x:v>
       </x:c>
@@ -2684,7 +2687,7 @@
         <x:v>FS-INIT-002</x:v>
       </x:c>
       <x:c r="D80" s="9" t="str">
-        <x:v>Build &amp; Packaging</x:v>
+        <x:v>DC-17 Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="E80" s="9" t="str">
         <x:v>이동 가능한 Configuration 패키지 시험</x:v>
@@ -2697,7 +2700,7 @@
         <x:v>DATA-LAYOUT-001~004</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="32" customHeight="1">
+    <x:row r="81" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A81" s="22" t="str">
         <x:v>REQ-IF-001</x:v>
       </x:c>
@@ -2708,7 +2711,7 @@
         <x:v>FS-INIT-001</x:v>
       </x:c>
       <x:c r="D81" s="9" t="str">
-        <x:v>CAPL ABI Adapter</x:v>
+        <x:v>DC-01 CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="E81" s="9" t="str">
         <x:v>Vector Sample 기반 x86 최소 ABI 시험</x:v>
@@ -2721,7 +2724,7 @@
         <x:v>FACT-DLL-001~005; IF-ABI-009</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="32" customHeight="1">
+    <x:row r="82" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A82" s="22" t="str">
         <x:v>REQ-IF-002</x:v>
       </x:c>
@@ -2732,7 +2735,7 @@
         <x:v>FS-INIT-001</x:v>
       </x:c>
       <x:c r="D82" s="9" t="str">
-        <x:v>CAPL Core; CAPL ABI Adapter</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-13 CAPL Core</x:v>
       </x:c>
       <x:c r="E82" s="9" t="str">
         <x:v>Export Table 이름·Wrapper 호출 시험</x:v>
@@ -2745,7 +2748,7 @@
         <x:v>IF-NAME-001~003; IF-CTX-001~006</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="32" customHeight="1">
+    <x:row r="83" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A83" s="22" t="str">
         <x:v>REQ-IF-003</x:v>
       </x:c>
@@ -2756,7 +2759,7 @@
         <x:v>FS-INIT-001</x:v>
       </x:c>
       <x:c r="D83" s="9" t="str">
-        <x:v>CAPL ABI Adapter</x:v>
+        <x:v>DC-01 CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="E83" s="9" t="str">
         <x:v>최소 ABI Probe 및 Buffer 불변 시험</x:v>
@@ -2769,7 +2772,7 @@
         <x:v>IF-ABI-001~011</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="32" customHeight="1">
+    <x:row r="84" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A84" s="22" t="str">
         <x:v>REQ-IF-004</x:v>
       </x:c>
@@ -2780,7 +2783,7 @@
         <x:v>FS-INIT-001,FS-LIFE-001~004,FS-REG-001~003,FS-SIG-002~003,FS-MON-001~004,FS-DIAG-001~002</x:v>
       </x:c>
       <x:c r="D84" s="9" t="str">
-        <x:v>CAPL ABI Adapter</x:v>
+        <x:v>DC-01 CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="E84" s="9" t="str">
         <x:v>21개 Export Table/Wrapper Contract 시험</x:v>
@@ -2793,7 +2796,7 @@
         <x:v>IF-API-001~021</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="32" customHeight="1">
+    <x:row r="85" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A85" s="22" t="str">
         <x:v>REQ-IF-005</x:v>
       </x:c>
@@ -2804,7 +2807,7 @@
         <x:v>FS-LIFE-003,FS-DIAG-001</x:v>
       </x:c>
       <x:c r="D85" s="9" t="str">
-        <x:v>CAPL ABI Adapter; DiagnosticService</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E85" s="9" t="str">
         <x:v>동기/비동기/No Data 반환 시험</x:v>
@@ -2817,7 +2820,7 @@
         <x:v>IF-RET-001~009; IF-CODE-001~004</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="32" customHeight="1">
+    <x:row r="86" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A86" s="22" t="str">
         <x:v>REQ-IF-006</x:v>
       </x:c>
@@ -2828,7 +2831,7 @@
         <x:v>FS-REG-001~002,FS-SIG-002,FS-MON-003~004</x:v>
       </x:c>
       <x:c r="D86" s="9" t="str">
-        <x:v>CAPL Core; CAPL ABI Adapter</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-13 CAPL Core</x:v>
       </x:c>
       <x:c r="E86" s="9" t="str">
         <x:v>Buffer 부족·Embedded NUL·실패 시 출력 유지 시험</x:v>
@@ -2841,7 +2844,7 @@
         <x:v>IF-ABI-006~007,010~011; IF-RET-002~007</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="32" customHeight="1">
+    <x:row r="87" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A87" s="22" t="str">
         <x:v>REQ-IF-007</x:v>
       </x:c>
@@ -2852,7 +2855,7 @@
         <x:v>FS-MON-003~005</x:v>
       </x:c>
       <x:c r="D87" s="9" t="str">
-        <x:v>SnapshotService; CAPL Monitoring</x:v>
+        <x:v>DC-11 SnapshotService; DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E87" s="9" t="str">
         <x:v>Version·Capacity·필드 Routing 시험</x:v>
@@ -2865,7 +2868,7 @@
         <x:v>IF-META-001~016</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="32" customHeight="1">
+    <x:row r="88" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A88" s="22" t="str">
         <x:v>REQ-IF-008</x:v>
       </x:c>
@@ -2876,7 +2879,7 @@
         <x:v>FS-LIFE-003</x:v>
       </x:c>
       <x:c r="D88" s="9" t="str">
-        <x:v>LifecycleController</x:v>
+        <x:v>DC-03 LifecycleController</x:v>
       </x:c>
       <x:c r="E88" s="9" t="str">
         <x:v>상태 Snapshot 원자성과 Version 시험</x:v>
@@ -2889,7 +2892,7 @@
         <x:v>IF-LSTAT-001~014</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="32" customHeight="1">
+    <x:row r="89" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A89" s="22" t="str">
         <x:v>REQ-IF-009</x:v>
       </x:c>
@@ -2900,7 +2903,7 @@
         <x:v>FS-DIAG-001,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D89" s="9" t="str">
-        <x:v>DiagnosticService; SnapshotService</x:v>
+        <x:v>DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E89" s="9" t="str">
         <x:v>Version·ValidMask·Capacity·NUL 시험</x:v>
@@ -2913,7 +2916,7 @@
         <x:v>IF-EMETA-001~025; IF-ESTAT-001~002; IF-CSTAT-001~002</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="32" customHeight="1">
+    <x:row r="90" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A90" s="22" t="str">
         <x:v>REQ-IF-010</x:v>
       </x:c>
@@ -2924,7 +2927,7 @@
         <x:v>FS-INIT-002,FS-COM-001,FS-DIAG-001</x:v>
       </x:c>
       <x:c r="D90" s="9" t="str">
-        <x:v>Generated Contracts</x:v>
+        <x:v>DC-16 Generated Contracts</x:v>
       </x:c>
       <x:c r="E90" s="9" t="str">
         <x:v>C++/CAPL 상수 목록 일치 시험</x:v>
@@ -2937,7 +2940,7 @@
         <x:v>IF-CONST-001~004; IF-ECLASS-001~004</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="32" customHeight="1">
+    <x:row r="91" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A91" s="22" t="str">
         <x:v>REQ-IF-011</x:v>
       </x:c>
@@ -2948,7 +2951,7 @@
         <x:v>FS-CSV-002,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D91" s="9" t="str">
-        <x:v>Generated Contracts; ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-16 Generated Contracts</x:v>
       </x:c>
       <x:c r="E91" s="9" t="str">
         <x:v>모든 한도 경계와 초과 시험</x:v>
@@ -2961,7 +2964,7 @@
         <x:v>IF-LIMIT-001~008</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="32" customHeight="1">
+    <x:row r="92" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A92" s="22" t="str">
         <x:v>REQ-IF-012</x:v>
       </x:c>
@@ -2972,7 +2975,7 @@
         <x:v>FS-REG-001,FS-REG-002</x:v>
       </x:c>
       <x:c r="D92" s="9" t="str">
-        <x:v>RegisterService; CAPL ABI Adapter</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-06 RegisterService</x:v>
       </x:c>
       <x:c r="E92" s="9" t="str">
         <x:v>Quantity/Capacity 조합 및 실패 불변 시험</x:v>
@@ -2985,7 +2988,7 @@
         <x:v>IF-REG-001~012</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="32" customHeight="1">
+    <x:row r="93" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A93" s="22" t="str">
         <x:v>REQ-IF-013</x:v>
       </x:c>
@@ -2996,7 +2999,7 @@
         <x:v>FS-SIG-002,FS-SIG-003</x:v>
       </x:c>
       <x:c r="D93" s="9" t="str">
-        <x:v>SignalCodec; CAPL ABI Adapter</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E93" s="9" t="str">
         <x:v>정상/오류 시 Reference copy-restore 시험</x:v>
@@ -3009,7 +3012,7 @@
         <x:v>IF-SIG-001~007</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="32" customHeight="1">
+    <x:row r="94" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A94" s="22" t="str">
         <x:v>REQ-IF-014</x:v>
       </x:c>
@@ -3020,7 +3023,7 @@
         <x:v>FS-MON-003,FS-MON-004</x:v>
       </x:c>
       <x:c r="D94" s="9" t="str">
-        <x:v>SnapshotService; CAPL ABI Adapter</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-11 SnapshotService</x:v>
       </x:c>
       <x:c r="E94" s="9" t="str">
         <x:v>COM 비대기, Queue No Data, Buffer 부족 시험</x:v>
@@ -3033,7 +3036,7 @@
         <x:v>IF-MON-001~012</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="32" customHeight="1">
+    <x:row r="95" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A95" s="22" t="str">
         <x:v>REQ-ERR-001</x:v>
       </x:c>
@@ -3044,7 +3047,7 @@
         <x:v>FS-CSV-002,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D95" s="9" t="str">
-        <x:v>ConfigurationLoader; DiagnosticService</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E95" s="9" t="str">
         <x:v>각 CSV 오류 강제 및 Context 정확성 시험</x:v>
@@ -3057,7 +3060,7 @@
         <x:v>ERR-009~023; LOG-009</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="32" customHeight="1">
+    <x:row r="96" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A96" s="22" t="str">
         <x:v>REQ-ERR-002</x:v>
       </x:c>
@@ -3068,7 +3071,7 @@
         <x:v>FS-CSV-003,FS-REG-001~003,FS-SIG-002~004</x:v>
       </x:c>
       <x:c r="D96" s="9" t="str">
-        <x:v>All core services</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-04 ConfigurationLoader; DC-06 RegisterService; DC-07 SignalCodec; DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E96" s="9" t="str">
         <x:v>실패 주입 및 전후 메모리 비교 시험</x:v>
@@ -3081,7 +3084,7 @@
         <x:v>ERR-001~007,010~018,024~036,042</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="32" customHeight="1">
+    <x:row r="97" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A97" s="22" t="str">
         <x:v>REQ-ERR-003</x:v>
       </x:c>
@@ -3092,7 +3095,7 @@
         <x:v>FS-MODBUS-005</x:v>
       </x:c>
       <x:c r="D97" s="9" t="str">
-        <x:v>ModbusRtuEngine</x:v>
+        <x:v>DC-08 ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="E97" s="9" t="str">
         <x:v>Exception Golden Vector 시험</x:v>
@@ -3105,7 +3108,7 @@
         <x:v>ERR-039~043; FR-RTU-033</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="32" customHeight="1">
+    <x:row r="98" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A98" s="22" t="str">
         <x:v>REQ-ERR-004</x:v>
       </x:c>
@@ -3116,7 +3119,7 @@
         <x:v>FS-DIAG-001,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D98" s="9" t="str">
-        <x:v>DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E98" s="9" t="str">
         <x:v>영역별 오류와 OsError 분리 시험</x:v>
@@ -3129,7 +3132,7 @@
         <x:v>IF-CODE-005~016</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="32" customHeight="1">
+    <x:row r="99" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A99" s="22" t="str">
         <x:v>REQ-ERR-005</x:v>
       </x:c>
@@ -3140,7 +3143,7 @@
         <x:v>FS-DIAG-001,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D99" s="9" t="str">
-        <x:v>Generated Contracts</x:v>
+        <x:v>DC-16 Generated Contracts</x:v>
       </x:c>
       <x:c r="E99" s="9" t="str">
         <x:v>90개 목록 일치 및 신규 코드 추가 회귀 시험</x:v>
@@ -3153,7 +3156,7 @@
         <x:v>IF-CODE-017~020; TBD-064</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="32" customHeight="1">
+    <x:row r="100" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A100" s="22" t="str">
         <x:v>REQ-ERR-006</x:v>
       </x:c>
@@ -3164,7 +3167,7 @@
         <x:v>FS-DIAG-001,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D100" s="9" t="str">
-        <x:v>DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E100" s="9" t="str">
         <x:v>동시 오류·Context 격리·Polling 시험</x:v>
@@ -3177,7 +3180,7 @@
         <x:v>IF-ERR-001~015; DES-ERR-001~004</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="32" customHeight="1">
+    <x:row r="101" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A101" s="22" t="str">
         <x:v>REQ-ERR-007</x:v>
       </x:c>
@@ -3188,7 +3191,7 @@
         <x:v>FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D101" s="9" t="str">
-        <x:v>DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E101" s="9" t="str">
         <x:v>반복 Noise·Overflow·Sequence 시험</x:v>
@@ -3201,7 +3204,7 @@
         <x:v>ERR-032~033,040; LOG-011~013</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="32" customHeight="1">
+    <x:row r="102" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A102" s="22" t="str">
         <x:v>REQ-ERR-008</x:v>
       </x:c>
@@ -3212,7 +3215,7 @@
         <x:v>FS-LIFE-001,FS-LIFE-004</x:v>
       </x:c>
       <x:c r="D102" s="9" t="str">
-        <x:v>LifecycleController</x:v>
+        <x:v>DC-03 LifecycleController</x:v>
       </x:c>
       <x:c r="E102" s="9" t="str">
         <x:v>실패 등급별 상태 전이 시험</x:v>
@@ -3225,7 +3228,7 @@
         <x:v>FR-LIFE-013; ERR-028,034~038</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="32" customHeight="1">
+    <x:row r="103" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A103" s="22" t="str">
         <x:v>REQ-PERF-001</x:v>
       </x:c>
@@ -3236,7 +3239,7 @@
         <x:v>FS-MODBUS-002~004</x:v>
       </x:c>
       <x:c r="D103" s="9" t="str">
-        <x:v>PortWorker; ModbusRtuEngine</x:v>
+        <x:v>DC-08 ModbusRtuEngine; DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E103" s="9" t="str">
         <x:v>회사 환경 실제 Timeout 기반 지연 측정</x:v>
@@ -3249,7 +3252,7 @@
         <x:v>PERF-001~003; TBD-039</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="32" customHeight="1">
+    <x:row r="104" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A104" s="22" t="str">
         <x:v>REQ-PERF-002</x:v>
       </x:c>
@@ -3260,7 +3263,7 @@
         <x:v>FS-MON-003,FS-MON-004,FS-MON-006</x:v>
       </x:c>
       <x:c r="D104" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E104" s="9" t="str">
         <x:v>Trace Timestamp 기반 지연 측정</x:v>
@@ -3273,7 +3276,7 @@
         <x:v>PERF-004~013; TBD-039</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="32" customHeight="1">
+    <x:row r="105" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A105" s="22" t="str">
         <x:v>REQ-PERF-003</x:v>
       </x:c>
@@ -3284,7 +3287,7 @@
         <x:v>FS-INIT-001,FS-LIFE-001~003,FS-MON-003~004</x:v>
       </x:c>
       <x:c r="D105" s="9" t="str">
-        <x:v>CAPL ABI Adapter</x:v>
+        <x:v>DC-01 CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="E105" s="9" t="str">
         <x:v>호출시간 계측과 정적 코드 검토</x:v>
@@ -3297,7 +3300,7 @@
         <x:v>NFR-007,010</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="32" customHeight="1">
+    <x:row r="106" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A106" s="22" t="str">
         <x:v>REQ-PERF-004</x:v>
       </x:c>
@@ -3308,7 +3311,7 @@
         <x:v>FS-MON-002,FS-MON-006</x:v>
       </x:c>
       <x:c r="D106" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E106" s="9" t="str">
         <x:v>200 Rule 최대/대표 부하 시험</x:v>
@@ -3321,7 +3324,7 @@
         <x:v>FR-LOAD-012~014,019; PERF-014~019</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="32" customHeight="1">
+    <x:row r="107" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A107" s="22" t="str">
         <x:v>REQ-PERF-005</x:v>
       </x:c>
@@ -3332,7 +3335,7 @@
         <x:v>FS-CSV-003</x:v>
       </x:c>
       <x:c r="D107" s="9" t="str">
-        <x:v>DeviceRegistry; ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-05 DeviceRegistry</x:v>
       </x:c>
       <x:c r="E107" s="9" t="str">
         <x:v>Peak Working Set 측정</x:v>
@@ -3345,7 +3348,7 @@
         <x:v>PERF-018</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="32" customHeight="1">
+    <x:row r="108" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A108" s="22" t="str">
         <x:v>REQ-PERF-006</x:v>
       </x:c>
@@ -3356,7 +3359,7 @@
         <x:v>FS-SHUT-001</x:v>
       </x:c>
       <x:c r="D108" s="9" t="str">
-        <x:v>LifecycleController</x:v>
+        <x:v>DC-03 LifecycleController</x:v>
       </x:c>
       <x:c r="E108" s="9" t="str">
         <x:v>각 상태 Finalize 시간 및 지연 Driver 시험</x:v>
@@ -3369,7 +3372,7 @@
         <x:v>PERF-020~022; TBD-065</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="32" customHeight="1">
+    <x:row r="109" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A109" s="22" t="str">
         <x:v>REQ-REL-001</x:v>
       </x:c>
@@ -3380,7 +3383,7 @@
         <x:v>FS-COM-002,FS-MODBUS-001</x:v>
       </x:c>
       <x:c r="D109" s="9" t="str">
-        <x:v>PortWorker</x:v>
+        <x:v>DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E109" s="9" t="str">
         <x:v>동시 두 Port I/O와 Handle 소유 검토</x:v>
@@ -3393,7 +3396,7 @@
         <x:v>DES-THREAD-001</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="32" customHeight="1">
+    <x:row r="110" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A110" s="22" t="str">
         <x:v>REQ-REL-002</x:v>
       </x:c>
@@ -3404,7 +3407,7 @@
         <x:v>FS-REG-001~003,FS-MON-004,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D110" s="9" t="str">
-        <x:v>RegisterService; SnapshotService; DiagnosticService</x:v>
+        <x:v>DC-06 RegisterService; DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E110" s="9" t="str">
         <x:v>동시 RTU/CAPL 접근 및 Race 시험</x:v>
@@ -3417,7 +3420,7 @@
         <x:v>DES-THREAD-002~003</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="32" customHeight="1">
+    <x:row r="111" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A111" s="22" t="str">
         <x:v>REQ-REL-003</x:v>
       </x:c>
@@ -3428,7 +3431,7 @@
         <x:v>FS-REG-002,FS-SHUT-001</x:v>
       </x:c>
       <x:c r="D111" s="9" t="str">
-        <x:v>All runtime services</x:v>
+        <x:v>DC-03 LifecycleController; DC-06 RegisterService; DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E111" s="9" t="str">
         <x:v>Deadlock Stress 및 Lock-order 검토</x:v>
@@ -3441,7 +3444,7 @@
         <x:v>DES-THREAD-004</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="32" customHeight="1">
+    <x:row r="112" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A112" s="22" t="str">
         <x:v>REQ-REL-004</x:v>
       </x:c>
@@ -3452,7 +3455,7 @@
         <x:v>FS-MON-004,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D112" s="9" t="str">
-        <x:v>SnapshotService; DiagnosticService</x:v>
+        <x:v>DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E112" s="9" t="str">
         <x:v>Allocator hook/Stress 시험</x:v>
@@ -3465,7 +3468,7 @@
         <x:v>DES-THREAD-003; DES-CAN-011~012</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="32" customHeight="1">
+    <x:row r="113" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A113" s="22" t="str">
         <x:v>REQ-REL-005</x:v>
       </x:c>
@@ -3476,7 +3479,7 @@
         <x:v>FS-MON-003,FS-MON-004</x:v>
       </x:c>
       <x:c r="D113" s="9" t="str">
-        <x:v>RegisterService; SnapshotService</x:v>
+        <x:v>DC-06 RegisterService; DC-11 SnapshotService</x:v>
       </x:c>
       <x:c r="E113" s="9" t="str">
         <x:v>동시 다중 Register Write와 Snapshot 일관성 시험</x:v>
@@ -3489,7 +3492,7 @@
         <x:v>IF-MON-002~003</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="32" customHeight="1">
+    <x:row r="114" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A114" s="22" t="str">
         <x:v>REQ-REL-006</x:v>
       </x:c>
@@ -3500,7 +3503,7 @@
         <x:v>FS-MON-004,FS-MON-006</x:v>
       </x:c>
       <x:c r="D114" s="9" t="str">
-        <x:v>SnapshotService; CAPL Monitoring</x:v>
+        <x:v>DC-11 SnapshotService; DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E114" s="9" t="str">
         <x:v>Burst/Overflow 중 RTU 응답 시험</x:v>
@@ -3513,7 +3516,7 @@
         <x:v>NFR-002~004; FR-LOAD-009</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="32" customHeight="1">
+    <x:row r="115" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A115" s="22" t="str">
         <x:v>REQ-RES-001</x:v>
       </x:c>
@@ -3524,7 +3527,7 @@
         <x:v>FS-DEV-001</x:v>
       </x:c>
       <x:c r="D115" s="9" t="str">
-        <x:v>DeviceRegistry</x:v>
+        <x:v>DC-05 DeviceRegistry</x:v>
       </x:c>
       <x:c r="E115" s="9" t="str">
         <x:v>Device 수별 메모리 및 직접 Address 시험</x:v>
@@ -3537,7 +3540,7 @@
         <x:v>DES-REG-005</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="32" customHeight="1">
+    <x:row r="116" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A116" s="22" t="str">
         <x:v>REQ-RES-002</x:v>
       </x:c>
@@ -3548,7 +3551,7 @@
         <x:v>FS-SHUT-001</x:v>
       </x:c>
       <x:c r="D116" s="9" t="str">
-        <x:v>LifecycleController</x:v>
+        <x:v>DC-03 LifecycleController</x:v>
       </x:c>
       <x:c r="E116" s="9" t="str">
         <x:v>Thread/Handle 누수와 종료 Race 시험</x:v>
@@ -3561,7 +3564,7 @@
         <x:v>FR-LIFE-018~019; DES-THREAD-005</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="32" customHeight="1">
+    <x:row r="117" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A117" s="22" t="str">
         <x:v>REQ-RES-003</x:v>
       </x:c>
@@ -3572,7 +3575,7 @@
         <x:v>FS-MON-003,FS-MON-004,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D117" s="9" t="str">
-        <x:v>SnapshotService; DiagnosticService</x:v>
+        <x:v>DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E117" s="9" t="str">
         <x:v>Capacity 경계와 Overflow 정책 시험</x:v>
@@ -3585,7 +3588,7 @@
         <x:v>IF-LIMIT-006</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="32" customHeight="1">
+    <x:row r="118" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A118" s="22" t="str">
         <x:v>REQ-RES-004</x:v>
       </x:c>
@@ -3596,7 +3599,7 @@
         <x:v>FS-MON-004,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D118" s="9" t="str">
-        <x:v>SnapshotService; DiagnosticService</x:v>
+        <x:v>DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E118" s="9" t="str">
         <x:v>포화 및 Sequence wrap 시험</x:v>
@@ -3609,7 +3612,7 @@
         <x:v>IF-QSTAT-001~004</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="32" customHeight="1">
+    <x:row r="119" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A119" s="22" t="str">
         <x:v>REQ-DIAG-001</x:v>
       </x:c>
@@ -3620,7 +3623,7 @@
         <x:v>FS-DIAG-001</x:v>
       </x:c>
       <x:c r="D119" s="9" t="str">
-        <x:v>CAPL Core; DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService; DC-13 CAPL Core</x:v>
       </x:c>
       <x:c r="E119" s="9" t="str">
         <x:v>오류별 Write Window 출력 시험</x:v>
@@ -3633,7 +3636,7 @@
         <x:v>LOG-004,009~010</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="32" customHeight="1">
+    <x:row r="120" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A120" s="22" t="str">
         <x:v>REQ-DIAG-002</x:v>
       </x:c>
@@ -3644,7 +3647,7 @@
         <x:v>FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D120" s="9" t="str">
-        <x:v>CAPL Core; DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService; DC-13 CAPL Core</x:v>
       </x:c>
       <x:c r="E120" s="9" t="str">
         <x:v>비동기 오류 순서·병합·Overflow 출력 시험</x:v>
@@ -3657,7 +3660,7 @@
         <x:v>LOG-011~013</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="32" customHeight="1">
+    <x:row r="121" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A121" s="22" t="str">
         <x:v>REQ-DIAG-003</x:v>
       </x:c>
@@ -3668,7 +3671,7 @@
         <x:v>FS-MON-006,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D121" s="9" t="str">
-        <x:v>CAPL Monitoring; DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService; DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E121" s="9" t="str">
         <x:v>부하 시험 진단값 상호 검증</x:v>
@@ -3681,7 +3684,7 @@
         <x:v>LOG-002~008,014~017</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="32" customHeight="1">
+    <x:row r="122" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A122" s="22" t="str">
         <x:v>REQ-DIAG-004</x:v>
       </x:c>
@@ -3692,7 +3695,7 @@
         <x:v>FS-LIFE-001,FS-LIFE-004,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D122" s="9" t="str">
-        <x:v>Win32SerialPort; DiagnosticService</x:v>
+        <x:v>DC-09 Win32SerialPort; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E122" s="9" t="str">
         <x:v>강제 Win32 오류와 Context 시험</x:v>
@@ -3705,7 +3708,7 @@
         <x:v>ERR-027~038; LOG-013</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="32" customHeight="1">
+    <x:row r="123" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A123" s="22" t="str">
         <x:v>REQ-DIAG-005</x:v>
       </x:c>
@@ -3716,7 +3719,7 @@
         <x:v>FS-COM-003,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D123" s="9" t="str">
-        <x:v>DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E123" s="9" t="str">
         <x:v>반복 동일 오류 부하 시험</x:v>
@@ -3729,7 +3732,7 @@
         <x:v>ERR-040; LOG-011</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="32" customHeight="1">
+    <x:row r="124" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A124" s="22" t="str">
         <x:v>REQ-COMP-001</x:v>
       </x:c>
@@ -3740,7 +3743,7 @@
         <x:v>FS-INIT-001</x:v>
       </x:c>
       <x:c r="D124" s="9" t="str">
-        <x:v>Build &amp; Packaging</x:v>
+        <x:v>DC-17 Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="E124" s="9" t="str">
         <x:v>깨끗한 PC Win32 Build 및 CANalyzer 로딩 시험</x:v>
@@ -3753,7 +3756,7 @@
         <x:v>ENV-001~002,010~011; COMP-001~002,008</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="32" customHeight="1">
+    <x:row r="125" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A125" s="22" t="str">
         <x:v>REQ-COMP-002</x:v>
       </x:c>
@@ -3764,7 +3767,7 @@
         <x:v>FS-INIT-001</x:v>
       </x:c>
       <x:c r="D125" s="9" t="str">
-        <x:v>Build &amp; Packaging</x:v>
+        <x:v>DC-17 Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="E125" s="9" t="str">
         <x:v>설치 경로 변경·Clean Build 시험</x:v>
@@ -3777,7 +3780,7 @@
         <x:v>DES-BUILD-001~005; TBD-059</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="32" customHeight="1">
+    <x:row r="126" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A126" s="22" t="str">
         <x:v>REQ-COMP-003</x:v>
       </x:c>
@@ -3788,7 +3791,7 @@
         <x:v>FS-INIT-001</x:v>
       </x:c>
       <x:c r="D126" s="9" t="str">
-        <x:v>Build &amp; Packaging</x:v>
+        <x:v>DC-17 Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="E126" s="9" t="str">
         <x:v>공개 Export/문서에 Legacy 이름 부재 검토</x:v>
@@ -3801,7 +3804,7 @@
         <x:v>PRJ-005~006; COMP-009~010</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="32" customHeight="1">
+    <x:row r="127" ht="54" hidden="0" customHeight="1">
       <x:c r="A127" s="22" t="str">
         <x:v>REQ-COMP-004</x:v>
       </x:c>
@@ -3812,7 +3815,7 @@
         <x:v>FS-INIT-001</x:v>
       </x:c>
       <x:c r="D127" s="9" t="str">
-        <x:v>M485E.Core</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-05 DeviceRegistry; DC-06 RegisterService; DC-07 SignalCodec; DC-08 ModbusRtuEngine; DC-11 SnapshotService; DC-12 DiagnosticService; DC-17 Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="E127" s="9" t="str">
         <x:v>Win32 타입 크기 검토; x64는 후속 체크리스트</x:v>
@@ -3825,7 +3828,7 @@
         <x:v>ENV-011; FUT-001~005</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="32" customHeight="1">
+    <x:row r="128" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A128" s="22" t="str">
         <x:v>REQ-COMP-005</x:v>
       </x:c>
@@ -3836,7 +3839,7 @@
         <x:v>FS-COM-002,FS-COM-003,FS-MODBUS-002~005</x:v>
       </x:c>
       <x:c r="D128" s="9" t="str">
-        <x:v>ModbusRtuEngine</x:v>
+        <x:v>DC-08 ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="E128" s="9" t="str">
         <x:v>공식 Protocol Vector 및 경계 시험</x:v>
@@ -3849,7 +3852,7 @@
         <x:v>COMP-013</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="32" customHeight="1">
+    <x:row r="129" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A129" s="22" t="str">
         <x:v>REQ-COMP-006</x:v>
       </x:c>
@@ -3860,7 +3863,7 @@
         <x:v>FS-DIAG-001,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D129" s="9" t="str">
-        <x:v>Generated Contracts</x:v>
+        <x:v>DC-16 Generated Contracts</x:v>
       </x:c>
       <x:c r="E129" s="9" t="str">
         <x:v>구 Layout consumer 회귀 시험</x:v>
@@ -3873,7 +3876,7 @@
         <x:v>IF-META-015; IF-QSTAT-004; IF-LIMIT-008; IF-CODE-017</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="32" customHeight="1">
+    <x:row r="130" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A130" s="22" t="str">
         <x:v>REQ-SEC-001</x:v>
       </x:c>
@@ -3884,7 +3887,7 @@
         <x:v>FS-CSV-001,FS-CSV-002</x:v>
       </x:c>
       <x:c r="D130" s="9" t="str">
-        <x:v>ConfigurationLoader</x:v>
+        <x:v>DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E130" s="9" t="str">
         <x:v>로컬/UNC/권한 부족 경로 시험</x:v>
@@ -3897,7 +3900,7 @@
         <x:v>NFR-012; COMP-006; OOS-015</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="32" customHeight="1">
+    <x:row r="131" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A131" s="22" t="str">
         <x:v>REQ-SEC-002</x:v>
       </x:c>
@@ -3908,7 +3911,7 @@
         <x:v>FS-MODBUS-001</x:v>
       </x:c>
       <x:c r="D131" s="9" t="str">
-        <x:v>System boundary</x:v>
+        <x:v>DC-08 ModbusRtuEngine; DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E131" s="9" t="str">
         <x:v>보안 경계 문서 검토</x:v>
@@ -3921,7 +3924,7 @@
         <x:v>NFR-012</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="32" customHeight="1">
+    <x:row r="132" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A132" s="22" t="str">
         <x:v>REQ-SEC-003</x:v>
       </x:c>
@@ -3932,7 +3935,7 @@
         <x:v>FS-CSV-001,FS-DIAG-001</x:v>
       </x:c>
       <x:c r="D132" s="9" t="str">
-        <x:v>CAPL ABI Adapter; ConfigurationLoader</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-04 ConfigurationLoader</x:v>
       </x:c>
       <x:c r="E132" s="9" t="str">
         <x:v>ASCII/한글 경로·Text round-trip 시험</x:v>
@@ -3953,7 +3956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6578c94867b04602"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R225405ba02354d1c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7010,7 +7013,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd170a116ed7b4dae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R100a34472a584bbc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7024,7 +7027,7 @@
     <x:col min="3" max="3" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="21" t="str">
         <x:v>Functional Specification ID</x:v>
       </x:c>
@@ -7035,7 +7038,7 @@
         <x:v>Covered Requirement IDs</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="32" customHeight="1">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
         <x:v>FS-INIT-001</x:v>
       </x:c>
@@ -7043,10 +7046,10 @@
         <x:v>CAPL DLL 초기화</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>REQ-FUNC-001; REQ-IF-001~003; REQ-COMP-001~004</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-001; REQ-IF-001~004; REQ-PERF-003; REQ-COMP-001~004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="9" t="str">
         <x:v>FS-INIT-002</x:v>
       </x:c>
@@ -7054,10 +7057,10 @@
         <x:v>Configuration 입력 준비</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>REQ-FUNC-009~010; REQ-DATA-014; REQ-IF-010</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="32" customHeight="1">
+        <x:v>REQ-DATA-014; REQ-IF-010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="9" t="str">
         <x:v>FS-CSV-001</x:v>
       </x:c>
@@ -7065,10 +7068,10 @@
         <x:v>CSV 경로 처리</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>REQ-FUNC-009~010; REQ-SEC-001,REQ-SEC-003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-009~010; REQ-SEC-001, REQ-SEC-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="9" t="str">
         <x:v>FS-CSV-002</x:v>
       </x:c>
@@ -7076,10 +7079,10 @@
         <x:v>CSV Parsing 및 전체 검증</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>REQ-FUNC-011; REQ-DATA-001~013; REQ-ERR-001~002</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-011, REQ-FUNC-026; REQ-DATA-001~013; REQ-IF-011; REQ-ERR-001; REQ-SEC-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>FS-CSV-003</x:v>
       </x:c>
@@ -7087,10 +7090,10 @@
         <x:v>원자적 Refresh</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>REQ-FUNC-011~013; REQ-PERF-005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-011~013; REQ-ERR-002; REQ-PERF-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="9" t="str">
         <x:v>FS-LIFE-001</x:v>
       </x:c>
@@ -7098,10 +7101,10 @@
         <x:v>전체 Connect</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>REQ-FUNC-002~004; REQ-COM-002~004</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-002, REQ-FUNC-004; REQ-IF-004; REQ-ERR-008; REQ-PERF-003; REQ-DIAG-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>FS-LIFE-002</x:v>
       </x:c>
@@ -7109,10 +7112,10 @@
         <x:v>전체 Disconnect</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>REQ-FUNC-002,REQ-FUNC-005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-002, REQ-FUNC-005; REQ-IF-004; REQ-PERF-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="9" t="str">
         <x:v>FS-LIFE-003</x:v>
       </x:c>
@@ -7120,10 +7123,10 @@
         <x:v>Lifecycle 상태 Polling</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>REQ-FUNC-002~003; REQ-IF-005,REQ-IF-008</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-002~003; REQ-IF-004~005, REQ-IF-008; REQ-PERF-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>FS-LIFE-004</x:v>
       </x:c>
@@ -7131,10 +7134,10 @@
         <x:v>치명적 COM 장애 복구</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>REQ-FUNC-006~007; REQ-ERR-008</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-006~007; REQ-IF-004; REQ-ERR-008; REQ-DIAG-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="9" t="str">
         <x:v>FS-COM-001</x:v>
       </x:c>
@@ -7142,10 +7145,10 @@
         <x:v>Serial Port 설정</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>REQ-COM-001~005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="32" customHeight="1">
+        <x:v>REQ-COM-001~005; REQ-IF-010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="9" t="str">
         <x:v>FS-COM-002</x:v>
       </x:c>
@@ -7153,10 +7156,10 @@
         <x:v>RTU Stream Frame 조립</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>REQ-COM-012~013; REQ-REL-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="32" customHeight="1">
+        <x:v>REQ-COM-012~013; REQ-REL-001; REQ-COMP-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="9" t="str">
         <x:v>FS-COM-003</x:v>
       </x:c>
@@ -7164,10 +7167,10 @@
         <x:v>RTU Frame 및 CRC 검증</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>REQ-COM-011,REQ-COM-014; REQ-DIAG-005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="32" customHeight="1">
+        <x:v>REQ-COM-011, REQ-COM-014; REQ-DIAG-005; REQ-COMP-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="9" t="str">
         <x:v>FS-MODBUS-001</x:v>
       </x:c>
@@ -7175,10 +7178,10 @@
         <x:v>Slave Routing</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>REQ-FUNC-014; REQ-COM-010,REQ-COM-015; REQ-SEC-002</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="32" customHeight="1">
+        <x:v>REQ-COM-010, REQ-COM-015; REQ-REL-001; REQ-SEC-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="9" t="str">
         <x:v>FS-MODBUS-002</x:v>
       </x:c>
@@ -7186,10 +7189,10 @@
         <x:v>FC03 처리</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>REQ-COM-006~008,REQ-COM-011; REQ-DATA-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="32" customHeight="1">
+        <x:v>REQ-COM-006~008; REQ-DATA-001; REQ-PERF-001; REQ-COMP-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="9" t="str">
         <x:v>FS-MODBUS-003</x:v>
       </x:c>
@@ -7197,10 +7200,10 @@
         <x:v>FC04 처리</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>REQ-COM-006~008,REQ-COM-011; REQ-DATA-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="32" customHeight="1">
+        <x:v>REQ-COM-006~008; REQ-DATA-001; REQ-PERF-001; REQ-COMP-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="9" t="str">
         <x:v>FS-MODBUS-004</x:v>
       </x:c>
@@ -7208,10 +7211,10 @@
         <x:v>FC10 처리</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>REQ-COM-006~009; REQ-FUNC-018</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="32" customHeight="1">
+        <x:v>REQ-COM-006~009; REQ-DATA-001; REQ-PERF-001; REQ-COMP-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="9" t="str">
         <x:v>FS-MODBUS-005</x:v>
       </x:c>
@@ -7219,10 +7222,10 @@
         <x:v>무응답 및 Exception 처리</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>REQ-COM-006~010,REQ-COM-014; REQ-ERR-003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="32" customHeight="1">
+        <x:v>REQ-COM-006~007, REQ-COM-010, REQ-COM-014; REQ-ERR-003; REQ-COMP-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="9" t="str">
         <x:v>FS-DEV-001</x:v>
       </x:c>
@@ -7230,10 +7233,10 @@
         <x:v>Device Registry 구성</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>REQ-FUNC-014; REQ-DATA-006,REQ-DATA-012; REQ-RES-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-014; REQ-DATA-006; REQ-RES-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="9" t="str">
         <x:v>FS-REG-001</x:v>
       </x:c>
@@ -7241,10 +7244,10 @@
         <x:v>Register Read</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>REQ-FUNC-015~017; REQ-IF-006,REQ-IF-012</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-015~017; REQ-IF-004, REQ-IF-006, REQ-IF-012; REQ-ERR-002; REQ-REL-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="9" t="str">
         <x:v>FS-REG-002</x:v>
       </x:c>
@@ -7252,10 +7255,10 @@
         <x:v>Register Write Transaction</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>REQ-FUNC-016~018; REQ-IF-012; REQ-REL-002~003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-016~018; REQ-IF-004, REQ-IF-006, REQ-IF-012; REQ-ERR-002; REQ-REL-002~003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="9" t="str">
         <x:v>FS-REG-003</x:v>
       </x:c>
@@ -7263,10 +7266,10 @@
         <x:v>Device Reset</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>REQ-FUNC-019</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-019; REQ-IF-004; REQ-ERR-002; REQ-REL-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="9" t="str">
         <x:v>FS-SIG-001</x:v>
       </x:c>
@@ -7274,10 +7277,10 @@
         <x:v>Signal Map 구성</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>REQ-FUNC-020,REQ-FUNC-023~026; REQ-DATA-009~010</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-020, REQ-FUNC-023~026; REQ-DATA-009~010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="9" t="str">
         <x:v>FS-SIG-002</x:v>
       </x:c>
@@ -7285,10 +7288,10 @@
         <x:v>Signal 물리값 Read</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>REQ-FUNC-020~025,REQ-FUNC-028~029; REQ-IF-013</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-020~025, REQ-FUNC-028~029; REQ-IF-004, REQ-IF-006, REQ-IF-013; REQ-ERR-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="9" t="str">
         <x:v>FS-SIG-003</x:v>
       </x:c>
@@ -7296,10 +7299,10 @@
         <x:v>Signal 물리값 Write</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>REQ-FUNC-020~025,REQ-FUNC-028~029; REQ-IF-013</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-020~025, REQ-FUNC-028~029; REQ-IF-004, REQ-IF-013; REQ-ERR-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="9" t="str">
         <x:v>FS-SIG-004</x:v>
       </x:c>
@@ -7307,10 +7310,10 @@
         <x:v>Init Image 합성</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>REQ-FUNC-021~028; REQ-FUNC-012</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-021~025, REQ-FUNC-027~028; REQ-ERR-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="9" t="str">
         <x:v>FS-MON-001</x:v>
       </x:c>
@@ -7318,10 +7321,10 @@
         <x:v>Monitoring Start/Stop</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>REQ-FUNC-030,REQ-FUNC-032,REQ-FUNC-039</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-030, REQ-FUNC-032, REQ-FUNC-039; REQ-IF-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="9" t="str">
         <x:v>FS-MON-002</x:v>
       </x:c>
@@ -7329,10 +7332,10 @@
         <x:v>ReadOption Candidate 적용</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>REQ-FUNC-031,REQ-FUNC-038; REQ-PERF-004</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-031, REQ-FUNC-038; REQ-IF-004; REQ-PERF-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="9" t="str">
         <x:v>FS-MON-003</x:v>
       </x:c>
@@ -7340,10 +7343,10 @@
         <x:v>Periodic Snapshot 생성</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>REQ-FUNC-032~033; REQ-IF-007,REQ-IF-014</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-032~033; REQ-COM-021; REQ-IF-004, REQ-IF-006~007, REQ-IF-014; REQ-PERF-002~003; REQ-REL-005; REQ-RES-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A30" s="9" t="str">
         <x:v>FS-MON-004</x:v>
       </x:c>
@@ -7351,10 +7354,10 @@
         <x:v>Change Snapshot Queue</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v>REQ-FUNC-018,REQ-FUNC-034~035,REQ-FUNC-039; REQ-IF-014</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-018, REQ-FUNC-034~035, REQ-FUNC-039; REQ-COM-021; REQ-IF-004, REQ-IF-006~007, REQ-IF-014; REQ-PERF-002~003; REQ-REL-002, REQ-REL-004~006; REQ-RES-003~004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="9" t="str">
         <x:v>FS-MON-005</x:v>
       </x:c>
@@ -7365,7 +7368,7 @@
         <x:v>REQ-COM-016~021; REQ-IF-007</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="32" customHeight="1">
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="9" t="str">
         <x:v>FS-MON-006</x:v>
       </x:c>
@@ -7373,10 +7376,10 @@
         <x:v>10ms Output Pump</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>REQ-FUNC-036~038; REQ-PERF-002,REQ-PERF-004; REQ-DIAG-003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-033, REQ-FUNC-036~038; REQ-PERF-002, REQ-PERF-004; REQ-REL-006; REQ-DIAG-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="9" t="str">
         <x:v>FS-UI-001</x:v>
       </x:c>
@@ -7384,10 +7387,10 @@
         <x:v>Manual Read 및 Auto Read</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>REQ-FUNC-041,REQ-FUNC-043</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-040~041, REQ-FUNC-043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="9" t="str">
         <x:v>FS-UI-002</x:v>
       </x:c>
@@ -7395,10 +7398,10 @@
         <x:v>Manual Write</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>REQ-FUNC-042</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-040, REQ-FUNC-042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="9" t="str">
         <x:v>FS-UI-003</x:v>
       </x:c>
@@ -7406,10 +7409,10 @@
         <x:v>Signal Panel Control</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>REQ-FUNC-044</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-040, REQ-FUNC-044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="9" t="str">
         <x:v>FS-DIAG-001</x:v>
       </x:c>
@@ -7417,10 +7420,10 @@
         <x:v>동기 오류 조회</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>REQ-ERR-004~006; REQ-DIAG-001,REQ-DIAG-004; REQ-IF-009~010</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="32" customHeight="1">
+        <x:v>REQ-IF-004~005, REQ-IF-009~010; REQ-ERR-004~006; REQ-DIAG-001; REQ-COMP-006; REQ-SEC-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A37" s="9" t="str">
         <x:v>FS-DIAG-002</x:v>
       </x:c>
@@ -7428,10 +7431,10 @@
         <x:v>비동기 Error Event 및 Stats</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>REQ-ERR-006~008; REQ-DIAG-002~005; REQ-RES-003~004</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="32" customHeight="1">
+        <x:v>REQ-FUNC-035; REQ-IF-004, REQ-IF-009, REQ-IF-011; REQ-ERR-001, REQ-ERR-004~007; REQ-REL-002, REQ-REL-004; REQ-RES-003~004; REQ-DIAG-002~005; REQ-COMP-006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="9" t="str">
         <x:v>FS-SHUT-001</x:v>
       </x:c>
@@ -7439,13 +7442,13 @@
         <x:v>측정 종료 Finalize</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>REQ-FUNC-008; REQ-PERF-006; REQ-RES-002</x:v>
+        <x:v>REQ-FUNC-008; REQ-PERF-006; REQ-REL-003; REQ-RES-002</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbee46007bb24344"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd58cff352904931"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7454,12 +7457,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="88" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="62.130001068115234" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="21" t="str">
         <x:v>Design Component ID</x:v>
       </x:c>
@@ -7470,7 +7473,7 @@
         <x:v>Responsibility</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="32" customHeight="1">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
         <x:v>DC-01</x:v>
       </x:c>
@@ -7481,7 +7484,7 @@
         <x:v>CAPL_DLL_INFO4, __stdcall, Context Handle, Length/Capacity 검증, 21개 Export</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="32" customHeight="1">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="9" t="str">
         <x:v>DC-02</x:v>
       </x:c>
@@ -7492,7 +7495,7 @@
         <x:v>단일 활성 Context의 상태·Configuration·서비스·Queue 소유</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="32" customHeight="1">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="9" t="str">
         <x:v>DC-03</x:v>
       </x:c>
@@ -7503,7 +7506,7 @@
         <x:v>Refresh/Connect/Disconnect/Finalize, 상태·Generation, 자동 재연결</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="32" customHeight="1">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="9" t="str">
         <x:v>DC-04</x:v>
       </x:c>
@@ -7514,7 +7517,7 @@
         <x:v>UTF-8 CSV Parsing, 교차 검증, 임시 Configuration 및 원자 승격</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="32" customHeight="1">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>DC-05</x:v>
       </x:c>
@@ -7525,7 +7528,7 @@
         <x:v>Index/PortSlot/Slave_ID O(1) 조회와 Device Runtime 소유</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="32" customHeight="1">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="9" t="str">
         <x:v>DC-06</x:v>
       </x:c>
@@ -7536,7 +7539,7 @@
         <x:v>공유 Register, 권한 Bitmap, 원자 Read/Write/Reset</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="32" customHeight="1">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>DC-07</x:v>
       </x:c>
@@ -7547,7 +7550,7 @@
         <x:v>Frame/Bit/Endian/Type/Scale/Offset/Init 변환</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="32" customHeight="1">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="9" t="str">
         <x:v>DC-08</x:v>
       </x:c>
@@ -7558,7 +7561,7 @@
         <x:v>Frame 검증, CRC, FC03/04/10, Exception Response</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="32" customHeight="1">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>DC-09</x:v>
       </x:c>
@@ -7569,7 +7572,7 @@
         <x:v>Overlapped COM I/O, DCB, Cancel I/O, OS 오류 캡처</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="32" customHeight="1">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="9" t="str">
         <x:v>DC-10</x:v>
       </x:c>
@@ -7580,7 +7583,7 @@
         <x:v>Port 단독 소유, t1.5/t3.5 조립, 순차 요청 처리</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="32" customHeight="1">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="9" t="str">
         <x:v>DC-11</x:v>
       </x:c>
@@ -7591,7 +7594,7 @@
         <x:v>Periodic Snapshot, Port별 Change FIFO, Sequence/Stats</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="32" customHeight="1">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="9" t="str">
         <x:v>DC-12</x:v>
       </x:c>
@@ -7602,7 +7605,7 @@
         <x:v>LastSyncError, Error Event FIFO, Counter/Latch</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="32" customHeight="1">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="9" t="str">
         <x:v>DC-13</x:v>
       </x:c>
@@ -7613,7 +7616,7 @@
         <x:v>Context·경로·Buffer 은닉, Lifecycle Polling, 공통 오류 출력</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="32" customHeight="1">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="9" t="str">
         <x:v>DC-14</x:v>
       </x:c>
@@ -7624,7 +7627,7 @@
         <x:v>ReadOption, 1,000ms Cycle, 10ms Pump, CAN Frame 생성</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="32" customHeight="1">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="9" t="str">
         <x:v>DC-15</x:v>
       </x:c>
@@ -7635,7 +7638,7 @@
         <x:v>Connect/ReadSwitch, Manual Read/Write, Signal System Variable Adapter</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="32" customHeight="1">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="9" t="str">
         <x:v>DC-16</x:v>
       </x:c>
@@ -7644,12 +7647,23 @@
       </x:c>
       <x:c r="C17" s="9" t="str">
         <x:v>오류 코드·공개 상수의 C++/CAPL 단일 기준 생성 및 검증</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>DC-17</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Build &amp; Packaging</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="str">
+        <x:v>Win32/x86 빌드, Vector SDK 경로 주입, 배포 패키지 구조 및 후속 x64 경계 관리</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07fd9de29e91449d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84bc3bf431b74820"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7732,7 +7746,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdae6a788e5384210"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R599cce7077cf45ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R2b9ecc2e232c4856"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R2ce999600d0f4252"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R59c595e390414e66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R3415fec85e8f41ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Re2d75cebc01843d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="Rce6cbd40336845a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R0c861755561543e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rb1f59e8001fd474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="Radf4a759b93540cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R14fdc9525e104b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rb1202302cdb54ca8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="Ra3799b4c9b584386"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="Rb31731da52304c89"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -51,8 +52,32 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F4E78"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF375623"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF7F6000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -89,8 +114,23 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="4">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -106,11 +146,39 @@
         <x:color rgb="FFB7C9D6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -177,6 +245,46 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -818,11 +926,13 @@
         <x:v>DC-01 CAPL ABI Adapter; DC-02 EmulatorContext</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>CANalyzer 9.x x86 DLL 로딩 및 중복 Context 시험</x:v>
-      </x:c>
-      <x:c r="F2" s="23" t="str"/>
+        <x:v>Context 초기화·중복·잘못된 Handle·Finalize 후 호출·재초기화 자동 시험과 CANalyzer 9.x 실행</x:v>
+      </x:c>
+      <x:c r="F2" s="23" t="str">
+        <x:v>TC-P1-AUTO-002; TC-P1-ENV-001</x:v>
+      </x:c>
       <x:c r="G2" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
       </x:c>
       <x:c r="H2" s="9" t="str">
         <x:v>FR-LIFE-009,016; IF-CTX-001~003,007</x:v>
@@ -2714,11 +2824,13 @@
         <x:v>DC-01 CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="E81" s="9" t="str">
-        <x:v>Vector Sample 기반 x86 최소 ABI 시험</x:v>
-      </x:c>
-      <x:c r="F81" s="23" t="str"/>
+        <x:v>Win32/x86 DLL Load, caplDllTable4, __stdcall Export와 CAPL compile/runtime 시험</x:v>
+      </x:c>
+      <x:c r="F81" s="23" t="str">
+        <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001</x:v>
+      </x:c>
       <x:c r="G81" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
       </x:c>
       <x:c r="H81" s="9" t="str">
         <x:v>FACT-DLL-001~005; IF-ABI-009</x:v>
@@ -2740,9 +2852,11 @@
       <x:c r="E82" s="9" t="str">
         <x:v>Export Table 이름·Wrapper 호출 시험</x:v>
       </x:c>
-      <x:c r="F82" s="23" t="str"/>
+      <x:c r="F82" s="23" t="str">
+        <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001</x:v>
+      </x:c>
       <x:c r="G82" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
       </x:c>
       <x:c r="H82" s="9" t="str">
         <x:v>IF-NAME-001~003; IF-CTX-001~006</x:v>
@@ -2753,7 +2867,7 @@
         <x:v>REQ-IF-003</x:v>
       </x:c>
       <x:c r="B83" s="9" t="str">
-        <x:v>DLL 경계에는 32bit long 상태, Scalar, 숫자 Reference 및 1차원 char[]/word[]/long[]만 사용하고 사용자 struct와 C++ 객체를 노출하지 않아야 한다.</x:v>
+        <x:v>DLL 경계에는 32bit long 상태, Scalar 및 1차원 char[]/word[]/long[]만 사용하고 Signal 물리값 출력은 저수준 ABI에서 1요소 F[]로 전달해야 하며 사용자 struct와 C++ 객체를 노출하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C83" s="9" t="str">
         <x:v>FS-INIT-001</x:v>
@@ -2762,11 +2876,13 @@
         <x:v>DC-01 CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="E83" s="9" t="str">
-        <x:v>최소 ABI Probe 및 Buffer 불변 시험</x:v>
-      </x:c>
-      <x:c r="F83" s="23" t="str"/>
+        <x:v>생산 Table 메타데이터와 별도 ABI Fixture의 char[]/word[]/long[]/F[1] 성공 왕복 및 Buffer 불변 시험</x:v>
+      </x:c>
+      <x:c r="F83" s="23" t="str">
+        <x:v>TC-P1-AUTO-004; TC-P1-CAPL-001; TC-P1-ENV-001</x:v>
+      </x:c>
       <x:c r="G83" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
       </x:c>
       <x:c r="H83" s="9" t="str">
         <x:v>IF-ABI-001~011</x:v>
@@ -2788,9 +2904,11 @@
       <x:c r="E84" s="9" t="str">
         <x:v>21개 Export Table/Wrapper Contract 시험</x:v>
       </x:c>
-      <x:c r="F84" s="23" t="str"/>
+      <x:c r="F84" s="23" t="str">
+        <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001</x:v>
+      </x:c>
       <x:c r="G84" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
       </x:c>
       <x:c r="H84" s="9" t="str">
         <x:v>IF-API-001~021</x:v>
@@ -2812,9 +2930,11 @@
       <x:c r="E85" s="9" t="str">
         <x:v>동기/비동기/No Data 반환 시험</x:v>
       </x:c>
-      <x:c r="F85" s="23" t="str"/>
+      <x:c r="F85" s="23" t="str">
+        <x:v>TC-P1-AUTO-002; TC-P1-AUTO-003; TC-P1-ENV-001</x:v>
+      </x:c>
       <x:c r="G85" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
       </x:c>
       <x:c r="H85" s="9" t="str">
         <x:v>IF-RET-001~009; IF-CODE-001~004</x:v>
@@ -2836,9 +2956,11 @@
       <x:c r="E86" s="9" t="str">
         <x:v>Buffer 부족·Embedded NUL·실패 시 출력 유지 시험</x:v>
       </x:c>
-      <x:c r="F86" s="23" t="str"/>
+      <x:c r="F86" s="23" t="str">
+        <x:v>TC-P1-AUTO-003; TC-P1-CAPL-001; TC-P1-ENV-001</x:v>
+      </x:c>
       <x:c r="G86" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
       </x:c>
       <x:c r="H86" s="9" t="str">
         <x:v>IF-ABI-006~007,010~011; IF-RET-002~007</x:v>
@@ -2980,9 +3102,11 @@
       <x:c r="E92" s="9" t="str">
         <x:v>Quantity/Capacity 조합 및 실패 불변 시험</x:v>
       </x:c>
-      <x:c r="F92" s="23" t="str"/>
+      <x:c r="F92" s="23" t="str">
+        <x:v>TC-P1-AUTO-003; TC-P1-AUTO-004</x:v>
+      </x:c>
       <x:c r="G92" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS</x:v>
       </x:c>
       <x:c r="H92" s="9" t="str">
         <x:v>IF-REG-001~012</x:v>
@@ -2993,7 +3117,7 @@
         <x:v>REQ-IF-013</x:v>
       </x:c>
       <x:c r="B93" s="9" t="str">
-        <x:v>ReadSignal은 성공 시에만 OutPhysicalValue를 갱신하고 WriteSignal은 Index, SignalName, double 물리값을 사용해야 한다.</x:v>
+        <x:v>ReadSignal은 성공 시에만 저수준 OutPhysicalValue[0]을 갱신하고 CAPL Core는 이를 double&amp; 출력으로 감싸야 하며, WriteSignal은 Index, SignalName, double 물리값을 사용해야 한다.</x:v>
       </x:c>
       <x:c r="C93" s="9" t="str">
         <x:v>FS-SIG-002,FS-SIG-003</x:v>
@@ -3002,11 +3126,13 @@
         <x:v>DC-01 CAPL ABI Adapter; DC-07 SignalCodec</x:v>
       </x:c>
       <x:c r="E93" s="9" t="str">
-        <x:v>정상/오류 시 Reference copy-restore 시험</x:v>
-      </x:c>
-      <x:c r="F93" s="23" t="str"/>
+        <x:v>F[1] 출력 실패 불변성과 시험 Fixture 성공 왕복, CANalyzer x86 호출 시험</x:v>
+      </x:c>
+      <x:c r="F93" s="23" t="str">
+        <x:v>TC-P1-AUTO-003; TC-P1-AUTO-004; TC-P1-ENV-001</x:v>
+      </x:c>
       <x:c r="G93" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
       </x:c>
       <x:c r="H93" s="9" t="str">
         <x:v>IF-SIG-001~007</x:v>
@@ -3748,9 +3874,11 @@
       <x:c r="E124" s="9" t="str">
         <x:v>깨끗한 PC Win32 Build 및 CANalyzer 로딩 시험</x:v>
       </x:c>
-      <x:c r="F124" s="23" t="str"/>
+      <x:c r="F124" s="23" t="str">
+        <x:v>TC-P1-AUTO-001; TC-P1-ENV-001</x:v>
+      </x:c>
       <x:c r="G124" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
       </x:c>
       <x:c r="H124" s="9" t="str">
         <x:v>ENV-001~002,010~011; COMP-001~002,008</x:v>
@@ -3772,9 +3900,11 @@
       <x:c r="E125" s="9" t="str">
         <x:v>설치 경로 변경·Clean Build 시험</x:v>
       </x:c>
-      <x:c r="F125" s="23" t="str"/>
+      <x:c r="F125" s="23" t="str">
+        <x:v>TC-P1-AUTO-001</x:v>
+      </x:c>
       <x:c r="G125" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS</x:v>
       </x:c>
       <x:c r="H125" s="9" t="str">
         <x:v>DES-BUILD-001~005; TBD-059</x:v>
@@ -3796,9 +3926,11 @@
       <x:c r="E126" s="9" t="str">
         <x:v>공개 Export/문서에 Legacy 이름 부재 검토</x:v>
       </x:c>
-      <x:c r="F126" s="23" t="str"/>
+      <x:c r="F126" s="23" t="str">
+        <x:v>TC-P1-AUTO-001</x:v>
+      </x:c>
       <x:c r="G126" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS</x:v>
       </x:c>
       <x:c r="H126" s="9" t="str">
         <x:v>PRJ-005~006; COMP-009~010</x:v>
@@ -3820,9 +3952,11 @@
       <x:c r="E127" s="9" t="str">
         <x:v>Win32 타입 크기 검토; x64는 후속 체크리스트</x:v>
       </x:c>
-      <x:c r="F127" s="23" t="str"/>
+      <x:c r="F127" s="23" t="str">
+        <x:v>TC-P1-AUTO-001</x:v>
+      </x:c>
       <x:c r="G127" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 1 자동 검증 PASS</x:v>
       </x:c>
       <x:c r="H127" s="9" t="str">
         <x:v>ENV-011; FUT-001~005</x:v>
@@ -3956,7 +4090,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R225405ba02354d1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R514d4d82acc94649"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7013,7 +7147,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R100a34472a584bbc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaad5af6600346c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7448,7 +7582,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd58cff352904931"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4438aa5e2c6463b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7663,7 +7797,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84bc3bf431b74820"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e73861150a64c73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7693,10 +7827,10 @@
         <x:v>CANalyzer 9.x x86 ABI</x:v>
       </x:c>
       <x:c r="B2" s="25" t="str">
-        <x:v>검증 필요</x:v>
+        <x:v>자동 검증 PASS / CANalyzer 9.x 실환경 대기</x:v>
       </x:c>
       <x:c r="C2" s="25" t="str">
-        <x:v>Phase 1 minimum probe</x:v>
+        <x:v>생산 21 API + 시험 전용 ABI Fixture 자동 Probe 후 CANalyzer 9.x SP8 측정 실행</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
@@ -7746,7 +7880,164 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R599cce7077cf45ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5050e80d13e24eae"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="52" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="32" t="str">
+        <x:v>Test Case ID</x:v>
+      </x:c>
+      <x:c r="B1" s="32" t="str">
+        <x:v>검증 범위</x:v>
+      </x:c>
+      <x:c r="C1" s="32" t="str">
+        <x:v>실행 방법</x:v>
+      </x:c>
+      <x:c r="D1" s="32" t="str">
+        <x:v>환경</x:v>
+      </x:c>
+      <x:c r="E1" s="32" t="str">
+        <x:v>결과</x:v>
+      </x:c>
+      <x:c r="F1" s="32" t="str">
+        <x:v>비고</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A2" s="36" t="str">
+        <x:v>TC-P1-AUTO-001</x:v>
+      </x:c>
+      <x:c r="B2" s="35" t="str">
+        <x:v>Win32 빌드와 생산 CAPL Table 21 API</x:v>
+      </x:c>
+      <x:c r="C2" s="35" t="str">
+        <x:v>MSBuild Debug/Release, CMake Release, dumpbin 및 ABI 메타데이터 검사</x:v>
+      </x:c>
+      <x:c r="D2" s="35" t="str">
+        <x:v>Visual Studio 18 / Win32</x:v>
+      </x:c>
+      <x:c r="E2" s="39" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F2" s="35" t="str">
+        <x:v>x86(14C), 생산 API 정확히 21개, caplDllTable4 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="36" t="str">
+        <x:v>TC-P1-AUTO-002</x:v>
+      </x:c>
+      <x:c r="B3" s="35" t="str">
+        <x:v>Context 수명주기</x:v>
+      </x:c>
+      <x:c r="C3" s="35" t="str">
+        <x:v>네이티브 M485E.AbiProbe</x:v>
+      </x:c>
+      <x:c r="D3" s="35" t="str">
+        <x:v>Win32</x:v>
+      </x:c>
+      <x:c r="E3" s="39" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F3" s="35" t="str">
+        <x:v>0 Handle, 중복, 잘못된 Handle, Finalize 후 호출, 재초기화</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="36" t="str">
+        <x:v>TC-P1-AUTO-003</x:v>
+      </x:c>
+      <x:c r="B4" s="35" t="str">
+        <x:v>Capacity·문자열 검증·출력 불변성</x:v>
+      </x:c>
+      <x:c r="C4" s="35" t="str">
+        <x:v>네이티브 M485E.AbiProbe</x:v>
+      </x:c>
+      <x:c r="D4" s="35" t="str">
+        <x:v>Win32</x:v>
+      </x:c>
+      <x:c r="E4" s="39" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F4" s="35" t="str">
+        <x:v>작은 Capacity, Embedded NUL, 길이 불일치, 실패 시 caller-owned 출력 보존</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="36" t="str">
+        <x:v>TC-P1-AUTO-004</x:v>
+      </x:c>
+      <x:c r="B5" s="35" t="str">
+        <x:v>char[]/word[]/long[]/F[1] 성공 왕복</x:v>
+      </x:c>
+      <x:c r="C5" s="35" t="str">
+        <x:v>시험 전용 M485E.CaplAbiFixture + 네이티브/CAPL Probe</x:v>
+      </x:c>
+      <x:c r="D5" s="35" t="str">
+        <x:v>Win32</x:v>
+      </x:c>
+      <x:c r="E5" s="39" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F5" s="35" t="str">
+        <x:v>시험 Fixture는 생산 21 API와 분리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="36" t="str">
+        <x:v>TC-P1-CAPL-001</x:v>
+      </x:c>
+      <x:c r="B6" s="35" t="str">
+        <x:v>CAPL 소스 컴파일</x:v>
+      </x:c>
+      <x:c r="C6" s="35" t="str">
+        <x:v>CANalyzer 13 Exec32 caplcompexec</x:v>
+      </x:c>
+      <x:c r="D6" s="35" t="str">
+        <x:v>CANalyzer 13 x86 compiler</x:v>
+      </x:c>
+      <x:c r="E6" s="39" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F6" s="35" t="str">
+        <x:v>컴파일만 확인, Measurement 실행 아님</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="36" t="str">
+        <x:v>TC-P1-ENV-001</x:v>
+      </x:c>
+      <x:c r="B7" s="35" t="str">
+        <x:v>CANalyzer 9.x SP8 실제 로드·호출·측정</x:v>
+      </x:c>
+      <x:c r="C7" s="35" t="str">
+        <x:v>M485E_Phase1_AbiProbe.can Measurement 실행</x:v>
+      </x:c>
+      <x:c r="D7" s="35" t="str">
+        <x:v>회사 CANalyzer 9.x SP8 x86</x:v>
+      </x:c>
+      <x:c r="E7" s="42" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F7" s="35" t="str">
+        <x:v>실환경 결과를 임의로 PASS 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R0c861755561543e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rb1f59e8001fd474c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="Radf4a759b93540cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R14fdc9525e104b18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rb1202302cdb54ca8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="Ra3799b4c9b584386"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="Rb31731da52304c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Re899c4f230a04a7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rd260068490504f66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R6eb0dc4dff5941e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R064a3d9755ed456b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rc6309415d3894f1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R09d9acf916a34221"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R2493f50ff8154926"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4090,7 +4090,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R514d4d82acc94649"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re776782613fe4515"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7147,7 +7147,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaad5af6600346c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbf782bb967348ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7582,7 +7582,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4438aa5e2c6463b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd96c9efad414b7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7797,7 +7797,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e73861150a64c73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R270e4afe34244d10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7880,7 +7880,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5050e80d13e24eae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d209ff1ef644042"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7985,7 +7985,7 @@
         <x:v>char[]/word[]/long[]/F[1] 성공 왕복</x:v>
       </x:c>
       <x:c r="C5" s="35" t="str">
-        <x:v>시험 전용 M485E.CaplAbiFixture + 네이티브/CAPL Probe</x:v>
+        <x:v>시험 전용 M485E.CaplAbiFixture + 네이티브 ABI Probe</x:v>
       </x:c>
       <x:c r="D5" s="35" t="str">
         <x:v>Win32</x:v>

--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,13 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Re899c4f230a04a7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rd260068490504f66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R6eb0dc4dff5941e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R064a3d9755ed456b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rc6309415d3894f1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R09d9acf916a34221"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R2493f50ff8154926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R0121afb6d54c45c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R15996331584d415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R39b6aaa29a9d4005"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="Rc8b932bad8f64488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rad0c2b7f5425431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R44fd9fc79b264a70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R417753a131884d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R16ade59936224cb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R7c2b122e25184aaf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="10">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -76,8 +78,14 @@
       <x:color rgb="FF7F6000"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF006100"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="18">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -129,8 +137,43 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="6">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -174,11 +217,39 @@
         <x:color rgb="FFD9E2F3"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF9CA3AF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF9CA3AF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF9CA3AF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9CA3AF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -285,6 +356,73 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -702,7 +840,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>0.10</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Requirements with Design</x:v>
@@ -764,7 +902,7 @@
     <x:row r="13">
       <x:c r="A13" s="15" t="str">
         <x:v>사용 지침
-RTM 시트는 Requirement → Functional Specification → Design Component → Verification Method의 추적을 제공한다. Test Case ID는 테스트 명세 작성 전이므로 의도적으로 비워 두며, 요구사항을 삭제하거나 임의의 시험 ID를 만들지 않는다.</x:v>
+RTM 시트는 Requirement → Functional Specification → Design Component → Verification Method의 추적을 제공한다. 구현된 Phase는 Test Case ID와 Verification 시트에 연결하고, 미구현 Phase는 Test Case ID를 비워 둔다.</x:v>
       </x:c>
       <x:c r="B13" s="15" t="str">
         <x:v>사용 지침
@@ -929,10 +1067,10 @@
         <x:v>Context 초기화·중복·잘못된 Handle·Finalize 후 호출·재초기화 자동 시험과 CANalyzer 9.x 실행</x:v>
       </x:c>
       <x:c r="F2" s="23" t="str">
-        <x:v>TC-P1-AUTO-002; TC-P1-ENV-001</x:v>
+        <x:v>TC-P1-AUTO-002; TC-P1-ENV-001; TC-P8-AUTO-001</x:v>
       </x:c>
       <x:c r="G2" s="24" t="str">
-        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H2" s="9" t="str">
         <x:v>FR-LIFE-009,016; IF-CTX-001~003,007</x:v>
@@ -954,9 +1092,11 @@
       <x:c r="E3" s="9" t="str">
         <x:v>Lifecycle 상태·Generation·Busy 처리 통합 시험</x:v>
       </x:c>
-      <x:c r="F3" s="23" t="str"/>
+      <x:c r="F3" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G3" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H3" s="9" t="str">
         <x:v>FR-LIFE-010~015</x:v>
@@ -978,9 +1118,11 @@
       <x:c r="E4" s="9" t="str">
         <x:v>상태 전이 및 완료 결과 손실 방지 시험</x:v>
       </x:c>
-      <x:c r="F4" s="23" t="str"/>
+      <x:c r="F4" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G4" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H4" s="9" t="str">
         <x:v>FR-LIFE-013~015; IF-CONST-003; IF-LSTAT-001~014</x:v>
@@ -1002,9 +1144,11 @@
       <x:c r="E5" s="9" t="str">
         <x:v>두 번째 Port 실패 강제 및 전체 Rollback 시험</x:v>
       </x:c>
-      <x:c r="F5" s="23" t="str"/>
+      <x:c r="F5" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G5" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H5" s="9" t="str">
         <x:v>FR-PORT-007~017</x:v>
@@ -1026,9 +1170,11 @@
       <x:c r="E6" s="9" t="str">
         <x:v>Disconnect/재Connect 데이터 보존 시험</x:v>
       </x:c>
-      <x:c r="F6" s="23" t="str"/>
+      <x:c r="F6" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G6" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
         <x:v>FR-LIFE-020,025,033</x:v>
@@ -1050,9 +1196,11 @@
       <x:c r="E7" s="9" t="str">
         <x:v>USB 제거·복귀, 10회 실패 및 수동 복구 시험</x:v>
       </x:c>
-      <x:c r="F7" s="23" t="str"/>
+      <x:c r="F7" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G7" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H7" s="9" t="str">
         <x:v>FR-LIFE-023~032</x:v>
@@ -1074,9 +1222,11 @@
       <x:c r="E8" s="9" t="str">
         <x:v>부분 Open Rollback과 데이터 보존 시험</x:v>
       </x:c>
-      <x:c r="F8" s="23" t="str"/>
+      <x:c r="F8" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G8" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H8" s="9" t="str">
         <x:v>FR-LIFE-025~032; ERR-037~038</x:v>
@@ -1098,9 +1248,11 @@
       <x:c r="E9" s="9" t="str">
         <x:v>각 상태 Finalize, Cancel I/O, 재초기화 시험</x:v>
       </x:c>
-      <x:c r="F9" s="23" t="str"/>
+      <x:c r="F9" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G9" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H9" s="9" t="str">
         <x:v>FR-LIFE-017~022</x:v>
@@ -1122,9 +1274,11 @@
       <x:c r="E10" s="9" t="str">
         <x:v>프로젝트 이동·파일명 변경·경로 변환 실패 시험</x:v>
       </x:c>
-      <x:c r="F10" s="23" t="str"/>
+      <x:c r="F10" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G10" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H10" s="9" t="str">
         <x:v>FR-CSV-001~003; DATA-001~002</x:v>
@@ -1146,9 +1300,11 @@
       <x:c r="E11" s="9" t="str">
         <x:v>다수 CSV 혼재 환경의 정확한 파일 선택 시험</x:v>
       </x:c>
-      <x:c r="F11" s="23" t="str"/>
+      <x:c r="F11" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G11" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H11" s="9" t="str">
         <x:v>FR-CSV-001~003; IF-CORE-009</x:v>
@@ -1170,9 +1326,11 @@
       <x:c r="E12" s="9" t="str">
         <x:v>성공/실패 원자성 및 Connected 거부 시험</x:v>
       </x:c>
-      <x:c r="F12" s="23" t="str"/>
+      <x:c r="F12" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G12" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H12" s="9" t="str">
         <x:v>FR-CSV-004~010,014~019</x:v>
@@ -1194,9 +1352,11 @@
       <x:c r="E13" s="9" t="str">
         <x:v>Refresh 전후 값과 런타임 상태 초기화 시험</x:v>
       </x:c>
-      <x:c r="F13" s="23" t="str"/>
+      <x:c r="F13" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G13" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H13" s="9" t="str">
         <x:v>FR-CSV-005,012,017~019</x:v>
@@ -1218,9 +1378,11 @@
       <x:c r="E14" s="9" t="str">
         <x:v>Stale Configuration 차단 및 재시도 시험</x:v>
       </x:c>
-      <x:c r="F14" s="23" t="str"/>
+      <x:c r="F14" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G14" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H14" s="9" t="str">
         <x:v>FR-CSV-006~008,015~016; ERR-035~036</x:v>
@@ -1242,9 +1404,11 @@
       <x:c r="E15" s="9" t="str">
         <x:v>동일 Port 다중 Slave와 다른 Port 동일 Slave ID 시험</x:v>
       </x:c>
-      <x:c r="F15" s="23" t="str"/>
+      <x:c r="F15" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G15" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H15" s="9" t="str">
         <x:v>FR-RTU-007; DATA-DEV-001~006</x:v>
@@ -1266,9 +1430,11 @@
       <x:c r="E16" s="9" t="str">
         <x:v>동일 Address의 FC03/FC04 동일값 시험</x:v>
       </x:c>
-      <x:c r="F16" s="23" t="str"/>
+      <x:c r="F16" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G16" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H16" s="9" t="str">
         <x:v>FR-REG-001~009</x:v>
@@ -1290,9 +1456,11 @@
       <x:c r="E17" s="9" t="str">
         <x:v>Rule-only, Map-only, 공백 범위 접근 시험</x:v>
       </x:c>
-      <x:c r="F17" s="23" t="str"/>
+      <x:c r="F17" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G17" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H17" s="9" t="str">
         <x:v>FR-REG-013~017; DATA-020,024</x:v>
@@ -1314,9 +1482,11 @@
       <x:c r="E18" s="9" t="str">
         <x:v>경계·Buffer 부족·동시 접근 원자성 시험</x:v>
       </x:c>
-      <x:c r="F18" s="23" t="str"/>
+      <x:c r="F18" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G18" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H18" s="9" t="str">
         <x:v>FR-REG-015~018; IF-REG-001~012</x:v>
@@ -1338,9 +1508,11 @@
       <x:c r="E19" s="9" t="str">
         <x:v>중첩 Rule, 동일값 Write 및 중복 제거 시험</x:v>
       </x:c>
-      <x:c r="F19" s="23" t="str"/>
+      <x:c r="F19" s="23" t="str">
+        <x:v>TC-P4-AUTO-001; TC-P6-AUTO-001</x:v>
+      </x:c>
       <x:c r="G19" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H19" s="9" t="str">
         <x:v>FR-REG-010~012,018</x:v>
@@ -1362,9 +1534,11 @@
       <x:c r="E20" s="9" t="str">
         <x:v>Connected/Disconnected Reset과 실패 Rollback 시험</x:v>
       </x:c>
-      <x:c r="F20" s="23" t="str"/>
+      <x:c r="F20" s="23" t="str">
+        <x:v>TC-P4-AUTO-001; TC-P6-AUTO-001</x:v>
+      </x:c>
       <x:c r="G20" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H20" s="9" t="str">
         <x:v>FR-RESET-001~007</x:v>
@@ -1386,9 +1560,11 @@
       <x:c r="E21" s="9" t="str">
         <x:v>SignalName 대소문자·중복·미존재 시험</x:v>
       </x:c>
-      <x:c r="F21" s="23" t="str"/>
+      <x:c r="F21" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G21" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H21" s="9" t="str">
         <x:v>FR-SIG-001~006; DATA-MAP-023</x:v>
@@ -1410,9 +1586,11 @@
       <x:c r="E22" s="9" t="str">
         <x:v>양·음수 Scale/Offset 및 ±0.5 반올림 시험</x:v>
       </x:c>
-      <x:c r="F22" s="23" t="str"/>
+      <x:c r="F22" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G22" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H22" s="9" t="str">
         <x:v>FR-SIG-025~030</x:v>
@@ -1434,9 +1612,11 @@
       <x:c r="E23" s="9" t="str">
         <x:v>Float/Double Raw round-trip 및 비유한 값 시험</x:v>
       </x:c>
-      <x:c r="F23" s="23" t="str"/>
+      <x:c r="F23" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G23" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H23" s="9" t="str">
         <x:v>FR-SIG-007~008; DATA-MAP-008~009</x:v>
@@ -1458,9 +1638,11 @@
       <x:c r="E24" s="9" t="str">
         <x:v>2/4 Word Address별 Raw 배치 시험</x:v>
       </x:c>
-      <x:c r="F24" s="23" t="str"/>
+      <x:c r="F24" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G24" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H24" s="9" t="str">
         <x:v>FR-SIG-009~010; DATA-MAP-010</x:v>
@@ -1482,9 +1664,11 @@
       <x:c r="E25" s="9" t="str">
         <x:v>Length 2/4/6/8의 Bit 경계·비정렬 Signal 시험</x:v>
       </x:c>
-      <x:c r="F25" s="23" t="str"/>
+      <x:c r="F25" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G25" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H25" s="9" t="str">
         <x:v>FR-SIG-011~014</x:v>
@@ -1506,9 +1690,11 @@
       <x:c r="E26" s="9" t="str">
         <x:v>Big/Little Endian Read/Write 역변환 시험</x:v>
       </x:c>
-      <x:c r="F26" s="23" t="str"/>
+      <x:c r="F26" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G26" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H26" s="9" t="str">
         <x:v>FR-SIG-020~024</x:v>
@@ -1530,9 +1716,11 @@
       <x:c r="E27" s="9" t="str">
         <x:v>Frame 공유·중복·경계 검증 시험</x:v>
       </x:c>
-      <x:c r="F27" s="23" t="str"/>
+      <x:c r="F27" s="23" t="str">
+        <x:v>TC-P3-AUTO-001; TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G27" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H27" s="9" t="str">
         <x:v>FR-SIG-012,015~019; DATA-MAP-011~014</x:v>
@@ -1554,9 +1742,11 @@
       <x:c r="E28" s="9" t="str">
         <x:v>행 순서 변경·부분 실패 Rollback 시험</x:v>
       </x:c>
-      <x:c r="F28" s="23" t="str"/>
+      <x:c r="F28" s="23" t="str">
+        <x:v>TC-P3-AUTO-001; TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G28" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H28" s="9" t="str">
         <x:v>FR-SIG-025~027; DATA-MAP-004</x:v>
@@ -1578,9 +1768,11 @@
       <x:c r="E29" s="9" t="str">
         <x:v>Min/Max 경계, Raw 우회 및 NaN/Infinity 시험</x:v>
       </x:c>
-      <x:c r="F29" s="23" t="str"/>
+      <x:c r="F29" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G29" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H29" s="9" t="str">
         <x:v>FR-SIG-031~037</x:v>
@@ -1602,9 +1794,11 @@
       <x:c r="E30" s="9" t="str">
         <x:v>±2^53 경계 및 word[4] Raw 우회 시험</x:v>
       </x:c>
-      <x:c r="F30" s="23" t="str"/>
+      <x:c r="F30" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G30" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H30" s="9" t="str">
         <x:v>FR-SIG-038~041; IF-SIG-006~007</x:v>
@@ -1626,9 +1820,11 @@
       <x:c r="E31" s="9" t="str">
         <x:v>ON/OFF 중 RTU 유지와 Queue 정책 시험</x:v>
       </x:c>
-      <x:c r="F31" s="23" t="str"/>
+      <x:c r="F31" s="23" t="str">
+        <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G31" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H31" s="9" t="str">
         <x:v>FR-LIFE-004~006; FR-CAN-049~056</x:v>
@@ -1650,9 +1846,11 @@
       <x:c r="E32" s="9" t="str">
         <x:v>다중 Checkbox 원자 적용·복원 시험</x:v>
       </x:c>
-      <x:c r="F32" s="23" t="str"/>
+      <x:c r="F32" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G32" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H32" s="9" t="str">
         <x:v>FR-CAN-020~027,047,057</x:v>
@@ -1674,9 +1872,11 @@
       <x:c r="E33" s="9" t="str">
         <x:v>Connect/ReadSwitch 순서 및 최초 출력 시험</x:v>
       </x:c>
-      <x:c r="F33" s="23" t="str"/>
+      <x:c r="F33" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G33" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H33" s="9" t="str">
         <x:v>FR-LIFE-007~008; FR-CAN-055</x:v>
@@ -1698,9 +1898,11 @@
       <x:c r="E34" s="9" t="str">
         <x:v>Deadline Miss·Latest-wins·공정성 시험</x:v>
       </x:c>
-      <x:c r="F34" s="23" t="str"/>
+      <x:c r="F34" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G34" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H34" s="9" t="str">
         <x:v>FR-CAN-022,042~048; FR-LOAD-007</x:v>
@@ -1722,9 +1924,11 @@
       <x:c r="E35" s="9" t="str">
         <x:v>동시 Write·불변 Snapshot·Buffer 부족 시험</x:v>
       </x:c>
-      <x:c r="F35" s="23" t="str"/>
+      <x:c r="F35" s="23" t="str">
+        <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G35" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H35" s="9" t="str">
         <x:v>FR-CAN-029~037; IF-MON-006~010</x:v>
@@ -1746,9 +1950,11 @@
       <x:c r="E36" s="9" t="str">
         <x:v>Queue 257건 입력 및 oldest-drop 시험</x:v>
       </x:c>
-      <x:c r="F36" s="23" t="str"/>
+      <x:c r="F36" s="23" t="str">
+        <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G36" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H36" s="9" t="str">
         <x:v>FR-CAN-038~039; ERR-008; FR-LOAD-008</x:v>
@@ -1770,9 +1976,11 @@
       <x:c r="E37" s="9" t="str">
         <x:v>두 Port Burst·Rule Cursor·묶음 원자 출력 시험</x:v>
       </x:c>
-      <x:c r="F37" s="23" t="str"/>
+      <x:c r="F37" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G37" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H37" s="9" t="str">
         <x:v>FR-CAN-040~046; DES-CAN-014~017</x:v>
@@ -1794,9 +2002,11 @@
       <x:c r="E38" s="9" t="str">
         <x:v>Quantity 125 Snapshot과 Tick 시간 실측</x:v>
       </x:c>
-      <x:c r="F38" s="23" t="str"/>
+      <x:c r="F38" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G38" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H38" s="9" t="str">
         <x:v>FR-LOAD-006,019</x:v>
@@ -1818,9 +2028,11 @@
       <x:c r="E39" s="9" t="str">
         <x:v>Performance Monitor 유무·임의값 불변 동작 시험</x:v>
       </x:c>
-      <x:c r="F39" s="23" t="str"/>
+      <x:c r="F39" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G39" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H39" s="9" t="str">
         <x:v>FR-LOAD-001~005,010,018</x:v>
@@ -1842,9 +2054,11 @@
       <x:c r="E40" s="9" t="str">
         <x:v>OFF 전후 Queue·Counter·재시작 Burst 시험</x:v>
       </x:c>
-      <x:c r="F40" s="23" t="str"/>
+      <x:c r="F40" s="23" t="str">
+        <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G40" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H40" s="9" t="str">
         <x:v>FR-CAN-051~056; FR-LOAD-015~018</x:v>
@@ -1866,9 +2080,11 @@
       <x:c r="E41" s="9" t="str">
         <x:v>CAPL 정적 분석 및 컴파일 시험</x:v>
       </x:c>
-      <x:c r="F41" s="23" t="str"/>
+      <x:c r="F41" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; TC-P10-STATIC-001; EV-008; EV-009; EV-010; EV-011; EV-012; EV-013; EV-016</x:v>
+      </x:c>
       <x:c r="G41" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H41" s="9" t="str">
         <x:v>FR-CAPL-001~006; IF-CTX-006</x:v>
@@ -1890,9 +2106,11 @@
       <x:c r="E42" s="9" t="str">
         <x:v>Panel 수동 Read 및 실패 시 결과 유지 시험</x:v>
       </x:c>
-      <x:c r="F42" s="23" t="str"/>
+      <x:c r="F42" s="23" t="str">
+        <x:v>TC-P10-STATIC-001; EV-012; EV-013; EV-016</x:v>
+      </x:c>
       <x:c r="G42" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H42" s="9" t="str">
         <x:v>FR-UI-001~006; IF-REG-001,004</x:v>
@@ -1914,9 +2132,11 @@
       <x:c r="E43" s="9" t="str">
         <x:v>Panel 편집 중간 상태와 실행 Snapshot 분리 시험</x:v>
       </x:c>
-      <x:c r="F43" s="23" t="str"/>
+      <x:c r="F43" s="23" t="str">
+        <x:v>TC-P10-STATIC-001; EV-012; EV-013; EV-016</x:v>
+      </x:c>
       <x:c r="G43" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H43" s="9" t="str">
         <x:v>FR-UI-007~011; IF-REG-002~016</x:v>
@@ -1938,9 +2158,11 @@
       <x:c r="E44" s="9" t="str">
         <x:v>Auto Read, Send momentary 및 invalid edit 시험</x:v>
       </x:c>
-      <x:c r="F44" s="23" t="str"/>
+      <x:c r="F44" s="23" t="str">
+        <x:v>TC-P10-STATIC-001; EV-012; EV-013; EV-016</x:v>
+      </x:c>
       <x:c r="G44" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H44" s="9" t="str">
         <x:v>FR-UI-012~016</x:v>
@@ -1962,9 +2184,11 @@
       <x:c r="E45" s="9" t="str">
         <x:v>양수·음수·소수 Panel round-trip 시험</x:v>
       </x:c>
-      <x:c r="F45" s="23" t="str"/>
+      <x:c r="F45" s="23" t="str">
+        <x:v>TC-P10-STATIC-001; EV-012; EV-013; EV-016</x:v>
+      </x:c>
       <x:c r="G45" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H45" s="9" t="str">
         <x:v>FR-SIG-003; IF-SIG-001~007</x:v>
@@ -1986,9 +2210,11 @@
       <x:c r="E46" s="9" t="str">
         <x:v>회사 환경 SystemBase Multi USB-485 통합 시험</x:v>
       </x:c>
-      <x:c r="F46" s="23" t="str"/>
+      <x:c r="F46" s="23" t="str">
+        <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G46" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H46" s="9" t="str">
         <x:v>ENV-003,014~015; CON-017</x:v>
@@ -2010,9 +2236,11 @@
       <x:c r="E47" s="9" t="str">
         <x:v>Port 등록 순서·중복·누락·Routing 시험</x:v>
       </x:c>
-      <x:c r="F47" s="23" t="str"/>
+      <x:c r="F47" s="23" t="str">
+        <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G47" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H47" s="9" t="str">
         <x:v>ENV-003~005; FR-PORT-018~020</x:v>
@@ -2034,9 +2262,11 @@
       <x:c r="E48" s="9" t="str">
         <x:v>지원/비지원 설정 및 상태 제한 시험</x:v>
       </x:c>
-      <x:c r="F48" s="23" t="str"/>
+      <x:c r="F48" s="23" t="str">
+        <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G48" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H48" s="9" t="str">
         <x:v>FR-PORT-001~006</x:v>
@@ -2058,9 +2288,11 @@
       <x:c r="E49" s="9" t="str">
         <x:v>BaudRate·Parity·StopBits 조합과 OS 오류 Context 시험</x:v>
       </x:c>
-      <x:c r="F49" s="23" t="str"/>
+      <x:c r="F49" s="23" t="str">
+        <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G49" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H49" s="9" t="str">
         <x:v>FR-PORT-002,010~012</x:v>
@@ -2082,9 +2314,11 @@
       <x:c r="E50" s="9" t="str">
         <x:v>RTS 미조작 및 Echo 없는 Adapter 확인</x:v>
       </x:c>
-      <x:c r="F50" s="23" t="str"/>
+      <x:c r="F50" s="23" t="str">
+        <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G50" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H50" s="9" t="str">
         <x:v>FR-PORT-022~023</x:v>
@@ -2106,9 +2340,11 @@
       <x:c r="E51" s="9" t="str">
         <x:v>Function별 정상·미지원 요청 시험</x:v>
       </x:c>
-      <x:c r="F51" s="23" t="str"/>
+      <x:c r="F51" s="23" t="str">
+        <x:v>TC-P5-AUTO-001</x:v>
+      </x:c>
       <x:c r="G51" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H51" s="9" t="str">
         <x:v>FR-RTU-001~006,015~016</x:v>
@@ -2130,9 +2366,11 @@
       <x:c r="E52" s="9" t="str">
         <x:v>최소·최대·초과 및 ByteCount 오류 시험</x:v>
       </x:c>
-      <x:c r="F52" s="23" t="str"/>
+      <x:c r="F52" s="23" t="str">
+        <x:v>TC-P5-AUTO-001</x:v>
+      </x:c>
       <x:c r="G52" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H52" s="9" t="str">
         <x:v>FR-RTU-017~020,028~031</x:v>
@@ -2154,9 +2392,11 @@
       <x:c r="E53" s="9" t="str">
         <x:v>인접·중첩 Rule 횡단과 공백 거부 시험</x:v>
       </x:c>
-      <x:c r="F53" s="23" t="str"/>
+      <x:c r="F53" s="23" t="str">
+        <x:v>TC-P5-AUTO-001</x:v>
+      </x:c>
       <x:c r="G53" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H53" s="9" t="str">
         <x:v>FR-RTU-010~014; DATA-RULE-012</x:v>
@@ -2178,9 +2418,11 @@
       <x:c r="E54" s="9" t="str">
         <x:v>적용 전/후 송신 실패 Stage 시험</x:v>
       </x:c>
-      <x:c r="F54" s="23" t="str"/>
+      <x:c r="F54" s="23" t="str">
+        <x:v>TC-P5-AUTO-001</x:v>
+      </x:c>
       <x:c r="G54" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H54" s="9" t="str">
         <x:v>FR-RTU-031~032; ERR-043</x:v>
@@ -2202,9 +2444,11 @@
       <x:c r="E55" s="9" t="str">
         <x:v>Broadcast·예약·미등록 주소 시험</x:v>
       </x:c>
-      <x:c r="F55" s="23" t="str"/>
+      <x:c r="F55" s="23" t="str">
+        <x:v>TC-P5-AUTO-001</x:v>
+      </x:c>
       <x:c r="G55" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H55" s="9" t="str">
         <x:v>FR-RTU-021~022</x:v>
@@ -2226,9 +2470,11 @@
       <x:c r="E56" s="9" t="str">
         <x:v>공식 CRC Vector·최대 ADU 시험</x:v>
       </x:c>
-      <x:c r="F56" s="23" t="str"/>
+      <x:c r="F56" s="23" t="str">
+        <x:v>TC-P5-AUTO-001</x:v>
+      </x:c>
       <x:c r="G56" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H56" s="9" t="str">
         <x:v>FR-RTU-023,026~030</x:v>
@@ -2250,9 +2496,11 @@
       <x:c r="E57" s="9" t="str">
         <x:v>Partial Read, Noise, t1.5/t3.5 경계 시험</x:v>
       </x:c>
-      <x:c r="F57" s="23" t="str"/>
+      <x:c r="F57" s="23" t="str">
+        <x:v>TC-P5-AUTO-001; TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G57" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H57" s="9" t="str">
         <x:v>FR-RTU-024~025,035; FR-PORT-021</x:v>
@@ -2274,9 +2522,11 @@
       <x:c r="E58" s="9" t="str">
         <x:v>다양한 BaudRate/Parity/StopBits Timing 시험</x:v>
       </x:c>
-      <x:c r="F58" s="23" t="str"/>
+      <x:c r="F58" s="23" t="str">
+        <x:v>TC-P5-AUTO-001; TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G58" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H58" s="9" t="str">
         <x:v>FR-RTU-025; FR-PORT-021</x:v>
@@ -2298,9 +2548,11 @@
       <x:c r="E59" s="9" t="str">
         <x:v>Noise 반복 시 FIFO 고갈 방지 시험</x:v>
       </x:c>
-      <x:c r="F59" s="23" t="str"/>
+      <x:c r="F59" s="23" t="str">
+        <x:v>TC-P5-AUTO-001</x:v>
+      </x:c>
       <x:c r="G59" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H59" s="9" t="str">
         <x:v>FR-RTU-027; ERR-040</x:v>
@@ -2322,9 +2574,11 @@
       <x:c r="E60" s="9" t="str">
         <x:v>두 Port 동시 요청·순서·격리 시험</x:v>
       </x:c>
-      <x:c r="F60" s="23" t="str"/>
+      <x:c r="F60" s="23" t="str">
+        <x:v>TC-P5-AUTO-001; TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G60" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H60" s="9" t="str">
         <x:v>FR-RTU-034</x:v>
@@ -2346,9 +2600,11 @@
       <x:c r="E61" s="9" t="str">
         <x:v>두 가상 채널 Extended CAN 출력 시험</x:v>
       </x:c>
-      <x:c r="F61" s="23" t="str"/>
+      <x:c r="F61" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G61" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H61" s="9" t="str">
         <x:v>ENV-007,012</x:v>
@@ -2370,9 +2626,11 @@
       <x:c r="E62" s="9" t="str">
         <x:v>실제 ID/Vector 표현 Mask 시험</x:v>
       </x:c>
-      <x:c r="F62" s="23" t="str"/>
+      <x:c r="F62" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G62" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H62" s="9" t="str">
         <x:v>FR-CAN-001~002,021; CON-001</x:v>
@@ -2394,9 +2652,11 @@
       <x:c r="E63" s="9" t="str">
         <x:v>Quantity 1,4,5,125 Frame 수·mm 시험</x:v>
       </x:c>
-      <x:c r="F63" s="23" t="str"/>
+      <x:c r="F63" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G63" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H63" s="9" t="str">
         <x:v>FR-CAN-003~019,028</x:v>
@@ -2418,9 +2678,11 @@
       <x:c r="E64" s="9" t="str">
         <x:v>Header Byte 단위 Golden Vector 시험</x:v>
       </x:c>
-      <x:c r="F64" s="23" t="str"/>
+      <x:c r="F64" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G64" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H64" s="9" t="str">
         <x:v>FR-CAN-003~012</x:v>
@@ -2442,9 +2704,11 @@
       <x:c r="E65" s="9" t="str">
         <x:v>마지막 가변 DLC 및 무패딩 시험</x:v>
       </x:c>
-      <x:c r="F65" s="23" t="str"/>
+      <x:c r="F65" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G65" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H65" s="9" t="str">
         <x:v>FR-CAN-013~019</x:v>
@@ -2466,9 +2730,11 @@
       <x:c r="E66" s="9" t="str">
         <x:v>원인별 Header 및 0x04 미송출 시험</x:v>
       </x:c>
-      <x:c r="F66" s="23" t="str"/>
+      <x:c r="F66" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G66" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H66" s="9" t="str">
         <x:v>FR-SRC-001~005; FR-LIFE-008</x:v>
@@ -2490,7 +2756,7 @@
       <x:c r="E67" s="9" t="str">
         <x:v>Address 0,40000,65535 경계 시험</x:v>
       </x:c>
-      <x:c r="F67" s="23" t="str"/>
+      <x:c r="F67" s="23"/>
       <x:c r="G67" s="24" t="str">
         <x:v>Defined</x:v>
       </x:c>
@@ -2514,9 +2780,11 @@
       <x:c r="E68" s="9" t="str">
         <x:v>인코딩·Quote·개행 오류 시험</x:v>
       </x:c>
-      <x:c r="F68" s="23" t="str"/>
+      <x:c r="F68" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G68" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H68" s="9" t="str">
         <x:v>DATA-003,015~019</x:v>
@@ -2538,9 +2806,11 @@
       <x:c r="E69" s="9" t="str">
         <x:v>Header 별칭·순서·칼럼 수 오류 시험</x:v>
       </x:c>
-      <x:c r="F69" s="23" t="str"/>
+      <x:c r="F69" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G69" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H69" s="9" t="str">
         <x:v>DATA-006,011; ERR-020,022</x:v>
@@ -2562,9 +2832,11 @@
       <x:c r="E70" s="9" t="str">
         <x:v>숫자 문법·범위·NaN/Infinity 시험</x:v>
       </x:c>
-      <x:c r="F70" s="23" t="str"/>
+      <x:c r="F70" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G70" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H70" s="9" t="str">
         <x:v>DATA-007~009; ERR-018,021</x:v>
@@ -2586,9 +2858,11 @@
       <x:c r="E71" s="9" t="str">
         <x:v>빈 Cell·공백·필수값 시험</x:v>
       </x:c>
-      <x:c r="F71" s="23" t="str"/>
+      <x:c r="F71" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G71" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H71" s="9" t="str">
         <x:v>DATA-010~014</x:v>
@@ -2610,9 +2884,11 @@
       <x:c r="E72" s="9" t="str">
         <x:v>Schema와 Index/Port/Slave 유일성 시험</x:v>
       </x:c>
-      <x:c r="F72" s="23" t="str"/>
+      <x:c r="F72" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G72" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H72" s="9" t="str">
         <x:v>DATA-DEV-001~006</x:v>
@@ -2634,9 +2910,11 @@
       <x:c r="E73" s="9" t="str">
         <x:v>Schema, Rule_ID, Quantity, 완전 중복 시험</x:v>
       </x:c>
-      <x:c r="F73" s="23" t="str"/>
+      <x:c r="F73" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G73" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H73" s="9" t="str">
         <x:v>DATA-RULE-001~012</x:v>
@@ -2658,9 +2936,11 @@
       <x:c r="E74" s="9" t="str">
         <x:v>Rule 충돌 조합 시험</x:v>
       </x:c>
-      <x:c r="F74" s="23" t="str"/>
+      <x:c r="F74" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G74" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H74" s="9" t="str">
         <x:v>DATA-RULE-007~010</x:v>
@@ -2682,9 +2962,11 @@
       <x:c r="E75" s="9" t="str">
         <x:v>Schema와 행 단위 검증 시험</x:v>
       </x:c>
-      <x:c r="F75" s="23" t="str"/>
+      <x:c r="F75" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G75" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H75" s="9" t="str">
         <x:v>DATA-MAP-001~023</x:v>
@@ -2706,9 +2988,11 @@
       <x:c r="E76" s="9" t="str">
         <x:v>Enum 별칭·오타 거부 시험</x:v>
       </x:c>
-      <x:c r="F76" s="23" t="str"/>
+      <x:c r="F76" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G76" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H76" s="9" t="str">
         <x:v>DATA-MAP-001~003</x:v>
@@ -2730,9 +3014,11 @@
       <x:c r="E77" s="9" t="str">
         <x:v>Value_Table 유무/내용 변경의 Runtime 불변 시험</x:v>
       </x:c>
-      <x:c r="F77" s="23" t="str"/>
+      <x:c r="F77" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G77" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H77" s="9" t="str">
         <x:v>DATA-MAP-005,017~021</x:v>
@@ -2754,9 +3040,11 @@
       <x:c r="E78" s="9" t="str">
         <x:v>한도/초과 및 x86 Peak 메모리 시험</x:v>
       </x:c>
-      <x:c r="F78" s="23" t="str"/>
+      <x:c r="F78" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G78" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H78" s="9" t="str">
         <x:v>IF-LIMIT-003; DATA-DEV-006; DATA-RULE-011; DATA-MAP-022</x:v>
@@ -2778,9 +3066,11 @@
       <x:c r="E79" s="9" t="str">
         <x:v>Byte 기반 한도·UTF-8 다중 Byte 시험</x:v>
       </x:c>
-      <x:c r="F79" s="23" t="str"/>
+      <x:c r="F79" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G79" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H79" s="9" t="str">
         <x:v>IF-LIMIT-004~005; DATA-022~023</x:v>
@@ -2802,9 +3092,11 @@
       <x:c r="E80" s="9" t="str">
         <x:v>이동 가능한 Configuration 패키지 시험</x:v>
       </x:c>
-      <x:c r="F80" s="23" t="str"/>
+      <x:c r="F80" s="23" t="str">
+        <x:v>TC-P10-STATIC-001; EV-012; EV-013; EV-016</x:v>
+      </x:c>
       <x:c r="G80" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H80" s="9" t="str">
         <x:v>DATA-LAYOUT-001~004</x:v>
@@ -2827,10 +3119,10 @@
         <x:v>Win32/x86 DLL Load, caplDllTable4, __stdcall Export와 CAPL compile/runtime 시험</x:v>
       </x:c>
       <x:c r="F81" s="23" t="str">
-        <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001</x:v>
+        <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001; EV-001</x:v>
       </x:c>
       <x:c r="G81" s="24" t="str">
-        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
+        <x:v>External Verification Pending</x:v>
       </x:c>
       <x:c r="H81" s="9" t="str">
         <x:v>FACT-DLL-001~005; IF-ABI-009</x:v>
@@ -2853,10 +3145,10 @@
         <x:v>Export Table 이름·Wrapper 호출 시험</x:v>
       </x:c>
       <x:c r="F82" s="23" t="str">
-        <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001</x:v>
+        <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001; EV-001</x:v>
       </x:c>
       <x:c r="G82" s="24" t="str">
-        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
+        <x:v>External Verification Pending</x:v>
       </x:c>
       <x:c r="H82" s="9" t="str">
         <x:v>IF-NAME-001~003; IF-CTX-001~006</x:v>
@@ -2879,10 +3171,10 @@
         <x:v>생산 Table 메타데이터와 별도 ABI Fixture의 char[]/word[]/long[]/F[1] 성공 왕복 및 Buffer 불변 시험</x:v>
       </x:c>
       <x:c r="F83" s="23" t="str">
-        <x:v>TC-P1-AUTO-004; TC-P1-CAPL-001; TC-P1-ENV-001</x:v>
+        <x:v>TC-P1-AUTO-004; TC-P1-CAPL-001; TC-P1-ENV-001; EV-001</x:v>
       </x:c>
       <x:c r="G83" s="24" t="str">
-        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
+        <x:v>External Verification Pending</x:v>
       </x:c>
       <x:c r="H83" s="9" t="str">
         <x:v>IF-ABI-001~011</x:v>
@@ -2905,10 +3197,10 @@
         <x:v>21개 Export Table/Wrapper Contract 시험</x:v>
       </x:c>
       <x:c r="F84" s="23" t="str">
-        <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001</x:v>
+        <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001; EV-001</x:v>
       </x:c>
       <x:c r="G84" s="24" t="str">
-        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
+        <x:v>External Verification Pending</x:v>
       </x:c>
       <x:c r="H84" s="9" t="str">
         <x:v>IF-API-001~021</x:v>
@@ -2931,10 +3223,10 @@
         <x:v>동기/비동기/No Data 반환 시험</x:v>
       </x:c>
       <x:c r="F85" s="23" t="str">
-        <x:v>TC-P1-AUTO-002; TC-P1-AUTO-003; TC-P1-ENV-001</x:v>
+        <x:v>TC-P1-AUTO-002; TC-P1-AUTO-003; TC-P1-ENV-001; TC-P8-AUTO-001; EV-001</x:v>
       </x:c>
       <x:c r="G85" s="24" t="str">
-        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H85" s="9" t="str">
         <x:v>IF-RET-001~009; IF-CODE-001~004</x:v>
@@ -2957,10 +3249,10 @@
         <x:v>Buffer 부족·Embedded NUL·실패 시 출력 유지 시험</x:v>
       </x:c>
       <x:c r="F86" s="23" t="str">
-        <x:v>TC-P1-AUTO-003; TC-P1-CAPL-001; TC-P1-ENV-001</x:v>
+        <x:v>TC-P1-AUTO-003; TC-P1-CAPL-001; TC-P1-ENV-001; EV-001</x:v>
       </x:c>
       <x:c r="G86" s="24" t="str">
-        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
+        <x:v>External Verification Pending</x:v>
       </x:c>
       <x:c r="H86" s="9" t="str">
         <x:v>IF-ABI-006~007,010~011; IF-RET-002~007</x:v>
@@ -2982,9 +3274,11 @@
       <x:c r="E87" s="9" t="str">
         <x:v>Version·Capacity·필드 Routing 시험</x:v>
       </x:c>
-      <x:c r="F87" s="23" t="str"/>
+      <x:c r="F87" s="23" t="str">
+        <x:v>TC-P6-AUTO-001; EV-001</x:v>
+      </x:c>
       <x:c r="G87" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H87" s="9" t="str">
         <x:v>IF-META-001~016</x:v>
@@ -3006,9 +3300,11 @@
       <x:c r="E88" s="9" t="str">
         <x:v>상태 Snapshot 원자성과 Version 시험</x:v>
       </x:c>
-      <x:c r="F88" s="23" t="str"/>
+      <x:c r="F88" s="23" t="str">
+        <x:v>TC-P8-AUTO-001; EV-001</x:v>
+      </x:c>
       <x:c r="G88" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H88" s="9" t="str">
         <x:v>IF-LSTAT-001~014</x:v>
@@ -3030,9 +3326,11 @@
       <x:c r="E89" s="9" t="str">
         <x:v>Version·ValidMask·Capacity·NUL 시험</x:v>
       </x:c>
-      <x:c r="F89" s="23" t="str"/>
+      <x:c r="F89" s="23" t="str">
+        <x:v>TC-P6-AUTO-001; EV-001</x:v>
+      </x:c>
       <x:c r="G89" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H89" s="9" t="str">
         <x:v>IF-EMETA-001~025; IF-ESTAT-001~002; IF-CSTAT-001~002</x:v>
@@ -3054,9 +3352,11 @@
       <x:c r="E90" s="9" t="str">
         <x:v>C++/CAPL 상수 목록 일치 시험</x:v>
       </x:c>
-      <x:c r="F90" s="23" t="str"/>
+      <x:c r="F90" s="23" t="str">
+        <x:v>TC-P2-AUTO-001; TC-P2-AUTO-003; TC-P2-CAPL-001; TC-P2-ENV-001</x:v>
+      </x:c>
       <x:c r="G90" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 2 자동 검증 PASS / CAPL 실환경 대기</x:v>
       </x:c>
       <x:c r="H90" s="9" t="str">
         <x:v>IF-CONST-001~004; IF-ECLASS-001~004</x:v>
@@ -3078,9 +3378,11 @@
       <x:c r="E91" s="9" t="str">
         <x:v>모든 한도 경계와 초과 시험</x:v>
       </x:c>
-      <x:c r="F91" s="23" t="str"/>
+      <x:c r="F91" s="23" t="str">
+        <x:v>TC-P2-AUTO-001; TC-P2-AUTO-002; TC-P2-AUTO-003; TC-P2-CAPL-001</x:v>
+      </x:c>
       <x:c r="G91" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 2 자동 검증 PASS / CAPL 실환경 대기</x:v>
       </x:c>
       <x:c r="H91" s="9" t="str">
         <x:v>IF-LIMIT-001~008</x:v>
@@ -3103,10 +3405,10 @@
         <x:v>Quantity/Capacity 조합 및 실패 불변 시험</x:v>
       </x:c>
       <x:c r="F92" s="23" t="str">
-        <x:v>TC-P1-AUTO-003; TC-P1-AUTO-004</x:v>
+        <x:v>TC-P1-AUTO-003; TC-P1-AUTO-004; TC-P4-AUTO-001</x:v>
       </x:c>
       <x:c r="G92" s="24" t="str">
-        <x:v>Phase 1 자동 검증 PASS</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H92" s="9" t="str">
         <x:v>IF-REG-001~012</x:v>
@@ -3129,10 +3431,10 @@
         <x:v>F[1] 출력 실패 불변성과 시험 Fixture 성공 왕복, CANalyzer x86 호출 시험</x:v>
       </x:c>
       <x:c r="F93" s="23" t="str">
-        <x:v>TC-P1-AUTO-003; TC-P1-AUTO-004; TC-P1-ENV-001</x:v>
+        <x:v>TC-P1-AUTO-003; TC-P1-AUTO-004; TC-P1-ENV-001; TC-P4-AUTO-001</x:v>
       </x:c>
       <x:c r="G93" s="24" t="str">
-        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H93" s="9" t="str">
         <x:v>IF-SIG-001~007</x:v>
@@ -3154,9 +3456,11 @@
       <x:c r="E94" s="9" t="str">
         <x:v>COM 비대기, Queue No Data, Buffer 부족 시험</x:v>
       </x:c>
-      <x:c r="F94" s="23" t="str"/>
+      <x:c r="F94" s="23" t="str">
+        <x:v>TC-P6-AUTO-001</x:v>
+      </x:c>
       <x:c r="G94" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H94" s="9" t="str">
         <x:v>IF-MON-001~012</x:v>
@@ -3178,9 +3482,11 @@
       <x:c r="E95" s="9" t="str">
         <x:v>각 CSV 오류 강제 및 Context 정확성 시험</x:v>
       </x:c>
-      <x:c r="F95" s="23" t="str"/>
+      <x:c r="F95" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G95" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H95" s="9" t="str">
         <x:v>ERR-009~023; LOG-009</x:v>
@@ -3202,9 +3508,11 @@
       <x:c r="E96" s="9" t="str">
         <x:v>실패 주입 및 전후 메모리 비교 시험</x:v>
       </x:c>
-      <x:c r="F96" s="23" t="str"/>
+      <x:c r="F96" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G96" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H96" s="9" t="str">
         <x:v>ERR-001~007,010~018,024~036,042</x:v>
@@ -3226,9 +3534,11 @@
       <x:c r="E97" s="9" t="str">
         <x:v>Exception Golden Vector 시험</x:v>
       </x:c>
-      <x:c r="F97" s="23" t="str"/>
+      <x:c r="F97" s="23" t="str">
+        <x:v>TC-P5-AUTO-001</x:v>
+      </x:c>
       <x:c r="G97" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H97" s="9" t="str">
         <x:v>ERR-039~043; FR-RTU-033</x:v>
@@ -3250,7 +3560,7 @@
       <x:c r="E98" s="9" t="str">
         <x:v>영역별 오류와 OsError 분리 시험</x:v>
       </x:c>
-      <x:c r="F98" s="23" t="str"/>
+      <x:c r="F98" s="23"/>
       <x:c r="G98" s="24" t="str">
         <x:v>Defined</x:v>
       </x:c>
@@ -3274,9 +3584,11 @@
       <x:c r="E99" s="9" t="str">
         <x:v>90개 목록 일치 및 신규 코드 추가 회귀 시험</x:v>
       </x:c>
-      <x:c r="F99" s="23" t="str"/>
+      <x:c r="F99" s="23" t="str">
+        <x:v>TC-P2-AUTO-001; TC-P2-AUTO-002; TC-P2-AUTO-003; TC-P2-CAPL-001</x:v>
+      </x:c>
       <x:c r="G99" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 2 자동 검증 PASS / CAPL 실환경 대기</x:v>
       </x:c>
       <x:c r="H99" s="9" t="str">
         <x:v>IF-CODE-017~020; TBD-064</x:v>
@@ -3298,9 +3610,11 @@
       <x:c r="E100" s="9" t="str">
         <x:v>동시 오류·Context 격리·Polling 시험</x:v>
       </x:c>
-      <x:c r="F100" s="23" t="str"/>
+      <x:c r="F100" s="23" t="str">
+        <x:v>TC-P6-AUTO-001</x:v>
+      </x:c>
       <x:c r="G100" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H100" s="9" t="str">
         <x:v>IF-ERR-001~015; DES-ERR-001~004</x:v>
@@ -3322,9 +3636,11 @@
       <x:c r="E101" s="9" t="str">
         <x:v>반복 Noise·Overflow·Sequence 시험</x:v>
       </x:c>
-      <x:c r="F101" s="23" t="str"/>
+      <x:c r="F101" s="23" t="str">
+        <x:v>TC-P6-AUTO-001</x:v>
+      </x:c>
       <x:c r="G101" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H101" s="9" t="str">
         <x:v>ERR-032~033,040; LOG-011~013</x:v>
@@ -3346,9 +3662,11 @@
       <x:c r="E102" s="9" t="str">
         <x:v>실패 등급별 상태 전이 시험</x:v>
       </x:c>
-      <x:c r="F102" s="23" t="str"/>
+      <x:c r="F102" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G102" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H102" s="9" t="str">
         <x:v>FR-LIFE-013; ERR-028,034~038</x:v>
@@ -3370,9 +3688,11 @@
       <x:c r="E103" s="9" t="str">
         <x:v>회사 환경 실제 Timeout 기반 지연 측정</x:v>
       </x:c>
-      <x:c r="F103" s="23" t="str"/>
+      <x:c r="F103" s="23" t="str">
+        <x:v>EV-004</x:v>
+      </x:c>
       <x:c r="G103" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>External Verification Pending</x:v>
       </x:c>
       <x:c r="H103" s="9" t="str">
         <x:v>PERF-001~003; TBD-039</x:v>
@@ -3394,9 +3714,11 @@
       <x:c r="E104" s="9" t="str">
         <x:v>Trace Timestamp 기반 지연 측정</x:v>
       </x:c>
-      <x:c r="F104" s="23" t="str"/>
+      <x:c r="F104" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G104" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H104" s="9" t="str">
         <x:v>PERF-004~013; TBD-039</x:v>
@@ -3418,9 +3740,11 @@
       <x:c r="E105" s="9" t="str">
         <x:v>호출시간 계측과 정적 코드 검토</x:v>
       </x:c>
-      <x:c r="F105" s="23" t="str"/>
+      <x:c r="F105" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G105" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H105" s="9" t="str">
         <x:v>NFR-007,010</x:v>
@@ -3442,9 +3766,11 @@
       <x:c r="E106" s="9" t="str">
         <x:v>200 Rule 최대/대표 부하 시험</x:v>
       </x:c>
-      <x:c r="F106" s="23" t="str"/>
+      <x:c r="F106" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G106" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H106" s="9" t="str">
         <x:v>FR-LOAD-012~014,019; PERF-014~019</x:v>
@@ -3466,9 +3792,11 @@
       <x:c r="E107" s="9" t="str">
         <x:v>Peak Working Set 측정</x:v>
       </x:c>
-      <x:c r="F107" s="23" t="str"/>
+      <x:c r="F107" s="23" t="str">
+        <x:v>EV-016</x:v>
+      </x:c>
       <x:c r="G107" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>External Verification Pending</x:v>
       </x:c>
       <x:c r="H107" s="9" t="str">
         <x:v>PERF-018</x:v>
@@ -3490,9 +3818,11 @@
       <x:c r="E108" s="9" t="str">
         <x:v>각 상태 Finalize 시간 및 지연 Driver 시험</x:v>
       </x:c>
-      <x:c r="F108" s="23" t="str"/>
+      <x:c r="F108" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G108" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H108" s="9" t="str">
         <x:v>PERF-020~022; TBD-065</x:v>
@@ -3514,9 +3844,11 @@
       <x:c r="E109" s="9" t="str">
         <x:v>동시 두 Port I/O와 Handle 소유 검토</x:v>
       </x:c>
-      <x:c r="F109" s="23" t="str"/>
+      <x:c r="F109" s="23" t="str">
+        <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G109" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H109" s="9" t="str">
         <x:v>DES-THREAD-001</x:v>
@@ -3538,9 +3870,11 @@
       <x:c r="E110" s="9" t="str">
         <x:v>동시 RTU/CAPL 접근 및 Race 시험</x:v>
       </x:c>
-      <x:c r="F110" s="23" t="str"/>
+      <x:c r="F110" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G110" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H110" s="9" t="str">
         <x:v>DES-THREAD-002~003</x:v>
@@ -3562,9 +3896,11 @@
       <x:c r="E111" s="9" t="str">
         <x:v>Deadlock Stress 및 Lock-order 검토</x:v>
       </x:c>
-      <x:c r="F111" s="23" t="str"/>
+      <x:c r="F111" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G111" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H111" s="9" t="str">
         <x:v>DES-THREAD-004</x:v>
@@ -3586,9 +3922,11 @@
       <x:c r="E112" s="9" t="str">
         <x:v>Allocator hook/Stress 시험</x:v>
       </x:c>
-      <x:c r="F112" s="23" t="str"/>
+      <x:c r="F112" s="23" t="str">
+        <x:v>TC-P6-AUTO-001</x:v>
+      </x:c>
       <x:c r="G112" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H112" s="9" t="str">
         <x:v>DES-THREAD-003; DES-CAN-011~012</x:v>
@@ -3610,9 +3948,11 @@
       <x:c r="E113" s="9" t="str">
         <x:v>동시 다중 Register Write와 Snapshot 일관성 시험</x:v>
       </x:c>
-      <x:c r="F113" s="23" t="str"/>
+      <x:c r="F113" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G113" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H113" s="9" t="str">
         <x:v>IF-MON-002~003</x:v>
@@ -3634,9 +3974,11 @@
       <x:c r="E114" s="9" t="str">
         <x:v>Burst/Overflow 중 RTU 응답 시험</x:v>
       </x:c>
-      <x:c r="F114" s="23" t="str"/>
+      <x:c r="F114" s="23" t="str">
+        <x:v>TC-P6-AUTO-001</x:v>
+      </x:c>
       <x:c r="G114" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H114" s="9" t="str">
         <x:v>NFR-002~004; FR-LOAD-009</x:v>
@@ -3658,9 +4000,11 @@
       <x:c r="E115" s="9" t="str">
         <x:v>Device 수별 메모리 및 직접 Address 시험</x:v>
       </x:c>
-      <x:c r="F115" s="23" t="str"/>
+      <x:c r="F115" s="23" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
       <x:c r="G115" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H115" s="9" t="str">
         <x:v>DES-REG-005</x:v>
@@ -3682,9 +4026,11 @@
       <x:c r="E116" s="9" t="str">
         <x:v>Thread/Handle 누수와 종료 Race 시험</x:v>
       </x:c>
-      <x:c r="F116" s="23" t="str"/>
+      <x:c r="F116" s="23" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
       <x:c r="G116" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H116" s="9" t="str">
         <x:v>FR-LIFE-018~019; DES-THREAD-005</x:v>
@@ -3706,9 +4052,11 @@
       <x:c r="E117" s="9" t="str">
         <x:v>Capacity 경계와 Overflow 정책 시험</x:v>
       </x:c>
-      <x:c r="F117" s="23" t="str"/>
+      <x:c r="F117" s="23" t="str">
+        <x:v>TC-P6-AUTO-001</x:v>
+      </x:c>
       <x:c r="G117" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H117" s="9" t="str">
         <x:v>IF-LIMIT-006</x:v>
@@ -3730,9 +4078,11 @@
       <x:c r="E118" s="9" t="str">
         <x:v>포화 및 Sequence wrap 시험</x:v>
       </x:c>
-      <x:c r="F118" s="23" t="str"/>
+      <x:c r="F118" s="23" t="str">
+        <x:v>TC-P6-AUTO-001</x:v>
+      </x:c>
       <x:c r="G118" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H118" s="9" t="str">
         <x:v>IF-QSTAT-001~004</x:v>
@@ -3754,7 +4104,7 @@
       <x:c r="E119" s="9" t="str">
         <x:v>오류별 Write Window 출력 시험</x:v>
       </x:c>
-      <x:c r="F119" s="23" t="str"/>
+      <x:c r="F119" s="23"/>
       <x:c r="G119" s="24" t="str">
         <x:v>Defined</x:v>
       </x:c>
@@ -3778,7 +4128,7 @@
       <x:c r="E120" s="9" t="str">
         <x:v>비동기 오류 순서·병합·Overflow 출력 시험</x:v>
       </x:c>
-      <x:c r="F120" s="23" t="str"/>
+      <x:c r="F120" s="23"/>
       <x:c r="G120" s="24" t="str">
         <x:v>Defined</x:v>
       </x:c>
@@ -3802,9 +4152,11 @@
       <x:c r="E121" s="9" t="str">
         <x:v>부하 시험 진단값 상호 검증</x:v>
       </x:c>
-      <x:c r="F121" s="23" t="str"/>
+      <x:c r="F121" s="23" t="str">
+        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+      </x:c>
       <x:c r="G121" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H121" s="9" t="str">
         <x:v>LOG-002~008,014~017</x:v>
@@ -3826,9 +4178,11 @@
       <x:c r="E122" s="9" t="str">
         <x:v>강제 Win32 오류와 Context 시험</x:v>
       </x:c>
-      <x:c r="F122" s="23" t="str"/>
+      <x:c r="F122" s="23" t="str">
+        <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G122" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H122" s="9" t="str">
         <x:v>ERR-027~038; LOG-013</x:v>
@@ -3850,9 +4204,11 @@
       <x:c r="E123" s="9" t="str">
         <x:v>반복 동일 오류 부하 시험</x:v>
       </x:c>
-      <x:c r="F123" s="23" t="str"/>
+      <x:c r="F123" s="23" t="str">
+        <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
+      </x:c>
       <x:c r="G123" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H123" s="9" t="str">
         <x:v>ERR-040; LOG-011</x:v>
@@ -3875,10 +4231,10 @@
         <x:v>깨끗한 PC Win32 Build 및 CANalyzer 로딩 시험</x:v>
       </x:c>
       <x:c r="F124" s="23" t="str">
-        <x:v>TC-P1-AUTO-001; TC-P1-ENV-001</x:v>
+        <x:v>TC-P1-AUTO-001; TC-P1-ENV-001; EV-001</x:v>
       </x:c>
       <x:c r="G124" s="24" t="str">
-        <x:v>Phase 1 자동 검증 PASS / CANalyzer 9.x 대기</x:v>
+        <x:v>External Verification Pending</x:v>
       </x:c>
       <x:c r="H124" s="9" t="str">
         <x:v>ENV-001~002,010~011; COMP-001~002,008</x:v>
@@ -3978,9 +4334,11 @@
       <x:c r="E128" s="9" t="str">
         <x:v>공식 Protocol Vector 및 경계 시험</x:v>
       </x:c>
-      <x:c r="F128" s="23" t="str"/>
+      <x:c r="F128" s="23" t="str">
+        <x:v>TC-P5-AUTO-001</x:v>
+      </x:c>
       <x:c r="G128" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H128" s="9" t="str">
         <x:v>COMP-013</x:v>
@@ -4002,9 +4360,11 @@
       <x:c r="E129" s="9" t="str">
         <x:v>구 Layout consumer 회귀 시험</x:v>
       </x:c>
-      <x:c r="F129" s="23" t="str"/>
+      <x:c r="F129" s="23" t="str">
+        <x:v>TC-P2-AUTO-003; TC-P2-BUILD-001; TC-P2-REG-001; TC-P2-CAPL-001; TC-P2-ENV-001</x:v>
+      </x:c>
       <x:c r="G129" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Phase 2 자동 검증 PASS / CAPL 실환경 대기</x:v>
       </x:c>
       <x:c r="H129" s="9" t="str">
         <x:v>IF-META-015; IF-QSTAT-004; IF-LIMIT-008; IF-CODE-017</x:v>
@@ -4026,9 +4386,11 @@
       <x:c r="E130" s="9" t="str">
         <x:v>로컬/UNC/권한 부족 경로 시험</x:v>
       </x:c>
-      <x:c r="F130" s="23" t="str"/>
+      <x:c r="F130" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G130" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H130" s="9" t="str">
         <x:v>NFR-012; COMP-006; OOS-015</x:v>
@@ -4050,7 +4412,7 @@
       <x:c r="E131" s="9" t="str">
         <x:v>보안 경계 문서 검토</x:v>
       </x:c>
-      <x:c r="F131" s="23" t="str"/>
+      <x:c r="F131" s="23"/>
       <x:c r="G131" s="24" t="str">
         <x:v>Defined</x:v>
       </x:c>
@@ -4074,9 +4436,11 @@
       <x:c r="E132" s="9" t="str">
         <x:v>ASCII/한글 경로·Text round-trip 시험</x:v>
       </x:c>
-      <x:c r="F132" s="23" t="str"/>
+      <x:c r="F132" s="23" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
       <x:c r="G132" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H132" s="9" t="str">
         <x:v>NFR-013</x:v>
@@ -4090,7 +4454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re776782613fe4515"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra12b444decf54c59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7147,7 +7511,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbf782bb967348ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb604c9e89694dd8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7582,7 +7946,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd96c9efad414b7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R479e48cd063641e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7780,7 +8144,7 @@
         <x:v>Generated Contracts</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>오류 코드·공개 상수의 C++/CAPL 단일 기준 생성 및 검증</x:v>
+        <x:v>ErrorCodes.csv·PublicConstants.csv 단일 원본 검증, PowerShell 생성기, C++/CAPL 생성 계약과 stale 결과 Build 차단</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -7797,7 +8161,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R270e4afe34244d10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c69596c262d4ceb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7877,10 +8241,65 @@
         <x:v>최대 Configuration Refresh peak</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="35" t="str">
+        <x:v>Phase 2 CAPL generated contracts</x:v>
+      </x:c>
+      <x:c r="B7" s="35" t="str">
+        <x:v>자동 생성·텍스트 검증 PASS / CANalyzer 컴파일 대기</x:v>
+      </x:c>
+      <x:c r="C7" s="35" t="str">
+        <x:v>M485E_Phase2_ContractsProbe.can을 CANalyzer 13 및 9.x SP8에서 Compile·Measurement 실행</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>External Verification Guide</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>작성 완료</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>docs/05_Test/External_Verification_Guide.docx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>External Test Result</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>16건 Not Tested</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="63" t="str">
+        <x:v>CANalyzer 13 CAPL compiler evidence</x:v>
+      </x:c>
+      <x:c r="B10" s="63" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C10" s="63" t="str">
+        <x:v>Phase 1/2/9 probes compiled warning-free with Exec32 caplcompexec.exe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="63" t="str">
+        <x:v>CANalyzer 9.x SP8 / Board / Panel</x:v>
+      </x:c>
+      <x:c r="B11" s="63" t="str">
+        <x:v>External Verification Pending</x:v>
+      </x:c>
+      <x:c r="C11" s="63" t="str">
+        <x:v>docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d209ff1ef644042"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99d12defaa494243"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8040,4 +8459,475 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="56" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="48" t="str">
+        <x:v>Test Case ID</x:v>
+      </x:c>
+      <x:c r="B1" s="48" t="str">
+        <x:v>검증 범위</x:v>
+      </x:c>
+      <x:c r="C1" s="48" t="str">
+        <x:v>실행 방법</x:v>
+      </x:c>
+      <x:c r="D1" s="48" t="str">
+        <x:v>환경</x:v>
+      </x:c>
+      <x:c r="E1" s="48" t="str">
+        <x:v>결과</x:v>
+      </x:c>
+      <x:c r="F1" s="48" t="str">
+        <x:v>비고</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="36" t="str">
+        <x:v>TC-P2-AUTO-001</x:v>
+      </x:c>
+      <x:c r="B2" s="35" t="str">
+        <x:v>계약 단일 원본·생성 결과 일치</x:v>
+      </x:c>
+      <x:c r="C2" s="35" t="str">
+        <x:v>Generate/Check 모드와 stale 결과 검사</x:v>
+      </x:c>
+      <x:c r="D2" s="35" t="str">
+        <x:v>Windows PowerShell 5.1</x:v>
+      </x:c>
+      <x:c r="E2" s="51" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F2" s="35" t="str">
+        <x:v>오류 코드 90개, 공개 상수 183개에서 C++/CAPL 생성</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A3" s="36" t="str">
+        <x:v>TC-P2-AUTO-002</x:v>
+      </x:c>
+      <x:c r="B3" s="35" t="str">
+        <x:v>잘못된 입력·경계·호환 확장</x:v>
+      </x:c>
+      <x:c r="C3" s="35" t="str">
+        <x:v>생성기 오류 주입 시험</x:v>
+      </x:c>
+      <x:c r="D3" s="35" t="str">
+        <x:v>Windows PowerShell 5.1</x:v>
+      </x:c>
+      <x:c r="E3" s="51" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F3" s="35" t="str">
+        <x:v>중복 코드·상수, 잘못된 Severity, stale 출력 거부; 91번째 오류 append 허용; 임시 자원 정리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="36" t="str">
+        <x:v>TC-P2-AUTO-003</x:v>
+      </x:c>
+      <x:c r="B4" s="35" t="str">
+        <x:v>공개 상수·Layout·오류 테이블</x:v>
+      </x:c>
+      <x:c r="C4" s="35" t="str">
+        <x:v>M485E.ContractTests</x:v>
+      </x:c>
+      <x:c r="D4" s="35" t="str">
+        <x:v>Win32 Debug/Release</x:v>
+      </x:c>
+      <x:c r="E4" s="51" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F4" s="35" t="str">
+        <x:v>32bit long, Count/Index, 한도, 90개 오류의 숫자·Severity·Symbol·Message Key 검사</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="36" t="str">
+        <x:v>TC-P2-BUILD-001</x:v>
+      </x:c>
+      <x:c r="B5" s="35" t="str">
+        <x:v>Win32 Debug/Release 및 경고</x:v>
+      </x:c>
+      <x:c r="C5" s="35" t="str">
+        <x:v>MSBuild Solution과 CMake Build/CTest</x:v>
+      </x:c>
+      <x:c r="D5" s="35" t="str">
+        <x:v>Visual Studio 18 / Win32</x:v>
+      </x:c>
+      <x:c r="E5" s="51" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F5" s="35" t="str">
+        <x:v>/W4 /WX, Debug/Release 경고 0개; CTest 각 3/3 PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="36" t="str">
+        <x:v>TC-P2-REG-001</x:v>
+      </x:c>
+      <x:c r="B6" s="35" t="str">
+        <x:v>Phase 1 ABI 회귀</x:v>
+      </x:c>
+      <x:c r="C6" s="35" t="str">
+        <x:v>M485E.AbiProbe Debug/Release</x:v>
+      </x:c>
+      <x:c r="D6" s="35" t="str">
+        <x:v>Win32</x:v>
+      </x:c>
+      <x:c r="E6" s="51" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F6" s="35" t="str">
+        <x:v>생산 21 API와 caplDllTable4 ABI, 수명주기, Buffer 보호 회귀 통과</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="36" t="str">
+        <x:v>TC-P2-CAPL-001</x:v>
+      </x:c>
+      <x:c r="B7" s="35" t="str">
+        <x:v>CAPL generated include 컴파일·상수 확인</x:v>
+      </x:c>
+      <x:c r="C7" s="35" t="str">
+        <x:v>M485E_Phase2_ContractsProbe.can</x:v>
+      </x:c>
+      <x:c r="D7" s="35" t="str">
+        <x:v>CANalyzer 13 x86</x:v>
+      </x:c>
+      <x:c r="E7" s="54" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F7" s="35" t="str">
+        <x:v>GUI 자동화 불가; 실환경 Compile과 Write Window 확인 필요</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A8" s="36" t="str">
+        <x:v>TC-P2-ENV-001</x:v>
+      </x:c>
+      <x:c r="B8" s="35" t="str">
+        <x:v>CANalyzer 9.x SP8 CAPL 계약 호환</x:v>
+      </x:c>
+      <x:c r="C8" s="35" t="str">
+        <x:v>M485E_Phase1_AbiProbe.can + M485E_Phase2_ContractsProbe.can</x:v>
+      </x:c>
+      <x:c r="D8" s="35" t="str">
+        <x:v>회사 CANalyzer 9.x SP8 x86</x:v>
+      </x:c>
+      <x:c r="E8" s="54" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F8" s="35" t="str">
+        <x:v>실환경 결과를 임의로 PASS 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="35" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="60" t="str">
+        <x:v>Test Case ID</x:v>
+      </x:c>
+      <x:c r="B1" s="60" t="str">
+        <x:v>Phase</x:v>
+      </x:c>
+      <x:c r="C1" s="60" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="D1" s="60" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="E1" s="60" t="str">
+        <x:v>Method</x:v>
+      </x:c>
+      <x:c r="F1" s="60" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="G1" s="60" t="str">
+        <x:v>External Follow-up</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="63" t="str">
+        <x:v>TC-P3-AUTO-001</x:v>
+      </x:c>
+      <x:c r="B2" s="63" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C2" s="63" t="str">
+        <x:v>Automated</x:v>
+      </x:c>
+      <x:c r="D2" s="63" t="str">
+        <x:v>CSV parsing, schema, cross validation, cardinality/file limits, atomic refresh</x:v>
+      </x:c>
+      <x:c r="E2" s="63" t="str">
+        <x:v>M485E.Core.Tests</x:v>
+      </x:c>
+      <x:c r="F2" s="65" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G2" s="63" t="str">
+        <x:v>EV-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="63" t="str">
+        <x:v>TC-P4-AUTO-001</x:v>
+      </x:c>
+      <x:c r="B3" s="63" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="63" t="str">
+        <x:v>Automated</x:v>
+      </x:c>
+      <x:c r="D3" s="63" t="str">
+        <x:v>Register/Signal/Init/Reset, atomic failure and snapshot impact</x:v>
+      </x:c>
+      <x:c r="E3" s="63" t="str">
+        <x:v>M485E.Core.Tests</x:v>
+      </x:c>
+      <x:c r="F3" s="65" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G3" s="63" t="str">
+        <x:v>EV-006, EV-013</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="63" t="str">
+        <x:v>TC-P5-AUTO-001</x:v>
+      </x:c>
+      <x:c r="B4" s="63" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="63" t="str">
+        <x:v>Automated</x:v>
+      </x:c>
+      <x:c r="D4" s="63" t="str">
+        <x:v>CRC16, FC03/04/10, silent discard, exception vectors</x:v>
+      </x:c>
+      <x:c r="E4" s="63" t="str">
+        <x:v>M485E.Core.Tests</x:v>
+      </x:c>
+      <x:c r="F4" s="65" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G4" s="63" t="str">
+        <x:v>EV-004~EV-007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="63" t="str">
+        <x:v>TC-P6-AUTO-001</x:v>
+      </x:c>
+      <x:c r="B5" s="63" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C5" s="63" t="str">
+        <x:v>Automated</x:v>
+      </x:c>
+      <x:c r="D5" s="63" t="str">
+        <x:v>Snapshot/Error queues, immutable payload, overflow/coalesce/stats</x:v>
+      </x:c>
+      <x:c r="E5" s="63" t="str">
+        <x:v>M485E.Core.Tests</x:v>
+      </x:c>
+      <x:c r="F5" s="65" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G5" s="63" t="str">
+        <x:v>EV-008~EV-010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="63" t="str">
+        <x:v>TC-P7-AUTO-001</x:v>
+      </x:c>
+      <x:c r="B6" s="63" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="63" t="str">
+        <x:v>Automated</x:v>
+      </x:c>
+      <x:c r="D6" s="63" t="str">
+        <x:v>RTU timing/framing, partial I/O, cancellation, worker response</x:v>
+      </x:c>
+      <x:c r="E6" s="63" t="str">
+        <x:v>M485E.Core.Tests + FakeSerialTransport</x:v>
+      </x:c>
+      <x:c r="F6" s="65" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G6" s="63" t="str">
+        <x:v>EV-003~EV-007, EV-014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="63" t="str">
+        <x:v>TC-P8-AUTO-001</x:v>
+      </x:c>
+      <x:c r="B7" s="63" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C7" s="63" t="str">
+        <x:v>Automated</x:v>
+      </x:c>
+      <x:c r="D7" s="63" t="str">
+        <x:v>Async refresh/connect, two-Port rollback, 21 API integration, finalize</x:v>
+      </x:c>
+      <x:c r="E7" s="63" t="str">
+        <x:v>M485E.IntegrationTests</x:v>
+      </x:c>
+      <x:c r="F7" s="65" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G7" s="63" t="str">
+        <x:v>EV-002, EV-003, EV-014, EV-015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="63" t="str">
+        <x:v>TC-P9-STATIC-001</x:v>
+      </x:c>
+      <x:c r="B8" s="63" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C8" s="63" t="str">
+        <x:v>Static + CAPL Compile</x:v>
+      </x:c>
+      <x:c r="D8" s="63" t="str">
+        <x:v>CAPL Core wrappers, 1s/10ms pump policy, 66/33 budget, Extended CAN</x:v>
+      </x:c>
+      <x:c r="E8" s="63" t="str">
+        <x:v>Test-M485ECaplSources.ps1 + CANalyzer 13 Exec32 caplcompexec</x:v>
+      </x:c>
+      <x:c r="F8" s="65" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G8" s="63" t="str">
+        <x:v>EV-008~EV-011, EV-016</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="63" t="str">
+        <x:v>TC-P10-STATIC-001</x:v>
+      </x:c>
+      <x:c r="B9" s="63" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C9" s="63" t="str">
+        <x:v>Static</x:v>
+      </x:c>
+      <x:c r="D9" s="63" t="str">
+        <x:v>UI System Variable adapter, manual/auto read, write, signal control</x:v>
+      </x:c>
+      <x:c r="E9" s="63" t="str">
+        <x:v>Test-M485ECaplSources.ps1; Main compile in configured CANalyzer environment</x:v>
+      </x:c>
+      <x:c r="F9" s="65" t="str">
+        <x:v>Static PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="G9" s="63" t="str">
+        <x:v>EV-011~EV-013, EV-016</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="63" t="str">
+        <x:v>TC-REG-AUTO-001</x:v>
+      </x:c>
+      <x:c r="B10" s="63" t="str">
+        <x:v>1~10</x:v>
+      </x:c>
+      <x:c r="C10" s="63" t="str">
+        <x:v>Automated</x:v>
+      </x:c>
+      <x:c r="D10" s="63" t="str">
+        <x:v>Win32 Debug/Release, /W4 /WX, ABI, contract, core, integration, CAPL probes</x:v>
+      </x:c>
+      <x:c r="E10" s="63" t="str">
+        <x:v>MSBuild + CMake + CTest + CANalyzer 13 x86 CAPL compiler</x:v>
+      </x:c>
+      <x:c r="F10" s="65" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G10" s="63" t="str">
+        <x:v>EV-001~EV-016</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="63" t="str">
+        <x:v>EV-001~EV-016</x:v>
+      </x:c>
+      <x:c r="B11" s="63" t="str">
+        <x:v>External</x:v>
+      </x:c>
+      <x:c r="C11" s="63" t="str">
+        <x:v>External</x:v>
+      </x:c>
+      <x:c r="D11" s="63" t="str">
+        <x:v>CANalyzer 9.x, SystemBase Multi USB-485, Board, Panel, virtual CAN, stress</x:v>
+      </x:c>
+      <x:c r="E11" s="63" t="str">
+        <x:v>External Verification Guide</x:v>
+      </x:c>
+      <x:c r="F11" s="67" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="G11" s="63" t="str">
+        <x:v>회사 환경에서 결과 기록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="63" t="str">
+        <x:v>TC-CAPL13-COMPILE-001</x:v>
+      </x:c>
+      <x:c r="B12" s="63" t="str">
+        <x:v>1/2/9</x:v>
+      </x:c>
+      <x:c r="C12" s="63" t="str">
+        <x:v>Compiler</x:v>
+      </x:c>
+      <x:c r="D12" s="63" t="str">
+        <x:v>Phase 1 ABI, Phase 2 Contracts, Phase 9 Core/Monitoring CAPL probes</x:v>
+      </x:c>
+      <x:c r="E12" s="63" t="str">
+        <x:v>CANalyzer 13 Exec32 caplcompexec.exe</x:v>
+      </x:c>
+      <x:c r="F12" s="69" t="str">
+        <x:v>PASS (warning-free)</x:v>
+      </x:c>
+      <x:c r="G12" s="63" t="str">
+        <x:v>CANalyzer 9.x SP8 Compile/Measurement remains EV-001</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R0121afb6d54c45c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R15996331584d415b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R39b6aaa29a9d4005"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="Rc8b932bad8f64488"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rad0c2b7f5425431c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R44fd9fc79b264a70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R417753a131884d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R16ade59936224cb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R7c2b122e25184aaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rbedd41e4dcd244cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rd017401cd7274d7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R695db8112d884c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R19d986d5b7b04800"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Ra2683d5f4fbd46ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R665d7b4daa4c4b98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R0238c366d51445ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R63fa9e6352f74b5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R4db10e335ada438d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -840,7 +840,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>0.11</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Requirements with Design</x:v>
@@ -868,7 +868,7 @@
         <x:v>Baseline Date</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-09</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>Test Case IDs</x:v>
@@ -1055,7 +1055,7 @@
         <x:v>REQ-FUNC-001</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>시스템은 CAPL 프로그램별 Context Handle을 사용하여 하나의 활성 Emulator Context를 초기화하고, 성공 시 Disconnected 상태를 생성해야 한다.</x:v>
+        <x:v>시스템은 CAPL 프로그램별 불투명 Context Handle(0 포함)을 사용하여 하나의 활성 Emulator Context를 초기화하고, 성공 시 Disconnected 상태를 생성해야 한다.</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
         <x:v>FS-INIT-001</x:v>
@@ -1064,7 +1064,7 @@
         <x:v>DC-01 CAPL ABI Adapter; DC-02 EmulatorContext</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>Context 초기화·중복·잘못된 Handle·Finalize 후 호출·재초기화 자동 시험과 CANalyzer 9.x 실행</x:v>
+        <x:v>zero/nonzero Handle Initialize·중복·잘못된 Handle·Finalize 후 호출·재초기화 시험</x:v>
       </x:c>
       <x:c r="F2" s="23" t="str">
         <x:v>TC-P1-AUTO-002; TC-P1-ENV-001; TC-P8-AUTO-001</x:v>
@@ -1133,7 +1133,7 @@
         <x:v>REQ-FUNC-004</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>Connect는 두 Port 모두 Open되고 Worker 준비가 완료된 경우에만 Connected로 전환하는 전체 성공/전체 실패 방식으로 동작해야 한다.</x:v>
+        <x:v>Connect는 구성된 모든 활성 Port(1~4)가 Open되고 Worker 준비가 완료된 경우에만 Connected로 전환하는 전체 성공/전체 실패 방식으로 동작해야 한다.</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
         <x:v>FS-LIFE-001</x:v>
@@ -1142,7 +1142,7 @@
         <x:v>DC-03 LifecycleController; DC-09 Win32SerialPort; DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>두 번째 Port 실패 강제 및 전체 Rollback 시험</x:v>
+        <x:v>1/4 Port Connect와 각 active Port 실패 위치별 전체 Rollback 시험</x:v>
       </x:c>
       <x:c r="F5" s="23" t="str">
         <x:v>TC-P8-AUTO-001</x:v>
@@ -1185,7 +1185,7 @@
         <x:v>REQ-FUNC-006</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>정상 유휴와 Serial Read Timeout은 연결 장애로 간주하지 않고, 치명적 COM 장애만 두 Port를 정리한 뒤 3,000ms 간격 최대 10회 자동 재연결해야 한다.</x:v>
+        <x:v>정상 유휴와 Serial Read Timeout은 연결 장애로 간주하지 않고, 치명적 COM 장애만 모든 활성 Port(1~4)를 정리한 뒤 3,000ms 간격 최대 10회 자동 재연결해야 한다.</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
         <x:v>FS-LIFE-004</x:v>
@@ -1194,7 +1194,7 @@
         <x:v>DC-03 LifecycleController; DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>USB 제거·복귀, 10회 실패 및 수동 복구 시험</x:v>
+        <x:v>1/4 Port USB 제거·복귀, 부분 Open Rollback, 10회 실패 및 수동 복구 시험</x:v>
       </x:c>
       <x:c r="F7" s="23" t="str">
         <x:v>TC-P8-AUTO-001</x:v>
@@ -1809,7 +1809,7 @@
         <x:v>REQ-FUNC-030</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>ReadSwitch는 두 Port의 Monitoring 전체를 제어하는 CAPL UI 입력이며 DLL은 하나의 MonitoringEnabled 상태만 유지해야 한다.</x:v>
+        <x:v>ReadSwitch는 모든 활성 Port(1~4)의 Monitoring 전체를 제어하는 CAPL UI 입력이며 DLL은 하나의 MonitoringEnabled 상태만 유지해야 한다.</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
         <x:v>FS-MON-001</x:v>
@@ -1818,7 +1818,7 @@
         <x:v>DC-11 SnapshotService; DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>ON/OFF 중 RTU 유지와 Queue 정책 시험</x:v>
+        <x:v>1/4 Port에서 ON/OFF 중 RTU 유지와 Queue 정책 시험</x:v>
       </x:c>
       <x:c r="F31" s="23" t="str">
         <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -1965,7 +1965,7 @@
         <x:v>REQ-FUNC-036</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>CAPL은 10ms Output Pump에서 두 Port를 Round-robin하고 Snapshot 묶음을 Tick 중간에 분할하지 않아야 한다.</x:v>
+        <x:v>CAPL은 10ms Output Pump에서 모든 활성 Port(1~4)를 Round-robin하고 Snapshot 묶음을 Tick 중간에 분할하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
         <x:v>FS-MON-006</x:v>
@@ -1974,7 +1974,7 @@
         <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
-        <x:v>두 Port Burst·Rule Cursor·묶음 원자 출력 시험</x:v>
+        <x:v>1/4 Port Burst·Rule Cursor·빈 Queue·묶음 원자 출력 시험</x:v>
       </x:c>
       <x:c r="F37" s="23" t="str">
         <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -2225,7 +2225,7 @@
         <x:v>REQ-COM-002</x:v>
       </x:c>
       <x:c r="B47" s="9" t="str">
-        <x:v>고유 COM Port는 정확히 2개이고 PortSlot 0/1 및 가상 CAN 채널과 1:1로 매핑되어야 한다.</x:v>
+        <x:v>DeviceMap의 고유 COM Port는 1~4개이며 최초 등장 순서대로 PortSlot 0~3 및 같은 수의 가상 CAN 채널과 1:1로 매핑되어야 한다. 5개 이상은 거부한다.</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
         <x:v>FS-COM-001</x:v>
@@ -2234,7 +2234,7 @@
         <x:v>DC-05 DeviceRegistry; DC-13 CAPL Core</x:v>
       </x:c>
       <x:c r="E47" s="9" t="str">
-        <x:v>Port 등록 순서·중복·누락·Routing 시험</x:v>
+        <x:v>1/4 Port 등록 성공, 중복 Port 병합, PortSlot 3 경계, 5 Port 거부 및 Routing 시험</x:v>
       </x:c>
       <x:c r="F47" s="23" t="str">
         <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
@@ -2563,7 +2563,7 @@
         <x:v>REQ-COM-015</x:v>
       </x:c>
       <x:c r="B60" s="9" t="str">
-        <x:v>각 Port Worker는 한 번에 하나의 요청을 순차 처리하고 두 Port는 서로 독립적으로 동작해야 한다.</x:v>
+        <x:v>각 활성 Port Worker는 한 번에 하나의 요청을 순차 처리하고 모든 활성 Port(1~4)는 서로 독립적으로 동작해야 한다.</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
         <x:v>FS-MODBUS-001</x:v>
@@ -2572,7 +2572,7 @@
         <x:v>DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E60" s="9" t="str">
-        <x:v>두 Port 동시 요청·순서·격리 시험</x:v>
+        <x:v>1/4 Port 동시 요청·순서·격리와 PortSlot 3 Routing 시험</x:v>
       </x:c>
       <x:c r="F60" s="23" t="str">
         <x:v>TC-P5-AUTO-001; TC-P7-AUTO-001; EV-003; EV-004</x:v>
@@ -2598,7 +2598,7 @@
         <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E61" s="9" t="str">
-        <x:v>두 가상 채널 Extended CAN 출력 시험</x:v>
+        <x:v>활성 Port 수와 같은 1~4개 가상 채널의 Extended CAN 출력 시험</x:v>
       </x:c>
       <x:c r="F61" s="23" t="str">
         <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -3133,7 +3133,7 @@
         <x:v>REQ-IF-002</x:v>
       </x:c>
       <x:c r="B82" s="9" t="str">
-        <x:v>공개 CAPL 함수는 M485E_Core_, 저수준 Export는 M485E_Dll_ Prefix를 사용하고 Context Handle은 Core가 숨겨 전달해야 한다.</x:v>
+        <x:v>공개 CAPL 함수는 M485E_Core_, 저수준 Export는 M485E_Dll_ Prefix를 사용한다. Core는 Vector Context Handle을 불투명 값으로 숨겨 전달하며 0도 유효하므로 등록/초기화 상태를 별도 관리해야 한다.</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
         <x:v>FS-INIT-001</x:v>
@@ -3142,7 +3142,7 @@
         <x:v>DC-01 CAPL ABI Adapter; DC-13 CAPL Core</x:v>
       </x:c>
       <x:c r="E82" s="9" t="str">
-        <x:v>Export Table 이름·Wrapper 호출 시험</x:v>
+        <x:v>Export Table·Wrapper 호출 및 zero/nonzero Handle 등록·Initialize·Finalize ABI Probe</x:v>
       </x:c>
       <x:c r="F82" s="23" t="str">
         <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001; EV-001</x:v>
@@ -3833,7 +3833,7 @@
         <x:v>REQ-REL-001</x:v>
       </x:c>
       <x:c r="B109" s="9" t="str">
-        <x:v>Port Worker만 자신의 COM Handle을 소유하고 두 Worker는 독립적으로 동작해야 한다.</x:v>
+        <x:v>각 활성 Port Worker만 자신의 COM Handle을 소유하고 모든 활성 Worker(1~4)는 독립적으로 동작해야 한다.</x:v>
       </x:c>
       <x:c r="C109" s="9" t="str">
         <x:v>FS-COM-002,FS-MODBUS-001</x:v>
@@ -3842,7 +3842,7 @@
         <x:v>DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E109" s="9" t="str">
-        <x:v>동시 두 Port I/O와 Handle 소유 검토</x:v>
+        <x:v>1/4 Port 동시 I/O, PortSlot 0~3 Handle 소유 및 장애 격리 검토</x:v>
       </x:c>
       <x:c r="F109" s="23" t="str">
         <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
@@ -4454,7 +4454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra12b444decf54c59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1fe41ae26354ee6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4503,7 +4503,7 @@
         <x:v>Lifecycle</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>시스템은 CAPL 프로그램별 Context Handle을 사용하여 하나의 활성 Emulator Context를 초기화하고, 성공 시 Disconnected 상태를 생성해야 한다.</x:v>
+        <x:v>시스템은 CAPL 프로그램별 불투명 Context Handle(0 포함)을 사용하여 하나의 활성 Emulator Context를 초기화하고, 성공 시 Disconnected 상태를 생성해야 한다.</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
         <x:v>FR-LIFE-009,016; IF-CTX-001~003,007</x:v>
@@ -4515,7 +4515,7 @@
         <x:v>CAPL ABI Adapter; EmulatorContext</x:v>
       </x:c>
       <x:c r="G2" s="9" t="str">
-        <x:v>CANalyzer 9.x x86 DLL 로딩 및 중복 Context 시험</x:v>
+        <x:v>zero/nonzero Handle Initialize·중복·잘못된 Handle·Finalize 후 호출·재초기화 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
@@ -4572,7 +4572,7 @@
         <x:v>Lifecycle</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>Connect는 두 Port 모두 Open되고 Worker 준비가 완료된 경우에만 Connected로 전환하는 전체 성공/전체 실패 방식으로 동작해야 한다.</x:v>
+        <x:v>Connect는 구성된 모든 활성 Port(1~4)가 Open되고 Worker 준비가 완료된 경우에만 Connected로 전환하는 전체 성공/전체 실패 방식으로 동작해야 한다.</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
         <x:v>FR-PORT-007~017</x:v>
@@ -4584,7 +4584,7 @@
         <x:v>LifecycleController; Win32SerialPort; PortWorker</x:v>
       </x:c>
       <x:c r="G5" s="9" t="str">
-        <x:v>두 번째 Port 실패 강제 및 전체 Rollback 시험</x:v>
+        <x:v>1/4 Port Connect와 각 active Port 실패 위치별 전체 Rollback 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
@@ -4618,7 +4618,7 @@
         <x:v>Lifecycle</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>정상 유휴와 Serial Read Timeout은 연결 장애로 간주하지 않고, 치명적 COM 장애만 두 Port를 정리한 뒤 3,000ms 간격 최대 10회 자동 재연결해야 한다.</x:v>
+        <x:v>정상 유휴와 Serial Read Timeout은 연결 장애로 간주하지 않고, 치명적 COM 장애만 모든 활성 Port(1~4)를 정리한 뒤 3,000ms 간격 최대 10회 자동 재연결해야 한다.</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
         <x:v>FR-LIFE-023~032</x:v>
@@ -4630,7 +4630,7 @@
         <x:v>LifecycleController; PortWorker</x:v>
       </x:c>
       <x:c r="G7" s="9" t="str">
-        <x:v>USB 제거·복귀, 10회 실패 및 수동 복구 시험</x:v>
+        <x:v>1/4 Port USB 제거·복귀, 부분 Open Rollback, 10회 실패 및 수동 복구 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
@@ -5170,7 +5170,7 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v>ReadSwitch는 두 Port의 Monitoring 전체를 제어하는 CAPL UI 입력이며 DLL은 하나의 MonitoringEnabled 상태만 유지해야 한다.</x:v>
+        <x:v>ReadSwitch는 모든 활성 Port(1~4)의 Monitoring 전체를 제어하는 CAPL UI 입력이며 DLL은 하나의 MonitoringEnabled 상태만 유지해야 한다.</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
         <x:v>FR-LIFE-004~006; FR-CAN-049~056</x:v>
@@ -5182,7 +5182,7 @@
         <x:v>CAPL UI; SnapshotService</x:v>
       </x:c>
       <x:c r="G31" s="9" t="str">
-        <x:v>ON/OFF 중 RTU 유지와 Queue 정책 시험</x:v>
+        <x:v>1/4 Port에서 ON/OFF 중 RTU 유지와 Queue 정책 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
@@ -5308,7 +5308,7 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>CAPL은 10ms Output Pump에서 두 Port를 Round-robin하고 Snapshot 묶음을 Tick 중간에 분할하지 않아야 한다.</x:v>
+        <x:v>CAPL은 10ms Output Pump에서 모든 활성 Port(1~4)를 Round-robin하고 Snapshot 묶음을 Tick 중간에 분할하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
         <x:v>FR-CAN-040~046; DES-CAN-014~017</x:v>
@@ -5320,7 +5320,7 @@
         <x:v>CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G37" s="9" t="str">
-        <x:v>두 Port Burst·Rule Cursor·묶음 원자 출력 시험</x:v>
+        <x:v>1/4 Port Burst·Rule Cursor·빈 Queue·묶음 원자 출력 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="32" customHeight="1">
@@ -5538,7 +5538,7 @@
         <x:v>RS-485</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
-        <x:v>고유 COM Port는 정확히 2개이고 PortSlot 0/1 및 가상 CAN 채널과 1:1로 매핑되어야 한다.</x:v>
+        <x:v>DeviceMap의 고유 COM Port는 1~4개이며 최초 등장 순서대로 PortSlot 0~3 및 같은 수의 가상 CAN 채널과 1:1로 매핑되어야 한다. 5개 이상은 거부한다.</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
         <x:v>ENV-003~005; FR-PORT-018~020</x:v>
@@ -5550,7 +5550,7 @@
         <x:v>DeviceRegistry; CAPL Core</x:v>
       </x:c>
       <x:c r="G47" s="9" t="str">
-        <x:v>Port 등록 순서·중복·누락·Routing 시험</x:v>
+        <x:v>1/4 Port 등록 성공, 중복 Port 병합, PortSlot 3 경계, 5 Port 거부 및 Routing 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="32" customHeight="1">
@@ -5837,7 +5837,7 @@
         <x:v>RTU</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
-        <x:v>각 Port Worker는 한 번에 하나의 요청을 순차 처리하고 두 Port는 서로 독립적으로 동작해야 한다.</x:v>
+        <x:v>각 활성 Port Worker는 한 번에 하나의 요청을 순차 처리하고 모든 활성 Port(1~4)는 서로 독립적으로 동작해야 한다.</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
         <x:v>FR-RTU-034</x:v>
@@ -5849,7 +5849,7 @@
         <x:v>PortWorker</x:v>
       </x:c>
       <x:c r="G60" s="9" t="str">
-        <x:v>두 Port 동시 요청·순서·격리 시험</x:v>
+        <x:v>1/4 Port 동시 요청·순서·격리와 PortSlot 3 Routing 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="32" customHeight="1">
@@ -5872,7 +5872,7 @@
         <x:v>CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G61" s="9" t="str">
-        <x:v>두 가상 채널 Extended CAN 출력 시험</x:v>
+        <x:v>활성 Port 수와 같은 1~4개 가상 채널의 Extended CAN 출력 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="32" customHeight="1">
@@ -6343,7 +6343,7 @@
         <x:v>CAPL DLL</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
-        <x:v>공개 CAPL 함수는 M485E_Core_, 저수준 Export는 M485E_Dll_ Prefix를 사용하고 Context Handle은 Core가 숨겨 전달해야 한다.</x:v>
+        <x:v>공개 CAPL 함수는 M485E_Core_, 저수준 Export는 M485E_Dll_ Prefix를 사용한다. Core는 Vector Context Handle을 불투명 값으로 숨겨 전달하며 0도 유효하므로 등록/초기화 상태를 별도 관리해야 한다.</x:v>
       </x:c>
       <x:c r="D82" s="9" t="str">
         <x:v>IF-NAME-001~003; IF-CTX-001~006</x:v>
@@ -6355,7 +6355,7 @@
         <x:v>CAPL Core; CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="G82" s="9" t="str">
-        <x:v>Export Table 이름·Wrapper 호출 시험</x:v>
+        <x:v>Export Table·Wrapper 호출 및 zero/nonzero Handle 등록·Initialize·Finalize ABI Probe</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="32" customHeight="1">
@@ -6964,7 +6964,7 @@
         <x:v>Concurrency</x:v>
       </x:c>
       <x:c r="C109" s="9" t="str">
-        <x:v>Port Worker만 자신의 COM Handle을 소유하고 두 Worker는 독립적으로 동작해야 한다.</x:v>
+        <x:v>각 활성 Port Worker만 자신의 COM Handle을 소유하고 모든 활성 Worker(1~4)는 독립적으로 동작해야 한다.</x:v>
       </x:c>
       <x:c r="D109" s="9" t="str">
         <x:v>DES-THREAD-001</x:v>
@@ -6976,7 +6976,7 @@
         <x:v>PortWorker</x:v>
       </x:c>
       <x:c r="G109" s="9" t="str">
-        <x:v>동시 두 Port I/O와 Handle 소유 검토</x:v>
+        <x:v>1/4 Port 동시 I/O, PortSlot 0~3 Handle 소유 및 장애 격리 검토</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="32" customHeight="1">
@@ -7511,7 +7511,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb604c9e89694dd8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff35aaa8d59b43d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7946,7 +7946,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R479e48cd063641e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dbebcbfb0a74ea5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7979,7 +7979,7 @@
         <x:v>CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>CAPL_DLL_INFO4, __stdcall, Context Handle, Length/Capacity 검증, 21개 Export</x:v>
+        <x:v>CAPL_DLL_INFO4, __stdcall, 불투명 Context Handle(0 포함), Length/Capacity 검증, 21개 Export</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -7990,7 +7990,7 @@
         <x:v>EmulatorContext</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>단일 활성 Context의 상태·Configuration·서비스·Queue 소유</x:v>
+        <x:v>단일 활성 Context의 별도 등록/초기화 상태·Configuration·Service·Queue 소유</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -8001,7 +8001,7 @@
         <x:v>LifecycleController</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>Refresh/Connect/Disconnect/Finalize, 상태·Generation, 자동 재연결</x:v>
+        <x:v>Refresh/Connect/Disconnect/Finalize, 1~4 active Port 원자 수명주기, 상태/Generation, 자동 재연결</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -8078,7 +8078,7 @@
         <x:v>PortWorker</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>Port 단독 소유, t1.5/t3.5 조립, 순차 요청 처리</x:v>
+        <x:v>활성 PortSlot 0~3별 COM Handle 단독 소유, 1~4 Worker, t1.5/t3.5 준수, 순차 요청 처리</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -8161,7 +8161,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c69596c262d4ceb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd73799b487b24809"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8299,7 +8299,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99d12defaa494243"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f58abfc4311463c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8361,7 +8361,7 @@
         <x:v>TC-P1-AUTO-002</x:v>
       </x:c>
       <x:c r="B3" s="35" t="str">
-        <x:v>Context 수명주기</x:v>
+        <x:v>Context 수명주기와 zero/nonzero Handle</x:v>
       </x:c>
       <x:c r="C3" s="35" t="str">
         <x:v>네이티브 M485E.AbiProbe</x:v>
@@ -8373,7 +8373,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F3" s="35" t="str">
-        <x:v>0 Handle, 중복, 잘못된 Handle, Finalize 후 호출, 재초기화</x:v>
+        <x:v>0/nonzero Handle, 중복, 잘못된 Handle, Finalize 후 호출, 재초기화</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8578,7 +8578,7 @@
         <x:v>TC-P2-REG-001</x:v>
       </x:c>
       <x:c r="B6" s="35" t="str">
-        <x:v>Phase 1 ABI 회귀</x:v>
+        <x:v>Phase 1 ABI 회귀(zero/nonzero Handle 포함)</x:v>
       </x:c>
       <x:c r="C6" s="35" t="str">
         <x:v>M485E.AbiProbe Debug/Release</x:v>
@@ -8590,7 +8590,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F6" s="35" t="str">
-        <x:v>생산 21 API와 caplDllTable4 ABI, 수명주기, Buffer 보호 회귀 통과</x:v>
+        <x:v>생산 21 API와 caplDllTable4 ABI 및 zero/nonzero Handle 수명주기 회귀 통과</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -8685,7 +8685,7 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D2" s="63" t="str">
-        <x:v>CSV parsing, schema, cross validation, cardinality/file limits, atomic refresh</x:v>
+        <x:v>CSV parsing, schema, cross validation, 1/4 Port 경계, 5 Port 거부, file limits, atomic refresh</x:v>
       </x:c>
       <x:c r="E2" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
@@ -8777,7 +8777,7 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D6" s="63" t="str">
-        <x:v>RTU timing/framing, partial I/O, cancellation, worker response</x:v>
+        <x:v>1~4 Port RTU timing/framing, partial I/O, cancellation, worker response</x:v>
       </x:c>
       <x:c r="E6" s="63" t="str">
         <x:v>M485E.Core.Tests + FakeSerialTransport</x:v>
@@ -8800,7 +8800,7 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D7" s="63" t="str">
-        <x:v>Async refresh/connect, two-Port rollback, 21 API integration, finalize</x:v>
+        <x:v>Async refresh/connect, 1~4 active-Port rollback, zero/nonzero Handle ABI integration</x:v>
       </x:c>
       <x:c r="E7" s="63" t="str">
         <x:v>M485E.IntegrationTests</x:v>
@@ -8823,7 +8823,7 @@
         <x:v>Static + CAPL Compile</x:v>
       </x:c>
       <x:c r="D8" s="63" t="str">
-        <x:v>CAPL Core wrappers, 1s/10ms pump policy, 66/33 budget, Extended CAN</x:v>
+        <x:v>CAPL Core wrappers, 별도 Context 상태 플래그, 1s/10ms pump, activePortCount 1~4, 66/33 budget, Extended CAN</x:v>
       </x:c>
       <x:c r="E8" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1 + CANalyzer 13 Exec32 caplcompexec</x:v>
@@ -8869,7 +8869,7 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D10" s="63" t="str">
-        <x:v>Win32 Debug/Release, /W4 /WX, ABI, contract, core, integration, CAPL probes</x:v>
+        <x:v>Win32 Debug/Release, /W4 /WX, ABI(zero/nonzero Handle), 1/4 Port 경계, 5 Port 거부, contract, core, integration, CAPL probes</x:v>
       </x:c>
       <x:c r="E10" s="63" t="str">
         <x:v>MSBuild + CMake + CTest + CANalyzer 13 x86 CAPL compiler</x:v>

--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rbedd41e4dcd244cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rd017401cd7274d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R695db8112d884c28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R19d986d5b7b04800"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Ra2683d5f4fbd46ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R665d7b4daa4c4b98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R0238c366d51445ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R63fa9e6352f74b5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R4db10e335ada438d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R11f3aa359ca0489d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rbfcb7f8e4f334b5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R83d6c240fa174fe0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R164520bd637f46f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="R936c2882891647b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R8614b6c61036427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="Rd7c01af7ff1e4074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R1633448f20bc415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R7b670e8196f54c53"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -840,7 +840,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>0.12</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Requirements with Design</x:v>
@@ -2433,7 +2433,7 @@
         <x:v>REQ-COM-010</x:v>
       </x:c>
       <x:c r="B55" s="9" t="str">
-        <x:v>Slave ID는 1~247만 구성 가능하고 Wire의 0, 248~255, 미등록 또는 다른 Slave 프레임에는 무응답·무적용해야 한다.</x:v>
+        <x:v>Slave ID는 1~247만 구성 가능하다. Wire Slave ID 0은 Broadcast 식별자로 예약되며 V1에서는 응답과 Write 적용을 하지 않는다. 이는 0부터 허용되는 Register Address와 무관하다. Wire 248~255, 미등록 또는 다른 Slave 프레임도 무응답·무적용해야 한다.</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
         <x:v>FS-MODBUS-001,FS-MODBUS-005</x:v>
@@ -2442,7 +2442,7 @@
         <x:v>DC-05 DeviceRegistry; DC-08 ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="E55" s="9" t="str">
-        <x:v>Broadcast·예약·미등록 주소 시험</x:v>
+        <x:v>Slave ID 0 Broadcast 무응답·무적용 및 Register Address 0 정상 처리 시험</x:v>
       </x:c>
       <x:c r="F55" s="23" t="str">
         <x:v>TC-P5-AUTO-001</x:v>
@@ -2485,7 +2485,7 @@
         <x:v>REQ-COM-012</x:v>
       </x:c>
       <x:c r="B57" s="9" t="str">
-        <x:v>수신기는 t3.5 Silence로 Frame을 구분하고 t1.5 초과의 부분 Frame을 폐기한 뒤 재동기화해야 한다.</x:v>
+        <x:v>수신기는 FC별 예상 길이와 CRC-16을 조합해 RTU Byte Stream에서 Frame을 분리해야 한다. OS Read timeout이나 Byte 수신 간격만으로 부분 Frame을 폐기하거나 Frame 경계를 결정하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
         <x:v>FS-COM-002</x:v>
@@ -2494,7 +2494,7 @@
         <x:v>DC-09 Win32SerialPort; DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E57" s="9" t="str">
-        <x:v>Partial Read, Noise, t1.5/t3.5 경계 시험</x:v>
+        <x:v>Chunk 분할·Read timeout 사이 Partial Frame 유지·Noise·CRC Sliding 재동기화 시험</x:v>
       </x:c>
       <x:c r="F57" s="23" t="str">
         <x:v>TC-P5-AUTO-001; TC-P7-AUTO-001; EV-003; EV-004</x:v>
@@ -2511,7 +2511,7 @@
         <x:v>REQ-COM-013</x:v>
       </x:c>
       <x:c r="B58" s="9" t="str">
-        <x:v>19,200bps 이하의 t1.5/t3.5는 실제 Character format으로 계산하고 초과에서는 750us/1,750us를 사용해야 한다.</x:v>
+        <x:v>19,200bps 이하의 t1.5/t3.5는 실제 Character format으로 계산하고 초과에서는 750us/1,750us를 사용해야 한다. 계산된 t3.5는 수신 경계가 아니라 응답 송신 전 Guard Time에 적용한다.</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
         <x:v>FS-COM-002</x:v>
@@ -2520,7 +2520,7 @@
         <x:v>DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E58" s="9" t="str">
-        <x:v>다양한 BaudRate/Parity/StopBits Timing 시험</x:v>
+        <x:v>다양한 BaudRate/Parity/StopBits Timing 계산 및 응답 t3.5 Guard 시험</x:v>
       </x:c>
       <x:c r="F58" s="23" t="str">
         <x:v>TC-P5-AUTO-001; TC-P7-AUTO-001; EV-003; EV-004</x:v>
@@ -4454,7 +4454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1fe41ae26354ee6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a4934a9b377434e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5722,7 +5722,7 @@
         <x:v>RTU</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
-        <x:v>Slave ID는 1~247만 구성 가능하고 Wire의 0, 248~255, 미등록 또는 다른 Slave 프레임에는 무응답·무적용해야 한다.</x:v>
+        <x:v>Slave ID는 1~247만 구성 가능하다. Wire Slave ID 0은 Broadcast 식별자로 예약되며 V1에서는 응답과 Write 적용을 하지 않는다. 이는 0부터 허용되는 Register Address와 무관하다. Wire 248~255, 미등록 또는 다른 Slave 프레임도 무응답·무적용해야 한다.</x:v>
       </x:c>
       <x:c r="D55" s="9" t="str">
         <x:v>FR-RTU-021~022</x:v>
@@ -5734,7 +5734,7 @@
         <x:v>DeviceRegistry; ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="G55" s="9" t="str">
-        <x:v>Broadcast·예약·미등록 주소 시험</x:v>
+        <x:v>Slave ID 0 Broadcast 무응답·무적용 및 Register Address 0 정상 처리 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="32" customHeight="1">
@@ -5768,7 +5768,7 @@
         <x:v>RTU</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
-        <x:v>수신기는 t3.5 Silence로 Frame을 구분하고 t1.5 초과의 부분 Frame을 폐기한 뒤 재동기화해야 한다.</x:v>
+        <x:v>수신기는 FC별 예상 길이와 CRC-16을 조합해 RTU Byte Stream에서 Frame을 분리해야 한다. OS Read timeout이나 Byte 수신 간격만으로 부분 Frame을 폐기하거나 Frame 경계를 결정하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D57" s="9" t="str">
         <x:v>FR-RTU-024~025,035; FR-PORT-021</x:v>
@@ -5780,7 +5780,7 @@
         <x:v>PortWorker; Win32SerialPort</x:v>
       </x:c>
       <x:c r="G57" s="9" t="str">
-        <x:v>Partial Read, Noise, t1.5/t3.5 경계 시험</x:v>
+        <x:v>Chunk 분할·Read timeout 사이 Partial Frame 유지·Noise·CRC Sliding 재동기화 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="32" customHeight="1">
@@ -5791,7 +5791,7 @@
         <x:v>RTU</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>19,200bps 이하의 t1.5/t3.5는 실제 Character format으로 계산하고 초과에서는 750us/1,750us를 사용해야 한다.</x:v>
+        <x:v>19,200bps 이하의 t1.5/t3.5는 실제 Character format으로 계산하고 초과에서는 750us/1,750us를 사용해야 한다. 계산된 t3.5는 수신 경계가 아니라 응답 송신 전 Guard Time에 적용한다.</x:v>
       </x:c>
       <x:c r="D58" s="9" t="str">
         <x:v>FR-RTU-025; FR-PORT-021</x:v>
@@ -5803,7 +5803,7 @@
         <x:v>PortWorker</x:v>
       </x:c>
       <x:c r="G58" s="9" t="str">
-        <x:v>다양한 BaudRate/Parity/StopBits Timing 시험</x:v>
+        <x:v>다양한 BaudRate/Parity/StopBits Timing 계산 및 응답 t3.5 Guard 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="32" customHeight="1">
@@ -7511,7 +7511,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff35aaa8d59b43d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb069f32252cd4fa1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7651,7 +7651,7 @@
         <x:v>FS-COM-002</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>RTU Stream Frame 조립</x:v>
+        <x:v>RTU Chunk/CRC Stream 조립</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
         <x:v>REQ-COM-012~013; REQ-REL-001; REQ-COMP-005</x:v>
@@ -7946,7 +7946,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dbebcbfb0a74ea5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf381a987f2e04161"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8078,7 +8078,7 @@
         <x:v>PortWorker</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>활성 PortSlot 0~3별 COM Handle 단독 소유, 1~4 Worker, t1.5/t3.5 준수, 순차 요청 처리</x:v>
+        <x:v>활성 PortSlot 0~3별 COM Handle 단독 소유, 1~4 Worker, Chunk 수신, 예상 길이·CRC Stream 조립, 응답 t3.5 Guard, 순차 요청 처리</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -8161,7 +8161,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd73799b487b24809"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cd3efc3a16841b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8299,7 +8299,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f58abfc4311463c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd43bcdc2980544c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8777,7 +8777,7 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D6" s="63" t="str">
-        <x:v>1~4 Port RTU timing/framing, partial I/O, cancellation, worker response</x:v>
+        <x:v>1~4 Port Chunk 수신, 예상 길이+CRC Stream framing, read timeout 사이 partial 유지, noise 재동기화, response t3.5 guard, cancellation, worker response</x:v>
       </x:c>
       <x:c r="E6" s="63" t="str">
         <x:v>M485E.Core.Tests + FakeSerialTransport</x:v>
@@ -8823,7 +8823,7 @@
         <x:v>Static + CAPL Compile</x:v>
       </x:c>
       <x:c r="D8" s="63" t="str">
-        <x:v>CAPL Core wrappers, 별도 Context 상태 플래그, 1s/10ms pump, activePortCount 1~4, 66/33 budget, Extended CAN</x:v>
+        <x:v>CAPL Core wrappers, 별도 Context 상태 플래그, 1s/10ms pump, activePortCount 1~4, Port별 지속 Rule Cursor와 Port round-robin, 66/33 budget, Extended CAN</x:v>
       </x:c>
       <x:c r="E8" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1 + CANalyzer 13 Exec32 caplcompexec</x:v>

--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R11f3aa359ca0489d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rbfcb7f8e4f334b5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R83d6c240fa174fe0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R164520bd637f46f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="R936c2882891647b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R8614b6c61036427f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="Rd7c01af7ff1e4074"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R1633448f20bc415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R7b670e8196f54c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rcc1feee5849b4787"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R6630cbc2bf20454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R90571d230bf549dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R2ca929215a764851"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="R147b66abb4624b2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="Rdf6c9247c39f4972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="Ref109da2075947ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R4b8f2020298a4d5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R0144399fc6194fc2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -85,7 +85,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="18">
+  <x:fills count="45">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -172,6 +172,141 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -249,7 +384,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="70">
+  <x:cellXfs count="111">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -422,6 +557,129 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="24" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="26" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="27" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="27" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="28" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="27" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="29" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="30" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="31" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="30" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="33" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="34" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="33" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="36" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="37" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="36" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="38" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="39" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="40" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="39" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="41" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="42" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="43" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="42" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="44" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -840,7 +1098,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>0.13</x:v>
+        <x:v>0.1.0</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Requirements with Design</x:v>
@@ -854,7 +1112,7 @@
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>Baseline Candidate</x:v>
+        <x:v>Release Baseline</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>Requirements with Verification</x:v>
@@ -868,13 +1126,13 @@
         <x:v>Baseline Date</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>Test Case IDs</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>후속 Test Specification에서 부여</x:v>
+        <x:v>자동·실환경 Test Case ID 부여 완료</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -902,7 +1160,7 @@
     <x:row r="13">
       <x:c r="A13" s="15" t="str">
         <x:v>사용 지침
-RTM 시트는 Requirement → Functional Specification → Design Component → Verification Method의 추적을 제공한다. 구현된 Phase는 Test Case ID와 Verification 시트에 연결하고, 미구현 Phase는 Test Case ID를 비워 둔다.</x:v>
+RTM 시트는 Requirement → Functional Specification → Design Component → Verification Method → Test Case ID/Status의 현재 Baseline 추적을 제공한다. 자동 검증 PASS와 실환경 검증 대기 상태를 구분하여 유지한다.</x:v>
       </x:c>
       <x:c r="B13" s="15" t="str">
         <x:v>사용 지침
@@ -1142,10 +1400,10 @@
         <x:v>DC-03 LifecycleController; DC-09 Win32SerialPort; DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>1/4 Port Connect와 각 active Port 실패 위치별 전체 Rollback 시험</x:v>
+        <x:v>1/4 Port Connect, 누락 active PortSlot 설정 거부, inactive stale Slot 무시 및 전체 Rollback 시험</x:v>
       </x:c>
       <x:c r="F5" s="23" t="str">
-        <x:v>TC-P8-AUTO-001</x:v>
+        <x:v>TC-P8-AUTO-001; TC-P9-STATIC-001</x:v>
       </x:c>
       <x:c r="G5" s="24" t="str">
         <x:v>Automated Verification PASS</x:v>
@@ -2095,25 +2353,25 @@
         <x:v>REQ-FUNC-041</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>수동 Register Read는 Index, StartAddress, Quantity를 사용하고 Function Code 없이 0x03/0x04 및 Map 할당 영역을 조회해야 한다.</x:v>
+        <x:v>CAPL UI와 System Variable DB는 Register Read 제어 Namespace와 Panel을 제공하지 않으며, 공개 Register Read API와 caller-owned 출력 Buffer 보호 계약은 유지해야 한다.</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
         <x:v>FS-UI-001</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>DC-06 RegisterService; DC-15 CAPL UI</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-06 RegisterService; DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
-        <x:v>Panel 수동 Read 및 실패 시 결과 유지 시험</x:v>
+        <x:v>Register Read UI Namespace·Handler 부재 정적 검사와 공개 Read API Buffer 불변 회귀 시험</x:v>
       </x:c>
       <x:c r="F42" s="23" t="str">
-        <x:v>TC-P10-STATIC-001; EV-012; EV-013; EV-016</x:v>
+        <x:v>TC-P1-AUTO-003; TC-P4-AUTO-001; TC-P10-STATIC-001</x:v>
       </x:c>
       <x:c r="G42" s="24" t="str">
-        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H42" s="9" t="str">
-        <x:v>FR-UI-001~006; IF-REG-001,004</x:v>
+        <x:v>FR-UI-008; IF-REG-016</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -2121,7 +2379,7 @@
         <x:v>REQ-FUNC-042</x:v>
       </x:c>
       <x:c r="B43" s="9" t="str">
-        <x:v>수동 Register Write는 Index, StartAddress, Quantity, word Data[]를 사용하고 Send 시점의 System Variable을 Private CAPL 요청 구조체로 Snapshot해야 한다.</x:v>
+        <x:v>수동 Register Write는 Index, StartAddress, Quantity, Data[122]를 사용하고 Send 시점의 System Variable을 Private CAPL 요청 구조체로 Snapshot해야 한다.</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
         <x:v>FS-UI-002</x:v>
@@ -2130,16 +2388,16 @@
         <x:v>DC-06 RegisterService; DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
-        <x:v>Panel 편집 중간 상태와 실행 Snapshot 분리 시험</x:v>
+        <x:v>Panel 편집 중간 상태와 Send Snapshot 분리, Quantity 1~122, 16bit 범위 및 원자 적용 시험</x:v>
       </x:c>
       <x:c r="F43" s="23" t="str">
-        <x:v>TC-P10-STATIC-001; EV-012; EV-013; EV-016</x:v>
+        <x:v>TC-P4-AUTO-001; TC-P10-STATIC-001; EV-012</x:v>
       </x:c>
       <x:c r="G43" s="24" t="str">
         <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H43" s="9" t="str">
-        <x:v>FR-UI-007~011; IF-REG-002~016</x:v>
+        <x:v>FR-UI-009~010,013; IF-REG-002~017</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -2147,7 +2405,7 @@
         <x:v>REQ-FUNC-043</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>Auto Read는 마지막으로 검증·확정된 수동 Read 요청을 1,000ms마다 반복하고 새 입력 편집값을 자동 채택하지 않아야 한다.</x:v>
+        <x:v>CAPL UI와 System Variable DB는 1,000ms 주기 Register Read Timer 및 제어값을 제공하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
         <x:v>FS-UI-001</x:v>
@@ -2156,16 +2414,16 @@
         <x:v>DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
-        <x:v>Auto Read, Send momentary 및 invalid edit 시험</x:v>
+        <x:v>주기 Register Read 제어값·Timer·Handler 부재 정적 검사</x:v>
       </x:c>
       <x:c r="F44" s="23" t="str">
-        <x:v>TC-P10-STATIC-001; EV-012; EV-013; EV-016</x:v>
+        <x:v>TC-P10-STATIC-001</x:v>
       </x:c>
       <x:c r="G44" s="24" t="str">
-        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H44" s="9" t="str">
-        <x:v>FR-UI-012~016</x:v>
+        <x:v>FR-UI-011</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -2208,7 +2466,7 @@
         <x:v>DC-09 Win32SerialPort</x:v>
       </x:c>
       <x:c r="E46" s="9" t="str">
-        <x:v>회사 환경 SystemBase Multi USB-485 통합 시험</x:v>
+        <x:v>CANalyzer 9.x SP8, SystemBase Multi USB-485 및 실제 Board 통합 시험</x:v>
       </x:c>
       <x:c r="F46" s="23" t="str">
         <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
@@ -2234,10 +2492,10 @@
         <x:v>DC-05 DeviceRegistry; DC-13 CAPL Core</x:v>
       </x:c>
       <x:c r="E47" s="9" t="str">
-        <x:v>1/4 Port 등록 성공, 중복 Port 병합, PortSlot 3 경계, 5 Port 거부 및 Routing 시험</x:v>
+        <x:v>1/4 Port·5 Port 경계, 누락 active PortSlot 거부, Routing 및 CAPL ActivePortCount와 Device CSV 고유 Port 수 일치 시험</x:v>
       </x:c>
       <x:c r="F47" s="23" t="str">
-        <x:v>TC-P7-AUTO-001; EV-003; EV-004</x:v>
+        <x:v>TC-P3-AUTO-001; TC-P8-AUTO-001; TC-P9-STATIC-001; EV-003</x:v>
       </x:c>
       <x:c r="G47" s="24" t="str">
         <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
@@ -2756,9 +3014,11 @@
       <x:c r="E67" s="9" t="str">
         <x:v>Address 0,40000,65535 경계 시험</x:v>
       </x:c>
-      <x:c r="F67" s="23"/>
+      <x:c r="F67" s="23" t="str">
+        <x:v>TC-P3-AUTO-001; TC-P4-AUTO-001; TC-P5-AUTO-001</x:v>
+      </x:c>
       <x:c r="G67" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H67" s="9" t="str">
         <x:v>DATA-005; TBD-031</x:v>
@@ -2873,7 +3133,7 @@
         <x:v>REQ-DATA-006</x:v>
       </x:c>
       <x:c r="B72" s="9" t="str">
-        <x:v>DeviceMap 정식 Header는 Index, Port, Slave_ID, Device_Name, CSV_DB_Name 순서여야 한다.</x:v>
+        <x:v>`M485E_Device.csv`(논리 FileType DeviceMap)는 Index, Port, Slave_ID, Device_Name, CSV_DB_Name Header를 사용하며 각 필드 제약을 만족해야 한다.</x:v>
       </x:c>
       <x:c r="C72" s="9" t="str">
         <x:v>FS-CSV-002,FS-DEV-001</x:v>
@@ -3560,9 +3820,11 @@
       <x:c r="E98" s="9" t="str">
         <x:v>영역별 오류와 OsError 분리 시험</x:v>
       </x:c>
-      <x:c r="F98" s="23"/>
+      <x:c r="F98" s="23" t="str">
+        <x:v>TC-P2-AUTO-003; TC-P6-AUTO-001</x:v>
+      </x:c>
       <x:c r="G98" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H98" s="9" t="str">
         <x:v>IF-CODE-005~016</x:v>
@@ -3686,7 +3948,7 @@
         <x:v>DC-08 ModbusRtuEngine; DC-10 PortWorker</x:v>
       </x:c>
       <x:c r="E103" s="9" t="str">
-        <x:v>회사 환경 실제 Timeout 기반 지연 측정</x:v>
+        <x:v>실제 Board Master Response Timeout을 기록한 뒤 Frame 완료~응답 첫 Byte 송신 시작 지연 측정</x:v>
       </x:c>
       <x:c r="F103" s="23" t="str">
         <x:v>EV-004</x:v>
@@ -4104,9 +4366,11 @@
       <x:c r="E119" s="9" t="str">
         <x:v>오류별 Write Window 출력 시험</x:v>
       </x:c>
-      <x:c r="F119" s="23"/>
+      <x:c r="F119" s="23" t="str">
+        <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001</x:v>
+      </x:c>
       <x:c r="G119" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H119" s="9" t="str">
         <x:v>LOG-004,009~010</x:v>
@@ -4126,11 +4390,13 @@
         <x:v>DC-12 DiagnosticService; DC-13 CAPL Core</x:v>
       </x:c>
       <x:c r="E120" s="9" t="str">
-        <x:v>비동기 오류 순서·병합·Overflow 출력 시험</x:v>
-      </x:c>
-      <x:c r="F120" s="23"/>
+        <x:v>Error Queue overflow·coalesce·stats 단위시험과 CAPL DropCount/OverflowLatch 변화기반 출력 정적 시험</x:v>
+      </x:c>
+      <x:c r="F120" s="23" t="str">
+        <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001</x:v>
+      </x:c>
       <x:c r="G120" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>Automated Verification PASS</x:v>
       </x:c>
       <x:c r="H120" s="9" t="str">
         <x:v>LOG-011~013</x:v>
@@ -4271,7 +4537,7 @@
         <x:v>REQ-COMP-003</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>기존 Prototype API, x64 중심 README, FC06 정상 처리와 구 문서의 설계를 호환 대상으로 유지하지 않아야 한다.</x:v>
+        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 21 API 및 현행 소스 구조를 사용해야 한다. FC 0x06은 Illegal Function으로 거부한다.</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
         <x:v>FS-INIT-001</x:v>
@@ -4280,7 +4546,7 @@
         <x:v>DC-17 Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="E126" s="9" t="str">
-        <x:v>공개 Export/문서에 Legacy 이름 부재 검토</x:v>
+        <x:v>공개 Export 21개, M485E Prefix, 현행 소스·문서 구조와 FC 0x06 거부 규칙 검사</x:v>
       </x:c>
       <x:c r="F126" s="23" t="str">
         <x:v>TC-P1-AUTO-001</x:v>
@@ -4412,9 +4678,11 @@
       <x:c r="E131" s="9" t="str">
         <x:v>보안 경계 문서 검토</x:v>
       </x:c>
-      <x:c r="F131" s="23"/>
+      <x:c r="F131" s="23" t="str">
+        <x:v>TC-P5-AUTO-001; EV-004</x:v>
+      </x:c>
       <x:c r="G131" s="24" t="str">
-        <x:v>Defined</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H131" s="9" t="str">
         <x:v>NFR-012</x:v>
@@ -4454,7 +4722,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a4934a9b377434e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55cce5d438de4a2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4584,7 +4852,7 @@
         <x:v>LifecycleController; Win32SerialPort; PortWorker</x:v>
       </x:c>
       <x:c r="G5" s="9" t="str">
-        <x:v>1/4 Port Connect와 각 active Port 실패 위치별 전체 Rollback 시험</x:v>
+        <x:v>1/4 Port Connect, 누락 active PortSlot 설정 거부, inactive stale Slot 무시 및 전체 Rollback 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
@@ -5423,19 +5691,19 @@
         <x:v>UI</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
-        <x:v>수동 Register Read는 Index, StartAddress, Quantity를 사용하고 Function Code 없이 0x03/0x04 및 Map 할당 영역을 조회해야 한다.</x:v>
+        <x:v>CAPL UI와 System Variable DB는 Register Read 제어 Namespace와 Panel을 제공하지 않으며, 공개 Register Read API와 caller-owned 출력 Buffer 보호 계약은 유지해야 한다.</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>FR-UI-001~006; IF-REG-001,004</x:v>
+        <x:v>FR-UI-008; IF-REG-016</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
         <x:v>FS-UI-001</x:v>
       </x:c>
       <x:c r="F42" s="9" t="str">
-        <x:v>CAPL UI; RegisterService</x:v>
+        <x:v>CAPL ABI Adapter; RegisterService; CAPL UI</x:v>
       </x:c>
       <x:c r="G42" s="9" t="str">
-        <x:v>Panel 수동 Read 및 실패 시 결과 유지 시험</x:v>
+        <x:v>Register Read UI Namespace·Handler 부재 정적 검사와 공개 Read API Buffer 불변 회귀 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="32" customHeight="1">
@@ -5446,10 +5714,10 @@
         <x:v>UI</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
-        <x:v>수동 Register Write는 Index, StartAddress, Quantity, word Data[]를 사용하고 Send 시점의 System Variable을 Private CAPL 요청 구조체로 Snapshot해야 한다.</x:v>
+        <x:v>수동 Register Write는 Index, StartAddress, Quantity, Data[122]를 사용하고 Send 시점의 System Variable을 Private CAPL 요청 구조체로 Snapshot해야 한다.</x:v>
       </x:c>
       <x:c r="D43" s="9" t="str">
-        <x:v>FR-UI-007~011; IF-REG-002~016</x:v>
+        <x:v>FR-UI-009~010,013; IF-REG-002~017</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
         <x:v>FS-UI-002</x:v>
@@ -5458,7 +5726,7 @@
         <x:v>CAPL UI; RegisterService</x:v>
       </x:c>
       <x:c r="G43" s="9" t="str">
-        <x:v>Panel 편집 중간 상태와 실행 Snapshot 분리 시험</x:v>
+        <x:v>Panel 편집 중간 상태와 Send Snapshot 분리, Quantity 1~122, 16bit 범위 및 원자 적용 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
@@ -5469,10 +5737,10 @@
         <x:v>UI</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
-        <x:v>Auto Read는 마지막으로 검증·확정된 수동 Read 요청을 1,000ms마다 반복하고 새 입력 편집값을 자동 채택하지 않아야 한다.</x:v>
+        <x:v>CAPL UI와 System Variable DB는 1,000ms 주기 Register Read Timer 및 제어값을 제공하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D44" s="9" t="str">
-        <x:v>FR-UI-012~016</x:v>
+        <x:v>FR-UI-011</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
         <x:v>FS-UI-001</x:v>
@@ -5481,7 +5749,7 @@
         <x:v>CAPL UI</x:v>
       </x:c>
       <x:c r="G44" s="9" t="str">
-        <x:v>Auto Read, Send momentary 및 invalid edit 시험</x:v>
+        <x:v>주기 Register Read 제어값·Timer·Handler 부재 정적 검사</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="32" customHeight="1">
@@ -5527,7 +5795,7 @@
         <x:v>Win32SerialPort</x:v>
       </x:c>
       <x:c r="G46" s="9" t="str">
-        <x:v>회사 환경 SystemBase Multi USB-485 통합 시험</x:v>
+        <x:v>CANalyzer 9.x SP8, SystemBase Multi USB-485 및 실제 Board 통합 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="32" customHeight="1">
@@ -5550,7 +5818,7 @@
         <x:v>DeviceRegistry; CAPL Core</x:v>
       </x:c>
       <x:c r="G47" s="9" t="str">
-        <x:v>1/4 Port 등록 성공, 중복 Port 병합, PortSlot 3 경계, 5 Port 거부 및 Routing 시험</x:v>
+        <x:v>1/4 Port·5 Port 경계, 누락 active PortSlot 거부, Routing 및 CAPL ActivePortCount와 Device CSV 고유 Port 수 일치 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="32" customHeight="1">
@@ -6113,7 +6381,7 @@
         <x:v>DeviceMap</x:v>
       </x:c>
       <x:c r="C72" s="9" t="str">
-        <x:v>DeviceMap 정식 Header는 Index, Port, Slave_ID, Device_Name, CSV_DB_Name 순서여야 한다.</x:v>
+        <x:v>`M485E_Device.csv`(논리 FileType DeviceMap)는 Index, Port, Slave_ID, Device_Name, CSV_DB_Name Header를 사용하며 각 필드 제약을 만족해야 한다.</x:v>
       </x:c>
       <x:c r="D72" s="9" t="str">
         <x:v>DATA-DEV-001~006</x:v>
@@ -6838,7 +7106,7 @@
         <x:v>PortWorker; ModbusRtuEngine</x:v>
       </x:c>
       <x:c r="G103" s="9" t="str">
-        <x:v>회사 환경 실제 Timeout 기반 지연 측정</x:v>
+        <x:v>실제 Board Master Response Timeout을 기록한 뒤 Frame 완료~응답 첫 Byte 송신 시작 지연 측정</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="32" customHeight="1">
@@ -7229,7 +7497,7 @@
         <x:v>CAPL Core; DiagnosticService</x:v>
       </x:c>
       <x:c r="G120" s="9" t="str">
-        <x:v>비동기 오류 순서·병합·Overflow 출력 시험</x:v>
+        <x:v>Error Queue overflow·coalesce·stats 단위시험과 CAPL DropCount/OverflowLatch 변화기반 출력 정적 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="32" customHeight="1">
@@ -7352,10 +7620,10 @@
         <x:v>REQ-COMP-003</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>Prototype</x:v>
+        <x:v>Baseline</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
-        <x:v>기존 Prototype API, x64 중심 README, FC06 정상 처리와 구 문서의 설계를 호환 대상으로 유지하지 않아야 한다.</x:v>
+        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 21 API 및 현행 소스 구조를 사용해야 한다. FC 0x06은 Illegal Function으로 거부한다.</x:v>
       </x:c>
       <x:c r="D126" s="9" t="str">
         <x:v>PRJ-005~006; COMP-009~010</x:v>
@@ -7367,7 +7635,7 @@
         <x:v>Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="G126" s="9" t="str">
-        <x:v>공개 Export/문서에 Legacy 이름 부재 검토</x:v>
+        <x:v>공개 Export 21개, M485E Prefix, 현행 소스·문서 구조와 FC 0x06 거부 규칙 검사</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="32" customHeight="1">
@@ -7511,7 +7779,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb069f32252cd4fa1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf03c0ef741604614"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7882,7 +8150,7 @@
         <x:v>FS-UI-001</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>Manual Read 및 Auto Read</x:v>
+        <x:v>Register Read UI 미제공</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
         <x:v>REQ-FUNC-040~041, REQ-FUNC-043</x:v>
@@ -7893,7 +8161,7 @@
         <x:v>FS-UI-002</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>Manual Write</x:v>
+        <x:v>Manual Write Data[122]</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
         <x:v>REQ-FUNC-040, REQ-FUNC-042</x:v>
@@ -7946,7 +8214,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf381a987f2e04161"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1bddad7c2104b35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8125,7 +8393,7 @@
         <x:v>ReadOption, 1,000ms Cycle, 10ms Pump, CAN Frame 생성</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
+    <x:row r="16" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A16" s="9" t="str">
         <x:v>DC-15</x:v>
       </x:c>
@@ -8133,10 +8401,10 @@
         <x:v>CAPL UI</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>Connect/ReadSwitch, Manual Read/Write, Signal System Variable Adapter</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
+        <x:v>Connect/ReadSwitch, Manual Write Data[122], Signal System Variable Adapter, Register Read UI 미제공, Error Queue Stats 변화기반 진단 출력</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A17" s="9" t="str">
         <x:v>DC-16</x:v>
       </x:c>
@@ -8161,7 +8429,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cd3efc3a16841b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf25e843bda5343d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8202,7 +8470,7 @@
         <x:v>Board Master Response Timeout</x:v>
       </x:c>
       <x:c r="B3" s="25" t="str">
-        <x:v>회사 환경 입력 필요</x:v>
+        <x:v>실환경 입력 필요</x:v>
       </x:c>
       <x:c r="C3" s="25" t="str">
         <x:v>실제 Timeout의 50% 기준</x:v>
@@ -8299,7 +8567,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd43bcdc2980544c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffe53bb42f79459d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8447,7 +8715,7 @@
         <x:v>M485E_Phase1_AbiProbe.can Measurement 실행</x:v>
       </x:c>
       <x:c r="D7" s="35" t="str">
-        <x:v>회사 CANalyzer 9.x SP8 x86</x:v>
+        <x:v>CANalyzer 9.x SP8 x86</x:v>
       </x:c>
       <x:c r="E7" s="42" t="str">
         <x:v>Pending</x:v>
@@ -8510,7 +8778,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F2" s="35" t="str">
-        <x:v>오류 코드 90개, 공개 상수 183개에서 C++/CAPL 생성</x:v>
+        <x:v>오류 코드 90개, 공개 상수 185개에서 C++/CAPL 생성</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8606,11 +8874,11 @@
       <x:c r="D7" s="35" t="str">
         <x:v>CANalyzer 13 x86</x:v>
       </x:c>
-      <x:c r="E7" s="54" t="str">
-        <x:v>Pending</x:v>
+      <x:c r="E7" s="107" t="str">
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
-        <x:v>GUI 자동화 불가; 실환경 Compile과 Write Window 확인 필요</x:v>
+        <x:v>CAPL 컴파일 경고 0개; Measurement는 실환경 검증 대상</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8624,7 +8892,7 @@
         <x:v>M485E_Phase1_AbiProbe.can + M485E_Phase2_ContractsProbe.can</x:v>
       </x:c>
       <x:c r="D8" s="35" t="str">
-        <x:v>회사 CANalyzer 9.x SP8 x86</x:v>
+        <x:v>CANalyzer 9.x SP8 x86</x:v>
       </x:c>
       <x:c r="E8" s="54" t="str">
         <x:v>Pending</x:v>
@@ -8652,29 +8920,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="60" t="str">
+      <x:c r="A1" s="108" t="str">
         <x:v>Test Case ID</x:v>
       </x:c>
-      <x:c r="B1" s="60" t="str">
+      <x:c r="B1" s="108" t="str">
         <x:v>Phase</x:v>
       </x:c>
-      <x:c r="C1" s="60" t="str">
+      <x:c r="C1" s="108" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D1" s="60" t="str">
+      <x:c r="D1" s="108" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="E1" s="60" t="str">
+      <x:c r="E1" s="108" t="str">
         <x:v>Method</x:v>
       </x:c>
-      <x:c r="F1" s="60" t="str">
+      <x:c r="F1" s="108" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="G1" s="60" t="str">
+      <x:c r="G1" s="108" t="str">
         <x:v>External Follow-up</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A2" s="63" t="str">
         <x:v>TC-P3-AUTO-001</x:v>
       </x:c>
@@ -8685,19 +8953,19 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D2" s="63" t="str">
-        <x:v>CSV parsing, schema, cross validation, 1/4 Port 경계, 5 Port 거부, file limits, atomic refresh</x:v>
+        <x:v>CSV parsing, schema, cross validation, cardinality/file limits, atomic refresh</x:v>
       </x:c>
       <x:c r="E2" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F2" s="65" t="str">
+      <x:c r="F2" s="109" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G2" s="63" t="str">
         <x:v>EV-002</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A3" s="63" t="str">
         <x:v>TC-P4-AUTO-001</x:v>
       </x:c>
@@ -8713,14 +8981,14 @@
       <x:c r="E3" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F3" s="65" t="str">
+      <x:c r="F3" s="109" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G3" s="63" t="str">
         <x:v>EV-006, EV-013</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A4" s="63" t="str">
         <x:v>TC-P5-AUTO-001</x:v>
       </x:c>
@@ -8736,14 +9004,14 @@
       <x:c r="E4" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F4" s="65" t="str">
+      <x:c r="F4" s="109" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G4" s="63" t="str">
         <x:v>EV-004~EV-007</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="63" t="str">
         <x:v>TC-P6-AUTO-001</x:v>
       </x:c>
@@ -8754,19 +9022,19 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D5" s="63" t="str">
-        <x:v>Snapshot/Error queues, immutable payload, overflow/coalesce/stats</x:v>
+        <x:v>Snapshot/Error queues, immutable payload, Error Queue overflow/coalesce/drop/stats</x:v>
       </x:c>
       <x:c r="E5" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F5" s="65" t="str">
+      <x:c r="F5" s="109" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G5" s="63" t="str">
         <x:v>EV-008~EV-010</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="63" t="str">
         <x:v>TC-P7-AUTO-001</x:v>
       </x:c>
@@ -8777,19 +9045,19 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D6" s="63" t="str">
-        <x:v>1~4 Port Chunk 수신, 예상 길이+CRC Stream framing, read timeout 사이 partial 유지, noise 재동기화, response t3.5 guard, cancellation, worker response</x:v>
+        <x:v>RTU timing/framing, partial I/O, cancellation, worker response</x:v>
       </x:c>
       <x:c r="E6" s="63" t="str">
         <x:v>M485E.Core.Tests + FakeSerialTransport</x:v>
       </x:c>
-      <x:c r="F6" s="65" t="str">
+      <x:c r="F6" s="109" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G6" s="63" t="str">
         <x:v>EV-003~EV-007, EV-014</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A7" s="63" t="str">
         <x:v>TC-P8-AUTO-001</x:v>
       </x:c>
@@ -8800,19 +9068,19 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D7" s="63" t="str">
-        <x:v>Async refresh/connect, 1~4 active-Port rollback, zero/nonzero Handle ABI integration</x:v>
+        <x:v>Async refresh/connect, 1~4 active-Port rollback, 누락 active PortSlot 거부, inactive stale Slot 무시, zero/nonzero Handle ABI integration</x:v>
       </x:c>
       <x:c r="E7" s="63" t="str">
         <x:v>M485E.IntegrationTests</x:v>
       </x:c>
-      <x:c r="F7" s="65" t="str">
+      <x:c r="F7" s="109" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G7" s="63" t="str">
         <x:v>EV-002, EV-003, EV-014, EV-015</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="66" hidden="0" customHeight="1">
       <x:c r="A8" s="63" t="str">
         <x:v>TC-P9-STATIC-001</x:v>
       </x:c>
@@ -8823,19 +9091,19 @@
         <x:v>Static + CAPL Compile</x:v>
       </x:c>
       <x:c r="D8" s="63" t="str">
-        <x:v>CAPL Core wrappers, 별도 Context 상태 플래그, 1s/10ms pump, activePortCount 1~4, Port별 지속 Rule Cursor와 Port round-robin, 66/33 budget, Extended CAN</x:v>
+        <x:v>CAPL Core wrappers, Error Queue Stats 변화기반 출력, 1s/10ms pump, ActivePortCount=Device CSV 고유 Port 수, Port별 Rule Cursor/round-robin, 66/33 budget, Extended CAN</x:v>
       </x:c>
       <x:c r="E8" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1 + CANalyzer 13 Exec32 caplcompexec</x:v>
       </x:c>
-      <x:c r="F8" s="65" t="str">
+      <x:c r="F8" s="109" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="63" t="str">
         <x:v>EV-008~EV-011, EV-016</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A9" s="63" t="str">
         <x:v>TC-P10-STATIC-001</x:v>
       </x:c>
@@ -8846,19 +9114,19 @@
         <x:v>Static</x:v>
       </x:c>
       <x:c r="D9" s="63" t="str">
-        <x:v>UI System Variable adapter, manual/auto read, write, signal control</x:v>
+        <x:v>UI System Variable adapter, Manual Write Data[122], Signal Control, Register Read UI 부재 계약</x:v>
       </x:c>
       <x:c r="E9" s="63" t="str">
-        <x:v>Test-M485ECaplSources.ps1; Main compile in configured CANalyzer environment</x:v>
-      </x:c>
-      <x:c r="F9" s="65" t="str">
+        <x:v>Test-M485ECaplSources.ps1; Main compile in configured CANalyzer project</x:v>
+      </x:c>
+      <x:c r="F9" s="110" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="G9" s="63" t="str">
         <x:v>EV-011~EV-013, EV-016</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A10" s="63" t="str">
         <x:v>TC-REG-AUTO-001</x:v>
       </x:c>
@@ -8869,19 +9137,19 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D10" s="63" t="str">
-        <x:v>Win32 Debug/Release, /W4 /WX, ABI(zero/nonzero Handle), 1/4 Port 경계, 5 Port 거부, contract, core, integration, CAPL probes</x:v>
+        <x:v>Win32 Debug/Release, /W4 /WX, ErrorCodes 90/PublicConstants 185, ABI, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
       </x:c>
       <x:c r="E10" s="63" t="str">
         <x:v>MSBuild + CMake + CTest + CANalyzer 13 x86 CAPL compiler</x:v>
       </x:c>
-      <x:c r="F10" s="65" t="str">
+      <x:c r="F10" s="109" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G10" s="63" t="str">
         <x:v>EV-001~EV-016</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="63" t="str">
         <x:v>EV-001~EV-016</x:v>
       </x:c>
@@ -8897,14 +9165,14 @@
       <x:c r="E11" s="63" t="str">
         <x:v>External Verification Guide</x:v>
       </x:c>
-      <x:c r="F11" s="67" t="str">
+      <x:c r="F11" s="110" t="str">
         <x:v>Not Tested</x:v>
       </x:c>
       <x:c r="G11" s="63" t="str">
-        <x:v>회사 환경에서 결과 기록</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>대상 실환경에서 결과 기록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A12" s="63" t="str">
         <x:v>TC-CAPL13-COMPILE-001</x:v>
       </x:c>
@@ -8920,7 +9188,7 @@
       <x:c r="E12" s="63" t="str">
         <x:v>CANalyzer 13 Exec32 caplcompexec.exe</x:v>
       </x:c>
-      <x:c r="F12" s="69" t="str">
+      <x:c r="F12" s="109" t="str">
         <x:v>PASS (warning-free)</x:v>
       </x:c>
       <x:c r="G12" s="63" t="str">

--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rcc1feee5849b4787"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R6630cbc2bf20454e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R90571d230bf549dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R2ca929215a764851"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="R147b66abb4624b2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="Rdf6c9247c39f4972"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="Ref109da2075947ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R4b8f2020298a4d5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R0144399fc6194fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rfd0f8c50f3034253"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rea0ad96742f54bae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R89e556abef8745da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R1e2049ebccd04155"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rec9461b3922544c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R3f006a2705c24fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="Rb3a293b6b3c741f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R14304b288b854a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R258ef02e09c54758"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -85,7 +85,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="45">
+  <x:fills count="48">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -307,6 +307,21 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -384,7 +399,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="111">
+  <x:cellXfs count="115">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -680,6 +695,18 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="44" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="45" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="46" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="45" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="47" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1098,7 +1125,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>0.1.0</x:v>
+        <x:v>0.2.0</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Requirements with Design</x:v>
@@ -4722,7 +4749,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55cce5d438de4a2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d8453e2e1d4478d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7779,7 +7806,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf03c0ef741604614"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38a1af94fad14d86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8214,7 +8241,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1bddad7c2104b35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad34fc44f45842c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8429,7 +8456,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf25e843bda5343d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4890030d6c7e4cd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8567,7 +8594,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffe53bb42f79459d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd104b05d5c3844ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8715,7 +8742,7 @@
         <x:v>M485E_Phase1_AbiProbe.can Measurement 실행</x:v>
       </x:c>
       <x:c r="D7" s="35" t="str">
-        <x:v>CANalyzer 9.x SP8 x86</x:v>
+        <x:v>CANalyzer 9.x SP8 x86 / CANalyzer 18 x64</x:v>
       </x:c>
       <x:c r="E7" s="42" t="str">
         <x:v>Pending</x:v>
@@ -8874,7 +8901,7 @@
       <x:c r="D7" s="35" t="str">
         <x:v>CANalyzer 13 x86</x:v>
       </x:c>
-      <x:c r="E7" s="107" t="str">
+      <x:c r="E7" s="111" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
@@ -8920,25 +8947,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="108" t="str">
+      <x:c r="A1" s="112" t="str">
         <x:v>Test Case ID</x:v>
       </x:c>
-      <x:c r="B1" s="108" t="str">
+      <x:c r="B1" s="112" t="str">
         <x:v>Phase</x:v>
       </x:c>
-      <x:c r="C1" s="108" t="str">
+      <x:c r="C1" s="112" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D1" s="108" t="str">
+      <x:c r="D1" s="112" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="E1" s="108" t="str">
+      <x:c r="E1" s="112" t="str">
         <x:v>Method</x:v>
       </x:c>
-      <x:c r="F1" s="108" t="str">
+      <x:c r="F1" s="112" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="G1" s="108" t="str">
+      <x:c r="G1" s="112" t="str">
         <x:v>External Follow-up</x:v>
       </x:c>
     </x:row>
@@ -8958,7 +8985,7 @@
       <x:c r="E2" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F2" s="109" t="str">
+      <x:c r="F2" s="113" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G2" s="63" t="str">
@@ -8981,7 +9008,7 @@
       <x:c r="E3" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F3" s="109" t="str">
+      <x:c r="F3" s="113" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G3" s="63" t="str">
@@ -9004,7 +9031,7 @@
       <x:c r="E4" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F4" s="109" t="str">
+      <x:c r="F4" s="113" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G4" s="63" t="str">
@@ -9027,7 +9054,7 @@
       <x:c r="E5" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F5" s="109" t="str">
+      <x:c r="F5" s="113" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G5" s="63" t="str">
@@ -9050,7 +9077,7 @@
       <x:c r="E6" s="63" t="str">
         <x:v>M485E.Core.Tests + FakeSerialTransport</x:v>
       </x:c>
-      <x:c r="F6" s="109" t="str">
+      <x:c r="F6" s="113" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G6" s="63" t="str">
@@ -9073,7 +9100,7 @@
       <x:c r="E7" s="63" t="str">
         <x:v>M485E.IntegrationTests</x:v>
       </x:c>
-      <x:c r="F7" s="109" t="str">
+      <x:c r="F7" s="113" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G7" s="63" t="str">
@@ -9096,7 +9123,7 @@
       <x:c r="E8" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1 + CANalyzer 13 Exec32 caplcompexec</x:v>
       </x:c>
-      <x:c r="F8" s="109" t="str">
+      <x:c r="F8" s="113" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="63" t="str">
@@ -9119,7 +9146,7 @@
       <x:c r="E9" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1; Main compile in configured CANalyzer project</x:v>
       </x:c>
-      <x:c r="F9" s="110" t="str">
+      <x:c r="F9" s="114" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="G9" s="63" t="str">
@@ -9137,12 +9164,12 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D10" s="63" t="str">
-        <x:v>Win32 Debug/Release, /W4 /WX, ErrorCodes 90/PublicConstants 185, ABI, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
+        <x:v>Windows x86/x64 Debug/Release, /W4 /WX, ErrorCodes 90/PublicConstants 185, 21 API ABI, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
       </x:c>
       <x:c r="E10" s="63" t="str">
         <x:v>MSBuild + CMake + CTest + CANalyzer 13 x86 CAPL compiler</x:v>
       </x:c>
-      <x:c r="F10" s="109" t="str">
+      <x:c r="F10" s="113" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G10" s="63" t="str">
@@ -9165,7 +9192,7 @@
       <x:c r="E11" s="63" t="str">
         <x:v>External Verification Guide</x:v>
       </x:c>
-      <x:c r="F11" s="110" t="str">
+      <x:c r="F11" s="114" t="str">
         <x:v>Not Tested</x:v>
       </x:c>
       <x:c r="G11" s="63" t="str">
@@ -9188,7 +9215,7 @@
       <x:c r="E12" s="63" t="str">
         <x:v>CANalyzer 13 Exec32 caplcompexec.exe</x:v>
       </x:c>
-      <x:c r="F12" s="109" t="str">
+      <x:c r="F12" s="113" t="str">
         <x:v>PASS (warning-free)</x:v>
       </x:c>
       <x:c r="G12" s="63" t="str">

--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rfd0f8c50f3034253"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rea0ad96742f54bae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R89e556abef8745da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R1e2049ebccd04155"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rec9461b3922544c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R3f006a2705c24fd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="Rb3a293b6b3c741f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R14304b288b854a34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R258ef02e09c54758"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R39014ef9649249b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R53c7906d3c9e446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R648d665f395c4ff7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="Rc02737205d5a4fcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rd9f3da6d3c904acb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R31210ff8ae5b4d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R638f885808034d50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R106e0f1ed718413c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R4bac2b8fb3bf4d7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.3.0 Traceability" sheetId="10" r:id="Redaa57f67f304e1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -85,7 +86,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="48">
+  <x:fills count="57">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -322,6 +323,51 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -399,7 +445,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="115">
+  <x:cellXfs count="146">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -707,6 +753,81 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="47" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="48" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="49" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="48" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="50" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="48" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="49" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="49" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="49" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="50" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="51" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="52" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="51" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="53" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="52" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="52" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="52" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="53" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="54" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="55" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="54" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="56" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="55" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="55" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="55" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="55" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="55" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="56" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1103,8 +1224,9 @@
         <x:v>Design Components</x:v>
       </x:c>
       <x:c r="E5" s="9" t="n">
-        <x:v>17</x:v>
-      </x:c>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -1117,22 +1239,24 @@
         <x:v>Requirements with FS</x:v>
       </x:c>
       <x:c r="E6" s="9" t="n">
-        <x:v>131</x:v>
-      </x:c>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>0.2.0</x:v>
+        <x:v>0.3.0</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Requirements with Design</x:v>
       </x:c>
       <x:c r="E7" s="9" t="n">
-        <x:v>131</x:v>
-      </x:c>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -1145,8 +1269,9 @@
         <x:v>Requirements with Verification</x:v>
       </x:c>
       <x:c r="E8" s="9" t="n">
-        <x:v>131</x:v>
-      </x:c>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
@@ -1167,21 +1292,22 @@
         <x:v>Normalized Requirements</x:v>
       </x:c>
       <x:c r="B10" s="9" t="n">
-        <x:v>131</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>Baseline Coverage</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>131 / 131 mapped</x:v>
-      </x:c>
+        <x:v>138 / 138 mapped</x:v>
+      </x:c>
+      <x:c r="F10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
         <x:v>Functional Specifications</x:v>
       </x:c>
       <x:c r="B11" s="9" t="n">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1291,6 +1417,231 @@
     <x:mergeCell ref="A1:H3"/>
     <x:mergeCell ref="A13:H15"/>
   </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="137" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="B1" s="137" t="str">
+        <x:v>Functional Specification</x:v>
+      </x:c>
+      <x:c r="C1" s="137" t="str">
+        <x:v>Design</x:v>
+      </x:c>
+      <x:c r="D1" s="137" t="str">
+        <x:v>Implementation</x:v>
+      </x:c>
+      <x:c r="E1" s="137" t="str">
+        <x:v>Automated Verification</x:v>
+      </x:c>
+      <x:c r="F1" s="137" t="str">
+        <x:v>External Verification</x:v>
+      </x:c>
+      <x:c r="G1" s="137" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="63" t="str">
+        <x:v>REQ-FUNC-045</x:v>
+      </x:c>
+      <x:c r="B2" s="63" t="str">
+        <x:v>FS-DEVICE-001</x:v>
+      </x:c>
+      <x:c r="C2" s="63" t="str">
+        <x:v>DC-18</x:v>
+      </x:c>
+      <x:c r="D2" s="63" t="str">
+        <x:v>Runtime device gate; ModbusRtuEngine</x:v>
+      </x:c>
+      <x:c r="E2" s="63" t="str">
+        <x:v>TC-V03-AUTO-001</x:v>
+      </x:c>
+      <x:c r="F2" s="63" t="str">
+        <x:v>EV-017</x:v>
+      </x:c>
+      <x:c r="G2" s="139" t="str">
+        <x:v>Auto PASS / External Pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="63" t="str">
+        <x:v>REQ-FUNC-046</x:v>
+      </x:c>
+      <x:c r="B3" s="63" t="str">
+        <x:v>FS-DEVICE-001</x:v>
+      </x:c>
+      <x:c r="C3" s="63" t="str">
+        <x:v>DC-18</x:v>
+      </x:c>
+      <x:c r="D3" s="63" t="str">
+        <x:v>M485E_DeviceCommunication.cin</x:v>
+      </x:c>
+      <x:c r="E3" s="63" t="str">
+        <x:v>TC-V03-AUTO-001; TC-P9-STATIC-001</x:v>
+      </x:c>
+      <x:c r="F3" s="63" t="str">
+        <x:v>EV-017</x:v>
+      </x:c>
+      <x:c r="G3" s="139" t="str">
+        <x:v>Auto PASS / External Pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="63" t="str">
+        <x:v>REQ-FUNC-047</x:v>
+      </x:c>
+      <x:c r="B4" s="63" t="str">
+        <x:v>FS-CONNECTION-LED-001</x:v>
+      </x:c>
+      <x:c r="C4" s="63" t="str">
+        <x:v>DC-15</x:v>
+      </x:c>
+      <x:c r="D4" s="63" t="str">
+        <x:v>M485E_Control.cin; M485E.vsysvar</x:v>
+      </x:c>
+      <x:c r="E4" s="63" t="str">
+        <x:v>TC-P9-STATIC-001</x:v>
+      </x:c>
+      <x:c r="F4" s="63" t="str">
+        <x:v>EV-017</x:v>
+      </x:c>
+      <x:c r="G4" s="139" t="str">
+        <x:v>Static PASS / External Pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A5" s="63" t="str">
+        <x:v>REQ-FUNC-048</x:v>
+      </x:c>
+      <x:c r="B5" s="63" t="str">
+        <x:v>FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="C5" s="63" t="str">
+        <x:v>DC-19</x:v>
+      </x:c>
+      <x:c r="D5" s="63" t="str">
+        <x:v>RtuLogQueue; PortWorker; M485E_RtuLog.cin</x:v>
+      </x:c>
+      <x:c r="E5" s="63" t="str">
+        <x:v>TC-V03-AUTO-001</x:v>
+      </x:c>
+      <x:c r="F5" s="63" t="str">
+        <x:v>EV-018</x:v>
+      </x:c>
+      <x:c r="G5" s="139" t="str">
+        <x:v>Auto PASS / External Pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="63" t="str">
+        <x:v>REQ-FUNC-049</x:v>
+      </x:c>
+      <x:c r="B6" s="63" t="str">
+        <x:v>FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="C6" s="63" t="str">
+        <x:v>DC-19</x:v>
+      </x:c>
+      <x:c r="D6" s="63" t="str">
+        <x:v>M485E_RtuLog.cin CAPL CSV writer</x:v>
+      </x:c>
+      <x:c r="E6" s="63" t="str">
+        <x:v>TC-P9-STATIC-001</x:v>
+      </x:c>
+      <x:c r="F6" s="63" t="str">
+        <x:v>EV-018</x:v>
+      </x:c>
+      <x:c r="G6" s="139" t="str">
+        <x:v>Static PASS / External Pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="63" t="str">
+        <x:v>REQ-IF-015</x:v>
+      </x:c>
+      <x:c r="B7" s="63" t="str">
+        <x:v>FS-DEVICE-001; FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="C7" s="63" t="str">
+        <x:v>DC-01; DC-18; DC-19</x:v>
+      </x:c>
+      <x:c r="D7" s="63" t="str">
+        <x:v>caplDllTable4 entries 22~26</x:v>
+      </x:c>
+      <x:c r="E7" s="63" t="str">
+        <x:v>M485E.AbiProbe; TC-REG-AUTO-001</x:v>
+      </x:c>
+      <x:c r="F7" s="63" t="str">
+        <x:v>EV-001</x:v>
+      </x:c>
+      <x:c r="G7" s="139" t="str">
+        <x:v>Auto PASS / External Pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A8" s="63" t="str">
+        <x:v>REQ-IF-016</x:v>
+      </x:c>
+      <x:c r="B8" s="63" t="str">
+        <x:v>FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="C8" s="63" t="str">
+        <x:v>DC-19</x:v>
+      </x:c>
+      <x:c r="D8" s="63" t="str">
+        <x:v>Context RtuLogQueue; caller-owned line buffer</x:v>
+      </x:c>
+      <x:c r="E8" s="63" t="str">
+        <x:v>TC-V03-AUTO-001</x:v>
+      </x:c>
+      <x:c r="F8" s="63" t="str">
+        <x:v>EV-018</x:v>
+      </x:c>
+      <x:c r="G8" s="139" t="str">
+        <x:v>Auto PASS / External Pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A9" s="63" t="str">
+        <x:v>AC-GRP-009</x:v>
+      </x:c>
+      <x:c r="B9" s="63" t="str">
+        <x:v>FS-DEVICE-001; FS-CONNECTION-LED-001; FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="C9" s="63" t="str">
+        <x:v>DC-15; DC-18~19</x:v>
+      </x:c>
+      <x:c r="D9" s="63" t="str">
+        <x:v>Device gate, status LEDs, RTU CSV pipeline</x:v>
+      </x:c>
+      <x:c r="E9" s="63" t="str">
+        <x:v>TC-V03-AUTO-001; TC-P9-STATIC-001</x:v>
+      </x:c>
+      <x:c r="F9" s="63" t="str">
+        <x:v>EV-017~EV-018</x:v>
+      </x:c>
+      <x:c r="G9" s="139" t="str">
+        <x:v>Auto PASS / External Pending</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -4564,7 +4915,7 @@
         <x:v>REQ-COMP-003</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 21 API 및 현행 소스 구조를 사용해야 한다. FC 0x06은 Illegal Function으로 거부한다.</x:v>
+        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 26 API 및 현행 소스 구조를 사용해야 한다. 기존 21개 ABI 순서는 유지하고 FC 0x06은 Illegal Function으로 거부한다.</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
         <x:v>FS-INIT-001</x:v>
@@ -4739,6 +5090,188 @@
       </x:c>
       <x:c r="H132" s="9" t="str">
         <x:v>NFR-013</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A133" s="63" t="str">
+        <x:v>REQ-FUNC-045</x:v>
+      </x:c>
+      <x:c r="B133" s="63" t="str">
+        <x:v>Device Index별 외부 Modbus RTU 통신 활성/비활성; 비활성 Index는 FC03/04/10 무응답·무변경이며 peer Device와 Direct/CAN 기능 유지</x:v>
+      </x:c>
+      <x:c r="C133" s="63" t="str">
+        <x:v>FS-DEVICE-001</x:v>
+      </x:c>
+      <x:c r="D133" s="63" t="str">
+        <x:v>DC-18 Device Communication Gate</x:v>
+      </x:c>
+      <x:c r="E133" s="63" t="str">
+        <x:v>Index gate·Broadcast 필터·peer 격리·Refresh reset</x:v>
+      </x:c>
+      <x:c r="F133" s="63" t="str">
+        <x:v>TC-V03-AUTO-001; EV-017</x:v>
+      </x:c>
+      <x:c r="G133" s="63" t="str">
+        <x:v>Automated PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H133" s="63" t="str">
+        <x:v>FR-RTU-036~039</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A134" s="63" t="str">
+        <x:v>REQ-FUNC-046</x:v>
+      </x:c>
+      <x:c r="B134" s="63" t="str">
+        <x:v>Device Index별 Unconfigured/Disabled/Disconnected/Available 상태와 AvailableLed 100ms 게시</x:v>
+      </x:c>
+      <x:c r="C134" s="63" t="str">
+        <x:v>FS-DEVICE-001</x:v>
+      </x:c>
+      <x:c r="D134" s="63" t="str">
+        <x:v>DC-18 Device Communication Gate</x:v>
+      </x:c>
+      <x:c r="E134" s="63" t="str">
+        <x:v>CAPL 상태 Polling과 배열 게시</x:v>
+      </x:c>
+      <x:c r="F134" s="63" t="str">
+        <x:v>TC-V03-AUTO-001; TC-P9-STATIC-001; EV-017</x:v>
+      </x:c>
+      <x:c r="G134" s="63" t="str">
+        <x:v>Automated PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H134" s="63" t="str">
+        <x:v>FR-UI-019~020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A135" s="63" t="str">
+        <x:v>REQ-FUNC-047</x:v>
+      </x:c>
+      <x:c r="B135" s="63" t="str">
+        <x:v>실제 Lifecycle Connected/Disconnected 상태를 서로 독립된 LED로 표시</x:v>
+      </x:c>
+      <x:c r="C135" s="63" t="str">
+        <x:v>FS-CONNECTION-LED-001</x:v>
+      </x:c>
+      <x:c r="D135" s="63" t="str">
+        <x:v>DC-15 CAPL UI</x:v>
+      </x:c>
+      <x:c r="E135" s="63" t="str">
+        <x:v>Connected/Disconnected LED 상태표</x:v>
+      </x:c>
+      <x:c r="F135" s="63" t="str">
+        <x:v>TC-P9-STATIC-001; EV-017</x:v>
+      </x:c>
+      <x:c r="G135" s="63" t="str">
+        <x:v>Static PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H135" s="63" t="str">
+        <x:v>FR-UI-016~018</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A136" s="63" t="str">
+        <x:v>REQ-FUNC-048</x:v>
+      </x:c>
+      <x:c r="B136" s="63" t="str">
+        <x:v>RTU 요청과 실제 응답 또는 무응답을 동일 Sequence의 REQ/RES 또는 REQ/NO_RES CSV 행으로 기록</x:v>
+      </x:c>
+      <x:c r="C136" s="63" t="str">
+        <x:v>FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="D136" s="63" t="str">
+        <x:v>DC-19 RTU Log Pipeline</x:v>
+      </x:c>
+      <x:c r="E136" s="63" t="str">
+        <x:v>Transaction pair·overflow·send result</x:v>
+      </x:c>
+      <x:c r="F136" s="63" t="str">
+        <x:v>TC-V03-AUTO-001; EV-018</x:v>
+      </x:c>
+      <x:c r="G136" s="63" t="str">
+        <x:v>Automated PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H136" s="63" t="str">
+        <x:v>LOG-018~024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A137" s="63" t="str">
+        <x:v>REQ-FUNC-049</x:v>
+      </x:c>
+      <x:c r="B137" s="63" t="str">
+        <x:v>RTU Log OFF→ON마다 새 Timestamp 파일을 만들고 CAPL만 파일 I/O 수행</x:v>
+      </x:c>
+      <x:c r="C137" s="63" t="str">
+        <x:v>FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="D137" s="63" t="str">
+        <x:v>DC-19 RTU Log Pipeline</x:v>
+      </x:c>
+      <x:c r="E137" s="63" t="str">
+        <x:v>CAPL file lifecycle·naming·drain</x:v>
+      </x:c>
+      <x:c r="F137" s="63" t="str">
+        <x:v>TC-P9-STATIC-001; EV-018</x:v>
+      </x:c>
+      <x:c r="G137" s="63" t="str">
+        <x:v>Static PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H137" s="63" t="str">
+        <x:v>FR-UI-021; LOG-022~024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A138" s="63" t="str">
+        <x:v>REQ-IF-015</x:v>
+      </x:c>
+      <x:c r="B138" s="63" t="str">
+        <x:v>기존 21개 Entry 순서를 유지하고 Device 통신 2개와 RTU Log 3개 API를 22~26번에 추가</x:v>
+      </x:c>
+      <x:c r="C138" s="63" t="str">
+        <x:v>FS-DEVICE-001; FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="D138" s="63" t="str">
+        <x:v>DC-01; DC-18; DC-19</x:v>
+      </x:c>
+      <x:c r="E138" s="63" t="str">
+        <x:v>26-entry x86/x64 ABI table</x:v>
+      </x:c>
+      <x:c r="F138" s="63" t="str">
+        <x:v>M485E.AbiProbe; TC-REG-AUTO-001; EV-001</x:v>
+      </x:c>
+      <x:c r="G138" s="63" t="str">
+        <x:v>Automated PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H138" s="63" t="str">
+        <x:v>IF-API-022~026; COMP-009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A139" s="63" t="str">
+        <x:v>REQ-IF-016</x:v>
+      </x:c>
+      <x:c r="B139" s="63" t="str">
+        <x:v>Context별 완결 Transaction 256개와 caller-owned RTU CSV line Buffer; DLL 파일 I/O 금지</x:v>
+      </x:c>
+      <x:c r="C139" s="63" t="str">
+        <x:v>FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="D139" s="63" t="str">
+        <x:v>DC-19 RTU Log Pipeline</x:v>
+      </x:c>
+      <x:c r="E139" s="63" t="str">
+        <x:v>Capacity/caller-owned buffer/file boundary</x:v>
+      </x:c>
+      <x:c r="F139" s="63" t="str">
+        <x:v>TC-V03-AUTO-001; EV-018</x:v>
+      </x:c>
+      <x:c r="G139" s="63" t="str">
+        <x:v>Automated PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H139" s="63" t="str">
+        <x:v>IF-LIMIT-009; LOG-023~024</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4749,7 +5282,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d8453e2e1d4478d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7be832f1e2c4e83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7650,7 +8183,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
-        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 21 API 및 현행 소스 구조를 사용해야 한다. FC 0x06은 Illegal Function으로 거부한다.</x:v>
+        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 26 API 및 현행 소스 구조를 사용해야 한다. 기존 21개 ABI 순서는 유지하고 FC 0x06은 Illegal Function으로 거부한다.</x:v>
       </x:c>
       <x:c r="D126" s="9" t="str">
         <x:v>PRJ-005~006; COMP-009~010</x:v>
@@ -7803,10 +8336,171 @@
         <x:v>ASCII/한글 경로·Text round-trip 시험</x:v>
       </x:c>
     </x:row>
+    <x:row r="133" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A133" s="63" t="str">
+        <x:v>REQ-FUNC-045</x:v>
+      </x:c>
+      <x:c r="B133" s="63" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="C133" s="63" t="str">
+        <x:v>Device Index별 외부 Modbus RTU 통신 활성/비활성; 비활성 Index는 FC03/04/10 무응답·무변경이며 peer Device와 Direct/CAN 기능 유지</x:v>
+      </x:c>
+      <x:c r="D133" s="63" t="str">
+        <x:v>FR-RTU-036~039</x:v>
+      </x:c>
+      <x:c r="E133" s="63" t="str">
+        <x:v>FS-DEVICE-001</x:v>
+      </x:c>
+      <x:c r="F133" s="63" t="str">
+        <x:v>DC-18</x:v>
+      </x:c>
+      <x:c r="G133" s="63" t="str">
+        <x:v>Index gate·Broadcast 필터·peer 격리·Refresh reset 자동 시험과 EV-017</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A134" s="63" t="str">
+        <x:v>REQ-FUNC-046</x:v>
+      </x:c>
+      <x:c r="B134" s="63" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="C134" s="63" t="str">
+        <x:v>Device Index별 Unconfigured/Disabled/Disconnected/Available 상태와 AvailableLed 100ms 게시</x:v>
+      </x:c>
+      <x:c r="D134" s="63" t="str">
+        <x:v>FR-UI-019~020</x:v>
+      </x:c>
+      <x:c r="E134" s="63" t="str">
+        <x:v>FS-DEVICE-001</x:v>
+      </x:c>
+      <x:c r="F134" s="63" t="str">
+        <x:v>DC-18</x:v>
+      </x:c>
+      <x:c r="G134" s="63" t="str">
+        <x:v>CAPL source contract와 EV-017</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="15" hidden="0" customHeight="1">
+      <x:c r="A135" s="63" t="str">
+        <x:v>REQ-FUNC-047</x:v>
+      </x:c>
+      <x:c r="B135" s="63" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="C135" s="63" t="str">
+        <x:v>실제 Lifecycle Connected/Disconnected 상태를 서로 독립된 LED로 표시</x:v>
+      </x:c>
+      <x:c r="D135" s="63" t="str">
+        <x:v>FR-UI-016~018</x:v>
+      </x:c>
+      <x:c r="E135" s="63" t="str">
+        <x:v>FS-CONNECTION-LED-001</x:v>
+      </x:c>
+      <x:c r="F135" s="63" t="str">
+        <x:v>DC-15</x:v>
+      </x:c>
+      <x:c r="G135" s="63" t="str">
+        <x:v>CAPL source contract와 EV-017</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A136" s="63" t="str">
+        <x:v>REQ-FUNC-048</x:v>
+      </x:c>
+      <x:c r="B136" s="63" t="str">
+        <x:v>Diagnostics</x:v>
+      </x:c>
+      <x:c r="C136" s="63" t="str">
+        <x:v>RTU 요청과 실제 응답 또는 무응답을 동일 Sequence의 REQ/RES 또는 REQ/NO_RES CSV 행으로 기록</x:v>
+      </x:c>
+      <x:c r="D136" s="63" t="str">
+        <x:v>LOG-018~024</x:v>
+      </x:c>
+      <x:c r="E136" s="63" t="str">
+        <x:v>FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="F136" s="63" t="str">
+        <x:v>DC-19</x:v>
+      </x:c>
+      <x:c r="G136" s="63" t="str">
+        <x:v>RtuLogQueue/PortWorker 자동 시험과 EV-018</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A137" s="63" t="str">
+        <x:v>REQ-FUNC-049</x:v>
+      </x:c>
+      <x:c r="B137" s="63" t="str">
+        <x:v>Diagnostics</x:v>
+      </x:c>
+      <x:c r="C137" s="63" t="str">
+        <x:v>RTU Log OFF→ON마다 새 Timestamp 파일을 만들고 CAPL만 파일 I/O 수행</x:v>
+      </x:c>
+      <x:c r="D137" s="63" t="str">
+        <x:v>FR-UI-021; LOG-022~024</x:v>
+      </x:c>
+      <x:c r="E137" s="63" t="str">
+        <x:v>FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="F137" s="63" t="str">
+        <x:v>DC-19</x:v>
+      </x:c>
+      <x:c r="G137" s="63" t="str">
+        <x:v>CAPL source contract와 EV-018</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A138" s="63" t="str">
+        <x:v>REQ-IF-015</x:v>
+      </x:c>
+      <x:c r="B138" s="63" t="str">
+        <x:v>API</x:v>
+      </x:c>
+      <x:c r="C138" s="63" t="str">
+        <x:v>기존 21개 Entry 순서를 유지하고 Device 통신 2개와 RTU Log 3개 API를 22~26번에 추가</x:v>
+      </x:c>
+      <x:c r="D138" s="63" t="str">
+        <x:v>IF-API-022~026; COMP-009</x:v>
+      </x:c>
+      <x:c r="E138" s="63" t="str">
+        <x:v>FS-DEVICE-001; FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="F138" s="63" t="str">
+        <x:v>DC-01; DC-18; DC-19</x:v>
+      </x:c>
+      <x:c r="G138" s="63" t="str">
+        <x:v>x86/x64 ABI Probe와 EV-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A139" s="63" t="str">
+        <x:v>REQ-IF-016</x:v>
+      </x:c>
+      <x:c r="B139" s="63" t="str">
+        <x:v>Buffer</x:v>
+      </x:c>
+      <x:c r="C139" s="63" t="str">
+        <x:v>Context별 완결 Transaction 256개와 caller-owned RTU CSV line Buffer; DLL 파일 I/O 금지</x:v>
+      </x:c>
+      <x:c r="D139" s="63" t="str">
+        <x:v>IF-LIMIT-009; LOG-023~024</x:v>
+      </x:c>
+      <x:c r="E139" s="63" t="str">
+        <x:v>FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="F139" s="63" t="str">
+        <x:v>DC-19</x:v>
+      </x:c>
+      <x:c r="G139" s="63" t="str">
+        <x:v>Queue 경계·overflow·pair 보존 자동 시험과 EV-018</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38a1af94fad14d86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f57d8b20c4d4863"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8238,10 +8932,43 @@
         <x:v>REQ-FUNC-008; REQ-PERF-006; REQ-REL-003; REQ-RES-002</x:v>
       </x:c>
     </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="63" t="str">
+        <x:v>FS-DEVICE-001</x:v>
+      </x:c>
+      <x:c r="B39" s="63" t="str">
+        <x:v>Index별 RTU 통신 제어</x:v>
+      </x:c>
+      <x:c r="C39" s="63" t="str">
+        <x:v>REQ-FUNC-045~046; REQ-IF-015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
+      <x:c r="A40" s="63" t="str">
+        <x:v>FS-CONNECTION-LED-001</x:v>
+      </x:c>
+      <x:c r="B40" s="63" t="str">
+        <x:v>Connected/Disconnected 실제 상태 표시</x:v>
+      </x:c>
+      <x:c r="C40" s="63" t="str">
+        <x:v>REQ-FUNC-047</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
+      <x:c r="A41" s="63" t="str">
+        <x:v>FS-RTULOG-001</x:v>
+      </x:c>
+      <x:c r="B41" s="63" t="str">
+        <x:v>RTU 요청·응답 CSV 기록</x:v>
+      </x:c>
+      <x:c r="C41" s="63" t="str">
+        <x:v>REQ-FUNC-048~049; REQ-IF-015~016</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad34fc44f45842c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc906e431b6c3471b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8274,7 +9001,7 @@
         <x:v>CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>CAPL_DLL_INFO4, __stdcall, 불투명 Context Handle(0 포함), Length/Capacity 검증, 21개 Export</x:v>
+        <x:v>CAPL_DLL_INFO4, __stdcall, 불투명 Context Handle(0 포함), Length/Capacity 검증, caller-owned 출력 보호, Signal F[1] 저수준 출력, 생산 26개 Export(기존 21개 순서 유지)</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -8453,10 +9180,32 @@
         <x:v>Win32/x86 빌드, Vector SDK 경로 주입, 배포 패키지 구조 및 후속 x64 경계 관리</x:v>
       </x:c>
     </x:row>
+    <x:row r="19" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A19" s="63" t="str">
+        <x:v>DC-18</x:v>
+      </x:c>
+      <x:c r="B19" s="63" t="str">
+        <x:v>Device Communication Gate</x:v>
+      </x:c>
+      <x:c r="C19" s="63" t="str">
+        <x:v>Index별 RTU 활성 상태, addressed 요청 사전 차단, Broadcast 대상 필터와 상태 Snapshot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A20" s="63" t="str">
+        <x:v>DC-19</x:v>
+      </x:c>
+      <x:c r="B20" s="63" t="str">
+        <x:v>RTU Log Pipeline</x:v>
+      </x:c>
+      <x:c r="C20" s="63" t="str">
+        <x:v>PortWorker 관측점, Transaction Queue, REQ/RES·NO_RES pairing과 CAPL-only CSV Writer</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4890030d6c7e4cd5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14a9a2f4e17141a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8489,7 +9238,7 @@
         <x:v>자동 검증 PASS / CANalyzer 9.x 실환경 대기</x:v>
       </x:c>
       <x:c r="C2" s="25" t="str">
-        <x:v>생산 21 API + 시험 전용 ABI Fixture 자동 Probe 후 CANalyzer 9.x SP8 측정 실행</x:v>
+        <x:v>생산 26 API + 시험 전용 ABI Fixture 자동 Probe 후 CANalyzer 9.x SP8 측정 실행</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
@@ -8563,7 +9312,7 @@
         <x:v>External Test Result</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>16건 Not Tested</x:v>
+        <x:v>18건 Not Tested</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx</x:v>
@@ -8594,7 +9343,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd104b05d5c3844ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08901678363f4cb2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8636,7 +9385,7 @@
         <x:v>TC-P1-AUTO-001</x:v>
       </x:c>
       <x:c r="B2" s="35" t="str">
-        <x:v>Win32 빌드와 생산 CAPL Table 21 API</x:v>
+        <x:v>Win32 빌드와 생산 CAPL Table 26 API</x:v>
       </x:c>
       <x:c r="C2" s="35" t="str">
         <x:v>MSBuild Debug/Release, CMake Release, dumpbin 및 ABI 메타데이터 검사</x:v>
@@ -8648,7 +9397,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F2" s="35" t="str">
-        <x:v>x86(14C), 생산 API 정확히 21개, caplDllTable4 확인</x:v>
+        <x:v>x86(14C), 생산 API 정확히 26개, caplDllTable4 확인</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -8688,7 +9437,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F4" s="35" t="str">
-        <x:v>작은 Capacity, Embedded NUL, 길이 불일치, 실패 시 caller-owned 출력 보존</x:v>
+        <x:v>시험 Fixture는 생산 26개 API와 분리</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -8805,7 +9554,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F2" s="35" t="str">
-        <x:v>오류 코드 90개, 공개 상수 185개에서 C++/CAPL 생성</x:v>
+        <x:v>오류 코드 92개, 공개 상수 207개에서 C++/CAPL 생성</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8901,7 +9650,7 @@
       <x:c r="D7" s="35" t="str">
         <x:v>CANalyzer 13 x86</x:v>
       </x:c>
-      <x:c r="E7" s="111" t="str">
+      <x:c r="E7" s="136" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
@@ -8947,25 +9696,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="112" t="str">
+      <x:c r="A1" s="137" t="str">
         <x:v>Test Case ID</x:v>
       </x:c>
-      <x:c r="B1" s="112" t="str">
+      <x:c r="B1" s="137" t="str">
         <x:v>Phase</x:v>
       </x:c>
-      <x:c r="C1" s="112" t="str">
+      <x:c r="C1" s="137" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D1" s="112" t="str">
+      <x:c r="D1" s="137" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="E1" s="112" t="str">
+      <x:c r="E1" s="137" t="str">
         <x:v>Method</x:v>
       </x:c>
-      <x:c r="F1" s="112" t="str">
+      <x:c r="F1" s="137" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="G1" s="112" t="str">
+      <x:c r="G1" s="137" t="str">
         <x:v>External Follow-up</x:v>
       </x:c>
     </x:row>
@@ -8985,7 +9734,7 @@
       <x:c r="E2" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F2" s="113" t="str">
+      <x:c r="F2" s="138" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G2" s="63" t="str">
@@ -9008,7 +9757,7 @@
       <x:c r="E3" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F3" s="113" t="str">
+      <x:c r="F3" s="138" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G3" s="63" t="str">
@@ -9031,7 +9780,7 @@
       <x:c r="E4" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F4" s="113" t="str">
+      <x:c r="F4" s="138" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G4" s="63" t="str">
@@ -9054,7 +9803,7 @@
       <x:c r="E5" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F5" s="113" t="str">
+      <x:c r="F5" s="138" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G5" s="63" t="str">
@@ -9077,7 +9826,7 @@
       <x:c r="E6" s="63" t="str">
         <x:v>M485E.Core.Tests + FakeSerialTransport</x:v>
       </x:c>
-      <x:c r="F6" s="113" t="str">
+      <x:c r="F6" s="138" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G6" s="63" t="str">
@@ -9100,7 +9849,7 @@
       <x:c r="E7" s="63" t="str">
         <x:v>M485E.IntegrationTests</x:v>
       </x:c>
-      <x:c r="F7" s="113" t="str">
+      <x:c r="F7" s="138" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G7" s="63" t="str">
@@ -9123,7 +9872,7 @@
       <x:c r="E8" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1 + CANalyzer 13 Exec32 caplcompexec</x:v>
       </x:c>
-      <x:c r="F8" s="113" t="str">
+      <x:c r="F8" s="138" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="63" t="str">
@@ -9146,7 +9895,7 @@
       <x:c r="E9" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1; Main compile in configured CANalyzer project</x:v>
       </x:c>
-      <x:c r="F9" s="114" t="str">
+      <x:c r="F9" s="139" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="G9" s="63" t="str">
@@ -9164,61 +9913,84 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D10" s="63" t="str">
-        <x:v>Windows x86/x64 Debug/Release, /W4 /WX, ErrorCodes 90/PublicConstants 185, 21 API ABI, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
+        <x:v>Windows x86/x64 Debug/Release, /W4 /WX, ErrorCodes 92/PublicConstants 207, 26 API ABI, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
       </x:c>
       <x:c r="E10" s="63" t="str">
         <x:v>MSBuild + CMake + CTest + CANalyzer 13 x86 CAPL compiler</x:v>
       </x:c>
-      <x:c r="F10" s="113" t="str">
+      <x:c r="F10" s="138" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G10" s="63" t="str">
-        <x:v>EV-001~EV-016</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>EV-001~EV-018</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A11" s="63" t="str">
-        <x:v>EV-001~EV-016</x:v>
+        <x:v>TC-V03-AUTO-001</x:v>
       </x:c>
       <x:c r="B11" s="63" t="str">
+        <x:v>5/7/10</x:v>
+      </x:c>
+      <x:c r="C11" s="63" t="str">
+        <x:v>Automated + Static</x:v>
+      </x:c>
+      <x:c r="D11" s="63" t="str">
+        <x:v>Index별 RTU 비활성화, Broadcast 제외, RTU Log REQ/RES/NO_RES pairing, queue overflow, CAPL Device/Log adapters</x:v>
+      </x:c>
+      <x:c r="E11" s="63" t="str">
+        <x:v>M485E.Core.Tests + M485E.IntegrationTests + Test-M485ECaplSources.ps1</x:v>
+      </x:c>
+      <x:c r="F11" s="139" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G11" s="63" t="str">
+        <x:v>EV-017~EV-018</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A12" s="63" t="str">
+        <x:v>EV-001~EV-018</x:v>
+      </x:c>
+      <x:c r="B12" s="63" t="str">
         <x:v>External</x:v>
       </x:c>
-      <x:c r="C11" s="63" t="str">
+      <x:c r="C12" s="63" t="str">
         <x:v>External</x:v>
       </x:c>
-      <x:c r="D11" s="63" t="str">
-        <x:v>CANalyzer 9.x, SystemBase Multi USB-485, Board, Panel, virtual CAN, stress</x:v>
-      </x:c>
-      <x:c r="E11" s="63" t="str">
+      <x:c r="D12" s="63" t="str">
+        <x:v>CANalyzer 9.x/18, SystemBase Multi USB-485, Board, Panel, virtual CAN, RTU CSV</x:v>
+      </x:c>
+      <x:c r="E12" s="63" t="str">
         <x:v>External Verification Guide</x:v>
       </x:c>
-      <x:c r="F11" s="114" t="str">
+      <x:c r="F12" s="138" t="str">
         <x:v>Not Tested</x:v>
       </x:c>
-      <x:c r="G11" s="63" t="str">
+      <x:c r="G12" s="63" t="str">
         <x:v>대상 실환경에서 결과 기록</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A12" s="63" t="str">
+    <x:row r="13" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A13" s="63" t="str">
         <x:v>TC-CAPL13-COMPILE-001</x:v>
       </x:c>
-      <x:c r="B12" s="63" t="str">
+      <x:c r="B13" s="63" t="str">
         <x:v>1/2/9</x:v>
       </x:c>
-      <x:c r="C12" s="63" t="str">
+      <x:c r="C13" s="63" t="str">
         <x:v>Compiler</x:v>
       </x:c>
-      <x:c r="D12" s="63" t="str">
+      <x:c r="D13" s="63" t="str">
         <x:v>Phase 1 ABI, Phase 2 Contracts, Phase 9 Core/Monitoring CAPL probes</x:v>
       </x:c>
-      <x:c r="E12" s="63" t="str">
+      <x:c r="E13" s="63" t="str">
         <x:v>CANalyzer 13 Exec32 caplcompexec.exe</x:v>
       </x:c>
-      <x:c r="F12" s="113" t="str">
+      <x:c r="F13" s="138" t="str">
         <x:v>PASS (warning-free)</x:v>
       </x:c>
-      <x:c r="G12" s="63" t="str">
+      <x:c r="G13" s="63" t="str">
         <x:v>CANalyzer 9.x SP8 Compile/Measurement remains EV-001</x:v>
       </x:c>
     </x:row>

--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R39014ef9649249b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R53c7906d3c9e446f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R648d665f395c4ff7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="Rc02737205d5a4fcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rd9f3da6d3c904acb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R31210ff8ae5b4d85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R638f885808034d50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R106e0f1ed718413c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R4bac2b8fb3bf4d7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.3.0 Traceability" sheetId="10" r:id="Redaa57f67f304e1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rf7fc1b0405224edf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Re5bd85c9c315407b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="Rb4ec22fbc3b74cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="Rb9f897399d3541be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rcdee6e1838424645"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R984ab5dc08be4db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="Rf54521df11494da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="Rcb8a825d3da241e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R6133a757acd74a71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.3.0 Traceability" sheetId="10" r:id="R0338c9bcc65a4dd5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -86,7 +86,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="57">
+  <x:fills count="66">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -368,6 +368,51 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -445,7 +490,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="146">
+  <x:cellXfs count="176">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -828,6 +873,78 @@
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="56" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="57" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="58" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="57" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="59" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="58" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="58" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="58" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="59" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="60" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="61" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="60" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="62" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="61" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="61" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="61" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="61" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="61" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="62" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="63" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="64" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="63" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="65" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="64" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="64" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="64" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="65" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1278,7 +1395,7 @@
         <x:v>Baseline Date</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>Test Case IDs</x:v>
@@ -1435,25 +1552,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="137" t="str">
+      <x:c r="A1" s="167" t="str">
         <x:v>Requirement</x:v>
       </x:c>
-      <x:c r="B1" s="137" t="str">
+      <x:c r="B1" s="167" t="str">
         <x:v>Functional Specification</x:v>
       </x:c>
-      <x:c r="C1" s="137" t="str">
+      <x:c r="C1" s="167" t="str">
         <x:v>Design</x:v>
       </x:c>
-      <x:c r="D1" s="137" t="str">
+      <x:c r="D1" s="167" t="str">
         <x:v>Implementation</x:v>
       </x:c>
-      <x:c r="E1" s="137" t="str">
+      <x:c r="E1" s="167" t="str">
         <x:v>Automated Verification</x:v>
       </x:c>
-      <x:c r="F1" s="137" t="str">
+      <x:c r="F1" s="167" t="str">
         <x:v>External Verification</x:v>
       </x:c>
-      <x:c r="G1" s="137" t="str">
+      <x:c r="G1" s="167" t="str">
         <x:v>Status</x:v>
       </x:c>
     </x:row>
@@ -1476,7 +1593,7 @@
       <x:c r="F2" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G2" s="139" t="str">
+      <x:c r="G2" s="169" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1499,7 +1616,7 @@
       <x:c r="F3" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G3" s="139" t="str">
+      <x:c r="G3" s="169" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1522,7 +1639,7 @@
       <x:c r="F4" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G4" s="139" t="str">
+      <x:c r="G4" s="169" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1545,11 +1662,11 @@
       <x:c r="F5" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G5" s="139" t="str">
+      <x:c r="G5" s="169" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="63" t="str">
         <x:v>REQ-FUNC-049</x:v>
       </x:c>
@@ -1560,16 +1677,16 @@
         <x:v>DC-19</x:v>
       </x:c>
       <x:c r="D6" s="63" t="str">
-        <x:v>M485E_RtuLog.cin CAPL CSV writer</x:v>
+        <x:v>M485E_RtuLog.cin CAPL CSV writer; M485E_Dll_WaitRtuLogIdle</x:v>
       </x:c>
       <x:c r="E6" s="63" t="str">
-        <x:v>TC-P9-STATIC-001</x:v>
+        <x:v>TC-V03-AUTO-001; TC-P9-STATIC-001</x:v>
       </x:c>
       <x:c r="F6" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G6" s="139" t="str">
-        <x:v>Static PASS / External Pending</x:v>
+      <x:c r="G6" s="169" t="str">
+        <x:v>Auto/Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -1583,7 +1700,7 @@
         <x:v>DC-01; DC-18; DC-19</x:v>
       </x:c>
       <x:c r="D7" s="63" t="str">
-        <x:v>caplDllTable4 entries 22~26</x:v>
+        <x:v>caplDllTable4 entries 22~27</x:v>
       </x:c>
       <x:c r="E7" s="63" t="str">
         <x:v>M485E.AbiProbe; TC-REG-AUTO-001</x:v>
@@ -1591,7 +1708,7 @@
       <x:c r="F7" s="63" t="str">
         <x:v>EV-001</x:v>
       </x:c>
-      <x:c r="G7" s="139" t="str">
+      <x:c r="G7" s="169" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1606,16 +1723,16 @@
         <x:v>DC-19</x:v>
       </x:c>
       <x:c r="D8" s="63" t="str">
-        <x:v>Context RtuLogQueue; caller-owned line buffer</x:v>
+        <x:v>Context RtuLogQueue; caller-owned line buffer; capture-disabled idle wait</x:v>
       </x:c>
       <x:c r="E8" s="63" t="str">
-        <x:v>TC-V03-AUTO-001</x:v>
+        <x:v>TC-V03-AUTO-001; TC-P9-STATIC-001</x:v>
       </x:c>
       <x:c r="F8" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G8" s="139" t="str">
-        <x:v>Auto PASS / External Pending</x:v>
+      <x:c r="G8" s="169" t="str">
+        <x:v>Auto/Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -1637,7 +1754,7 @@
       <x:c r="F9" s="63" t="str">
         <x:v>EV-017~EV-018</x:v>
       </x:c>
-      <x:c r="G9" s="139" t="str">
+      <x:c r="G9" s="169" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -4915,7 +5032,7 @@
         <x:v>REQ-COMP-003</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 26 API 및 현행 소스 구조를 사용해야 한다. 기존 21개 ABI 순서는 유지하고 FC 0x06은 Illegal Function으로 거부한다.</x:v>
+        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 27 API 및 현행 소스 구조를 사용해야 한다. 기존 21개 ABI 순서는 유지하고 FC 0x06은 Illegal Function으로 거부한다.</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
         <x:v>FS-INIT-001</x:v>
@@ -4924,7 +5041,7 @@
         <x:v>DC-17 Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="E126" s="9" t="str">
-        <x:v>공개 Export 21개, M485E Prefix, 현행 소스·문서 구조와 FC 0x06 거부 규칙 검사</x:v>
+        <x:v>전체 공개 Export 27개와 기존 21개 순서, M485E Prefix, 현행 소스·문서 구조 및 FC 0x06 거부 규칙 검사</x:v>
       </x:c>
       <x:c r="F126" s="23" t="str">
         <x:v>TC-P1-AUTO-001</x:v>
@@ -5196,12 +5313,12 @@
         <x:v>LOG-018~024</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="137" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A137" s="63" t="str">
         <x:v>REQ-FUNC-049</x:v>
       </x:c>
       <x:c r="B137" s="63" t="str">
-        <x:v>RTU Log OFF→ON마다 새 Timestamp 파일을 만들고 CAPL만 파일 I/O 수행</x:v>
+        <x:v>RTU Log 파일 Open 성공 후 Capture를 시작하고, OFF·종료 시 최대 2,000ms Idle 대기 후 완료 행을 배출</x:v>
       </x:c>
       <x:c r="C137" s="63" t="str">
         <x:v>FS-RTULOG-001</x:v>
@@ -5210,16 +5327,16 @@
         <x:v>DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E137" s="63" t="str">
-        <x:v>CAPL file lifecycle·naming·drain</x:v>
+        <x:v>Open-before-capture·2,000ms idle wait·drain</x:v>
       </x:c>
       <x:c r="F137" s="63" t="str">
-        <x:v>TC-P9-STATIC-001; EV-018</x:v>
+        <x:v>TC-V03-AUTO-001; TC-P9-STATIC-001; EV-018</x:v>
       </x:c>
       <x:c r="G137" s="63" t="str">
-        <x:v>Static PASS / External Pending</x:v>
+        <x:v>Automated/Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="H137" s="63" t="str">
-        <x:v>FR-UI-021; LOG-022~024</x:v>
+        <x:v>FR-UI-021; LOG-022~024; ERR-044</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -5227,7 +5344,7 @@
         <x:v>REQ-IF-015</x:v>
       </x:c>
       <x:c r="B138" s="63" t="str">
-        <x:v>기존 21개 Entry 순서를 유지하고 Device 통신 2개와 RTU Log 3개 API를 22~26번에 추가</x:v>
+        <x:v>기존 21개 Entry 순서를 유지하고 Device 통신 2개와 RTU Log 4개 API를 22~27번에 추가</x:v>
       </x:c>
       <x:c r="C138" s="63" t="str">
         <x:v>FS-DEVICE-001; FS-RTULOG-001</x:v>
@@ -5236,7 +5353,7 @@
         <x:v>DC-01; DC-18; DC-19</x:v>
       </x:c>
       <x:c r="E138" s="63" t="str">
-        <x:v>26-entry x86/x64 ABI table</x:v>
+        <x:v>27-entry x86/x64 ABI table</x:v>
       </x:c>
       <x:c r="F138" s="63" t="str">
         <x:v>M485E.AbiProbe; TC-REG-AUTO-001; EV-001</x:v>
@@ -5245,15 +5362,15 @@
         <x:v>Automated PASS / External Pending</x:v>
       </x:c>
       <x:c r="H138" s="63" t="str">
-        <x:v>IF-API-022~026; COMP-009</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>IF-API-022~027; COMP-009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A139" s="63" t="str">
         <x:v>REQ-IF-016</x:v>
       </x:c>
       <x:c r="B139" s="63" t="str">
-        <x:v>Context별 완결 Transaction 256개와 caller-owned RTU CSV line Buffer; DLL 파일 I/O 금지</x:v>
+        <x:v>Context별 완결 Transaction 256개와 caller-owned RTU CSV line Buffer; Capture Disabled에서만 Idle 대기; DLL 파일 I/O 금지</x:v>
       </x:c>
       <x:c r="C139" s="63" t="str">
         <x:v>FS-RTULOG-001</x:v>
@@ -5262,16 +5379,16 @@
         <x:v>DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E139" s="63" t="str">
-        <x:v>Capacity/caller-owned buffer/file boundary</x:v>
+        <x:v>Capacity/caller-owned buffer/file boundary/idle wait</x:v>
       </x:c>
       <x:c r="F139" s="63" t="str">
-        <x:v>TC-V03-AUTO-001; EV-018</x:v>
+        <x:v>TC-V03-AUTO-001; TC-P9-STATIC-001; EV-018</x:v>
       </x:c>
       <x:c r="G139" s="63" t="str">
-        <x:v>Automated PASS / External Pending</x:v>
+        <x:v>Automated/Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="H139" s="63" t="str">
-        <x:v>IF-LIMIT-009; LOG-023~024</x:v>
+        <x:v>IF-LIMIT-009; LOG-023~024; ERR-044</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5282,7 +5399,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7be832f1e2c4e83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re631f8a041d54f29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8183,7 +8300,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
-        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 26 API 및 현행 소스 구조를 사용해야 한다. 기존 21개 ABI 순서는 유지하고 FC 0x06은 Illegal Function으로 거부한다.</x:v>
+        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 27 API 및 현행 소스 구조를 사용해야 한다. 기존 21개 ABI 순서는 유지하고 FC 0x06은 Illegal Function으로 거부한다.</x:v>
       </x:c>
       <x:c r="D126" s="9" t="str">
         <x:v>PRJ-005~006; COMP-009~010</x:v>
@@ -8195,7 +8312,7 @@
         <x:v>Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="G126" s="9" t="str">
-        <x:v>공개 Export 21개, M485E Prefix, 현행 소스·문서 구조와 FC 0x06 거부 규칙 검사</x:v>
+        <x:v>전체 공개 Export 27개와 기존 21개 순서, M485E Prefix, 현행 소스·문서 구조 및 FC 0x06 거부 규칙 검사</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="32" customHeight="1">
@@ -8436,10 +8553,10 @@
         <x:v>Diagnostics</x:v>
       </x:c>
       <x:c r="C137" s="63" t="str">
-        <x:v>RTU Log OFF→ON마다 새 Timestamp 파일을 만들고 CAPL만 파일 I/O 수행</x:v>
+        <x:v>RTU Log 파일 Open 성공 후 Capture를 시작하고, OFF·종료 시 최대 2,000ms Idle 대기 후 완료 행을 배출</x:v>
       </x:c>
       <x:c r="D137" s="63" t="str">
-        <x:v>FR-UI-021; LOG-022~024</x:v>
+        <x:v>FR-UI-021; LOG-022~024; ERR-044</x:v>
       </x:c>
       <x:c r="E137" s="63" t="str">
         <x:v>FS-RTULOG-001</x:v>
@@ -8448,7 +8565,7 @@
         <x:v>DC-19</x:v>
       </x:c>
       <x:c r="G137" s="63" t="str">
-        <x:v>CAPL source contract와 EV-018</x:v>
+        <x:v>Core/Integration/CAPL source contract와 EV-018</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8459,10 +8576,10 @@
         <x:v>API</x:v>
       </x:c>
       <x:c r="C138" s="63" t="str">
-        <x:v>기존 21개 Entry 순서를 유지하고 Device 통신 2개와 RTU Log 3개 API를 22~26번에 추가</x:v>
+        <x:v>기존 21개 Entry 순서를 유지하고 Device 통신 2개와 RTU Log 4개 API를 22~27번에 추가</x:v>
       </x:c>
       <x:c r="D138" s="63" t="str">
-        <x:v>IF-API-022~026; COMP-009</x:v>
+        <x:v>IF-API-022~027; COMP-009</x:v>
       </x:c>
       <x:c r="E138" s="63" t="str">
         <x:v>FS-DEVICE-001; FS-RTULOG-001</x:v>
@@ -8482,10 +8599,10 @@
         <x:v>Buffer</x:v>
       </x:c>
       <x:c r="C139" s="63" t="str">
-        <x:v>Context별 완결 Transaction 256개와 caller-owned RTU CSV line Buffer; DLL 파일 I/O 금지</x:v>
+        <x:v>Context별 완결 Transaction 256개와 caller-owned RTU CSV line Buffer; Capture Disabled에서만 Idle 대기; DLL 파일 I/O 금지</x:v>
       </x:c>
       <x:c r="D139" s="63" t="str">
-        <x:v>IF-LIMIT-009; LOG-023~024</x:v>
+        <x:v>IF-LIMIT-009; LOG-023~024; ERR-044</x:v>
       </x:c>
       <x:c r="E139" s="63" t="str">
         <x:v>FS-RTULOG-001</x:v>
@@ -8494,13 +8611,13 @@
         <x:v>DC-19</x:v>
       </x:c>
       <x:c r="G139" s="63" t="str">
-        <x:v>Queue 경계·overflow·pair 보존 자동 시험과 EV-018</x:v>
+        <x:v>Queue 경계·overflow·idle wake/timeout·pair 보존 자동 시험과 EV-018</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f57d8b20c4d4863"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20787afb66a44764"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8968,7 +9085,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc906e431b6c3471b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c69425bb7704c9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9001,7 +9118,7 @@
         <x:v>CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>CAPL_DLL_INFO4, __stdcall, 불투명 Context Handle(0 포함), Length/Capacity 검증, caller-owned 출력 보호, Signal F[1] 저수준 출력, 생산 26개 Export(기존 21개 순서 유지)</x:v>
+        <x:v>CAPL_DLL_INFO4, __stdcall, 불투명 Context Handle(0 포함), Length/Capacity 검증, caller-owned 출력 보호, Signal F[1] 저수준 출력, 생산 27개 Export(기존 21개 순서 유지)</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -9205,7 +9322,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14a9a2f4e17141a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87e1c9b4c9c44659"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9238,7 +9355,7 @@
         <x:v>자동 검증 PASS / CANalyzer 9.x 실환경 대기</x:v>
       </x:c>
       <x:c r="C2" s="25" t="str">
-        <x:v>생산 26 API + 시험 전용 ABI Fixture 자동 Probe 후 CANalyzer 9.x SP8 측정 실행</x:v>
+        <x:v>생산 27 API + 시험 전용 ABI Fixture 자동 Probe 후 CANalyzer 9.x SP8 측정 실행</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
@@ -9343,7 +9460,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08901678363f4cb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa96e7d59c884f03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9385,7 +9502,7 @@
         <x:v>TC-P1-AUTO-001</x:v>
       </x:c>
       <x:c r="B2" s="35" t="str">
-        <x:v>Win32 빌드와 생산 CAPL Table 26 API</x:v>
+        <x:v>Win32 빌드와 생산 CAPL Table 27 API</x:v>
       </x:c>
       <x:c r="C2" s="35" t="str">
         <x:v>MSBuild Debug/Release, CMake Release, dumpbin 및 ABI 메타데이터 검사</x:v>
@@ -9397,7 +9514,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F2" s="35" t="str">
-        <x:v>x86(14C), 생산 API 정확히 26개, caplDllTable4 확인</x:v>
+        <x:v>x86(14C), 생산 API 정확히 27개, caplDllTable4 확인</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -9437,7 +9554,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F4" s="35" t="str">
-        <x:v>시험 Fixture는 생산 26개 API와 분리</x:v>
+        <x:v>시험 Fixture는 생산 27개 API와 분리</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -9554,7 +9671,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F2" s="35" t="str">
-        <x:v>오류 코드 92개, 공개 상수 207개에서 C++/CAPL 생성</x:v>
+        <x:v>오류 코드 93개, 공개 상수 210개에서 C++/CAPL 생성</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -9650,7 +9767,7 @@
       <x:c r="D7" s="35" t="str">
         <x:v>CANalyzer 13 x86</x:v>
       </x:c>
-      <x:c r="E7" s="136" t="str">
+      <x:c r="E7" s="166" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
@@ -9696,25 +9813,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="137" t="str">
+      <x:c r="A1" s="167" t="str">
         <x:v>Test Case ID</x:v>
       </x:c>
-      <x:c r="B1" s="137" t="str">
+      <x:c r="B1" s="167" t="str">
         <x:v>Phase</x:v>
       </x:c>
-      <x:c r="C1" s="137" t="str">
+      <x:c r="C1" s="167" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D1" s="137" t="str">
+      <x:c r="D1" s="167" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="E1" s="137" t="str">
+      <x:c r="E1" s="167" t="str">
         <x:v>Method</x:v>
       </x:c>
-      <x:c r="F1" s="137" t="str">
+      <x:c r="F1" s="167" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="G1" s="137" t="str">
+      <x:c r="G1" s="167" t="str">
         <x:v>External Follow-up</x:v>
       </x:c>
     </x:row>
@@ -9734,7 +9851,7 @@
       <x:c r="E2" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F2" s="138" t="str">
+      <x:c r="F2" s="168" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G2" s="63" t="str">
@@ -9757,7 +9874,7 @@
       <x:c r="E3" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F3" s="138" t="str">
+      <x:c r="F3" s="168" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G3" s="63" t="str">
@@ -9780,7 +9897,7 @@
       <x:c r="E4" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F4" s="138" t="str">
+      <x:c r="F4" s="168" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G4" s="63" t="str">
@@ -9803,7 +9920,7 @@
       <x:c r="E5" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F5" s="138" t="str">
+      <x:c r="F5" s="168" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G5" s="63" t="str">
@@ -9826,7 +9943,7 @@
       <x:c r="E6" s="63" t="str">
         <x:v>M485E.Core.Tests + FakeSerialTransport</x:v>
       </x:c>
-      <x:c r="F6" s="138" t="str">
+      <x:c r="F6" s="168" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G6" s="63" t="str">
@@ -9849,7 +9966,7 @@
       <x:c r="E7" s="63" t="str">
         <x:v>M485E.IntegrationTests</x:v>
       </x:c>
-      <x:c r="F7" s="138" t="str">
+      <x:c r="F7" s="168" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G7" s="63" t="str">
@@ -9872,7 +9989,7 @@
       <x:c r="E8" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1 + CANalyzer 13 Exec32 caplcompexec</x:v>
       </x:c>
-      <x:c r="F8" s="138" t="str">
+      <x:c r="F8" s="168" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="63" t="str">
@@ -9895,14 +10012,14 @@
       <x:c r="E9" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1; Main compile in configured CANalyzer project</x:v>
       </x:c>
-      <x:c r="F9" s="139" t="str">
+      <x:c r="F9" s="169" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="G9" s="63" t="str">
         <x:v>EV-011~EV-013, EV-016</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="10" ht="66" hidden="0" customHeight="1">
       <x:c r="A10" s="63" t="str">
         <x:v>TC-REG-AUTO-001</x:v>
       </x:c>
@@ -9913,12 +10030,12 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D10" s="63" t="str">
-        <x:v>Windows x86/x64 Debug/Release, /W4 /WX, ErrorCodes 92/PublicConstants 207, 26 API ABI, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
+        <x:v>Windows x86/x64 Debug/Release, /W4 /WX, ErrorCodes 93/PublicConstants 210, 27 API ABI, RTU 로그 idle wait, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
       </x:c>
       <x:c r="E10" s="63" t="str">
         <x:v>MSBuild + CMake + CTest + CANalyzer 13 x86 CAPL compiler</x:v>
       </x:c>
-      <x:c r="F10" s="138" t="str">
+      <x:c r="F10" s="168" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G10" s="63" t="str">
@@ -9941,7 +10058,7 @@
       <x:c r="E11" s="63" t="str">
         <x:v>M485E.Core.Tests + M485E.IntegrationTests + Test-M485ECaplSources.ps1</x:v>
       </x:c>
-      <x:c r="F11" s="139" t="str">
+      <x:c r="F11" s="169" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G11" s="63" t="str">
@@ -9964,7 +10081,7 @@
       <x:c r="E12" s="63" t="str">
         <x:v>External Verification Guide</x:v>
       </x:c>
-      <x:c r="F12" s="138" t="str">
+      <x:c r="F12" s="168" t="str">
         <x:v>Not Tested</x:v>
       </x:c>
       <x:c r="G12" s="63" t="str">
@@ -9987,7 +10104,7 @@
       <x:c r="E13" s="63" t="str">
         <x:v>CANalyzer 13 Exec32 caplcompexec.exe</x:v>
       </x:c>
-      <x:c r="F13" s="138" t="str">
+      <x:c r="F13" s="168" t="str">
         <x:v>PASS (warning-free)</x:v>
       </x:c>
       <x:c r="G13" s="63" t="str">

--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rf7fc1b0405224edf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Re5bd85c9c315407b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="Rb4ec22fbc3b74cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="Rb9f897399d3541be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="Rcdee6e1838424645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R984ab5dc08be4db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="Rf54521df11494da0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="Rcb8a825d3da241e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R6133a757acd74a71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.3.0 Traceability" sheetId="10" r:id="R0338c9bcc65a4dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R593d0f1a409c4bd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Ra94327c87b364616"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="Rdb7ae70dc0064db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R89bbcf80e9e34612"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="R3f8fd0682bcc4c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R063d534d39484d74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R0adc9d1fbc374ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R3c1465886ef44bf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R544e77aa1feb4397"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.3.0 Traceability" sheetId="10" r:id="R5076e0f5e9704c40"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -86,7 +86,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="66">
+  <x:fills count="72">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -413,6 +413,36 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -490,7 +520,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="176">
+  <x:cellXfs count="196">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -945,6 +975,54 @@
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="65" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="66" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="67" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="66" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="68" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="67" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="67" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="67" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="67" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="67" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="68" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="69" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="70" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="69" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="71" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="70" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="70" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="70" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="71" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1365,7 +1443,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>0.3.0</x:v>
+        <x:v>0.4.0</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Requirements with Design</x:v>
@@ -1552,25 +1630,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="167" t="str">
+      <x:c r="A1" s="187" t="str">
         <x:v>Requirement</x:v>
       </x:c>
-      <x:c r="B1" s="167" t="str">
+      <x:c r="B1" s="187" t="str">
         <x:v>Functional Specification</x:v>
       </x:c>
-      <x:c r="C1" s="167" t="str">
+      <x:c r="C1" s="187" t="str">
         <x:v>Design</x:v>
       </x:c>
-      <x:c r="D1" s="167" t="str">
+      <x:c r="D1" s="187" t="str">
         <x:v>Implementation</x:v>
       </x:c>
-      <x:c r="E1" s="167" t="str">
+      <x:c r="E1" s="187" t="str">
         <x:v>Automated Verification</x:v>
       </x:c>
-      <x:c r="F1" s="167" t="str">
+      <x:c r="F1" s="187" t="str">
         <x:v>External Verification</x:v>
       </x:c>
-      <x:c r="G1" s="167" t="str">
+      <x:c r="G1" s="187" t="str">
         <x:v>Status</x:v>
       </x:c>
     </x:row>
@@ -1593,7 +1671,7 @@
       <x:c r="F2" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G2" s="169" t="str">
+      <x:c r="G2" s="189" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1616,7 +1694,7 @@
       <x:c r="F3" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G3" s="169" t="str">
+      <x:c r="G3" s="189" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1639,7 +1717,7 @@
       <x:c r="F4" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G4" s="169" t="str">
+      <x:c r="G4" s="189" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1662,7 +1740,7 @@
       <x:c r="F5" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G5" s="169" t="str">
+      <x:c r="G5" s="189" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1685,7 +1763,7 @@
       <x:c r="F6" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G6" s="169" t="str">
+      <x:c r="G6" s="189" t="str">
         <x:v>Auto/Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1708,7 +1786,7 @@
       <x:c r="F7" s="63" t="str">
         <x:v>EV-001</x:v>
       </x:c>
-      <x:c r="G7" s="169" t="str">
+      <x:c r="G7" s="189" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1731,7 +1809,7 @@
       <x:c r="F8" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G8" s="169" t="str">
+      <x:c r="G8" s="189" t="str">
         <x:v>Auto/Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1754,7 +1832,7 @@
       <x:c r="F9" s="63" t="str">
         <x:v>EV-017~EV-018</x:v>
       </x:c>
-      <x:c r="G9" s="169" t="str">
+      <x:c r="G9" s="189" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1912,13 +1990,13 @@
         <x:v>REQ-FUNC-005</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>Disconnect는 통신과 Monitoring을 중지하되 Active Configuration, Port 설정, Register 현재값과 진단 상태를 유지해야 한다.</x:v>
+        <x:v>Disconnect는 통신과 CAPL Periodic Monitoring을 중지하되 Active Configuration, Port 설정, Register 현재값과 진단 상태를 유지해야 한다.</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
         <x:v>FS-LIFE-002</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>DC-03 LifecycleController; DC-11 SnapshotService</x:v>
+        <x:v>DC-03 LifecycleController; DC-11 Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
         <x:v>Disconnect/재Connect 데이터 보존 시험</x:v>
@@ -2094,13 +2172,13 @@
         <x:v>REQ-FUNC-012</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>Refresh 성공은 새 Init_Value를 적용한 Register Memory로 교체하고 Queue, Pending, Sequence, Counter 및 Latch를 초기화해야 한다.</x:v>
+        <x:v>Refresh 성공은 새 Init_Value를 적용한 Register Memory로 교체하고 CAPL이 다음 Monitoring 시작 전에 ReadOption과 Device/Port Mapping을 재검증하게 해야 한다. Error Queue와 RTU Log의 독립 진단 계약은 유지한다.</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
         <x:v>FS-CSV-003</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>DC-04 ConfigurationLoader; DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-11 Runtime Rule Data Provider; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
         <x:v>Refresh 전후 값과 런타임 상태 초기화 시험</x:v>
@@ -2250,22 +2328,22 @@
         <x:v>REQ-FUNC-018</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>실제 값이 변경된 Write만 영향 Rule별 변경 Snapshot을 한 번씩 생성하며 동일값 Write는 Snapshot을 생성하지 않아야 한다.</x:v>
+        <x:v>RTU 또는 Direct Write의 최종 Register 값은 다음 선택된 0x80 Periodic Rule Data에서 조회되며, Monitoring은 중간 변경 상태나 별도 변경 Event를 보존하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>FS-REG-002,FS-MON-004</x:v>
+        <x:v>FS-REG-002; FS-MON-004</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>DC-06 RegisterService; DC-11 SnapshotService</x:v>
+        <x:v>DC-06 RegisterService; DC-11 Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>중첩 Rule, 동일값 Write 및 중복 제거 시험</x:v>
+        <x:v>Direct/RTU Write 뒤 ReadRuleData 최신값, 동일값 Write, 0x81·Change Queue 미생성 시험</x:v>
       </x:c>
       <x:c r="F19" s="23" t="str">
-        <x:v>TC-P4-AUTO-001; TC-P6-AUTO-001</x:v>
+        <x:v>TC-P4-AUTO-001; TC-P6-AUTO-001; EV-006; EV-009</x:v>
       </x:c>
       <x:c r="G19" s="24" t="str">
-        <x:v>Automated Verification PASS</x:v>
+        <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
       </x:c>
       <x:c r="H19" s="9" t="str">
         <x:v>FR-REG-010~012,018</x:v>
@@ -2276,16 +2354,16 @@
         <x:v>REQ-FUNC-019</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>Device Reset은 지정 Index의 전체 Register를 현재 Init Image로 원자 복원하고 실제 변경 Rule에 SourceType 0x03 Snapshot을 생성해야 한다.</x:v>
+        <x:v>Device Reset은 지정 Index의 전체 Register를 현재 Init Image로 원자 복원하고 최종값은 다음 선택된 0x80 Periodic Rule Data에서 확인해야 한다.</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
         <x:v>FS-REG-003</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>DC-06 RegisterService; DC-11 SnapshotService</x:v>
+        <x:v>DC-06 RegisterService; DC-11 Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Connected/Disconnected Reset과 실패 Rollback 시험</x:v>
+        <x:v>Connected/Disconnected Reset, 실패 Rollback, ReadRuleData 최종값 및 0x81 미생성 시험</x:v>
       </x:c>
       <x:c r="F20" s="23" t="str">
         <x:v>TC-P4-AUTO-001; TC-P6-AUTO-001</x:v>
@@ -2562,16 +2640,16 @@
         <x:v>REQ-FUNC-030</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>ReadSwitch는 모든 활성 Port(1~4)의 Monitoring 전체를 제어하는 CAPL UI 입력이며 DLL은 하나의 MonitoringEnabled 상태만 유지해야 한다.</x:v>
+        <x:v>ReadSwitch는 모든 활성 Port(1~4)의 CAPL Periodic Monitoring Timer를 제어해야 하며 DLL은 별도 Monitoring Enabled 상태를 유지하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
         <x:v>FS-MON-001</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>DC-11 SnapshotService; DC-15 CAPL UI</x:v>
+        <x:v>DC-14 CAPL Monitoring; DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>1/4 Port에서 ON/OFF 중 RTU 유지와 Queue 정책 시험</x:v>
+        <x:v>1/4 Port에서 ON/OFF 중 RTU 유지, CAPL Timer Start/Stop 및 DLL Monitoring API 부재 시험</x:v>
       </x:c>
       <x:c r="F31" s="23" t="str">
         <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -2614,13 +2692,13 @@
         <x:v>REQ-FUNC-032</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>Monitoring 시작 시 Applied Rule의 현재값을 0x80 Pending으로 즉시 한 번 등록하고 이후 1,000ms 공통 Cycle을 사용해야 한다.</x:v>
+        <x:v>Monitoring 시작 시 Applied Rule의 현재값을 첫 0x80 Cycle로 즉시 등록하고 이후 1,000ms 공통 Cycle을 사용해야 한다.</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
         <x:v>FS-MON-001,FS-MON-003</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>DC-11 SnapshotService; DC-14 CAPL Monitoring</x:v>
+        <x:v>DC-11 Runtime Rule Data Provider; DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
         <x:v>Connect/ReadSwitch 순서 및 최초 출력 시험</x:v>
@@ -2640,7 +2718,7 @@
         <x:v>REQ-FUNC-033</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>0x80 Periodic은 Rule별 최신 Pending 한 개만 유지하고 지연된 과거 Cycle을 누적하거나 Catch-up 재생하지 않아야 한다.</x:v>
+        <x:v>0x80 Periodic은 Cycle마다 선택된 Rule의 현재 최종값을 읽고 지연된 과거 Cycle이나 중간 변경 상태를 Catch-up 재생하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
         <x:v>FS-MON-003,FS-MON-006</x:v>
@@ -2649,7 +2727,7 @@
         <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>Deadline Miss·Latest-wins·공정성 시험</x:v>
+        <x:v>1,000ms Cycle, 최신값, Deadline Miss 및 Port 공정성 시험</x:v>
       </x:c>
       <x:c r="F34" s="23" t="str">
         <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -2666,16 +2744,16 @@
         <x:v>REQ-FUNC-034</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>Register 변경 Snapshot은 변경 당시 전체 Rule 값을 Port별 256개 불변 FIFO에 저장하고 CAPL이 단건 원자 Dequeue해야 한다.</x:v>
+        <x:v>ReadRuleData는 Index+Rule_ID의 현재 Rule Metadata와 Register 전체를 동기적으로 반환하고 Queue를 거치지 않으며 실패 시 caller-owned 출력 Buffer를 보존해야 한다.</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
         <x:v>FS-MON-004</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>DC-11 SnapshotService; DC-14 CAPL Monitoring</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-06 RegisterService; DC-11 Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>동시 Write·불변 Snapshot·Buffer 부족 시험</x:v>
+        <x:v>Quantity 1/4/5/125, Metadata 9필드, Buffer 부족·Rule 부재 및 출력 불변 시험</x:v>
       </x:c>
       <x:c r="F35" s="23" t="str">
         <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -2692,16 +2770,16 @@
         <x:v>REQ-FUNC-035</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>Change FIFO Overflow는 oldest-drop으로 처리하고 Register Write나 RTU를 Rollback하지 않으며 Counter, Latch와 Sequence 불연속으로 진단해야 한다.</x:v>
+        <x:v>Monitoring은 1초 사이의 중간 Register 상태, 변경 Sequence, Change FIFO 또는 Overflow 통계를 저장하지 않고 다음 0x80 Cycle의 최종값만 출력해야 한다.</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>FS-MON-004,FS-DIAG-002</x:v>
+        <x:v>FS-MON-004; FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
+        <x:v>DC-11 Runtime Rule Data Provider; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>Queue 257건 입력 및 oldest-drop 시험</x:v>
+        <x:v>다중 Write 뒤 최종값, 0x81/Change Queue/Change Stats 부재 및 Error Queue 회귀 시험</x:v>
       </x:c>
       <x:c r="F36" s="23" t="str">
         <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -2718,7 +2796,7 @@
         <x:v>REQ-FUNC-036</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>CAPL은 10ms Output Pump에서 모든 활성 Port(1~4)를 Round-robin하고 Snapshot 묶음을 Tick 중간에 분할하지 않아야 한다.</x:v>
+        <x:v>CAPL은 10ms Output Pump에서 모든 활성 Port(1~4)를 Round-robin하고 Periodic Rule Data 묶음을 Tick 중간에 분할하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
         <x:v>FS-MON-006</x:v>
@@ -2727,7 +2805,7 @@
         <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
-        <x:v>1/4 Port Burst·Rule Cursor·빈 Queue·묶음 원자 출력 시험</x:v>
+        <x:v>1/4 Port Rule Cursor, 66 Frame/Tick 및 묶음 원자 출력 시험</x:v>
       </x:c>
       <x:c r="F37" s="23" t="str">
         <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -2744,7 +2822,7 @@
         <x:v>REQ-FUNC-037</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>MaxFramesPerTick은 CAPL 코드 상수이며 최대 33 Frame Snapshot을 처리할 수 있도록 33 이상이어야 한다.</x:v>
+        <x:v>MaxFramesPerTick은 CAPL 코드 상수 66이며 Quantity 125 Rule Data 묶음을 분할하지 않고 처리할 수 있어야 한다.</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
         <x:v>FS-MON-006</x:v>
@@ -2753,7 +2831,7 @@
         <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>Quantity 125 Snapshot과 Tick 시간 실측</x:v>
+        <x:v>Quantity 125 Frame 수, 66 Frame/Tick 및 Tick 시간 실측</x:v>
       </x:c>
       <x:c r="F38" s="23" t="str">
         <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -2796,16 +2874,16 @@
         <x:v>REQ-FUNC-039</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>ReadSwitch OFF/StopMonitoring은 Pending과 Change Queue를 폐기하고 OFF 중 변경은 Sequence 없이 SuppressedCount만 증가시켜야 한다.</x:v>
+        <x:v>ReadSwitch OFF 또는 M485E_Monitoring_Stop은 CAPL Cycle/Pump Timer와 Pending Generation만 정리하고 DLL Runtime, Error Queue, RTU Log 및 RTU 처리를 변경하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>FS-MON-001,FS-MON-004</x:v>
+        <x:v>FS-MON-001; FS-MON-004</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
-        <x:v>DC-11 SnapshotService</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
-        <x:v>OFF 전후 Queue·Counter·재시작 Burst 시험</x:v>
+        <x:v>OFF/ON Timer, RTU 유지, 과거 상태 미재생 및 최신 0x80 재시작 시험</x:v>
       </x:c>
       <x:c r="F40" s="23" t="str">
         <x:v>TC-P6-AUTO-001; TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -3368,7 +3446,7 @@
         <x:v>REQ-COM-017</x:v>
       </x:c>
       <x:c r="B62" s="9" t="str">
-        <x:v>실제 29bit ID는 Periodic 0x00IIRRMM, Change 0x01IIRRMM이며 Vector API 표현은 bit31 Extended Flag를 더한 0x80IIRRMM/0x81IIRRMM이어야 한다.</x:v>
+        <x:v>실제 29bit ID는 Periodic 0x00IIRRMM이며 Vector API 표현은 bit31 Extended Flag를 더한 0x80IIRRMM이어야 한다. 0x81 Change Message는 출력하지 않는다.</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
         <x:v>FS-MON-005</x:v>
@@ -3377,7 +3455,7 @@
         <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E62" s="9" t="str">
-        <x:v>실제 ID/Vector 표현 Mask 시험</x:v>
+        <x:v>0x80 실제 ID/Vector 표현 Mask와 0x81 부재 시험</x:v>
       </x:c>
       <x:c r="F62" s="23" t="str">
         <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -3394,7 +3472,7 @@
         <x:v>REQ-COM-018</x:v>
       </x:c>
       <x:c r="B63" s="9" t="str">
-        <x:v>하나의 Rule Snapshot은 Header 1개와 ceil(Quantity/4) Data Message로 구성하고 mm은 0x01부터 순차 증가해야 한다.</x:v>
+        <x:v>하나의 Periodic Rule Data는 Header 1개와 ceil(Quantity/4) Data Message로 구성하고 mm은 0x01부터 순차 증가해야 한다.</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
         <x:v>FS-MON-005</x:v>
@@ -3420,7 +3498,7 @@
         <x:v>REQ-COM-019</x:v>
       </x:c>
       <x:c r="B64" s="9" t="str">
-        <x:v>Header DLC는 8이며 Index, Slave_ID, Function_Code, SourceType, Address, Quantity를 규정된 Byte 순서로 포함해야 한다.</x:v>
+        <x:v>Header DLC는 8이며 Index, Slave_ID, Function_Code, 고정값 0x00, Address, Quantity를 규정된 Byte 순서로 포함해야 한다.</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
         <x:v>FS-MON-005</x:v>
@@ -3472,16 +3550,16 @@
         <x:v>REQ-COM-021</x:v>
       </x:c>
       <x:c r="B66" s="9" t="str">
-        <x:v>SourceType은 0x00 Cyclic, 0x01 RTU Write, 0x02 Direct Write, 0x03 Default Reset을 사용하고 0x04는 예약하되 자동 송출하지 않아야 한다.</x:v>
+        <x:v>Periodic Header Byte 3은 CAPL이 항상 0x00으로 기록하고 RTU/Direct/Reset 원인이나 변경 Sequence를 CAN Metadata로 표현하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>FS-MON-003~005</x:v>
+        <x:v>FS-MON-003; FS-MON-005</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
-        <x:v>DC-11 SnapshotService</x:v>
+        <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
-        <x:v>원인별 Header 및 0x04 미송출 시험</x:v>
+        <x:v>Header Byte 3 고정 0, 0x81·원인별 SourceType 부재 시험</x:v>
       </x:c>
       <x:c r="F66" s="23" t="str">
         <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -3940,16 +4018,16 @@
         <x:v>REQ-IF-004</x:v>
       </x:c>
       <x:c r="B84" s="9" t="str">
-        <x:v>1차 공개 CAPL Core 및 저수준 DLL Export는 Appendix A의 21개 함수명, 순서, 논리 파라미터와 대응 관계를 따라야 한다.</x:v>
+        <x:v>공개 CAPL Core 및 저수준 DLL Export는 확정된 23개 함수명, 생존 API 상대 순서와 논리 파라미터 대응 관계를 따라야 한다.</x:v>
       </x:c>
       <x:c r="C84" s="9" t="str">
-        <x:v>FS-INIT-001,FS-LIFE-001~004,FS-REG-001~003,FS-SIG-002~003,FS-MON-001~004,FS-DIAG-001~002</x:v>
+        <x:v>FS-INIT-001; FS-LIFE-001~004; FS-REG-001~003; FS-SIG-002~003; FS-MON-003~004; FS-DIAG-001~002; FS-DEVICE-001; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="D84" s="9" t="str">
         <x:v>DC-01 CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="E84" s="9" t="str">
-        <x:v>21개 Export Table/Wrapper Contract 시험</x:v>
+        <x:v>x86/x64 23개 Export Table/Wrapper, 제거 4개 및 구 ReadRuleSnapshot 부재 시험</x:v>
       </x:c>
       <x:c r="F84" s="23" t="str">
         <x:v>TC-P1-AUTO-001; TC-P1-CAPL-001; TC-P1-ENV-001; EV-001</x:v>
@@ -3995,7 +4073,7 @@
         <x:v>Core는 strlen/elcount로 Length와 Capacity를 계산해 DLL에 전달하고 DLL은 최종 검증 후에만 caller-owned 출력 Buffer를 변경해야 한다.</x:v>
       </x:c>
       <x:c r="C86" s="9" t="str">
-        <x:v>FS-REG-001~002,FS-SIG-002,FS-MON-003~004</x:v>
+        <x:v>FS-REG-001~002; FS-SIG-002; FS-MON-003~004</x:v>
       </x:c>
       <x:c r="D86" s="9" t="str">
         <x:v>DC-01 CAPL ABI Adapter; DC-13 CAPL Core</x:v>
@@ -4018,16 +4096,16 @@
         <x:v>REQ-IF-007</x:v>
       </x:c>
       <x:c r="B87" s="9" t="str">
-        <x:v>Snapshot Metadata V1은 long[11]의 고정 Layout과 Version/FieldCount를 사용해야 한다.</x:v>
+        <x:v>RuleData Metadata V1은 long[9]의 고정 Layout과 Version/FieldCount를 사용해야 한다.</x:v>
       </x:c>
       <x:c r="C87" s="9" t="str">
         <x:v>FS-MON-003~005</x:v>
       </x:c>
       <x:c r="D87" s="9" t="str">
-        <x:v>DC-11 SnapshotService; DC-14 CAPL Monitoring</x:v>
+        <x:v>DC-11 Runtime Rule Data Provider; DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E87" s="9" t="str">
-        <x:v>Version·Capacity·필드 Routing 시험</x:v>
+        <x:v>Metadata 9필드 Version·Capacity·Port/Rule Routing 시험</x:v>
       </x:c>
       <x:c r="F87" s="23" t="str">
         <x:v>TC-P6-AUTO-001; EV-001</x:v>
@@ -4070,16 +4148,16 @@
         <x:v>REQ-IF-009</x:v>
       </x:c>
       <x:c r="B89" s="9" t="str">
-        <x:v>Error Metadata V1은 long[20]+char[]이고 Error Queue Stats V1은 long[11], Change Queue Stats V1은 long[12]의 고정 Layout을 사용해야 한다.</x:v>
+        <x:v>Error Metadata V1은 long[20]+char[]이고 Error Queue Stats V1은 long[11]의 고정 Layout을 사용해야 하며 Change Queue Stats Layout은 제공하지 않는다.</x:v>
       </x:c>
       <x:c r="C89" s="9" t="str">
         <x:v>FS-DIAG-001,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="D89" s="9" t="str">
-        <x:v>DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E89" s="9" t="str">
-        <x:v>Version·ValidMask·Capacity·NUL 시험</x:v>
+        <x:v>Error Metadata/Stats Version·ValidMask·Capacity·NUL 및 Change Stats Export 부재 시험</x:v>
       </x:c>
       <x:c r="F89" s="23" t="str">
         <x:v>TC-P6-AUTO-001; EV-001</x:v>
@@ -4200,16 +4278,16 @@
         <x:v>REQ-IF-014</x:v>
       </x:c>
       <x:c r="B94" s="9" t="str">
-        <x:v>Periodic Read는 Index+Rule_ID로 메모리 Snapshot을 반환하고 Change Dequeue는 PortSlot별 단건 원자 조회를 제공해야 한다.</x:v>
+        <x:v>ReadRuleData는 Index+Rule_ID로 현재 RuleData Metadata와 Register 값을 동기 조회하며 Change Dequeue 또는 Monitoring Start/Stop DLL API를 제공하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
-        <x:v>FS-MON-003,FS-MON-004</x:v>
+        <x:v>FS-MON-003; FS-MON-004</x:v>
       </x:c>
       <x:c r="D94" s="9" t="str">
-        <x:v>DC-01 CAPL ABI Adapter; DC-11 SnapshotService</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-11 Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="E94" s="9" t="str">
-        <x:v>COM 비대기, Queue No Data, Buffer 부족 시험</x:v>
+        <x:v>Connected/Configuration 상태, Rule/Buffer 경계, 출력 불변 및 제거 API 부재 시험</x:v>
       </x:c>
       <x:c r="F94" s="23" t="str">
         <x:v>TC-P6-AUTO-001</x:v>
@@ -4258,7 +4336,7 @@
         <x:v>FS-CSV-003,FS-REG-001~003,FS-SIG-002~004</x:v>
       </x:c>
       <x:c r="D96" s="9" t="str">
-        <x:v>DC-01 CAPL ABI Adapter; DC-04 ConfigurationLoader; DC-06 RegisterService; DC-07 SignalCodec; DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-04 ConfigurationLoader; DC-06 RegisterService; DC-07 SignalCodec; DC-11 Runtime Rule Data Provider; DC-12 DiagnosticService</x:v>
       </x:c>
       <x:c r="E96" s="9" t="str">
         <x:v>실패 주입 및 전후 메모리 비교 시험</x:v>
@@ -4460,16 +4538,16 @@
         <x:v>REQ-PERF-002</x:v>
       </x:c>
       <x:c r="B104" s="9" t="str">
-        <x:v>정상 지원 부하의 0x81은 변경 후 100ms 이내에 출력 시작하고 활성 0x80 묶음은 해당 1,000ms Generation 안에 출력 시작해야 한다.</x:v>
+        <x:v>활성 0x80 Rule Data 묶음은 해당 1,000ms Generation 안에 출력해야 하며 0x81 지연 목표는 사용하지 않는다.</x:v>
       </x:c>
       <x:c r="C104" s="9" t="str">
-        <x:v>FS-MON-003,FS-MON-004,FS-MON-006</x:v>
+        <x:v>FS-MON-003; FS-MON-006</x:v>
       </x:c>
       <x:c r="D104" s="9" t="str">
         <x:v>DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E104" s="9" t="str">
-        <x:v>Trace Timestamp 기반 지연 측정</x:v>
+        <x:v>0x80 Trace Timestamp 기반 1,000ms Cycle 측정</x:v>
       </x:c>
       <x:c r="F104" s="23" t="str">
         <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -4489,7 +4567,7 @@
         <x:v>Measurement 중 DLL Export는 제한 시간의 검증·복사·상태 조회·작업 접수만 수행하고 파일/COM I/O, Join 또는 동적 할당을 호출 Thread에서 수행하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C105" s="9" t="str">
-        <x:v>FS-INIT-001,FS-LIFE-001~003,FS-MON-003~004</x:v>
+        <x:v>FS-INIT-001; FS-LIFE-001~003; FS-MON-003~004</x:v>
       </x:c>
       <x:c r="D105" s="9" t="str">
         <x:v>DC-01 CAPL ABI Adapter</x:v>
@@ -4616,13 +4694,13 @@
         <x:v>REQ-REL-002</x:v>
       </x:c>
       <x:c r="B110" s="9" t="str">
-        <x:v>Device Register, Port Change Queue, Context Error Queue는 각각 짧은 임계구역과 bounded 저장소로 보호해야 한다.</x:v>
+        <x:v>Device Register, Context Error Queue와 RTU Log Queue는 각각의 짧은 임계구역과 bounded 저장소로 보호해야 한다.</x:v>
       </x:c>
       <x:c r="C110" s="9" t="str">
-        <x:v>FS-REG-001~003,FS-MON-004,FS-DIAG-002</x:v>
+        <x:v>FS-REG-001~003; FS-DIAG-002; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="D110" s="9" t="str">
-        <x:v>DC-06 RegisterService; DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
+        <x:v>DC-06 RegisterService; DC-12 DiagnosticService; DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E110" s="9" t="str">
         <x:v>동시 RTU/CAPL 접근 및 Race 시험</x:v>
@@ -4642,13 +4720,13 @@
         <x:v>REQ-REL-003</x:v>
       </x:c>
       <x:c r="B111" s="9" t="str">
-        <x:v>Lock 순서는 Device→Port Change Queue로 고정하고 I/O, 파일, CAN 출력 또는 Thread Join 중 Lock을 보유하지 않아야 한다.</x:v>
+        <x:v>Device Register, Error Queue와 RTU Log Queue Lock을 보유한 채 Serial I/O, 파일 I/O, CAN 출력 또는 Thread Join을 기다리지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C111" s="9" t="str">
         <x:v>FS-REG-002,FS-SHUT-001</x:v>
       </x:c>
       <x:c r="D111" s="9" t="str">
-        <x:v>DC-03 LifecycleController; DC-06 RegisterService; DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
+        <x:v>DC-03 LifecycleController; DC-06 RegisterService; DC-12 DiagnosticService; DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E111" s="9" t="str">
         <x:v>Deadlock Stress 및 Lock-order 검토</x:v>
@@ -4668,13 +4746,13 @@
         <x:v>REQ-REL-004</x:v>
       </x:c>
       <x:c r="B112" s="9" t="str">
-        <x:v>Runtime Queue와 Snapshot 저장소는 고정 용량으로 사전 할당하고 정상 RTU/Monitoring 경로에서 확장 할당하지 않아야 한다.</x:v>
+        <x:v>Error Queue와 RTU Log Queue는 고정 용량 bounded 저장소를 사용하고 Overflow 정책이 RTU 처리를 중단하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C112" s="9" t="str">
-        <x:v>FS-MON-004,FS-DIAG-002</x:v>
+        <x:v>FS-DIAG-002; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="D112" s="9" t="str">
-        <x:v>DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService; DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E112" s="9" t="str">
         <x:v>Allocator hook/Stress 시험</x:v>
@@ -4694,16 +4772,16 @@
         <x:v>REQ-REL-005</x:v>
       </x:c>
       <x:c r="B113" s="9" t="str">
-        <x:v>Snapshot Read는 동시 Write와 관계없이 하나의 일관된 시점의 전체 Rule Register를 반환해야 한다.</x:v>
+        <x:v>ReadRuleData는 동시 Write와 관계없이 하나의 일관된 시점의 전체 Rule Register를 반환해야 한다.</x:v>
       </x:c>
       <x:c r="C113" s="9" t="str">
-        <x:v>FS-MON-003,FS-MON-004</x:v>
+        <x:v>FS-MON-003; FS-MON-004</x:v>
       </x:c>
       <x:c r="D113" s="9" t="str">
-        <x:v>DC-06 RegisterService; DC-11 SnapshotService</x:v>
+        <x:v>DC-06 RegisterService; DC-11 Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="E113" s="9" t="str">
-        <x:v>동시 다중 Register Write와 Snapshot 일관성 시험</x:v>
+        <x:v>동시 다중 Register Write와 RuleData torn-read 부재 시험</x:v>
       </x:c>
       <x:c r="F113" s="23" t="str">
         <x:v>TC-P4-AUTO-001</x:v>
@@ -4720,13 +4798,13 @@
         <x:v>REQ-REL-006</x:v>
       </x:c>
       <x:c r="B114" s="9" t="str">
-        <x:v>Deadline Miss, Queue Overflow 및 Monitoring Stop은 Modbus RTU와 Register/Signal 처리의 정상 동작을 중단하지 않아야 한다.</x:v>
+        <x:v>Periodic Deadline Miss와 Monitoring Stop은 Modbus RTU와 Register/Signal 처리, Error Queue 또는 RTU Log의 정상 동작을 중단하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C114" s="9" t="str">
-        <x:v>FS-MON-004,FS-MON-006</x:v>
+        <x:v>FS-MON-006; FS-DIAG-002; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="D114" s="9" t="str">
-        <x:v>DC-11 SnapshotService; DC-14 CAPL Monitoring</x:v>
+        <x:v>DC-12 DiagnosticService; DC-14 CAPL Monitoring; DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E114" s="9" t="str">
         <x:v>Burst/Overflow 중 RTU 응답 시험</x:v>
@@ -4798,16 +4876,16 @@
         <x:v>REQ-RES-003</x:v>
       </x:c>
       <x:c r="B117" s="9" t="str">
-        <x:v>Port별 Change Queue 및 Context Error Queue Capacity는 각각 256이고 Periodic Pending은 Rule당 최대 한 개여야 한다.</x:v>
+        <x:v>Context Error Queue와 RTU Log Queue Capacity는 각각 256이며 DLL은 Change Queue 또는 Periodic Pending 저장소를 갖지 않아야 한다.</x:v>
       </x:c>
       <x:c r="C117" s="9" t="str">
-        <x:v>FS-MON-003,FS-MON-004,FS-DIAG-002</x:v>
+        <x:v>FS-DIAG-002; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="D117" s="9" t="str">
-        <x:v>DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService; DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E117" s="9" t="str">
-        <x:v>Capacity 경계와 Overflow 정책 시험</x:v>
+        <x:v>Error/RTU Log Queue Capacity 경계와 Change Queue 부재 시험</x:v>
       </x:c>
       <x:c r="F117" s="23" t="str">
         <x:v>TC-P6-AUTO-001</x:v>
@@ -4824,13 +4902,13 @@
         <x:v>REQ-RES-004</x:v>
       </x:c>
       <x:c r="B118" s="9" t="str">
-        <x:v>Queue Counter는 0x7FFFFFFF에서 포화하고 Sequence는 1~0x7FFFFFFF에서 순환하며 0은 미생성 상태로 예약해야 한다.</x:v>
+        <x:v>Error Queue와 RTU Log Queue Counter는 0x7FFFFFFF에서 포화하고 각 Queue Sequence는 정의된 범위에서 순환해야 한다.</x:v>
       </x:c>
       <x:c r="C118" s="9" t="str">
-        <x:v>FS-MON-004,FS-DIAG-002</x:v>
+        <x:v>FS-DIAG-002; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="D118" s="9" t="str">
-        <x:v>DC-11 SnapshotService; DC-12 DiagnosticService</x:v>
+        <x:v>DC-12 DiagnosticService; DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E118" s="9" t="str">
         <x:v>포화 및 Sequence wrap 시험</x:v>
@@ -4902,7 +4980,7 @@
         <x:v>REQ-DIAG-003</x:v>
       </x:c>
       <x:c r="B121" s="9" t="str">
-        <x:v>Output Pump Frame 수, 실행시간 예산, Deadline Miss, Pending, Missed Cycle, Queue Pending/High-water/Drop/Suppressed를 조회·기록할 수 있어야 한다.</x:v>
+        <x:v>Output Pump Frame 수·실행시간 예산·Deadline Miss와 Error Queue Pending/High-water/Drop을 조회·기록할 수 있어야 하며 Change Queue 통계는 제공하지 않는다.</x:v>
       </x:c>
       <x:c r="C121" s="9" t="str">
         <x:v>FS-MON-006,FS-DIAG-002</x:v>
@@ -4911,7 +4989,7 @@
         <x:v>DC-12 DiagnosticService; DC-14 CAPL Monitoring</x:v>
       </x:c>
       <x:c r="E121" s="9" t="str">
-        <x:v>부하 시험 진단값 상호 검증</x:v>
+        <x:v>Periodic 부하 시험과 Error Queue 진단값 상호 검증, Change Stats 부재 검사</x:v>
       </x:c>
       <x:c r="F121" s="23" t="str">
         <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
@@ -5032,7 +5110,7 @@
         <x:v>REQ-COMP-003</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 27 API 및 현행 소스 구조를 사용해야 한다. 기존 21개 ABI 순서는 유지하고 FC 0x06은 Illegal Function으로 거부한다.</x:v>
+        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 23 API 및 현행 소스 구조를 사용해야 한다. v0.3에서 생존한 API의 상대 순서와 Operation 번호를 유지하고 FC 0x06은 Illegal Function으로 거부한다.</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
         <x:v>FS-INIT-001</x:v>
@@ -5041,7 +5119,7 @@
         <x:v>DC-17 Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="E126" s="9" t="str">
-        <x:v>전체 공개 Export 27개와 기존 21개 순서, M485E Prefix, 현행 소스·문서 구조 및 FC 0x06 거부 규칙 검사</x:v>
+        <x:v>전체 공개 Export 23개, 제거 Export 부재, 생존 API 상대 순서, M485E Prefix, 현행 소스·문서 구조 및 FC 0x06 거부 규칙 검사</x:v>
       </x:c>
       <x:c r="F126" s="23" t="str">
         <x:v>TC-P1-AUTO-001</x:v>
@@ -5058,16 +5136,16 @@
         <x:v>REQ-COMP-004</x:v>
       </x:c>
       <x:c r="B127" s="9" t="str">
-        <x:v>공통 Core는 후속 x64 이식을 방해하지 않는 고정폭 타입을 사용하되 v1에 x64 바이너리 또는 .vmodule을 포함하지 않아야 한다.</x:v>
+        <x:v>공통 Core는 고정폭 타입을 사용하고 Windows x86/x64 DLL과 .vmodule이 동일한 23개 공개 계약과 Runtime 동작을 제공해야 한다.</x:v>
       </x:c>
       <x:c r="C127" s="9" t="str">
         <x:v>FS-INIT-001</x:v>
       </x:c>
       <x:c r="D127" s="9" t="str">
-        <x:v>DC-04 ConfigurationLoader; DC-05 DeviceRegistry; DC-06 RegisterService; DC-07 SignalCodec; DC-08 ModbusRtuEngine; DC-11 SnapshotService; DC-12 DiagnosticService; DC-17 Build &amp; Packaging</x:v>
+        <x:v>DC-04 ConfigurationLoader; DC-05 DeviceRegistry; DC-06 RegisterService; DC-07 SignalCodec; DC-08 ModbusRtuEngine; DC-11 Runtime Rule Data Provider; DC-12 DiagnosticService; DC-17 Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="E127" s="9" t="str">
-        <x:v>Win32 타입 크기 검토; x64는 후속 체크리스트</x:v>
+        <x:v>x86/x64 /W4 /WX Build, ABI Probe, PE Architecture 및 .vmodule 경로 시험</x:v>
       </x:c>
       <x:c r="F127" s="23" t="str">
         <x:v>TC-P1-AUTO-001</x:v>
@@ -5339,21 +5417,21 @@
         <x:v>FR-UI-021; LOG-022~024; ERR-044</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="138" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A138" s="63" t="str">
         <x:v>REQ-IF-015</x:v>
       </x:c>
       <x:c r="B138" s="63" t="str">
-        <x:v>기존 21개 Entry 순서를 유지하고 Device 통신 2개와 RTU Log 4개 API를 22~27번에 추가</x:v>
+        <x:v>CAPL DLL Export Table은 Appendix A의 v0.4.0 23개 Entry를 정확히 제공하고 제거된 Monitoring·Change Queue API를 공개하지 않는다</x:v>
       </x:c>
       <x:c r="C138" s="63" t="str">
-        <x:v>FS-DEVICE-001; FS-RTULOG-001</x:v>
+        <x:v>FS-INIT-001; FS-MON-003; FS-DEVICE-001; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="D138" s="63" t="str">
-        <x:v>DC-01; DC-18; DC-19</x:v>
+        <x:v>DC-01 CAPL ABI Adapter; DC-11 Runtime Rule Data Provider; DC-18 Device Communication Gate; DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E138" s="63" t="str">
-        <x:v>27-entry x86/x64 ABI table</x:v>
+        <x:v>caplDllTable4 23-entry, ReadRuleData와 생존 Device/RTU Log API</x:v>
       </x:c>
       <x:c r="F138" s="63" t="str">
         <x:v>M485E.AbiProbe; TC-REG-AUTO-001; EV-001</x:v>
@@ -5362,7 +5440,7 @@
         <x:v>Automated PASS / External Pending</x:v>
       </x:c>
       <x:c r="H138" s="63" t="str">
-        <x:v>IF-API-022~027; COMP-009</x:v>
+        <x:v>IF-API-001~008; IF-API-011; IF-API-014~027; COMP-009</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -5399,7 +5477,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re631f8a041d54f29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R850ab91f2a644e33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5540,7 +5618,7 @@
         <x:v>Lifecycle</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>Disconnect는 통신과 Monitoring을 중지하되 Active Configuration, Port 설정, Register 현재값과 진단 상태를 유지해야 한다.</x:v>
+        <x:v>Disconnect는 통신과 CAPL Periodic Monitoring을 중지하되 Active Configuration, Port 설정, Register 현재값과 진단 상태를 유지해야 한다.</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
         <x:v>FR-LIFE-020,025,033</x:v>
@@ -5549,7 +5627,7 @@
         <x:v>FS-LIFE-002</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
-        <x:v>LifecycleController; SnapshotService</x:v>
+        <x:v>LifecycleController; Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="G6" s="9" t="str">
         <x:v>Disconnect/재Connect 데이터 보존 시험</x:v>
@@ -5701,7 +5779,7 @@
         <x:v>Configuration</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>Refresh 성공은 새 Init_Value를 적용한 Register Memory로 교체하고 Queue, Pending, Sequence, Counter 및 Latch를 초기화해야 한다.</x:v>
+        <x:v>Refresh 성공은 새 Init_Value를 적용한 Register Memory로 교체하고 CAPL이 다음 Monitoring 시작 전에 ReadOption과 Device/Port Mapping을 재검증하게 해야 한다. Error Queue와 RTU Log의 독립 진단 계약은 유지한다.</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
         <x:v>FR-CSV-005,012,017~019</x:v>
@@ -5710,7 +5788,7 @@
         <x:v>FS-CSV-003</x:v>
       </x:c>
       <x:c r="F13" s="9" t="str">
-        <x:v>ConfigurationLoader; SnapshotService; DiagnosticService</x:v>
+        <x:v>ConfigurationLoader; Runtime Rule Data Provider; DiagnosticService</x:v>
       </x:c>
       <x:c r="G13" s="9" t="str">
         <x:v>Refresh 전후 값과 런타임 상태 초기화 시험</x:v>
@@ -5839,19 +5917,19 @@
         <x:v>Register</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>실제 값이 변경된 Write만 영향 Rule별 변경 Snapshot을 한 번씩 생성하며 동일값 Write는 Snapshot을 생성하지 않아야 한다.</x:v>
+        <x:v>RTU 또는 Direct Write의 최종 Register 값은 다음 선택된 0x80 Periodic Rule Data에서 조회되며, Monitoring은 중간 변경 상태나 별도 변경 Event를 보존하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
         <x:v>FR-REG-010~012,018</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>FS-REG-002,FS-MON-004</x:v>
+        <x:v>FS-REG-002; FS-MON-004</x:v>
       </x:c>
       <x:c r="F19" s="9" t="str">
-        <x:v>RegisterService; SnapshotService</x:v>
+        <x:v>RegisterService; Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
-        <x:v>중첩 Rule, 동일값 Write 및 중복 제거 시험</x:v>
+        <x:v>Direct/RTU Write 뒤 ReadRuleData 최신값, 동일값 Write, 0x81·Change Queue 미생성 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="32" customHeight="1">
@@ -5862,7 +5940,7 @@
         <x:v>Register</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>Device Reset은 지정 Index의 전체 Register를 현재 Init Image로 원자 복원하고 실제 변경 Rule에 SourceType 0x03 Snapshot을 생성해야 한다.</x:v>
+        <x:v>Device Reset은 지정 Index의 전체 Register를 현재 Init Image로 원자 복원하고 최종값은 다음 선택된 0x80 Periodic Rule Data에서 확인해야 한다.</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
         <x:v>FR-RESET-001~007</x:v>
@@ -5871,10 +5949,10 @@
         <x:v>FS-REG-003</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
-        <x:v>RegisterService; SnapshotService</x:v>
+        <x:v>RegisterService; Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="G20" s="9" t="str">
-        <x:v>Connected/Disconnected Reset과 실패 Rollback 시험</x:v>
+        <x:v>Connected/Disconnected Reset, 실패 Rollback, ReadRuleData 최종값 및 0x81 미생성 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
@@ -6115,7 +6193,7 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v>ReadSwitch는 모든 활성 Port(1~4)의 Monitoring 전체를 제어하는 CAPL UI 입력이며 DLL은 하나의 MonitoringEnabled 상태만 유지해야 한다.</x:v>
+        <x:v>ReadSwitch는 모든 활성 Port(1~4)의 CAPL Periodic Monitoring Timer를 제어해야 하며 DLL은 별도 Monitoring Enabled 상태를 유지하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
         <x:v>FR-LIFE-004~006; FR-CAN-049~056</x:v>
@@ -6124,10 +6202,10 @@
         <x:v>FS-MON-001</x:v>
       </x:c>
       <x:c r="F31" s="9" t="str">
-        <x:v>CAPL UI; SnapshotService</x:v>
+        <x:v>CAPL Monitoring; CAPL UI</x:v>
       </x:c>
       <x:c r="G31" s="9" t="str">
-        <x:v>1/4 Port에서 ON/OFF 중 RTU 유지와 Queue 정책 시험</x:v>
+        <x:v>1/4 Port에서 ON/OFF 중 RTU 유지, CAPL Timer Start/Stop 및 DLL Monitoring API 부재 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
@@ -6161,7 +6239,7 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>Monitoring 시작 시 Applied Rule의 현재값을 0x80 Pending으로 즉시 한 번 등록하고 이후 1,000ms 공통 Cycle을 사용해야 한다.</x:v>
+        <x:v>Monitoring 시작 시 Applied Rule의 현재값을 첫 0x80 Cycle로 즉시 등록하고 이후 1,000ms 공통 Cycle을 사용해야 한다.</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
         <x:v>FR-LIFE-007~008; FR-CAN-055</x:v>
@@ -6170,7 +6248,7 @@
         <x:v>FS-MON-001,FS-MON-003</x:v>
       </x:c>
       <x:c r="F33" s="9" t="str">
-        <x:v>CAPL Monitoring; SnapshotService</x:v>
+        <x:v>Runtime Rule Data Provider; CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G33" s="9" t="str">
         <x:v>Connect/ReadSwitch 순서 및 최초 출력 시험</x:v>
@@ -6184,7 +6262,7 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>0x80 Periodic은 Rule별 최신 Pending 한 개만 유지하고 지연된 과거 Cycle을 누적하거나 Catch-up 재생하지 않아야 한다.</x:v>
+        <x:v>0x80 Periodic은 Cycle마다 선택된 Rule의 현재 최종값을 읽고 지연된 과거 Cycle이나 중간 변경 상태를 Catch-up 재생하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
         <x:v>FR-CAN-022,042~048; FR-LOAD-007</x:v>
@@ -6196,7 +6274,7 @@
         <x:v>CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G34" s="9" t="str">
-        <x:v>Deadline Miss·Latest-wins·공정성 시험</x:v>
+        <x:v>1,000ms Cycle, 최신값, Deadline Miss 및 Port 공정성 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="32" customHeight="1">
@@ -6207,7 +6285,7 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>Register 변경 Snapshot은 변경 당시 전체 Rule 값을 Port별 256개 불변 FIFO에 저장하고 CAPL이 단건 원자 Dequeue해야 한다.</x:v>
+        <x:v>ReadRuleData는 Index+Rule_ID의 현재 Rule Metadata와 Register 전체를 동기적으로 반환하고 Queue를 거치지 않으며 실패 시 caller-owned 출력 Buffer를 보존해야 한다.</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
         <x:v>FR-CAN-029~037; IF-MON-006~010</x:v>
@@ -6216,10 +6294,10 @@
         <x:v>FS-MON-004</x:v>
       </x:c>
       <x:c r="F35" s="9" t="str">
-        <x:v>SnapshotService; CAPL Monitoring</x:v>
+        <x:v>CAPL ABI Adapter; RegisterService; Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="G35" s="9" t="str">
-        <x:v>동시 Write·불변 Snapshot·Buffer 부족 시험</x:v>
+        <x:v>Quantity 1/4/5/125, Metadata 9필드, Buffer 부족·Rule 부재 및 출력 불변 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="32" customHeight="1">
@@ -6230,19 +6308,19 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>Change FIFO Overflow는 oldest-drop으로 처리하고 Register Write나 RTU를 Rollback하지 않으며 Counter, Latch와 Sequence 불연속으로 진단해야 한다.</x:v>
+        <x:v>Monitoring은 1초 사이의 중간 Register 상태, 변경 Sequence, Change FIFO 또는 Overflow 통계를 저장하지 않고 다음 0x80 Cycle의 최종값만 출력해야 한다.</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
         <x:v>FR-CAN-038~039; ERR-008; FR-LOAD-008</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>FS-MON-004,FS-DIAG-002</x:v>
+        <x:v>FS-MON-004; FS-DIAG-002</x:v>
       </x:c>
       <x:c r="F36" s="9" t="str">
-        <x:v>SnapshotService; DiagnosticService</x:v>
+        <x:v>Runtime Rule Data Provider; DiagnosticService</x:v>
       </x:c>
       <x:c r="G36" s="9" t="str">
-        <x:v>Queue 257건 입력 및 oldest-drop 시험</x:v>
+        <x:v>다중 Write 뒤 최종값, 0x81/Change Queue/Change Stats 부재 및 Error Queue 회귀 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="32" customHeight="1">
@@ -6253,7 +6331,7 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>CAPL은 10ms Output Pump에서 모든 활성 Port(1~4)를 Round-robin하고 Snapshot 묶음을 Tick 중간에 분할하지 않아야 한다.</x:v>
+        <x:v>CAPL은 10ms Output Pump에서 모든 활성 Port(1~4)를 Round-robin하고 Periodic Rule Data 묶음을 Tick 중간에 분할하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
         <x:v>FR-CAN-040~046; DES-CAN-014~017</x:v>
@@ -6265,7 +6343,7 @@
         <x:v>CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G37" s="9" t="str">
-        <x:v>1/4 Port Burst·Rule Cursor·빈 Queue·묶음 원자 출력 시험</x:v>
+        <x:v>1/4 Port Rule Cursor, 66 Frame/Tick 및 묶음 원자 출력 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="32" customHeight="1">
@@ -6276,7 +6354,7 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>MaxFramesPerTick은 CAPL 코드 상수이며 최대 33 Frame Snapshot을 처리할 수 있도록 33 이상이어야 한다.</x:v>
+        <x:v>MaxFramesPerTick은 CAPL 코드 상수 66이며 Quantity 125 Rule Data 묶음을 분할하지 않고 처리할 수 있어야 한다.</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
         <x:v>FR-LOAD-006,019</x:v>
@@ -6288,7 +6366,7 @@
         <x:v>CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G38" s="9" t="str">
-        <x:v>Quantity 125 Snapshot과 Tick 시간 실측</x:v>
+        <x:v>Quantity 125 Frame 수, 66 Frame/Tick 및 Tick 시간 실측</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="32" customHeight="1">
@@ -6322,19 +6400,19 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>ReadSwitch OFF/StopMonitoring은 Pending과 Change Queue를 폐기하고 OFF 중 변경은 Sequence 없이 SuppressedCount만 증가시켜야 한다.</x:v>
+        <x:v>ReadSwitch OFF 또는 M485E_Monitoring_Stop은 CAPL Cycle/Pump Timer와 Pending Generation만 정리하고 DLL Runtime, Error Queue, RTU Log 및 RTU 처리를 변경하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
         <x:v>FR-CAN-051~056; FR-LOAD-015~018</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
-        <x:v>FS-MON-001,FS-MON-004</x:v>
+        <x:v>FS-MON-001; FS-MON-004</x:v>
       </x:c>
       <x:c r="F40" s="9" t="str">
-        <x:v>SnapshotService</x:v>
+        <x:v>CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G40" s="9" t="str">
-        <x:v>OFF 전후 Queue·Counter·재시작 Burst 시험</x:v>
+        <x:v>OFF/ON Timer, RTU 유지, 과거 상태 미재생 및 최신 0x80 재시작 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="32" customHeight="1">
@@ -6828,7 +6906,7 @@
         <x:v>CAN</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>실제 29bit ID는 Periodic 0x00IIRRMM, Change 0x01IIRRMM이며 Vector API 표현은 bit31 Extended Flag를 더한 0x80IIRRMM/0x81IIRRMM이어야 한다.</x:v>
+        <x:v>실제 29bit ID는 Periodic 0x00IIRRMM이며 Vector API 표현은 bit31 Extended Flag를 더한 0x80IIRRMM이어야 한다. 0x81 Change Message는 출력하지 않는다.</x:v>
       </x:c>
       <x:c r="D62" s="9" t="str">
         <x:v>FR-CAN-001~002,021; CON-001</x:v>
@@ -6840,7 +6918,7 @@
         <x:v>CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G62" s="9" t="str">
-        <x:v>실제 ID/Vector 표현 Mask 시험</x:v>
+        <x:v>0x80 실제 ID/Vector 표현 Mask와 0x81 부재 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="32" customHeight="1">
@@ -6851,7 +6929,7 @@
         <x:v>CAN</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
-        <x:v>하나의 Rule Snapshot은 Header 1개와 ceil(Quantity/4) Data Message로 구성하고 mm은 0x01부터 순차 증가해야 한다.</x:v>
+        <x:v>하나의 Periodic Rule Data는 Header 1개와 ceil(Quantity/4) Data Message로 구성하고 mm은 0x01부터 순차 증가해야 한다.</x:v>
       </x:c>
       <x:c r="D63" s="9" t="str">
         <x:v>FR-CAN-003~019,028</x:v>
@@ -6874,7 +6952,7 @@
         <x:v>CAN</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>Header DLC는 8이며 Index, Slave_ID, Function_Code, SourceType, Address, Quantity를 규정된 Byte 순서로 포함해야 한다.</x:v>
+        <x:v>Header DLC는 8이며 Index, Slave_ID, Function_Code, 고정값 0x00, Address, Quantity를 규정된 Byte 순서로 포함해야 한다.</x:v>
       </x:c>
       <x:c r="D64" s="9" t="str">
         <x:v>FR-CAN-003~012</x:v>
@@ -6920,19 +6998,19 @@
         <x:v>CAN</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>SourceType은 0x00 Cyclic, 0x01 RTU Write, 0x02 Direct Write, 0x03 Default Reset을 사용하고 0x04는 예약하되 자동 송출하지 않아야 한다.</x:v>
+        <x:v>Periodic Header Byte 3은 CAPL이 항상 0x00으로 기록하고 RTU/Direct/Reset 원인이나 변경 Sequence를 CAN Metadata로 표현하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
         <x:v>FR-SRC-001~005; FR-LIFE-008</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
-        <x:v>FS-MON-003~005</x:v>
+        <x:v>FS-MON-003; FS-MON-005</x:v>
       </x:c>
       <x:c r="F66" s="9" t="str">
-        <x:v>SnapshotService</x:v>
+        <x:v>CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G66" s="9" t="str">
-        <x:v>원인별 Header 및 0x04 미송출 시험</x:v>
+        <x:v>Header Byte 3 고정 0, 0x81·원인별 SourceType 부재 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="32" customHeight="1">
@@ -7334,19 +7412,19 @@
         <x:v>API</x:v>
       </x:c>
       <x:c r="C84" s="9" t="str">
-        <x:v>1차 공개 CAPL Core 및 저수준 DLL Export는 Appendix A의 21개 함수명, 순서, 논리 파라미터와 대응 관계를 따라야 한다.</x:v>
+        <x:v>공개 CAPL Core 및 저수준 DLL Export는 확정된 23개 함수명, 생존 API 상대 순서와 논리 파라미터 대응 관계를 따라야 한다.</x:v>
       </x:c>
       <x:c r="D84" s="9" t="str">
         <x:v>IF-API-001~021</x:v>
       </x:c>
       <x:c r="E84" s="9" t="str">
-        <x:v>FS-INIT-001,FS-LIFE-001~004,FS-REG-001~003,FS-SIG-002~003,FS-MON-001~004,FS-DIAG-001~002</x:v>
+        <x:v>FS-INIT-001; FS-LIFE-001~004; FS-REG-001~003; FS-SIG-002~003; FS-MON-003~004; FS-DIAG-001~002; FS-DEVICE-001; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="F84" s="9" t="str">
         <x:v>CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="G84" s="9" t="str">
-        <x:v>21개 Export Table/Wrapper Contract 시험</x:v>
+        <x:v>x86/x64 23개 Export Table/Wrapper, 제거 4개 및 구 ReadRuleSnapshot 부재 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="32" customHeight="1">
@@ -7386,7 +7464,7 @@
         <x:v>IF-ABI-006~007,010~011; IF-RET-002~007</x:v>
       </x:c>
       <x:c r="E86" s="9" t="str">
-        <x:v>FS-REG-001~002,FS-SIG-002,FS-MON-003~004</x:v>
+        <x:v>FS-REG-001~002; FS-SIG-002; FS-MON-003~004</x:v>
       </x:c>
       <x:c r="F86" s="9" t="str">
         <x:v>CAPL Core; CAPL ABI Adapter</x:v>
@@ -7403,7 +7481,7 @@
         <x:v>Metadata</x:v>
       </x:c>
       <x:c r="C87" s="9" t="str">
-        <x:v>Snapshot Metadata V1은 long[11]의 고정 Layout과 Version/FieldCount를 사용해야 한다.</x:v>
+        <x:v>RuleData Metadata V1은 long[9]의 고정 Layout과 Version/FieldCount를 사용해야 한다.</x:v>
       </x:c>
       <x:c r="D87" s="9" t="str">
         <x:v>IF-META-001~016</x:v>
@@ -7412,10 +7490,10 @@
         <x:v>FS-MON-003~005</x:v>
       </x:c>
       <x:c r="F87" s="9" t="str">
-        <x:v>SnapshotService; CAPL Monitoring</x:v>
+        <x:v>Runtime Rule Data Provider; CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G87" s="9" t="str">
-        <x:v>Version·Capacity·필드 Routing 시험</x:v>
+        <x:v>Metadata 9필드 Version·Capacity·Port/Rule Routing 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="32" customHeight="1">
@@ -7449,7 +7527,7 @@
         <x:v>Diagnostics</x:v>
       </x:c>
       <x:c r="C89" s="9" t="str">
-        <x:v>Error Metadata V1은 long[20]+char[]이고 Error Queue Stats V1은 long[11], Change Queue Stats V1은 long[12]의 고정 Layout을 사용해야 한다.</x:v>
+        <x:v>Error Metadata V1은 long[20]+char[]이고 Error Queue Stats V1은 long[11]의 고정 Layout을 사용해야 하며 Change Queue Stats Layout은 제공하지 않는다.</x:v>
       </x:c>
       <x:c r="D89" s="9" t="str">
         <x:v>IF-EMETA-001~025; IF-ESTAT-001~002; IF-CSTAT-001~002</x:v>
@@ -7458,10 +7536,10 @@
         <x:v>FS-DIAG-001,FS-DIAG-002</x:v>
       </x:c>
       <x:c r="F89" s="9" t="str">
-        <x:v>DiagnosticService; SnapshotService</x:v>
+        <x:v>DiagnosticService</x:v>
       </x:c>
       <x:c r="G89" s="9" t="str">
-        <x:v>Version·ValidMask·Capacity·NUL 시험</x:v>
+        <x:v>Error Metadata/Stats Version·ValidMask·Capacity·NUL 및 Change Stats Export 부재 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="32" customHeight="1">
@@ -7564,19 +7642,19 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
-        <x:v>Periodic Read는 Index+Rule_ID로 메모리 Snapshot을 반환하고 Change Dequeue는 PortSlot별 단건 원자 조회를 제공해야 한다.</x:v>
+        <x:v>ReadRuleData는 Index+Rule_ID로 현재 RuleData Metadata와 Register 값을 동기 조회하며 Change Dequeue 또는 Monitoring Start/Stop DLL API를 제공하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D94" s="9" t="str">
         <x:v>IF-MON-001~012</x:v>
       </x:c>
       <x:c r="E94" s="9" t="str">
-        <x:v>FS-MON-003,FS-MON-004</x:v>
+        <x:v>FS-MON-003; FS-MON-004</x:v>
       </x:c>
       <x:c r="F94" s="9" t="str">
-        <x:v>SnapshotService; CAPL ABI Adapter</x:v>
+        <x:v>CAPL ABI Adapter; Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="G94" s="9" t="str">
-        <x:v>COM 비대기, Queue No Data, Buffer 부족 시험</x:v>
+        <x:v>Connected/Configuration 상태, Rule/Buffer 경계, 출력 불변 및 제거 API 부재 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="32" customHeight="1">
@@ -7619,7 +7697,7 @@
         <x:v>FS-CSV-003,FS-REG-001~003,FS-SIG-002~004</x:v>
       </x:c>
       <x:c r="F96" s="9" t="str">
-        <x:v>All core services</x:v>
+        <x:v>CAPL ABI Adapter; ConfigurationLoader; RegisterService; SignalCodec; Runtime Rule Data Provider; DiagnosticService</x:v>
       </x:c>
       <x:c r="G96" s="9" t="str">
         <x:v>실패 주입 및 전후 메모리 비교 시험</x:v>
@@ -7794,19 +7872,19 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C104" s="9" t="str">
-        <x:v>정상 지원 부하의 0x81은 변경 후 100ms 이내에 출력 시작하고 활성 0x80 묶음은 해당 1,000ms Generation 안에 출력 시작해야 한다.</x:v>
+        <x:v>활성 0x80 Rule Data 묶음은 해당 1,000ms Generation 안에 출력해야 하며 0x81 지연 목표는 사용하지 않는다.</x:v>
       </x:c>
       <x:c r="D104" s="9" t="str">
         <x:v>PERF-004~013; TBD-039</x:v>
       </x:c>
       <x:c r="E104" s="9" t="str">
-        <x:v>FS-MON-003,FS-MON-004,FS-MON-006</x:v>
+        <x:v>FS-MON-003; FS-MON-006</x:v>
       </x:c>
       <x:c r="F104" s="9" t="str">
         <x:v>CAPL Monitoring</x:v>
       </x:c>
       <x:c r="G104" s="9" t="str">
-        <x:v>Trace Timestamp 기반 지연 측정</x:v>
+        <x:v>0x80 Trace Timestamp 기반 1,000ms Cycle 측정</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="32" customHeight="1">
@@ -7823,7 +7901,7 @@
         <x:v>NFR-007,010</x:v>
       </x:c>
       <x:c r="E105" s="9" t="str">
-        <x:v>FS-INIT-001,FS-LIFE-001~003,FS-MON-003~004</x:v>
+        <x:v>FS-INIT-001; FS-LIFE-001~003; FS-MON-003~004</x:v>
       </x:c>
       <x:c r="F105" s="9" t="str">
         <x:v>CAPL ABI Adapter</x:v>
@@ -7932,16 +8010,16 @@
         <x:v>Concurrency</x:v>
       </x:c>
       <x:c r="C110" s="9" t="str">
-        <x:v>Device Register, Port Change Queue, Context Error Queue는 각각 짧은 임계구역과 bounded 저장소로 보호해야 한다.</x:v>
+        <x:v>Device Register, Context Error Queue와 RTU Log Queue는 각각의 짧은 임계구역과 bounded 저장소로 보호해야 한다.</x:v>
       </x:c>
       <x:c r="D110" s="9" t="str">
         <x:v>DES-THREAD-002~003</x:v>
       </x:c>
       <x:c r="E110" s="9" t="str">
-        <x:v>FS-REG-001~003,FS-MON-004,FS-DIAG-002</x:v>
+        <x:v>FS-REG-001~003; FS-DIAG-002; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="F110" s="9" t="str">
-        <x:v>RegisterService; SnapshotService; DiagnosticService</x:v>
+        <x:v>RegisterService; DiagnosticService; RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="G110" s="9" t="str">
         <x:v>동시 RTU/CAPL 접근 및 Race 시험</x:v>
@@ -7955,7 +8033,7 @@
         <x:v>Concurrency</x:v>
       </x:c>
       <x:c r="C111" s="9" t="str">
-        <x:v>Lock 순서는 Device→Port Change Queue로 고정하고 I/O, 파일, CAN 출력 또는 Thread Join 중 Lock을 보유하지 않아야 한다.</x:v>
+        <x:v>Device Register, Error Queue와 RTU Log Queue Lock을 보유한 채 Serial I/O, 파일 I/O, CAN 출력 또는 Thread Join을 기다리지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D111" s="9" t="str">
         <x:v>DES-THREAD-004</x:v>
@@ -7978,16 +8056,16 @@
         <x:v>Queues</x:v>
       </x:c>
       <x:c r="C112" s="9" t="str">
-        <x:v>Runtime Queue와 Snapshot 저장소는 고정 용량으로 사전 할당하고 정상 RTU/Monitoring 경로에서 확장 할당하지 않아야 한다.</x:v>
+        <x:v>Error Queue와 RTU Log Queue는 고정 용량 bounded 저장소를 사용하고 Overflow 정책이 RTU 처리를 중단하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D112" s="9" t="str">
         <x:v>DES-THREAD-003; DES-CAN-011~012</x:v>
       </x:c>
       <x:c r="E112" s="9" t="str">
-        <x:v>FS-MON-004,FS-DIAG-002</x:v>
+        <x:v>FS-DIAG-002; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="F112" s="9" t="str">
-        <x:v>SnapshotService; DiagnosticService</x:v>
+        <x:v>DiagnosticService; RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="G112" s="9" t="str">
         <x:v>Allocator hook/Stress 시험</x:v>
@@ -8001,19 +8079,19 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="C113" s="9" t="str">
-        <x:v>Snapshot Read는 동시 Write와 관계없이 하나의 일관된 시점의 전체 Rule Register를 반환해야 한다.</x:v>
+        <x:v>ReadRuleData는 동시 Write와 관계없이 하나의 일관된 시점의 전체 Rule Register를 반환해야 한다.</x:v>
       </x:c>
       <x:c r="D113" s="9" t="str">
         <x:v>IF-MON-002~003</x:v>
       </x:c>
       <x:c r="E113" s="9" t="str">
-        <x:v>FS-MON-003,FS-MON-004</x:v>
+        <x:v>FS-MON-003; FS-MON-004</x:v>
       </x:c>
       <x:c r="F113" s="9" t="str">
-        <x:v>RegisterService; SnapshotService</x:v>
+        <x:v>RegisterService; Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="G113" s="9" t="str">
-        <x:v>동시 다중 Register Write와 Snapshot 일관성 시험</x:v>
+        <x:v>동시 다중 Register Write와 RuleData torn-read 부재 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="32" customHeight="1">
@@ -8024,16 +8102,16 @@
         <x:v>Recovery</x:v>
       </x:c>
       <x:c r="C114" s="9" t="str">
-        <x:v>Deadline Miss, Queue Overflow 및 Monitoring Stop은 Modbus RTU와 Register/Signal 처리의 정상 동작을 중단하지 않아야 한다.</x:v>
+        <x:v>Periodic Deadline Miss와 Monitoring Stop은 Modbus RTU와 Register/Signal 처리, Error Queue 또는 RTU Log의 정상 동작을 중단하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D114" s="9" t="str">
         <x:v>NFR-002~004; FR-LOAD-009</x:v>
       </x:c>
       <x:c r="E114" s="9" t="str">
-        <x:v>FS-MON-004,FS-MON-006</x:v>
+        <x:v>FS-MON-006; FS-DIAG-002; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="F114" s="9" t="str">
-        <x:v>SnapshotService; CAPL Monitoring</x:v>
+        <x:v>DiagnosticService; CAPL Monitoring; RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="G114" s="9" t="str">
         <x:v>Burst/Overflow 중 RTU 응답 시험</x:v>
@@ -8093,19 +8171,19 @@
         <x:v>Queues</x:v>
       </x:c>
       <x:c r="C117" s="9" t="str">
-        <x:v>Port별 Change Queue 및 Context Error Queue Capacity는 각각 256이고 Periodic Pending은 Rule당 최대 한 개여야 한다.</x:v>
+        <x:v>Context Error Queue와 RTU Log Queue Capacity는 각각 256이며 DLL은 Change Queue 또는 Periodic Pending 저장소를 갖지 않아야 한다.</x:v>
       </x:c>
       <x:c r="D117" s="9" t="str">
         <x:v>IF-LIMIT-006</x:v>
       </x:c>
       <x:c r="E117" s="9" t="str">
-        <x:v>FS-MON-003,FS-MON-004,FS-DIAG-002</x:v>
+        <x:v>FS-DIAG-002; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="F117" s="9" t="str">
-        <x:v>SnapshotService; DiagnosticService</x:v>
+        <x:v>DiagnosticService; RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="G117" s="9" t="str">
-        <x:v>Capacity 경계와 Overflow 정책 시험</x:v>
+        <x:v>Error/RTU Log Queue Capacity 경계와 Change Queue 부재 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="32" customHeight="1">
@@ -8116,16 +8194,16 @@
         <x:v>Counters</x:v>
       </x:c>
       <x:c r="C118" s="9" t="str">
-        <x:v>Queue Counter는 0x7FFFFFFF에서 포화하고 Sequence는 1~0x7FFFFFFF에서 순환하며 0은 미생성 상태로 예약해야 한다.</x:v>
+        <x:v>Error Queue와 RTU Log Queue Counter는 0x7FFFFFFF에서 포화하고 각 Queue Sequence는 정의된 범위에서 순환해야 한다.</x:v>
       </x:c>
       <x:c r="D118" s="9" t="str">
         <x:v>IF-QSTAT-001~004</x:v>
       </x:c>
       <x:c r="E118" s="9" t="str">
-        <x:v>FS-MON-004,FS-DIAG-002</x:v>
+        <x:v>FS-DIAG-002; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="F118" s="9" t="str">
-        <x:v>SnapshotService; DiagnosticService</x:v>
+        <x:v>DiagnosticService; RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="G118" s="9" t="str">
         <x:v>포화 및 Sequence wrap 시험</x:v>
@@ -8185,7 +8263,7 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C121" s="9" t="str">
-        <x:v>Output Pump Frame 수, 실행시간 예산, Deadline Miss, Pending, Missed Cycle, Queue Pending/High-water/Drop/Suppressed를 조회·기록할 수 있어야 한다.</x:v>
+        <x:v>Output Pump Frame 수·실행시간 예산·Deadline Miss와 Error Queue Pending/High-water/Drop을 조회·기록할 수 있어야 하며 Change Queue 통계는 제공하지 않는다.</x:v>
       </x:c>
       <x:c r="D121" s="9" t="str">
         <x:v>LOG-002~008,014~017</x:v>
@@ -8197,7 +8275,7 @@
         <x:v>CAPL Monitoring; DiagnosticService</x:v>
       </x:c>
       <x:c r="G121" s="9" t="str">
-        <x:v>부하 시험 진단값 상호 검증</x:v>
+        <x:v>Periodic 부하 시험과 Error Queue 진단값 상호 검증, Change Stats 부재 검사</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="32" customHeight="1">
@@ -8300,7 +8378,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
-        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 27 API 및 현행 소스 구조를 사용해야 한다. 기존 21개 ABI 순서는 유지하고 FC 0x06은 Illegal Function으로 거부한다.</x:v>
+        <x:v>요구사항·설계·구현·시험·사용 안내는 저장소의 정식 산출물만으로 완결되어야 하며, 모든 공개 Export와 CAPL/DLL/Build 문서는 확정된 M485E 23 API 및 현행 소스 구조를 사용해야 한다. v0.3에서 생존한 API의 상대 순서와 Operation 번호를 유지하고 FC 0x06은 Illegal Function으로 거부한다.</x:v>
       </x:c>
       <x:c r="D126" s="9" t="str">
         <x:v>PRJ-005~006; COMP-009~010</x:v>
@@ -8312,7 +8390,7 @@
         <x:v>Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="G126" s="9" t="str">
-        <x:v>전체 공개 Export 27개와 기존 21개 순서, M485E Prefix, 현행 소스·문서 구조 및 FC 0x06 거부 규칙 검사</x:v>
+        <x:v>전체 공개 Export 23개, 제거 Export 부재, 생존 API 상대 순서, M485E Prefix, 현행 소스·문서 구조 및 FC 0x06 거부 규칙 검사</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="32" customHeight="1">
@@ -8323,7 +8401,7 @@
         <x:v>Future</x:v>
       </x:c>
       <x:c r="C127" s="9" t="str">
-        <x:v>공통 Core는 후속 x64 이식을 방해하지 않는 고정폭 타입을 사용하되 v1에 x64 바이너리 또는 .vmodule을 포함하지 않아야 한다.</x:v>
+        <x:v>공통 Core는 고정폭 타입을 사용하고 Windows x86/x64 DLL과 .vmodule이 동일한 23개 공개 계약과 Runtime 동작을 제공해야 한다.</x:v>
       </x:c>
       <x:c r="D127" s="9" t="str">
         <x:v>ENV-011; FUT-001~005</x:v>
@@ -8332,10 +8410,10 @@
         <x:v>FS-INIT-001</x:v>
       </x:c>
       <x:c r="F127" s="9" t="str">
-        <x:v>M485E.Core</x:v>
+        <x:v>ConfigurationLoader; DeviceRegistry; RegisterService; SignalCodec; ModbusRtuEngine; Runtime Rule Data Provider; DiagnosticService; Build &amp; Packaging</x:v>
       </x:c>
       <x:c r="G127" s="9" t="str">
-        <x:v>Win32 타입 크기 검토; x64는 후속 체크리스트</x:v>
+        <x:v>x86/x64 /W4 /WX Build, ABI Probe, PE Architecture 및 .vmodule 경로 시험</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="32" customHeight="1">
@@ -8576,19 +8654,19 @@
         <x:v>API</x:v>
       </x:c>
       <x:c r="C138" s="63" t="str">
-        <x:v>기존 21개 Entry 순서를 유지하고 Device 통신 2개와 RTU Log 4개 API를 22~27번에 추가</x:v>
+        <x:v>CAPL DLL Export Table은 Appendix A의 v0.4.0 23개 Entry를 정확히 제공하고 제거된 Monitoring·Change Queue API를 공개하지 않는다</x:v>
       </x:c>
       <x:c r="D138" s="63" t="str">
-        <x:v>IF-API-022~027; COMP-009</x:v>
+        <x:v>IF-API-001~008; IF-API-011; IF-API-014~027; COMP-009</x:v>
       </x:c>
       <x:c r="E138" s="63" t="str">
-        <x:v>FS-DEVICE-001; FS-RTULOG-001</x:v>
+        <x:v>FS-INIT-001; FS-MON-003; FS-DEVICE-001; FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="F138" s="63" t="str">
-        <x:v>DC-01; DC-18; DC-19</x:v>
+        <x:v>DC-01; DC-11; DC-18; DC-19</x:v>
       </x:c>
       <x:c r="G138" s="63" t="str">
-        <x:v>x86/x64 ABI Probe와 EV-001</x:v>
+        <x:v>x86/x64 23-entry ABI Probe, 제거 Export 부재 검사와 EV-001</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8617,7 +8695,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20787afb66a44764"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8467b2888f743c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8922,7 +9000,7 @@
         <x:v>FS-MON-001</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>Monitoring Start/Stop</x:v>
+        <x:v>CAPL Periodic Monitoring Start/Stop</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
         <x:v>REQ-FUNC-030, REQ-FUNC-032, REQ-FUNC-039; REQ-IF-004</x:v>
@@ -8944,7 +9022,7 @@
         <x:v>FS-MON-003</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>Periodic Snapshot 생성</x:v>
+        <x:v>Periodic Rule Data 조회</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
         <x:v>REQ-FUNC-032~033; REQ-COM-021; REQ-IF-004, REQ-IF-006~007, REQ-IF-014; REQ-PERF-002~003; REQ-REL-005; REQ-RES-003</x:v>
@@ -8955,7 +9033,7 @@
         <x:v>FS-MON-004</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>Change Snapshot Queue</x:v>
+        <x:v>RuleData 최신값·일관성</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
         <x:v>REQ-FUNC-018, REQ-FUNC-034~035, REQ-FUNC-039; REQ-COM-021; REQ-IF-004, REQ-IF-006~007, REQ-IF-014; REQ-PERF-002~003; REQ-REL-002, REQ-REL-004~006; REQ-RES-003~004</x:v>
@@ -8966,7 +9044,7 @@
         <x:v>FS-MON-005</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>CAN Snapshot Encoding</x:v>
+        <x:v>0x80 Periodic CAN Encoding</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
         <x:v>REQ-COM-016~021; REQ-IF-007</x:v>
@@ -9085,7 +9163,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c69425bb7704c9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67be2c7f869f476c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9118,7 +9196,7 @@
         <x:v>CAPL ABI Adapter</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>CAPL_DLL_INFO4, __stdcall, 불투명 Context Handle(0 포함), Length/Capacity 검증, caller-owned 출력 보호, Signal F[1] 저수준 출력, 생산 27개 Export(기존 21개 순서 유지)</x:v>
+        <x:v>CAPL_DLL_INFO4, __stdcall, 불투명 Context Handle(0 포함), Length/Capacity 검증, caller-owned 출력 보호, Signal F[1] 저수준 출력, 생산 23개 Export와 생존 API 상대 순서 유지</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -9225,10 +9303,10 @@
         <x:v>DC-11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>SnapshotService</x:v>
+        <x:v>Runtime Rule Data Provider</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>Periodic Snapshot, Port별 Change FIFO, Sequence/Stats</x:v>
+        <x:v>RuntimeModel::ReadRule 기반 동기 현재값 조회, RuleDataMeta[9], Queue 없는 caller-owned 출력 보호</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -9322,7 +9400,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87e1c9b4c9c44659"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51fb07d3bff146b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9355,7 +9433,7 @@
         <x:v>자동 검증 PASS / CANalyzer 9.x 실환경 대기</x:v>
       </x:c>
       <x:c r="C2" s="25" t="str">
-        <x:v>생산 27 API + 시험 전용 ABI Fixture 자동 Probe 후 CANalyzer 9.x SP8 측정 실행</x:v>
+        <x:v>생산 23 API + 시험 전용 ABI Fixture 자동 Probe 후 CANalyzer 9.x SP8 측정 실행</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
@@ -9385,10 +9463,10 @@
         <x:v>MaxFramesPerTick / time budget</x:v>
       </x:c>
       <x:c r="B5" s="25" t="str">
-        <x:v>최소 33 확정, 최종 실측</x:v>
+        <x:v>66 Frame/Tick, 최종 실측</x:v>
       </x:c>
       <x:c r="C5" s="25" t="str">
-        <x:v>200 Rule + 0x81 burst</x:v>
+        <x:v>200 Rule 0x80-only Periodic profile</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
@@ -9460,7 +9538,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa96e7d59c884f03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdddb4b30b6e74683"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9502,7 +9580,7 @@
         <x:v>TC-P1-AUTO-001</x:v>
       </x:c>
       <x:c r="B2" s="35" t="str">
-        <x:v>Win32 빌드와 생산 CAPL Table 27 API</x:v>
+        <x:v>Win32 빌드와 생산 CAPL Table 23 API</x:v>
       </x:c>
       <x:c r="C2" s="35" t="str">
         <x:v>MSBuild Debug/Release, CMake Release, dumpbin 및 ABI 메타데이터 검사</x:v>
@@ -9514,7 +9592,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F2" s="35" t="str">
-        <x:v>x86(14C), 생산 API 정확히 27개, caplDllTable4 확인</x:v>
+        <x:v>x86(14C), 생산 API 정확히 23개, 제거 Export 부재와 caplDllTable4 확인</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -9554,7 +9632,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F4" s="35" t="str">
-        <x:v>시험 Fixture는 생산 27개 API와 분리</x:v>
+        <x:v>시험 Fixture는 생산 23개 API와 분리</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -9671,7 +9749,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F2" s="35" t="str">
-        <x:v>오류 코드 93개, 공개 상수 210개에서 C++/CAPL 생성</x:v>
+        <x:v>오류 코드 91개, 공개 상수 189개에서 C++/CAPL 생성</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -9767,7 +9845,7 @@
       <x:c r="D7" s="35" t="str">
         <x:v>CANalyzer 13 x86</x:v>
       </x:c>
-      <x:c r="E7" s="166" t="str">
+      <x:c r="E7" s="186" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
@@ -9813,25 +9891,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="167" t="str">
+      <x:c r="A1" s="187" t="str">
         <x:v>Test Case ID</x:v>
       </x:c>
-      <x:c r="B1" s="167" t="str">
+      <x:c r="B1" s="187" t="str">
         <x:v>Phase</x:v>
       </x:c>
-      <x:c r="C1" s="167" t="str">
+      <x:c r="C1" s="187" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D1" s="167" t="str">
+      <x:c r="D1" s="187" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="E1" s="167" t="str">
+      <x:c r="E1" s="187" t="str">
         <x:v>Method</x:v>
       </x:c>
-      <x:c r="F1" s="167" t="str">
+      <x:c r="F1" s="187" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="G1" s="167" t="str">
+      <x:c r="G1" s="187" t="str">
         <x:v>External Follow-up</x:v>
       </x:c>
     </x:row>
@@ -9851,7 +9929,7 @@
       <x:c r="E2" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F2" s="168" t="str">
+      <x:c r="F2" s="188" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G2" s="63" t="str">
@@ -9869,16 +9947,16 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D3" s="63" t="str">
-        <x:v>Register/Signal/Init/Reset, atomic failure and snapshot impact</x:v>
+        <x:v>Register/Signal/Init/Reset, atomic failure and RuleData latest-value impact</x:v>
       </x:c>
       <x:c r="E3" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F3" s="168" t="str">
+      <x:c r="F3" s="188" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G3" s="63" t="str">
-        <x:v>EV-006, EV-013</x:v>
+        <x:v>EV-006, EV-009, EV-013</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -9897,14 +9975,14 @@
       <x:c r="E4" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F4" s="168" t="str">
+      <x:c r="F4" s="188" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G4" s="63" t="str">
         <x:v>EV-004~EV-007</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A5" s="63" t="str">
         <x:v>TC-P6-AUTO-001</x:v>
       </x:c>
@@ -9915,12 +9993,12 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D5" s="63" t="str">
-        <x:v>Snapshot/Error queues, immutable payload, Error Queue overflow/coalesce/drop/stats</x:v>
+        <x:v>RuleData metadata/quantity/current-value consistency, Error Queue overflow/coalesce/drop/stats</x:v>
       </x:c>
       <x:c r="E5" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F5" s="168" t="str">
+      <x:c r="F5" s="188" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G5" s="63" t="str">
@@ -9943,7 +10021,7 @@
       <x:c r="E6" s="63" t="str">
         <x:v>M485E.Core.Tests + FakeSerialTransport</x:v>
       </x:c>
-      <x:c r="F6" s="168" t="str">
+      <x:c r="F6" s="188" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G6" s="63" t="str">
@@ -9966,7 +10044,7 @@
       <x:c r="E7" s="63" t="str">
         <x:v>M485E.IntegrationTests</x:v>
       </x:c>
-      <x:c r="F7" s="168" t="str">
+      <x:c r="F7" s="188" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G7" s="63" t="str">
@@ -9984,12 +10062,12 @@
         <x:v>Static + CAPL Compile</x:v>
       </x:c>
       <x:c r="D8" s="63" t="str">
-        <x:v>CAPL Core wrappers, Error Queue Stats 변화기반 출력, 1s/10ms pump, ActivePortCount=Device CSV 고유 Port 수, Port별 Rule Cursor/round-robin, 66/33 budget, Extended CAN</x:v>
+        <x:v>CAPL Core 23 wrappers, Error Queue Stats 변화기반 출력, 1s/10ms pump, ActivePortCount=Device CSV 고유 Port 수, Port별 Rule Cursor/round-robin, 66 Frame budget, 0x80 Extended CAN</x:v>
       </x:c>
       <x:c r="E8" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1 + CANalyzer 13 Exec32 caplcompexec</x:v>
       </x:c>
-      <x:c r="F8" s="168" t="str">
+      <x:c r="F8" s="188" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="63" t="str">
@@ -10012,7 +10090,7 @@
       <x:c r="E9" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1; Main compile in configured CANalyzer project</x:v>
       </x:c>
-      <x:c r="F9" s="169" t="str">
+      <x:c r="F9" s="189" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="G9" s="63" t="str">
@@ -10030,12 +10108,12 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D10" s="63" t="str">
-        <x:v>Windows x86/x64 Debug/Release, /W4 /WX, ErrorCodes 93/PublicConstants 210, 27 API ABI, RTU 로그 idle wait, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
+        <x:v>Windows x86/x64 Debug/Release, /W4 /WX, ErrorCodes 91/PublicConstants 189, 23 API ABI, RuleDataMeta[9], RTU 로그 idle wait, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
       </x:c>
       <x:c r="E10" s="63" t="str">
         <x:v>MSBuild + CMake + CTest + CANalyzer 13 x86 CAPL compiler</x:v>
       </x:c>
-      <x:c r="F10" s="168" t="str">
+      <x:c r="F10" s="188" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G10" s="63" t="str">
@@ -10058,7 +10136,7 @@
       <x:c r="E11" s="63" t="str">
         <x:v>M485E.Core.Tests + M485E.IntegrationTests + Test-M485ECaplSources.ps1</x:v>
       </x:c>
-      <x:c r="F11" s="169" t="str">
+      <x:c r="F11" s="189" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G11" s="63" t="str">
@@ -10081,7 +10159,7 @@
       <x:c r="E12" s="63" t="str">
         <x:v>External Verification Guide</x:v>
       </x:c>
-      <x:c r="F12" s="168" t="str">
+      <x:c r="F12" s="188" t="str">
         <x:v>Not Tested</x:v>
       </x:c>
       <x:c r="G12" s="63" t="str">
@@ -10104,7 +10182,7 @@
       <x:c r="E13" s="63" t="str">
         <x:v>CANalyzer 13 Exec32 caplcompexec.exe</x:v>
       </x:c>
-      <x:c r="F13" s="168" t="str">
+      <x:c r="F13" s="188" t="str">
         <x:v>PASS (warning-free)</x:v>
       </x:c>
       <x:c r="G13" s="63" t="str">

--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R593d0f1a409c4bd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Ra94327c87b364616"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="Rdb7ae70dc0064db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R89bbcf80e9e34612"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="R3f8fd0682bcc4c81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R063d534d39484d74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R0adc9d1fbc374ad3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R3c1465886ef44bf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R544e77aa1feb4397"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.3.0 Traceability" sheetId="10" r:id="R5076e0f5e9704c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R9869f5ea61a442e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R4ee31e3544f642d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="Rbd19b3ee850444ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="Rbb215e9051664201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="R6528b4b8ab9e4d69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R4a88a93129ed4034"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R34fdfe7f134a4029"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R1eb5e5a782dd4a30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R07d6a19c9c1a44b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.3.0 Traceability" sheetId="10" r:id="Rdb5d9cf260854225"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -86,7 +86,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="72">
+  <x:fills count="75">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -443,6 +443,21 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -520,7 +535,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="196">
+  <x:cellXfs count="206">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1023,6 +1038,30 @@
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="71" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="72" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="73" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="72" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="74" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="73" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="73" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="73" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="73" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="73" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="74" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1443,7 +1482,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>0.4.0</x:v>
+        <x:v>0.5.0</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Requirements with Design</x:v>
@@ -1473,7 +1512,7 @@
         <x:v>Baseline Date</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>Test Case IDs</x:v>
@@ -1630,25 +1669,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="187" t="str">
+      <x:c r="A1" s="197" t="str">
         <x:v>Requirement</x:v>
       </x:c>
-      <x:c r="B1" s="187" t="str">
+      <x:c r="B1" s="197" t="str">
         <x:v>Functional Specification</x:v>
       </x:c>
-      <x:c r="C1" s="187" t="str">
+      <x:c r="C1" s="197" t="str">
         <x:v>Design</x:v>
       </x:c>
-      <x:c r="D1" s="187" t="str">
+      <x:c r="D1" s="197" t="str">
         <x:v>Implementation</x:v>
       </x:c>
-      <x:c r="E1" s="187" t="str">
+      <x:c r="E1" s="197" t="str">
         <x:v>Automated Verification</x:v>
       </x:c>
-      <x:c r="F1" s="187" t="str">
+      <x:c r="F1" s="197" t="str">
         <x:v>External Verification</x:v>
       </x:c>
-      <x:c r="G1" s="187" t="str">
+      <x:c r="G1" s="197" t="str">
         <x:v>Status</x:v>
       </x:c>
     </x:row>
@@ -1671,7 +1710,7 @@
       <x:c r="F2" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G2" s="189" t="str">
+      <x:c r="G2" s="199" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1694,7 +1733,7 @@
       <x:c r="F3" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G3" s="189" t="str">
+      <x:c r="G3" s="199" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1717,7 +1756,7 @@
       <x:c r="F4" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G4" s="189" t="str">
+      <x:c r="G4" s="199" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1740,7 +1779,7 @@
       <x:c r="F5" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G5" s="189" t="str">
+      <x:c r="G5" s="199" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1763,7 +1802,7 @@
       <x:c r="F6" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G6" s="189" t="str">
+      <x:c r="G6" s="199" t="str">
         <x:v>Auto/Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1786,7 +1825,7 @@
       <x:c r="F7" s="63" t="str">
         <x:v>EV-001</x:v>
       </x:c>
-      <x:c r="G7" s="189" t="str">
+      <x:c r="G7" s="199" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1809,7 +1848,7 @@
       <x:c r="F8" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G8" s="189" t="str">
+      <x:c r="G8" s="199" t="str">
         <x:v>Auto/Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1832,7 +1871,7 @@
       <x:c r="F9" s="63" t="str">
         <x:v>EV-017~EV-018</x:v>
       </x:c>
-      <x:c r="G9" s="189" t="str">
+      <x:c r="G9" s="199" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -2666,19 +2705,19 @@
         <x:v>REQ-FUNC-031</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>ReadOption은 최대 200개 Rule의 0x80 Periodic 선택만 제어하고 여러 변경을 다음 1,000ms Cycle 경계에 원자 적용해야 한다.</x:v>
+        <x:v>ReadOption은 최대 200개 Rule의 0x80 Periodic 선택만 제어하고 다음 1,000ms Cycle 경계에 원자 적용해야 한다. Monitoring::Btn_ReadOption은 int32 Scalar 편의 버튼으로만 제공하며 별도 CAPL Handler 없이 기존 Check_ReadOption[200], 100ms Candidate 동기화와 Cycle 적용 정책을 유지해야 한다.</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>FS-MON-002</x:v>
+        <x:v>FS-MON-002; FS-UI-001</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>DC-14 CAPL Monitoring</x:v>
+        <x:v>DC-14 CAPL Monitoring; DC-15 CAPL UI</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>다중 Checkbox 원자 적용·복원 시험</x:v>
+        <x:v>Btn_ReadOption int32 Scalar/no-handler, Check_ReadOption[200] 유지 및 Candidate/Applied 원자 적용 검사</x:v>
       </x:c>
       <x:c r="F32" s="23" t="str">
-        <x:v>TC-P9-STATIC-001; EV-008; EV-009; EV-010; EV-011</x:v>
+        <x:v>TC-P9-STATIC-001; TC-P10-STATIC-001; EV-011; EV-019</x:v>
       </x:c>
       <x:c r="G32" s="24" t="str">
         <x:v>부분 자동 검증 PASS / External Verification Pending</x:v>
@@ -5365,12 +5404,12 @@
         <x:v>FR-UI-016~018</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="136" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A136" s="63" t="str">
         <x:v>REQ-FUNC-048</x:v>
       </x:c>
       <x:c r="B136" s="63" t="str">
-        <x:v>RTU 요청과 실제 응답 또는 무응답을 동일 Sequence의 REQ/RES 또는 REQ/NO_RES CSV 행으로 기록</x:v>
+        <x:v>RTU 요청과 실제 응답 또는 무응답을 동일 Sequence의 REQ/RES 또는 REQ/NO_RES CSV 행으로 빠짐없이 기록하고, 같은 Dequeue 문자열을 별도 Consumer 없이 최근 10줄 Panel 표시에 재사용</x:v>
       </x:c>
       <x:c r="C136" s="63" t="str">
         <x:v>FS-RTULOG-001</x:v>
@@ -5379,24 +5418,24 @@
         <x:v>DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E136" s="63" t="str">
-        <x:v>Transaction pair·overflow·send result</x:v>
+        <x:v>Transaction pair·overflow·send result·single drain panel reuse</x:v>
       </x:c>
       <x:c r="F136" s="63" t="str">
-        <x:v>TC-V03-AUTO-001; EV-018</x:v>
+        <x:v>TC-V03-AUTO-001; TC-P10-STATIC-001; EV-018~019</x:v>
       </x:c>
       <x:c r="G136" s="63" t="str">
-        <x:v>Automated PASS / External Pending</x:v>
+        <x:v>Automated/Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="H136" s="63" t="str">
-        <x:v>LOG-018~024</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" ht="39.599998474121094" hidden="0" customHeight="1">
+        <x:v>LOG-018~028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A137" s="63" t="str">
         <x:v>REQ-FUNC-049</x:v>
       </x:c>
       <x:c r="B137" s="63" t="str">
-        <x:v>RTU Log 파일 Open 성공 후 Capture를 시작하고, OFF·종료 시 최대 2,000ms Idle 대기 후 완료 행을 배출</x:v>
+        <x:v>RTU Log 파일 Open 성공 후 Capture를 시작하고 OFF·종료 시 최대 2,000ms Idle 대기 후 완료 행을 배출한다. CAPL Output View는 설정 이름으로 최근 10줄을 200ms 이상 간격 Overwrite하며 실패가 CSV를 중단하지 않고 OFF 후 마지막 표시를 유지</x:v>
       </x:c>
       <x:c r="C137" s="63" t="str">
         <x:v>FS-RTULOG-001</x:v>
@@ -5405,16 +5444,16 @@
         <x:v>DC-19 RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="E137" s="63" t="str">
-        <x:v>Open-before-capture·2,000ms idle wait·drain</x:v>
+        <x:v>Open-before-capture·2,000ms idle wait·drain·최근10줄/200ms Output View</x:v>
       </x:c>
       <x:c r="F137" s="63" t="str">
-        <x:v>TC-V03-AUTO-001; TC-P9-STATIC-001; EV-018</x:v>
+        <x:v>TC-V03-AUTO-001; TC-P9-STATIC-001; TC-P10-STATIC-001; EV-018~019</x:v>
       </x:c>
       <x:c r="G137" s="63" t="str">
         <x:v>Automated/Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="H137" s="63" t="str">
-        <x:v>FR-UI-021; LOG-022~024; ERR-044</x:v>
+        <x:v>FR-UI-021~023; LOG-022~028; ERR-044</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="52.79999923706055" hidden="0" customHeight="1">
@@ -5422,7 +5461,7 @@
         <x:v>REQ-IF-015</x:v>
       </x:c>
       <x:c r="B138" s="63" t="str">
-        <x:v>CAPL DLL Export Table은 Appendix A의 v0.4.0 23개 Entry를 정확히 제공하고 제거된 Monitoring·Change Queue API를 공개하지 않는다</x:v>
+        <x:v>CAPL DLL Export Table은 Appendix A의 v0.5.0 23개 Entry를 정확히 제공하고 제거된 Monitoring·Change Queue API를 공개하지 않는다</x:v>
       </x:c>
       <x:c r="C138" s="63" t="str">
         <x:v>FS-INIT-001; FS-MON-003; FS-DEVICE-001; FS-RTULOG-001</x:v>
@@ -5477,7 +5516,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R850ab91f2a644e33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5c26bf976754e3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6216,19 +6255,19 @@
         <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>ReadOption은 최대 200개 Rule의 0x80 Periodic 선택만 제어하고 여러 변경을 다음 1,000ms Cycle 경계에 원자 적용해야 한다.</x:v>
+        <x:v>ReadOption은 최대 200개 Rule의 0x80 Periodic 선택만 제어하고 다음 1,000ms Cycle 경계에 원자 적용해야 한다. Monitoring::Btn_ReadOption은 int32 Scalar 편의 버튼으로만 제공하며 별도 CAPL Handler 없이 기존 Check_ReadOption[200], 100ms Candidate 동기화와 Cycle 적용 정책을 유지해야 한다.</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
         <x:v>FR-CAN-020~027,047,057</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>FS-MON-002</x:v>
+        <x:v>FS-MON-002; FS-UI-001</x:v>
       </x:c>
       <x:c r="F32" s="9" t="str">
-        <x:v>CAPL Monitoring</x:v>
+        <x:v>CAPL Monitoring; CAPL UI</x:v>
       </x:c>
       <x:c r="G32" s="9" t="str">
-        <x:v>다중 Checkbox 원자 적용·복원 시험</x:v>
+        <x:v>Btn_ReadOption int32 Scalar/no-handler, Check_ReadOption[200] 유지 및 Candidate/Applied 원자 적용 검사</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="32" customHeight="1">
@@ -8600,7 +8639,7 @@
         <x:v>CAPL source contract와 EV-017</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="136" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A136" s="63" t="str">
         <x:v>REQ-FUNC-048</x:v>
       </x:c>
@@ -8608,10 +8647,10 @@
         <x:v>Diagnostics</x:v>
       </x:c>
       <x:c r="C136" s="63" t="str">
-        <x:v>RTU 요청과 실제 응답 또는 무응답을 동일 Sequence의 REQ/RES 또는 REQ/NO_RES CSV 행으로 기록</x:v>
+        <x:v>RTU 요청과 실제 응답 또는 무응답을 동일 Sequence의 REQ/RES 또는 REQ/NO_RES CSV 행으로 빠짐없이 기록하고, 같은 Dequeue 문자열을 별도 Consumer 없이 최근 10줄 Panel 표시에 재사용</x:v>
       </x:c>
       <x:c r="D136" s="63" t="str">
-        <x:v>LOG-018~024</x:v>
+        <x:v>LOG-018~028</x:v>
       </x:c>
       <x:c r="E136" s="63" t="str">
         <x:v>FS-RTULOG-001</x:v>
@@ -8620,10 +8659,10 @@
         <x:v>DC-19</x:v>
       </x:c>
       <x:c r="G136" s="63" t="str">
-        <x:v>RtuLogQueue/PortWorker 자동 시험과 EV-018</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>RtuLogQueue/PortWorker 자동 시험, CAPL 단일 Consumer 정적 계약과 EV-018~019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A137" s="63" t="str">
         <x:v>REQ-FUNC-049</x:v>
       </x:c>
@@ -8631,10 +8670,10 @@
         <x:v>Diagnostics</x:v>
       </x:c>
       <x:c r="C137" s="63" t="str">
-        <x:v>RTU Log 파일 Open 성공 후 Capture를 시작하고, OFF·종료 시 최대 2,000ms Idle 대기 후 완료 행을 배출</x:v>
+        <x:v>RTU Log 파일 Open 성공 후 Capture를 시작하고 OFF·종료 시 최대 2,000ms Idle 대기 후 완료 행을 배출한다. CAPL Output View는 설정 이름으로 최근 10줄을 200ms 이상 간격 Overwrite하며 실패가 CSV를 중단하지 않고 OFF 후 마지막 표시를 유지</x:v>
       </x:c>
       <x:c r="D137" s="63" t="str">
-        <x:v>FR-UI-021; LOG-022~024; ERR-044</x:v>
+        <x:v>FR-UI-021~023; LOG-022~028; ERR-044</x:v>
       </x:c>
       <x:c r="E137" s="63" t="str">
         <x:v>FS-RTULOG-001</x:v>
@@ -8643,7 +8682,7 @@
         <x:v>DC-19</x:v>
       </x:c>
       <x:c r="G137" s="63" t="str">
-        <x:v>Core/Integration/CAPL source contract와 EV-018</x:v>
+        <x:v>Core/Integration/CAPL source contract와 EV-018~019</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8654,7 +8693,7 @@
         <x:v>API</x:v>
       </x:c>
       <x:c r="C138" s="63" t="str">
-        <x:v>CAPL DLL Export Table은 Appendix A의 v0.4.0 23개 Entry를 정확히 제공하고 제거된 Monitoring·Change Queue API를 공개하지 않는다</x:v>
+        <x:v>CAPL DLL Export Table은 Appendix A의 v0.5.0 23개 Entry를 정확히 제공하고 제거된 Monitoring·Change Queue API를 공개하지 않는다</x:v>
       </x:c>
       <x:c r="D138" s="63" t="str">
         <x:v>IF-API-001~008; IF-API-011; IF-API-014~027; COMP-009</x:v>
@@ -8695,7 +8734,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8467b2888f743c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a0611f3cc0146a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9154,7 +9193,7 @@
         <x:v>FS-RTULOG-001</x:v>
       </x:c>
       <x:c r="B41" s="63" t="str">
-        <x:v>RTU 요청·응답 CSV 기록</x:v>
+        <x:v>RTU 전체 CSV 및 최근 10줄 CAPL Output View</x:v>
       </x:c>
       <x:c r="C41" s="63" t="str">
         <x:v>REQ-FUNC-048~049; REQ-IF-015~016</x:v>
@@ -9163,7 +9202,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67be2c7f869f476c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R343186bef1974b68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9350,7 +9389,7 @@
         <x:v>CAPL UI</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>Connect/ReadSwitch, Manual Write Data[122], Signal System Variable Adapter, Register Read UI 미제공, Error Queue Stats 변화기반 진단 출력</x:v>
+        <x:v>Connect/ReadSwitch, Btn_ReadOption int32 Scalar 편의 변수(no-handler), Manual Write Data[122], Signal System Variable Adapter, Register Read UI 미제공, Error Queue Stats 변화기반 진단 출력</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -9394,13 +9433,13 @@
         <x:v>RTU Log Pipeline</x:v>
       </x:c>
       <x:c r="C20" s="63" t="str">
-        <x:v>PortWorker 관측점, Transaction Queue, REQ/RES·NO_RES pairing과 CAPL-only CSV Writer</x:v>
+        <x:v>PortWorker 관측점, Transaction Queue, REQ/RES·NO_RES pairing, CAPL-only 전체 CSV Writer와 동일 Drain 문자열의 최근 10줄·200ms Output View</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51fb07d3bff146b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R941f46324778426f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9507,7 +9546,7 @@
         <x:v>External Test Result</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>18건 Not Tested</x:v>
+        <x:v>19건 Not Tested</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx</x:v>
@@ -9538,7 +9577,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdddb4b30b6e74683"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bdaeff5f72c40fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9845,7 +9884,7 @@
       <x:c r="D7" s="35" t="str">
         <x:v>CANalyzer 13 x86</x:v>
       </x:c>
-      <x:c r="E7" s="186" t="str">
+      <x:c r="E7" s="196" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
@@ -9891,25 +9930,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="187" t="str">
+      <x:c r="A1" s="197" t="str">
         <x:v>Test Case ID</x:v>
       </x:c>
-      <x:c r="B1" s="187" t="str">
+      <x:c r="B1" s="197" t="str">
         <x:v>Phase</x:v>
       </x:c>
-      <x:c r="C1" s="187" t="str">
+      <x:c r="C1" s="197" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D1" s="187" t="str">
+      <x:c r="D1" s="197" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="E1" s="187" t="str">
+      <x:c r="E1" s="197" t="str">
         <x:v>Method</x:v>
       </x:c>
-      <x:c r="F1" s="187" t="str">
+      <x:c r="F1" s="197" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="G1" s="187" t="str">
+      <x:c r="G1" s="197" t="str">
         <x:v>External Follow-up</x:v>
       </x:c>
     </x:row>
@@ -9929,7 +9968,7 @@
       <x:c r="E2" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F2" s="188" t="str">
+      <x:c r="F2" s="198" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G2" s="63" t="str">
@@ -9952,7 +9991,7 @@
       <x:c r="E3" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F3" s="188" t="str">
+      <x:c r="F3" s="198" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G3" s="63" t="str">
@@ -9975,7 +10014,7 @@
       <x:c r="E4" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F4" s="188" t="str">
+      <x:c r="F4" s="198" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G4" s="63" t="str">
@@ -9998,7 +10037,7 @@
       <x:c r="E5" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F5" s="188" t="str">
+      <x:c r="F5" s="198" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G5" s="63" t="str">
@@ -10021,7 +10060,7 @@
       <x:c r="E6" s="63" t="str">
         <x:v>M485E.Core.Tests + FakeSerialTransport</x:v>
       </x:c>
-      <x:c r="F6" s="188" t="str">
+      <x:c r="F6" s="198" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G6" s="63" t="str">
@@ -10044,7 +10083,7 @@
       <x:c r="E7" s="63" t="str">
         <x:v>M485E.IntegrationTests</x:v>
       </x:c>
-      <x:c r="F7" s="188" t="str">
+      <x:c r="F7" s="198" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G7" s="63" t="str">
@@ -10067,14 +10106,14 @@
       <x:c r="E8" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1 + CANalyzer 13 Exec32 caplcompexec</x:v>
       </x:c>
-      <x:c r="F8" s="188" t="str">
+      <x:c r="F8" s="198" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="63" t="str">
-        <x:v>EV-008~EV-011, EV-016</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
+        <x:v>EV-008~EV-011, EV-016, EV-019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A9" s="63" t="str">
         <x:v>TC-P10-STATIC-001</x:v>
       </x:c>
@@ -10085,19 +10124,19 @@
         <x:v>Static</x:v>
       </x:c>
       <x:c r="D9" s="63" t="str">
-        <x:v>UI System Variable adapter, Manual Write Data[122], Signal Control, Register Read UI 부재 계약</x:v>
+        <x:v>UI System Variable adapter, Btn_ReadOption int32 Scalar/no-handler, Check_ReadOption[200] 유지, RTU Log 단일 Drain·최근 10줄·200ms putValueToControl, Manual Write Data[122], Signal Control, Register Read UI 부재 계약</x:v>
       </x:c>
       <x:c r="E9" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1; Main compile in configured CANalyzer project</x:v>
       </x:c>
-      <x:c r="F9" s="189" t="str">
+      <x:c r="F9" s="199" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="G9" s="63" t="str">
-        <x:v>EV-011~EV-013, EV-016</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="66" hidden="0" customHeight="1">
+        <x:v>EV-011~EV-013, EV-016, EV-019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A10" s="63" t="str">
         <x:v>TC-REG-AUTO-001</x:v>
       </x:c>
@@ -10108,16 +10147,16 @@
         <x:v>Automated</x:v>
       </x:c>
       <x:c r="D10" s="63" t="str">
-        <x:v>Windows x86/x64 Debug/Release, /W4 /WX, ErrorCodes 91/PublicConstants 189, 23 API ABI, RuleDataMeta[9], RTU 로그 idle wait, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
+        <x:v>Windows x86/x64 Debug/Release, /W4 /WX, ErrorCodes 91/PublicConstants 189, 23 API ABI, RuleDataMeta[9], RTU 로그 idle wait·단일 Drain Panel adapter, 1/4 Port·5 Port 경계, 누락 PortSlot, contract/core/integration/CAPL probes</x:v>
       </x:c>
       <x:c r="E10" s="63" t="str">
         <x:v>MSBuild + CMake + CTest + CANalyzer 13 x86 CAPL compiler</x:v>
       </x:c>
-      <x:c r="F10" s="188" t="str">
+      <x:c r="F10" s="198" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G10" s="63" t="str">
-        <x:v>EV-001~EV-018</x:v>
+        <x:v>EV-001~EV-019</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -10136,16 +10175,16 @@
       <x:c r="E11" s="63" t="str">
         <x:v>M485E.Core.Tests + M485E.IntegrationTests + Test-M485ECaplSources.ps1</x:v>
       </x:c>
-      <x:c r="F11" s="189" t="str">
+      <x:c r="F11" s="199" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G11" s="63" t="str">
-        <x:v>EV-017~EV-018</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>EV-017~EV-019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A12" s="63" t="str">
-        <x:v>EV-001~EV-018</x:v>
+        <x:v>EV-001~EV-019</x:v>
       </x:c>
       <x:c r="B12" s="63" t="str">
         <x:v>External</x:v>
@@ -10154,12 +10193,12 @@
         <x:v>External</x:v>
       </x:c>
       <x:c r="D12" s="63" t="str">
-        <x:v>CANalyzer 9.x/18, SystemBase Multi USB-485, Board, Panel, virtual CAN, RTU CSV</x:v>
+        <x:v>CANalyzer 9.x/18, SystemBase Multi USB-485, Board, Panel, CAPL Output View, virtual CAN, RTU CSV</x:v>
       </x:c>
       <x:c r="E12" s="63" t="str">
         <x:v>External Verification Guide</x:v>
       </x:c>
-      <x:c r="F12" s="188" t="str">
+      <x:c r="F12" s="198" t="str">
         <x:v>Not Tested</x:v>
       </x:c>
       <x:c r="G12" s="63" t="str">
@@ -10182,7 +10221,7 @@
       <x:c r="E13" s="63" t="str">
         <x:v>CANalyzer 13 Exec32 caplcompexec.exe</x:v>
       </x:c>
-      <x:c r="F13" s="188" t="str">
+      <x:c r="F13" s="198" t="str">
         <x:v>PASS (warning-free)</x:v>
       </x:c>
       <x:c r="G13" s="63" t="str">

--- a/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
+++ b/docs/04_Traceability/Modbus485Emulator_Traceability_Matrix.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R9869f5ea61a442e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R4ee31e3544f642d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="Rbd19b3ee850444ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="Rbb215e9051664201"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="R6528b4b8ab9e4d69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R4a88a93129ed4034"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R34fdfe7f134a4029"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R1eb5e5a782dd4a30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R07d6a19c9c1a44b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.3.0 Traceability" sheetId="10" r:id="Rdb5d9cf260854225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R1b4fb6db7b84491c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R5ab766f0f5ae4bbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R168c6cc0af8748f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Specs" sheetId="4" r:id="R61937d8273884b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Components" sheetId="5" r:id="R2658dc137f5f496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Inputs" sheetId="6" r:id="R3cb1e1d172ca43aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 Verification" sheetId="7" r:id="R7221a169bd1d47df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 Verification" sheetId="8" r:id="R9b3b3145a02a40dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3-10 Verification" sheetId="9" r:id="R0ba27448f7414c54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.3.0 Traceability" sheetId="10" r:id="R14e1374f79d0475c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -86,7 +86,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="75">
+  <x:fills count="78">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -458,6 +458,21 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -535,7 +550,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="206">
+  <x:cellXfs count="218">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1062,6 +1077,36 @@
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="74" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="76" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="77" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="77" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="75" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="76" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="76" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="76" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="76" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="76" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="77" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1458,7 +1503,7 @@
         <x:v>Design Components</x:v>
       </x:c>
       <x:c r="E5" s="9" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F5"/>
     </x:row>
@@ -1473,7 +1518,7 @@
         <x:v>Requirements with FS</x:v>
       </x:c>
       <x:c r="E6" s="9" t="n">
-        <x:v>138</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F6"/>
     </x:row>
@@ -1482,13 +1527,13 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>0.5.0</x:v>
+        <x:v>0.6.0</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Requirements with Design</x:v>
       </x:c>
       <x:c r="E7" s="9" t="n">
-        <x:v>138</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F7"/>
     </x:row>
@@ -1503,7 +1548,7 @@
         <x:v>Requirements with Verification</x:v>
       </x:c>
       <x:c r="E8" s="9" t="n">
-        <x:v>138</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F8"/>
     </x:row>
@@ -1512,7 +1557,7 @@
         <x:v>Baseline Date</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>Test Case IDs</x:v>
@@ -1526,13 +1571,13 @@
         <x:v>Normalized Requirements</x:v>
       </x:c>
       <x:c r="B10" s="9" t="n">
-        <x:v>138</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>Baseline Coverage</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>138 / 138 mapped</x:v>
+        <x:v>148 / 148 mapped</x:v>
       </x:c>
       <x:c r="F10"/>
     </x:row>
@@ -1541,7 +1586,7 @@
         <x:v>Functional Specifications</x:v>
       </x:c>
       <x:c r="B11" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1669,25 +1714,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="197" t="str">
+      <x:c r="A1" s="207" t="str">
         <x:v>Requirement</x:v>
       </x:c>
-      <x:c r="B1" s="197" t="str">
+      <x:c r="B1" s="207" t="str">
         <x:v>Functional Specification</x:v>
       </x:c>
-      <x:c r="C1" s="197" t="str">
+      <x:c r="C1" s="207" t="str">
         <x:v>Design</x:v>
       </x:c>
-      <x:c r="D1" s="197" t="str">
+      <x:c r="D1" s="207" t="str">
         <x:v>Implementation</x:v>
       </x:c>
-      <x:c r="E1" s="197" t="str">
+      <x:c r="E1" s="207" t="str">
         <x:v>Automated Verification</x:v>
       </x:c>
-      <x:c r="F1" s="197" t="str">
+      <x:c r="F1" s="207" t="str">
         <x:v>External Verification</x:v>
       </x:c>
-      <x:c r="G1" s="197" t="str">
+      <x:c r="G1" s="207" t="str">
         <x:v>Status</x:v>
       </x:c>
     </x:row>
@@ -1710,7 +1755,7 @@
       <x:c r="F2" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G2" s="199" t="str">
+      <x:c r="G2" s="209" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1733,7 +1778,7 @@
       <x:c r="F3" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G3" s="199" t="str">
+      <x:c r="G3" s="209" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1756,7 +1801,7 @@
       <x:c r="F4" s="63" t="str">
         <x:v>EV-017</x:v>
       </x:c>
-      <x:c r="G4" s="199" t="str">
+      <x:c r="G4" s="209" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1779,7 +1824,7 @@
       <x:c r="F5" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G5" s="199" t="str">
+      <x:c r="G5" s="209" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1802,7 +1847,7 @@
       <x:c r="F6" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G6" s="199" t="str">
+      <x:c r="G6" s="209" t="str">
         <x:v>Auto/Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1825,7 +1870,7 @@
       <x:c r="F7" s="63" t="str">
         <x:v>EV-001</x:v>
       </x:c>
-      <x:c r="G7" s="199" t="str">
+      <x:c r="G7" s="209" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1848,7 +1893,7 @@
       <x:c r="F8" s="63" t="str">
         <x:v>EV-018</x:v>
       </x:c>
-      <x:c r="G8" s="199" t="str">
+      <x:c r="G8" s="209" t="str">
         <x:v>Auto/Static PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -1871,7 +1916,7 @@
       <x:c r="F9" s="63" t="str">
         <x:v>EV-017~EV-018</x:v>
       </x:c>
-      <x:c r="G9" s="199" t="str">
+      <x:c r="G9" s="209" t="str">
         <x:v>Auto PASS / External Pending</x:v>
       </x:c>
     </x:row>
@@ -5461,7 +5506,7 @@
         <x:v>REQ-IF-015</x:v>
       </x:c>
       <x:c r="B138" s="63" t="str">
-        <x:v>CAPL DLL Export Table은 Appendix A의 v0.5.0 23개 Entry를 정확히 제공하고 제거된 Monitoring·Change Queue API를 공개하지 않는다</x:v>
+        <x:v>CAPL DLL Export Table은 Appendix A의 v0.6.0 23개 Entry를 정확히 제공하고 제거된 Monitoring·Change Queue API를 공개하지 않는다</x:v>
       </x:c>
       <x:c r="C138" s="63" t="str">
         <x:v>FS-INIT-001; FS-MON-003; FS-DEVICE-001; FS-RTULOG-001</x:v>
@@ -5506,6 +5551,266 @@
       </x:c>
       <x:c r="H139" s="63" t="str">
         <x:v>IF-LIMIT-009; LOG-023~024; ERR-044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A140" s="63" t="str">
+        <x:v>REQ-DPG-001</x:v>
+      </x:c>
+      <x:c r="B140" s="63" t="str">
+        <x:v>Device CSV와 각 CSV_DB_Name Register Map을 Core Loader 계약과 같은 Header·행·값·경로 규칙으로 분석하고 오류 파일/행/열/원인을 표시</x:v>
+      </x:c>
+      <x:c r="C140" s="63" t="str">
+        <x:v>FS-DPG-001</x:v>
+      </x:c>
+      <x:c r="D140" s="63" t="str">
+        <x:v>DC-20 Device Panel Generator</x:v>
+      </x:c>
+      <x:c r="E140" s="63" t="str">
+        <x:v>정상/오류 CSV fixture와 Core Loader 규칙 비교</x:v>
+      </x:c>
+      <x:c r="F140" s="63" t="str">
+        <x:v>TC-DPG-AUTO-001; EV-020</x:v>
+      </x:c>
+      <x:c r="G140" s="63" t="str">
+        <x:v>Automated PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H140" s="63" t="str">
+        <x:v>FR-DPG-001~003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A141" s="63" t="str">
+        <x:v>REQ-DPG-002</x:v>
+      </x:c>
+      <x:c r="B141" s="63" t="str">
+        <x:v>EXE 위치 기준 Output을 임시 경로에서 완전 생성·검증한 뒤 Manifest 소유 Output만 원자 교체하고 동일 입력은 byte-identical 결과를 생성</x:v>
+      </x:c>
+      <x:c r="C141" s="63" t="str">
+        <x:v>FS-DPG-001</x:v>
+      </x:c>
+      <x:c r="D141" s="63" t="str">
+        <x:v>DC-20 Device Panel Generator</x:v>
+      </x:c>
+      <x:c r="E141" s="63" t="str">
+        <x:v>deterministic output, transaction rollback, manifest guard와 다른 cwd EXE smoke</x:v>
+      </x:c>
+      <x:c r="F141" s="63" t="str">
+        <x:v>TC-DPG-AUTO-001; EV-020</x:v>
+      </x:c>
+      <x:c r="G141" s="63" t="str">
+        <x:v>Automated PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H141" s="63" t="str">
+        <x:v>FR-DPG-004~005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A142" s="63" t="str">
+        <x:v>REQ-DPG-003</x:v>
+      </x:c>
+      <x:c r="B142" s="63" t="str">
+        <x:v>실제 Device Index와 Decimal Address 31-register Group, 15행 Page로 독립 XVP Fragment를 만들고 고유 Object/Control/TabIndex와 정확한 바인딩을 제공</x:v>
+      </x:c>
+      <x:c r="C142" s="63" t="str">
+        <x:v>FS-DPG-002</x:v>
+      </x:c>
+      <x:c r="D142" s="63" t="str">
+        <x:v>DC-20 Device Panel Generator</x:v>
+      </x:c>
+      <x:c r="E142" s="63" t="str">
+        <x:v>34/45/72/150 Signal XVP XML·Address group·page·binding 검사</x:v>
+      </x:c>
+      <x:c r="F142" s="63" t="str">
+        <x:v>TC-DPG-AUTO-001; EV-020</x:v>
+      </x:c>
+      <x:c r="G142" s="63" t="str">
+        <x:v>Automated PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H142" s="63" t="str">
+        <x:v>FR-DPG-006~009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A143" s="63" t="str">
+        <x:v>REQ-DPG-004</x:v>
+      </x:c>
+      <x:c r="B143" s="63" t="str">
+        <x:v>Common 및 Device별 PhysicalValue/RawHex/Command/Snapshot/Result System Variable 계약을 생성하고 각 Device baseline과 결과를 격리</x:v>
+      </x:c>
+      <x:c r="C143" s="63" t="str">
+        <x:v>FS-DPG-002</x:v>
+      </x:c>
+      <x:c r="D143" s="63" t="str">
+        <x:v>DC-20 Generator; DC-21 Generated CAPL</x:v>
+      </x:c>
+      <x:c r="E143" s="63" t="str">
+        <x:v>vsysvar schema와 sample generated artifact stale 검사</x:v>
+      </x:c>
+      <x:c r="F143" s="63" t="str">
+        <x:v>TC-DPG-AUTO-001; EV-020</x:v>
+      </x:c>
+      <x:c r="G143" s="63" t="str">
+        <x:v>Automated/Static PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H143" s="63" t="str">
+        <x:v>FR-DPG-010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A144" s="63" t="str">
+        <x:v>REQ-DPG-005</x:v>
+      </x:c>
+      <x:c r="B144" s="63" t="str">
+        <x:v>Raw Hex는 정규화 논리 Signal Frame에서 Start_Bit/Size로 추출한 1~64bit unsigned pattern을 대문자·leading zero로 표시하고 frame 공유 Signal은 Register Read를 재사용</x:v>
+      </x:c>
+      <x:c r="C144" s="63" t="str">
+        <x:v>FS-DPG-003</x:v>
+      </x:c>
+      <x:c r="D144" s="63" t="str">
+        <x:v>DC-21 Generated Device Panel CAPL</x:v>
+      </x:c>
+      <x:c r="E144" s="63" t="str">
+        <x:v>1~64bit, endian, bit crossing, signed/float/double/full-range raw vectors</x:v>
+      </x:c>
+      <x:c r="F144" s="63" t="str">
+        <x:v>TC-DPG-AUTO-001; EV-020</x:v>
+      </x:c>
+      <x:c r="G144" s="63" t="str">
+        <x:v>Automated/Static PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H144" s="63" t="str">
+        <x:v>FR-DPG-011~012</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A145" s="63" t="str">
+        <x:v>REQ-DPG-006</x:v>
+      </x:c>
+      <x:c r="B145" s="63" t="str">
+        <x:v>Display Update는 15 Signal bounded timer chunk로 Physical/Raw를 요청 시에만 읽고 성공한 전체 결과만 baseline/SnapshotValid로 게시하며 재진입을 Busy로 거부</x:v>
+      </x:c>
+      <x:c r="C145" s="63" t="str">
+        <x:v>FS-DPG-003</x:v>
+      </x:c>
+      <x:c r="D145" s="63" t="str">
+        <x:v>DC-21 Generated Device Panel CAPL</x:v>
+      </x:c>
+      <x:c r="E145" s="63" t="str">
+        <x:v>chunk/busy/snapshot/raw stale-clear CAPL source contract</x:v>
+      </x:c>
+      <x:c r="F145" s="63" t="str">
+        <x:v>TC-DPG-AUTO-001; EV-020</x:v>
+      </x:c>
+      <x:c r="G145" s="63" t="str">
+        <x:v>Static PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H145" s="63" t="str">
+        <x:v>FR-DPG-013</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A146" s="63" t="str">
+        <x:v>REQ-DPG-007</x:v>
+      </x:c>
+      <x:c r="B146" s="63" t="str">
+        <x:v>Send Changed는 유효 Snapshot baseline과 다른 Signal만 CSV 순서로 Write하고 첫 실패에서 중단하며 성공 Signal read-back·양자화·결과를 반영</x:v>
+      </x:c>
+      <x:c r="C146" s="63" t="str">
+        <x:v>FS-DPG-004</x:v>
+      </x:c>
+      <x:c r="D146" s="63" t="str">
+        <x:v>DC-21 Generated Device Panel CAPL</x:v>
+      </x:c>
+      <x:c r="E146" s="63" t="str">
+        <x:v>baseline compare, ordered partial send, read-back/result source contract</x:v>
+      </x:c>
+      <x:c r="F146" s="63" t="str">
+        <x:v>TC-DPG-AUTO-001; EV-020</x:v>
+      </x:c>
+      <x:c r="G146" s="63" t="str">
+        <x:v>Static PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H146" s="63" t="str">
+        <x:v>FR-DPG-014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A147" s="63" t="str">
+        <x:v>REQ-DPG-008</x:v>
+      </x:c>
+      <x:c r="B147" s="63" t="str">
+        <x:v>Device Reset은 ResetDevice 후 read-back하고 Reset All은 실제 Index 오름차순으로 비원자 처리해 완료 수·첫 실패 Index·Result를 게시</x:v>
+      </x:c>
+      <x:c r="C147" s="63" t="str">
+        <x:v>FS-DPG-004</x:v>
+      </x:c>
+      <x:c r="D147" s="63" t="str">
+        <x:v>DC-21 Generated Device Panel CAPL</x:v>
+      </x:c>
+      <x:c r="E147" s="63" t="str">
+        <x:v>momentary reset, ascending sparse Index reset-all/result source contract</x:v>
+      </x:c>
+      <x:c r="F147" s="63" t="str">
+        <x:v>TC-DPG-AUTO-001; EV-020</x:v>
+      </x:c>
+      <x:c r="G147" s="63" t="str">
+        <x:v>Static PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H147" s="63" t="str">
+        <x:v>FR-DPG-015~016</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A148" s="63" t="str">
+        <x:v>REQ-DPG-009</x:v>
+      </x:c>
+      <x:c r="B148" s="63" t="str">
+        <x:v>Refresh 성공 시 모든 Snapshot을 무효화하고 Display Update가 Device 전체 동일시점 Snapshot이 아니며 Send/Reset All이 전체 Transaction 원자적이지 않음을 보존·표시</x:v>
+      </x:c>
+      <x:c r="C148" s="63" t="str">
+        <x:v>FS-DPG-004</x:v>
+      </x:c>
+      <x:c r="D148" s="63" t="str">
+        <x:v>DC-21 Generated Device Panel CAPL</x:v>
+      </x:c>
+      <x:c r="E148" s="63" t="str">
+        <x:v>Refresh 성공 invalidate, busy와 비원자 경계 정적/외부 시험</x:v>
+      </x:c>
+      <x:c r="F148" s="63" t="str">
+        <x:v>TC-DPG-AUTO-001; EV-020</x:v>
+      </x:c>
+      <x:c r="G148" s="63" t="str">
+        <x:v>Static PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H148" s="63" t="str">
+        <x:v>FR-DPG-017~019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A149" s="63" t="str">
+        <x:v>REQ-DPG-010</x:v>
+      </x:c>
+      <x:c r="B149" s="63" t="str">
+        <x:v>PyInstaller one-file Generator, Sample generated Config, Manifest/COPY_GUIDE와 회사 적용·재생성 절차를 배포하며 실제 회사 Map을 저장소에 포함하지 않음</x:v>
+      </x:c>
+      <x:c r="C149" s="63" t="str">
+        <x:v>FS-DPG-005</x:v>
+      </x:c>
+      <x:c r="D149" s="63" t="str">
+        <x:v>DC-20 Device Panel Generator</x:v>
+      </x:c>
+      <x:c r="E149" s="63" t="str">
+        <x:v>one-file EXE, portable package, COPY_GUIDE, manifest/hash 검사</x:v>
+      </x:c>
+      <x:c r="F149" s="63" t="str">
+        <x:v>TC-DPG-AUTO-001; EV-020</x:v>
+      </x:c>
+      <x:c r="G149" s="63" t="str">
+        <x:v>Automated PASS / External Pending</x:v>
+      </x:c>
+      <x:c r="H149" s="63" t="str">
+        <x:v>FR-DPG-020</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5516,7 +5821,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5c26bf976754e3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R355494b01d764169"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8693,7 +8998,7 @@
         <x:v>API</x:v>
       </x:c>
       <x:c r="C138" s="63" t="str">
-        <x:v>CAPL DLL Export Table은 Appendix A의 v0.5.0 23개 Entry를 정확히 제공하고 제거된 Monitoring·Change Queue API를 공개하지 않는다</x:v>
+        <x:v>CAPL DLL Export Table은 Appendix A의 v0.6.0 23개 Entry를 정확히 제공하고 제거된 Monitoring·Change Queue API를 공개하지 않는다</x:v>
       </x:c>
       <x:c r="D138" s="63" t="str">
         <x:v>IF-API-001~008; IF-API-011; IF-API-014~027; COMP-009</x:v>
@@ -8731,10 +9036,240 @@
         <x:v>Queue 경계·overflow·idle wake/timeout·pair 보존 자동 시험과 EV-018</x:v>
       </x:c>
     </x:row>
+    <x:row r="140" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A140" s="63" t="str">
+        <x:v>REQ-DPG-001</x:v>
+      </x:c>
+      <x:c r="B140" s="63" t="str">
+        <x:v>Generator</x:v>
+      </x:c>
+      <x:c r="C140" s="63" t="str">
+        <x:v>Device CSV와 각 CSV_DB_Name Register Map을 Core Loader 계약과 같은 Header·행·값·경로 규칙으로 분석하고 오류 파일/행/열/원인을 표시</x:v>
+      </x:c>
+      <x:c r="D140" s="63" t="str">
+        <x:v>FR-DPG-001~003</x:v>
+      </x:c>
+      <x:c r="E140" s="63" t="str">
+        <x:v>FS-DPG-001</x:v>
+      </x:c>
+      <x:c r="F140" s="63" t="str">
+        <x:v>DC-20</x:v>
+      </x:c>
+      <x:c r="G140" s="63" t="str">
+        <x:v>Python 자동시험과 EV-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A141" s="63" t="str">
+        <x:v>REQ-DPG-002</x:v>
+      </x:c>
+      <x:c r="B141" s="63" t="str">
+        <x:v>Generator</x:v>
+      </x:c>
+      <x:c r="C141" s="63" t="str">
+        <x:v>EXE 위치 기준 Output을 임시 경로에서 완전 생성·검증한 뒤 Manifest 소유 Output만 원자 교체하고 동일 입력은 byte-identical 결과를 생성</x:v>
+      </x:c>
+      <x:c r="D141" s="63" t="str">
+        <x:v>FR-DPG-004~005</x:v>
+      </x:c>
+      <x:c r="E141" s="63" t="str">
+        <x:v>FS-DPG-001</x:v>
+      </x:c>
+      <x:c r="F141" s="63" t="str">
+        <x:v>DC-20</x:v>
+      </x:c>
+      <x:c r="G141" s="63" t="str">
+        <x:v>transaction·determinism·manifest guard·다른 cwd EXE 시험과 EV-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A142" s="63" t="str">
+        <x:v>REQ-DPG-003</x:v>
+      </x:c>
+      <x:c r="B142" s="63" t="str">
+        <x:v>Panel</x:v>
+      </x:c>
+      <x:c r="C142" s="63" t="str">
+        <x:v>실제 Device Index와 Decimal Address 31-register Group, 15행 Page로 독립 XVP Fragment를 만들고 고유 Object/Control/TabIndex와 정확한 바인딩을 제공</x:v>
+      </x:c>
+      <x:c r="D142" s="63" t="str">
+        <x:v>FR-DPG-006~009</x:v>
+      </x:c>
+      <x:c r="E142" s="63" t="str">
+        <x:v>FS-DPG-002</x:v>
+      </x:c>
+      <x:c r="F142" s="63" t="str">
+        <x:v>DC-20</x:v>
+      </x:c>
+      <x:c r="G142" s="63" t="str">
+        <x:v>XVP XML·GroupBox·page·binding 자동시험과 EV-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A143" s="63" t="str">
+        <x:v>REQ-DPG-004</x:v>
+      </x:c>
+      <x:c r="B143" s="63" t="str">
+        <x:v>Interface</x:v>
+      </x:c>
+      <x:c r="C143" s="63" t="str">
+        <x:v>Common 및 Device별 PhysicalValue/RawHex/Command/Snapshot/Result System Variable 계약을 생성하고 각 Device baseline과 결과를 격리</x:v>
+      </x:c>
+      <x:c r="D143" s="63" t="str">
+        <x:v>FR-DPG-010</x:v>
+      </x:c>
+      <x:c r="E143" s="63" t="str">
+        <x:v>FS-DPG-002</x:v>
+      </x:c>
+      <x:c r="F143" s="63" t="str">
+        <x:v>DC-20; DC-21</x:v>
+      </x:c>
+      <x:c r="G143" s="63" t="str">
+        <x:v>generated vsysvar stale/source contract와 EV-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A144" s="63" t="str">
+        <x:v>REQ-DPG-005</x:v>
+      </x:c>
+      <x:c r="B144" s="63" t="str">
+        <x:v>Data</x:v>
+      </x:c>
+      <x:c r="C144" s="63" t="str">
+        <x:v>Raw Hex는 정규화 논리 Signal Frame에서 Start_Bit/Size로 추출한 1~64bit unsigned pattern을 대문자·leading zero로 표시하고 frame 공유 Signal은 Register Read를 재사용</x:v>
+      </x:c>
+      <x:c r="D144" s="63" t="str">
+        <x:v>FR-DPG-011~012</x:v>
+      </x:c>
+      <x:c r="E144" s="63" t="str">
+        <x:v>FS-DPG-003</x:v>
+      </x:c>
+      <x:c r="F144" s="63" t="str">
+        <x:v>DC-21</x:v>
+      </x:c>
+      <x:c r="G144" s="63" t="str">
+        <x:v>Endian/bit/nibble/frame-cache vector 자동시험과 EV-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A145" s="63" t="str">
+        <x:v>REQ-DPG-006</x:v>
+      </x:c>
+      <x:c r="B145" s="63" t="str">
+        <x:v>Panel</x:v>
+      </x:c>
+      <x:c r="C145" s="63" t="str">
+        <x:v>Display Update는 15 Signal bounded timer chunk로 Physical/Raw를 요청 시에만 읽고 성공한 전체 결과만 baseline/SnapshotValid로 게시하며 재진입을 Busy로 거부</x:v>
+      </x:c>
+      <x:c r="D145" s="63" t="str">
+        <x:v>FR-DPG-013</x:v>
+      </x:c>
+      <x:c r="E145" s="63" t="str">
+        <x:v>FS-DPG-003</x:v>
+      </x:c>
+      <x:c r="F145" s="63" t="str">
+        <x:v>DC-21</x:v>
+      </x:c>
+      <x:c r="G145" s="63" t="str">
+        <x:v>generated CAPL source contract와 EV-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A146" s="63" t="str">
+        <x:v>REQ-DPG-007</x:v>
+      </x:c>
+      <x:c r="B146" s="63" t="str">
+        <x:v>Panel</x:v>
+      </x:c>
+      <x:c r="C146" s="63" t="str">
+        <x:v>Send Changed는 유효 Snapshot baseline과 다른 Signal만 CSV 순서로 Write하고 첫 실패에서 중단하며 성공 Signal read-back·양자화·결과를 반영</x:v>
+      </x:c>
+      <x:c r="D146" s="63" t="str">
+        <x:v>FR-DPG-014</x:v>
+      </x:c>
+      <x:c r="E146" s="63" t="str">
+        <x:v>FS-DPG-004</x:v>
+      </x:c>
+      <x:c r="F146" s="63" t="str">
+        <x:v>DC-21</x:v>
+      </x:c>
+      <x:c r="G146" s="63" t="str">
+        <x:v>generated CAPL source contract와 EV-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A147" s="63" t="str">
+        <x:v>REQ-DPG-008</x:v>
+      </x:c>
+      <x:c r="B147" s="63" t="str">
+        <x:v>Panel</x:v>
+      </x:c>
+      <x:c r="C147" s="63" t="str">
+        <x:v>Device Reset은 ResetDevice 후 read-back하고 Reset All은 실제 Index 오름차순으로 비원자 처리해 완료 수·첫 실패 Index·Result를 게시</x:v>
+      </x:c>
+      <x:c r="D147" s="63" t="str">
+        <x:v>FR-DPG-015~016</x:v>
+      </x:c>
+      <x:c r="E147" s="63" t="str">
+        <x:v>FS-DPG-004</x:v>
+      </x:c>
+      <x:c r="F147" s="63" t="str">
+        <x:v>DC-21</x:v>
+      </x:c>
+      <x:c r="G147" s="63" t="str">
+        <x:v>generated CAPL source contract와 EV-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A148" s="63" t="str">
+        <x:v>REQ-DPG-009</x:v>
+      </x:c>
+      <x:c r="B148" s="63" t="str">
+        <x:v>Concurrency</x:v>
+      </x:c>
+      <x:c r="C148" s="63" t="str">
+        <x:v>Refresh 성공 시 모든 Snapshot을 무효화하고 Display Update가 Device 전체 동일시점 Snapshot이 아니며 Send/Reset All이 전체 Transaction 원자적이지 않음을 보존·표시</x:v>
+      </x:c>
+      <x:c r="D148" s="63" t="str">
+        <x:v>FR-DPG-017~019</x:v>
+      </x:c>
+      <x:c r="E148" s="63" t="str">
+        <x:v>FS-DPG-004</x:v>
+      </x:c>
+      <x:c r="F148" s="63" t="str">
+        <x:v>DC-21</x:v>
+      </x:c>
+      <x:c r="G148" s="63" t="str">
+        <x:v>refresh/busy/non-atomic source contract와 EV-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A149" s="63" t="str">
+        <x:v>REQ-DPG-010</x:v>
+      </x:c>
+      <x:c r="B149" s="63" t="str">
+        <x:v>Release</x:v>
+      </x:c>
+      <x:c r="C149" s="63" t="str">
+        <x:v>PyInstaller one-file Generator, Sample generated Config, Manifest/COPY_GUIDE와 회사 적용·재생성 절차를 배포하며 실제 회사 Map을 저장소에 포함하지 않음</x:v>
+      </x:c>
+      <x:c r="D149" s="63" t="str">
+        <x:v>FR-DPG-020</x:v>
+      </x:c>
+      <x:c r="E149" s="63" t="str">
+        <x:v>FS-DPG-005</x:v>
+      </x:c>
+      <x:c r="F149" s="63" t="str">
+        <x:v>DC-20</x:v>
+      </x:c>
+      <x:c r="G149" s="63" t="str">
+        <x:v>EXE/package/hash 자동시험과 EV-020</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a0611f3cc0146a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R213a7c266a614990"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9199,10 +9734,65 @@
         <x:v>REQ-FUNC-048~049; REQ-IF-015~016</x:v>
       </x:c>
     </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="A42" s="63" t="str">
+        <x:v>FS-DPG-001</x:v>
+      </x:c>
+      <x:c r="B42" s="63" t="str">
+        <x:v>Device/Register CSV 분석과 Transaction 생성</x:v>
+      </x:c>
+      <x:c r="C42" s="63" t="str">
+        <x:v>REQ-DPG-001~002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
+      <x:c r="A43" s="63" t="str">
+        <x:v>FS-DPG-002</x:v>
+      </x:c>
+      <x:c r="B43" s="63" t="str">
+        <x:v>XVP Fragment와 System Variable DB 생성</x:v>
+      </x:c>
+      <x:c r="C43" s="63" t="str">
+        <x:v>REQ-DPG-003~004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" s="63" t="str">
+        <x:v>FS-DPG-003</x:v>
+      </x:c>
+      <x:c r="B44" s="63" t="str">
+        <x:v>Raw Hex와 bounded Display Update</x:v>
+      </x:c>
+      <x:c r="C44" s="63" t="str">
+        <x:v>REQ-DPG-005~006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
+      <x:c r="A45" s="63" t="str">
+        <x:v>FS-DPG-004</x:v>
+      </x:c>
+      <x:c r="B45" s="63" t="str">
+        <x:v>Send Changed와 Device/All Reset</x:v>
+      </x:c>
+      <x:c r="C45" s="63" t="str">
+        <x:v>REQ-DPG-007~009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="15" hidden="0" customHeight="1">
+      <x:c r="A46" s="63" t="str">
+        <x:v>FS-DPG-005</x:v>
+      </x:c>
+      <x:c r="B46" s="63" t="str">
+        <x:v>Python-free 배포와 회사 적용 절차</x:v>
+      </x:c>
+      <x:c r="C46" s="63" t="str">
+        <x:v>REQ-DPG-010</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R343186bef1974b68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96ff1c0519b84583"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9436,10 +10026,32 @@
         <x:v>PortWorker 관측점, Transaction Queue, REQ/RES·NO_RES pairing, CAPL-only 전체 CSV Writer와 동일 Drain 문자열의 최근 10줄·200ms Output View</x:v>
       </x:c>
     </x:row>
+    <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A21" s="63" t="str">
+        <x:v>DC-20</x:v>
+      </x:c>
+      <x:c r="B21" s="63" t="str">
+        <x:v>Device Panel Generator</x:v>
+      </x:c>
+      <x:c r="C21" s="63" t="str">
+        <x:v>Python stdlib/tkinter GUI·CLI 공통 Parser/Generator, XVP·vsysvar·CAPL·Manifest Transaction 출력, PyInstaller one-file</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A22" s="63" t="str">
+        <x:v>DC-21</x:v>
+      </x:c>
+      <x:c r="B22" s="63" t="str">
+        <x:v>Generated Device Panel CAPL</x:v>
+      </x:c>
+      <x:c r="C22" s="63" t="str">
+        <x:v>M485E_UI include 체계, Device별 bounded timer 작업·baseline·Raw Hex frame cache·SnapshotValid·momentary command adapter</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R941f46324778426f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R671cbb1101a8456b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9546,7 +10158,7 @@
         <x:v>External Test Result</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>19건 Not Tested</x:v>
+        <x:v>20건 Not Tested</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx</x:v>
@@ -9577,7 +10189,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bdaeff5f72c40fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R761729bb63a04af6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9884,7 +10496,7 @@
       <x:c r="D7" s="35" t="str">
         <x:v>CANalyzer 13 x86</x:v>
       </x:c>
-      <x:c r="E7" s="196" t="str">
+      <x:c r="E7" s="206" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
@@ -9930,25 +10542,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="197" t="str">
+      <x:c r="A1" s="207" t="str">
         <x:v>Test Case ID</x:v>
       </x:c>
-      <x:c r="B1" s="197" t="str">
+      <x:c r="B1" s="207" t="str">
         <x:v>Phase</x:v>
       </x:c>
-      <x:c r="C1" s="197" t="str">
+      <x:c r="C1" s="207" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D1" s="197" t="str">
+      <x:c r="D1" s="207" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="E1" s="197" t="str">
+      <x:c r="E1" s="207" t="str">
         <x:v>Method</x:v>
       </x:c>
-      <x:c r="F1" s="197" t="str">
+      <x:c r="F1" s="207" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="G1" s="197" t="str">
+      <x:c r="G1" s="207" t="str">
         <x:v>External Follow-up</x:v>
       </x:c>
     </x:row>
@@ -9968,7 +10580,7 @@
       <x:c r="E2" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F2" s="198" t="str">
+      <x:c r="F2" s="208" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G2" s="63" t="str">
@@ -9991,7 +10603,7 @@
       <x:c r="E3" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F3" s="198" t="str">
+      <x:c r="F3" s="208" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G3" s="63" t="str">
@@ -10014,7 +10626,7 @@
       <x:c r="E4" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F4" s="198" t="str">
+      <x:c r="F4" s="208" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G4" s="63" t="str">
@@ -10037,7 +10649,7 @@
       <x:c r="E5" s="63" t="str">
         <x:v>M485E.Core.Tests</x:v>
       </x:c>
-      <x:c r="F5" s="198" t="str">
+      <x:c r="F5" s="208" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G5" s="63" t="str">
@@ -10060,7 +10672,7 @@
       <x:c r="E6" s="63" t="str">
         <x:v>M485E.Core.Tests + FakeSerialTransport</x:v>
       </x:c>
-      <x:c r="F6" s="198" t="str">
+      <x:c r="F6" s="208" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G6" s="63" t="str">
@@ -10083,7 +10695,7 @@
       <x:c r="E7" s="63" t="str">
         <x:v>M485E.IntegrationTests</x:v>
       </x:c>
-      <x:c r="F7" s="198" t="str">
+      <x:c r="F7" s="208" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G7" s="63" t="str">
@@ -10106,7 +10718,7 @@
       <x:c r="E8" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1 + CANalyzer 13 Exec32 caplcompexec</x:v>
       </x:c>
-      <x:c r="F8" s="198" t="str">
+      <x:c r="F8" s="208" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="63" t="str">
@@ -10129,7 +10741,7 @@
       <x:c r="E9" s="63" t="str">
         <x:v>Test-M485ECaplSources.ps1; Main compile in configured CANalyzer project</x:v>
       </x:c>
-      <x:c r="F9" s="199" t="str">
+      <x:c r="F9" s="209" t="str">
         <x:v>Static PASS / External Pending</x:v>
       </x:c>
       <x:c r="G9" s="63" t="str">
@@ -10152,7 +10764,7 @@
       <x:c r="E10" s="63" t="str">
         <x:v>MSBuild + CMake + CTest + CANalyzer 13 x86 CAPL compiler</x:v>
       </x:c>
-      <x:c r="F10" s="198" t="str">
+      <x:c r="F10" s="208" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G10" s="63" t="str">
@@ -10175,56 +10787,79 @@
       <x:c r="E11" s="63" t="str">
         <x:v>M485E.Core.Tests + M485E.IntegrationTests + Test-M485ECaplSources.ps1</x:v>
       </x:c>
-      <x:c r="F11" s="199" t="str">
+      <x:c r="F11" s="209" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G11" s="63" t="str">
         <x:v>EV-017~EV-019</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="12" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A12" s="63" t="str">
-        <x:v>EV-001~EV-019</x:v>
+        <x:v>TC-DPG-AUTO-001</x:v>
       </x:c>
       <x:c r="B12" s="63" t="str">
-        <x:v>External</x:v>
+        <x:v>10/11</x:v>
       </x:c>
       <x:c r="C12" s="63" t="str">
-        <x:v>External</x:v>
+        <x:v>Automated + Static</x:v>
       </x:c>
       <x:c r="D12" s="63" t="str">
-        <x:v>CANalyzer 9.x/18, SystemBase Multi USB-485, Board, Panel, CAPL Output View, virtual CAN, RTU CSV</x:v>
+        <x:v>CSV 계약·경로 안전성·deterministic transaction 출력, XVP XML/바인딩, Raw Hex vectors, generated CAPL/vsysvar stale, one-file EXE 다른 cwd smoke</x:v>
       </x:c>
       <x:c r="E12" s="63" t="str">
-        <x:v>External Verification Guide</x:v>
-      </x:c>
-      <x:c r="F12" s="198" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Python unittest + Test-M485EDevicePanelSources.ps1 + Test-PanelGeneratorExe.ps1</x:v>
+      </x:c>
+      <x:c r="F12" s="209" t="str">
+        <x:v>PASS / External Pending</x:v>
       </x:c>
       <x:c r="G12" s="63" t="str">
-        <x:v>대상 실환경에서 결과 기록</x:v>
+        <x:v>EV-020</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A13" s="63" t="str">
+        <x:v>EV-001~EV-020</x:v>
+      </x:c>
+      <x:c r="B13" s="63" t="str">
+        <x:v>External</x:v>
+      </x:c>
+      <x:c r="C13" s="63" t="str">
+        <x:v>External</x:v>
+      </x:c>
+      <x:c r="D13" s="63" t="str">
+        <x:v>CANalyzer 9.x/18, SystemBase Multi USB-485, Board, Panel/XVP copy, CAPL Output View, virtual CAN, RTU CSV</x:v>
+      </x:c>
+      <x:c r="E13" s="63" t="str">
+        <x:v>External Verification Guide</x:v>
+      </x:c>
+      <x:c r="F13" s="209" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="G13" s="63" t="str">
+        <x:v>대상 실환경에서 결과 기록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A14" s="63" t="str">
         <x:v>TC-CAPL13-COMPILE-001</x:v>
       </x:c>
-      <x:c r="B13" s="63" t="str">
+      <x:c r="B14" s="63" t="str">
         <x:v>1/2/9</x:v>
       </x:c>
-      <x:c r="C13" s="63" t="str">
+      <x:c r="C14" s="63" t="str">
         <x:v>Compiler</x:v>
       </x:c>
-      <x:c r="D13" s="63" t="str">
+      <x:c r="D14" s="63" t="str">
         <x:v>Phase 1 ABI, Phase 2 Contracts, Phase 9 Core/Monitoring CAPL probes</x:v>
       </x:c>
-      <x:c r="E13" s="63" t="str">
+      <x:c r="E14" s="63" t="str">
         <x:v>CANalyzer 13 Exec32 caplcompexec.exe</x:v>
       </x:c>
-      <x:c r="F13" s="198" t="str">
+      <x:c r="F14" s="208" t="str">
         <x:v>PASS (warning-free)</x:v>
       </x:c>
-      <x:c r="G13" s="63" t="str">
+      <x:c r="G14" s="63" t="str">
         <x:v>CANalyzer 9.x SP8 Compile/Measurement remains EV-001</x:v>
       </x:c>
     </x:row>
